--- a/model/cost-model.xlsx
+++ b/model/cost-model.xlsx
@@ -1205,7 +1205,7 @@
       </c>
       <c r="D33" s="10" t="inlineStr">
         <is>
-          <t>Production coach on Sonnet 5.5 if it passes the eval gate; prototype runs Opus 5.5.</t>
+          <t>Production coach on Sonnet 5.5 if it passes the eval gate; live prototype runs SEA-LION v4 (Workers AI, free).</t>
         </is>
       </c>
     </row>

--- a/model/cost-model.xlsx
+++ b/model/cost-model.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="Rdbea3feaff584256"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="2" r:id="Rbef76d4f471c4ef2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Build" sheetId="3" r:id="R6a44c788c4504740"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Run" sheetId="4" r:id="R9ca452cb7d834430"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pricing &amp; P&amp;L" sheetId="5" r:id="Rbe346883d57d4971"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AI Cost" sheetId="6" r:id="R7bdc0f1e537b4183"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Value" sheetId="7" r:id="Rfee0a26b29d5403e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="Re9c139b4f32b44dd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="2" r:id="R69b77b7fb6f24567"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Build" sheetId="3" r:id="Rb078780495aa4f74"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Run" sheetId="4" r:id="R50ba5a332b474f76"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pricing &amp; P&amp;L" sheetId="5" r:id="Rf66f3c0446054034"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AI Cost" sheetId="6" r:id="R3f0891b51cad4e2f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Value" sheetId="7" r:id="R60f3f89586a54148"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1623,7 +1623,7 @@
     <x:row r="55">
       <x:c r="A55" s="5" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Run team (client-dedicated + shared platform)</x:t>
+          <x:t xml:space="preserve">Run team (client-dedicated + platform)</x:t>
         </x:is>
       </x:c>
       <x:c r="B55" s="6" t="n"/>
@@ -1713,11 +1713,11 @@
     <x:row r="60">
       <x:c r="A60" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Shared platform team allocation up to 20k</x:t>
+          <x:t xml:space="preserve">Platform team up to 20k employees</x:t>
         </x:is>
       </x:c>
       <x:c r="B60" s="8" t="n">
-        <x:v>1.5</x:v>
+        <x:v>2.5</x:v>
       </x:c>
       <x:c r="C60" s="9" t="inlineStr">
         <x:is>
@@ -1726,18 +1726,18 @@
       </x:c>
       <x:c r="D60" s="10" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Engineering, AI ops, security; shared across IRIS clients.</x:t>
+          <x:t xml:space="preserve">Engineering, AI ops and security on call. Dedicated: this is the platform's first client, so no cost is shared yet.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="61">
       <x:c r="A61" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Shared platform team allocation above 20k</x:t>
+          <x:t xml:space="preserve">Platform team above 20k employees</x:t>
         </x:is>
       </x:c>
       <x:c r="B61" s="8" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C61" s="9" t="inlineStr">
         <x:is>
@@ -1746,7 +1746,7 @@
       </x:c>
       <x:c r="D61" s="10" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">Adds wave 2-3 integrations and the ASEAN languages.</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -2324,23 +2324,23 @@
         </x:is>
       </x:c>
       <x:c r="B10" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C10" s="19" t="n">
         <x:f>B10*Assumptions!$B$8</x:f>
-        <x:v>60</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="D10" s="20" t="n">
         <x:f>C10*Assumptions!$B$77/Assumptions!$B$7</x:f>
-        <x:v>428571.4285714286</x:v>
+        <x:v>857142.8571428572</x:v>
       </x:c>
       <x:c r="E10" s="20" t="n">
         <x:f>C10*Assumptions!$C$77</x:f>
-        <x:v>960000</x:v>
+        <x:v>1920000</x:v>
       </x:c>
       <x:c r="F10" s="10" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">HRIS, 2 LMS, SSO, data model, dashboards.</x:t>
+          <x:t xml:space="preserve">1 for HR system and sign-in (SSO, LINE Login, OTP); 1 for both LMSs, data model and dashboards.</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -2351,23 +2351,23 @@
         </x:is>
       </x:c>
       <x:c r="B11" s="8" t="n">
-        <x:v>0.8</x:v>
+        <x:v>1.5</x:v>
       </x:c>
       <x:c r="C11" s="19" t="n">
         <x:f>B11*Assumptions!$B$8</x:f>
-        <x:v>48</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D11" s="20" t="n">
         <x:f>C11*Assumptions!$B$78/Assumptions!$B$7</x:f>
-        <x:v>182857.14285714287</x:v>
+        <x:v>342857.14285714284</x:v>
       </x:c>
       <x:c r="E11" s="20" t="n">
         <x:f>C11*Assumptions!$C$78</x:f>
-        <x:v>408000</x:v>
+        <x:v>765000</x:v>
       </x:c>
       <x:c r="F11" s="10" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">From week 3; test automation and UAT.</x:t>
+          <x:t xml:space="preserve">From week 2; Thai and English test passes, automation, UAT and the 500-user pilot.</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -2405,23 +2405,23 @@
         </x:is>
       </x:c>
       <x:c r="B13" s="8" t="n">
-        <x:v>0.5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C13" s="19" t="n">
         <x:f>B13*Assumptions!$B$8</x:f>
-        <x:v>30</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D13" s="20" t="n">
         <x:f>C13*Assumptions!$B$80/Assumptions!$B$7</x:f>
-        <x:v>228571.42857142858</x:v>
+        <x:v>457142.85714285716</x:v>
       </x:c>
       <x:c r="E13" s="20" t="n">
         <x:f>C13*Assumptions!$C$80</x:f>
-        <x:v>480000</x:v>
+        <x:v>960000</x:v>
       </x:c>
       <x:c r="F13" s="10" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Environments, CI/CD, security controls, pen-test fixes.</x:t>
+          <x:t xml:space="preserve">Week-2 security pack, Thailand landing zone, CI/CD, pen-test fixes, staged go-live.</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -2541,19 +2541,19 @@
       </x:c>
       <x:c r="B18" s="21" t="n">
         <x:f>SUM(B5:B17)</x:f>
-        <x:v>14.200000000000001</x:v>
+        <x:v>16.4</x:v>
       </x:c>
       <x:c r="C18" s="21" t="n">
         <x:f>SUM(C5:C17)</x:f>
-        <x:v>852</x:v>
+        <x:v>984</x:v>
       </x:c>
       <x:c r="D18" s="22" t="n">
         <x:f>SUM(D5:D17)</x:f>
-        <x:v>5911428.571428572</x:v>
+        <x:v>6728571.428571429</x:v>
       </x:c>
       <x:c r="E18" s="22" t="n">
         <x:f>SUM(E5:E17)</x:f>
-        <x:v>13092000</x:v>
+        <x:v>14889000</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -2637,12 +2637,12 @@
     <x:row r="27">
       <x:c r="A27" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Delivery contingency (10% of team cost)</x:t>
+          <x:t xml:space="preserve">Delivery contingency (15% of team cost)</x:t>
         </x:is>
       </x:c>
       <x:c r="D27" s="20" t="n">
-        <x:f>0.1*D18</x:f>
-        <x:v>591142.8571428572</x:v>
+        <x:f>0.15*D18</x:f>
+        <x:v>1009285.7142857143</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -2653,7 +2653,7 @@
       </x:c>
       <x:c r="D28" s="22" t="n">
         <x:f>D18+D25+D27</x:f>
-        <x:v>7312571.428571429</x:v>
+        <x:v>8547857.142857144</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
@@ -2664,7 +2664,7 @@
       </x:c>
       <x:c r="E29" s="20" t="n">
         <x:f>E18+E25</x:f>
-        <x:v>13902000</x:v>
+        <x:v>15699000</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
@@ -2675,7 +2675,7 @@
       </x:c>
       <x:c r="E30" s="20" t="n">
         <x:f>E29*Assumptions!$B$65</x:f>
-        <x:v>1390200</x:v>
+        <x:v>1569900</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
@@ -2686,7 +2686,7 @@
       </x:c>
       <x:c r="E31" s="23" t="n">
         <x:f>ROUND((E29+E30)/500000,0)*500000</x:f>
-        <x:v>15500000</x:v>
+        <x:v>17500000</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
@@ -2697,7 +2697,7 @@
       </x:c>
       <x:c r="E32" s="24" t="n">
         <x:f>(E31-D28)/E31</x:f>
-        <x:v>0.528221198156682</x:v>
+        <x:v>0.5115510204081632</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
@@ -5159,7 +5159,7 @@
     <x:row r="20">
       <x:c r="A20" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Shared platform team allocation</x:t>
+          <x:t xml:space="preserve">Platform team</x:t>
         </x:is>
       </x:c>
       <x:c r="B20" s="20" t="n">
@@ -5176,135 +5176,135 @@
       </x:c>
       <x:c r="E20" s="20" t="n">
         <x:f>IF(E5&gt;0,IF(E5&gt;20000,Assumptions!$B$61,Assumptions!$B$60)*Assumptions!$B$74,0)</x:f>
-        <x:v>240000</x:v>
+        <x:v>400000</x:v>
       </x:c>
       <x:c r="F20" s="20" t="n">
         <x:f>IF(F5&gt;0,IF(F5&gt;20000,Assumptions!$B$61,Assumptions!$B$60)*Assumptions!$B$74,0)</x:f>
-        <x:v>240000</x:v>
+        <x:v>400000</x:v>
       </x:c>
       <x:c r="G20" s="20" t="n">
         <x:f>IF(G5&gt;0,IF(G5&gt;20000,Assumptions!$B$61,Assumptions!$B$60)*Assumptions!$B$74,0)</x:f>
-        <x:v>240000</x:v>
+        <x:v>400000</x:v>
       </x:c>
       <x:c r="H20" s="20" t="n">
         <x:f>IF(H5&gt;0,IF(H5&gt;20000,Assumptions!$B$61,Assumptions!$B$60)*Assumptions!$B$74,0)</x:f>
-        <x:v>320000</x:v>
+        <x:v>480000</x:v>
       </x:c>
       <x:c r="I20" s="20" t="n">
         <x:f>IF(I5&gt;0,IF(I5&gt;20000,Assumptions!$B$61,Assumptions!$B$60)*Assumptions!$B$74,0)</x:f>
-        <x:v>320000</x:v>
+        <x:v>480000</x:v>
       </x:c>
       <x:c r="J20" s="20" t="n">
         <x:f>IF(J5&gt;0,IF(J5&gt;20000,Assumptions!$B$61,Assumptions!$B$60)*Assumptions!$B$74,0)</x:f>
-        <x:v>320000</x:v>
+        <x:v>480000</x:v>
       </x:c>
       <x:c r="K20" s="20" t="n">
         <x:f>IF(K5&gt;0,IF(K5&gt;20000,Assumptions!$B$61,Assumptions!$B$60)*Assumptions!$B$74,0)</x:f>
-        <x:v>320000</x:v>
+        <x:v>480000</x:v>
       </x:c>
       <x:c r="L20" s="20" t="n">
         <x:f>IF(L5&gt;0,IF(L5&gt;20000,Assumptions!$B$61,Assumptions!$B$60)*Assumptions!$B$74,0)</x:f>
-        <x:v>320000</x:v>
+        <x:v>480000</x:v>
       </x:c>
       <x:c r="M20" s="20" t="n">
         <x:f>IF(M5&gt;0,IF(M5&gt;20000,Assumptions!$B$61,Assumptions!$B$60)*Assumptions!$B$74,0)</x:f>
-        <x:v>320000</x:v>
+        <x:v>480000</x:v>
       </x:c>
       <x:c r="N20" s="20" t="n">
         <x:f>IF(N5&gt;0,IF(N5&gt;20000,Assumptions!$B$61,Assumptions!$B$60)*Assumptions!$B$74,0)</x:f>
-        <x:v>320000</x:v>
+        <x:v>480000</x:v>
       </x:c>
       <x:c r="O20" s="20" t="n">
         <x:f>IF(O5&gt;0,IF(O5&gt;20000,Assumptions!$B$61,Assumptions!$B$60)*Assumptions!$B$74,0)</x:f>
-        <x:v>320000</x:v>
+        <x:v>480000</x:v>
       </x:c>
       <x:c r="P20" s="20" t="n">
         <x:f>IF(P5&gt;0,IF(P5&gt;20000,Assumptions!$B$61,Assumptions!$B$60)*Assumptions!$B$74,0)</x:f>
-        <x:v>320000</x:v>
+        <x:v>480000</x:v>
       </x:c>
       <x:c r="Q20" s="20" t="n">
         <x:f>IF(Q5&gt;0,IF(Q5&gt;20000,Assumptions!$B$61,Assumptions!$B$60)*Assumptions!$B$74,0)</x:f>
-        <x:v>320000</x:v>
+        <x:v>480000</x:v>
       </x:c>
       <x:c r="R20" s="20" t="n">
         <x:f>IF(R5&gt;0,IF(R5&gt;20000,Assumptions!$B$61,Assumptions!$B$60)*Assumptions!$B$74,0)</x:f>
-        <x:v>320000</x:v>
+        <x:v>480000</x:v>
       </x:c>
       <x:c r="S20" s="20" t="n">
         <x:f>IF(S5&gt;0,IF(S5&gt;20000,Assumptions!$B$61,Assumptions!$B$60)*Assumptions!$B$74,0)</x:f>
-        <x:v>320000</x:v>
+        <x:v>480000</x:v>
       </x:c>
       <x:c r="T20" s="20" t="n">
         <x:f>IF(T5&gt;0,IF(T5&gt;20000,Assumptions!$B$61,Assumptions!$B$60)*Assumptions!$B$74,0)</x:f>
-        <x:v>320000</x:v>
+        <x:v>480000</x:v>
       </x:c>
       <x:c r="U20" s="20" t="n">
         <x:f>IF(U5&gt;0,IF(U5&gt;20000,Assumptions!$B$61,Assumptions!$B$60)*Assumptions!$B$74,0)</x:f>
-        <x:v>320000</x:v>
+        <x:v>480000</x:v>
       </x:c>
       <x:c r="V20" s="20" t="n">
         <x:f>IF(V5&gt;0,IF(V5&gt;20000,Assumptions!$B$61,Assumptions!$B$60)*Assumptions!$B$74,0)</x:f>
-        <x:v>320000</x:v>
+        <x:v>480000</x:v>
       </x:c>
       <x:c r="W20" s="20" t="n">
         <x:f>IF(W5&gt;0,IF(W5&gt;20000,Assumptions!$B$61,Assumptions!$B$60)*Assumptions!$B$74,0)</x:f>
-        <x:v>320000</x:v>
+        <x:v>480000</x:v>
       </x:c>
       <x:c r="X20" s="20" t="n">
         <x:f>IF(X5&gt;0,IF(X5&gt;20000,Assumptions!$B$61,Assumptions!$B$60)*Assumptions!$B$74,0)</x:f>
-        <x:v>320000</x:v>
+        <x:v>480000</x:v>
       </x:c>
       <x:c r="Y20" s="20" t="n">
         <x:f>IF(Y5&gt;0,IF(Y5&gt;20000,Assumptions!$B$61,Assumptions!$B$60)*Assumptions!$B$74,0)</x:f>
-        <x:v>320000</x:v>
+        <x:v>480000</x:v>
       </x:c>
       <x:c r="Z20" s="20" t="n">
         <x:f>IF(Z5&gt;0,IF(Z5&gt;20000,Assumptions!$B$61,Assumptions!$B$60)*Assumptions!$B$74,0)</x:f>
-        <x:v>320000</x:v>
+        <x:v>480000</x:v>
       </x:c>
       <x:c r="AA20" s="20" t="n">
         <x:f>IF(AA5&gt;0,IF(AA5&gt;20000,Assumptions!$B$61,Assumptions!$B$60)*Assumptions!$B$74,0)</x:f>
-        <x:v>320000</x:v>
+        <x:v>480000</x:v>
       </x:c>
       <x:c r="AB20" s="20" t="n">
         <x:f>IF(AB5&gt;0,IF(AB5&gt;20000,Assumptions!$B$61,Assumptions!$B$60)*Assumptions!$B$74,0)</x:f>
-        <x:v>320000</x:v>
+        <x:v>480000</x:v>
       </x:c>
       <x:c r="AC20" s="20" t="n">
         <x:f>IF(AC5&gt;0,IF(AC5&gt;20000,Assumptions!$B$61,Assumptions!$B$60)*Assumptions!$B$74,0)</x:f>
-        <x:v>320000</x:v>
+        <x:v>480000</x:v>
       </x:c>
       <x:c r="AD20" s="20" t="n">
         <x:f>IF(AD5&gt;0,IF(AD5&gt;20000,Assumptions!$B$61,Assumptions!$B$60)*Assumptions!$B$74,0)</x:f>
-        <x:v>320000</x:v>
+        <x:v>480000</x:v>
       </x:c>
       <x:c r="AE20" s="20" t="n">
         <x:f>IF(AE5&gt;0,IF(AE5&gt;20000,Assumptions!$B$61,Assumptions!$B$60)*Assumptions!$B$74,0)</x:f>
-        <x:v>320000</x:v>
+        <x:v>480000</x:v>
       </x:c>
       <x:c r="AF20" s="20" t="n">
         <x:f>IF(AF5&gt;0,IF(AF5&gt;20000,Assumptions!$B$61,Assumptions!$B$60)*Assumptions!$B$74,0)</x:f>
-        <x:v>320000</x:v>
+        <x:v>480000</x:v>
       </x:c>
       <x:c r="AG20" s="20" t="n">
         <x:f>IF(AG5&gt;0,IF(AG5&gt;20000,Assumptions!$B$61,Assumptions!$B$60)*Assumptions!$B$74,0)</x:f>
-        <x:v>320000</x:v>
+        <x:v>480000</x:v>
       </x:c>
       <x:c r="AH20" s="20" t="n">
         <x:f>IF(AH5&gt;0,IF(AH5&gt;20000,Assumptions!$B$61,Assumptions!$B$60)*Assumptions!$B$74,0)</x:f>
-        <x:v>320000</x:v>
+        <x:v>480000</x:v>
       </x:c>
       <x:c r="AI20" s="20" t="n">
         <x:f>IF(AI5&gt;0,IF(AI5&gt;20000,Assumptions!$B$61,Assumptions!$B$60)*Assumptions!$B$74,0)</x:f>
-        <x:v>320000</x:v>
+        <x:v>480000</x:v>
       </x:c>
       <x:c r="AJ20" s="20" t="n">
         <x:f>IF(AJ5&gt;0,IF(AJ5&gt;20000,Assumptions!$B$61,Assumptions!$B$60)*Assumptions!$B$74,0)</x:f>
-        <x:v>320000</x:v>
+        <x:v>480000</x:v>
       </x:c>
       <x:c r="AK20" s="20" t="n">
         <x:f>IF(AK5&gt;0,IF(AK5&gt;20000,Assumptions!$B$61,Assumptions!$B$60)*Assumptions!$B$74,0)</x:f>
-        <x:v>320000</x:v>
+        <x:v>480000</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -5327,135 +5327,135 @@
       </x:c>
       <x:c r="E21" s="22" t="n">
         <x:f>E13+SUM(E14:E20)</x:f>
-        <x:v>743891.9648</x:v>
+        <x:v>903891.9648</x:v>
       </x:c>
       <x:c r="F21" s="22" t="n">
         <x:f>F13+SUM(F14:F20)</x:f>
-        <x:v>743891.9648</x:v>
+        <x:v>903891.9648</x:v>
       </x:c>
       <x:c r="G21" s="22" t="n">
         <x:f>G13+SUM(G14:G20)</x:f>
-        <x:v>743891.9648</x:v>
+        <x:v>903891.9648</x:v>
       </x:c>
       <x:c r="H21" s="22" t="n">
         <x:f>H13+SUM(H14:H20)</x:f>
-        <x:v>938169.4208</x:v>
+        <x:v>1098169.4208</x:v>
       </x:c>
       <x:c r="I21" s="22" t="n">
         <x:f>I13+SUM(I14:I20)</x:f>
-        <x:v>938169.4208</x:v>
+        <x:v>1098169.4208</x:v>
       </x:c>
       <x:c r="J21" s="22" t="n">
         <x:f>J13+SUM(J14:J20)</x:f>
-        <x:v>938169.4208</x:v>
+        <x:v>1098169.4208</x:v>
       </x:c>
       <x:c r="K21" s="22" t="n">
         <x:f>K13+SUM(K14:K20)</x:f>
-        <x:v>938169.4208</x:v>
+        <x:v>1098169.4208</x:v>
       </x:c>
       <x:c r="L21" s="22" t="n">
         <x:f>L13+SUM(L14:L20)</x:f>
-        <x:v>938169.4208</x:v>
+        <x:v>1098169.4208</x:v>
       </x:c>
       <x:c r="M21" s="22" t="n">
         <x:f>M13+SUM(M14:M20)</x:f>
-        <x:v>938169.4208</x:v>
+        <x:v>1098169.4208</x:v>
       </x:c>
       <x:c r="N21" s="22" t="n">
         <x:f>N13+SUM(N14:N20)</x:f>
-        <x:v>1112742.368</x:v>
+        <x:v>1272742.368</x:v>
       </x:c>
       <x:c r="O21" s="22" t="n">
         <x:f>O13+SUM(O14:O20)</x:f>
-        <x:v>1112742.368</x:v>
+        <x:v>1272742.368</x:v>
       </x:c>
       <x:c r="P21" s="22" t="n">
         <x:f>P13+SUM(P14:P20)</x:f>
-        <x:v>1112742.368</x:v>
+        <x:v>1272742.368</x:v>
       </x:c>
       <x:c r="Q21" s="22" t="n">
         <x:f>Q13+SUM(Q14:Q20)</x:f>
-        <x:v>1112742.368</x:v>
+        <x:v>1272742.368</x:v>
       </x:c>
       <x:c r="R21" s="22" t="n">
         <x:f>R13+SUM(R14:R20)</x:f>
-        <x:v>1112742.368</x:v>
+        <x:v>1272742.368</x:v>
       </x:c>
       <x:c r="S21" s="22" t="n">
         <x:f>S13+SUM(S14:S20)</x:f>
-        <x:v>1112742.368</x:v>
+        <x:v>1272742.368</x:v>
       </x:c>
       <x:c r="T21" s="22" t="n">
         <x:f>T13+SUM(T14:T20)</x:f>
-        <x:v>1112742.368</x:v>
+        <x:v>1272742.368</x:v>
       </x:c>
       <x:c r="U21" s="22" t="n">
         <x:f>U13+SUM(U14:U20)</x:f>
-        <x:v>1112742.368</x:v>
+        <x:v>1272742.368</x:v>
       </x:c>
       <x:c r="V21" s="22" t="n">
         <x:f>V13+SUM(V14:V20)</x:f>
-        <x:v>1112742.368</x:v>
+        <x:v>1272742.368</x:v>
       </x:c>
       <x:c r="W21" s="22" t="n">
         <x:f>W13+SUM(W14:W20)</x:f>
-        <x:v>1112742.368</x:v>
+        <x:v>1272742.368</x:v>
       </x:c>
       <x:c r="X21" s="22" t="n">
         <x:f>X13+SUM(X14:X20)</x:f>
-        <x:v>1112742.368</x:v>
+        <x:v>1272742.368</x:v>
       </x:c>
       <x:c r="Y21" s="22" t="n">
         <x:f>Y13+SUM(Y14:Y20)</x:f>
-        <x:v>1112742.368</x:v>
+        <x:v>1272742.368</x:v>
       </x:c>
       <x:c r="Z21" s="22" t="n">
         <x:f>Z13+SUM(Z14:Z20)</x:f>
-        <x:v>1112742.368</x:v>
+        <x:v>1272742.368</x:v>
       </x:c>
       <x:c r="AA21" s="22" t="n">
         <x:f>AA13+SUM(AA14:AA20)</x:f>
-        <x:v>1112742.368</x:v>
+        <x:v>1272742.368</x:v>
       </x:c>
       <x:c r="AB21" s="22" t="n">
         <x:f>AB13+SUM(AB14:AB20)</x:f>
-        <x:v>1112742.368</x:v>
+        <x:v>1272742.368</x:v>
       </x:c>
       <x:c r="AC21" s="22" t="n">
         <x:f>AC13+SUM(AC14:AC20)</x:f>
-        <x:v>1112742.368</x:v>
+        <x:v>1272742.368</x:v>
       </x:c>
       <x:c r="AD21" s="22" t="n">
         <x:f>AD13+SUM(AD14:AD20)</x:f>
-        <x:v>1112742.368</x:v>
+        <x:v>1272742.368</x:v>
       </x:c>
       <x:c r="AE21" s="22" t="n">
         <x:f>AE13+SUM(AE14:AE20)</x:f>
-        <x:v>1112742.368</x:v>
+        <x:v>1272742.368</x:v>
       </x:c>
       <x:c r="AF21" s="22" t="n">
         <x:f>AF13+SUM(AF14:AF20)</x:f>
-        <x:v>1112742.368</x:v>
+        <x:v>1272742.368</x:v>
       </x:c>
       <x:c r="AG21" s="22" t="n">
         <x:f>AG13+SUM(AG14:AG20)</x:f>
-        <x:v>1112742.368</x:v>
+        <x:v>1272742.368</x:v>
       </x:c>
       <x:c r="AH21" s="22" t="n">
         <x:f>AH13+SUM(AH14:AH20)</x:f>
-        <x:v>1112742.368</x:v>
+        <x:v>1272742.368</x:v>
       </x:c>
       <x:c r="AI21" s="22" t="n">
         <x:f>AI13+SUM(AI14:AI20)</x:f>
-        <x:v>1112742.368</x:v>
+        <x:v>1272742.368</x:v>
       </x:c>
       <x:c r="AJ21" s="22" t="n">
         <x:f>AJ13+SUM(AJ14:AJ20)</x:f>
-        <x:v>1112742.368</x:v>
+        <x:v>1272742.368</x:v>
       </x:c>
       <x:c r="AK21" s="22" t="n">
         <x:f>AK13+SUM(AK14:AK20)</x:f>
-        <x:v>1112742.368</x:v>
+        <x:v>1272742.368</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -5478,135 +5478,135 @@
       </x:c>
       <x:c r="E22" s="19" t="n">
         <x:f>IF(E5&gt;0,E21/E5,0)</x:f>
-        <x:v>61.990997066666665</x:v>
+        <x:v>75.3243304</x:v>
       </x:c>
       <x:c r="F22" s="19" t="n">
         <x:f>IF(F5&gt;0,F21/F5,0)</x:f>
-        <x:v>61.990997066666665</x:v>
+        <x:v>75.3243304</x:v>
       </x:c>
       <x:c r="G22" s="19" t="n">
         <x:f>IF(G5&gt;0,G21/G5,0)</x:f>
-        <x:v>61.990997066666665</x:v>
+        <x:v>75.3243304</x:v>
       </x:c>
       <x:c r="H22" s="19" t="n">
         <x:f>IF(H5&gt;0,H21/H5,0)</x:f>
-        <x:v>34.74701558518518</x:v>
+        <x:v>40.67294151111111</x:v>
       </x:c>
       <x:c r="I22" s="19" t="n">
         <x:f>IF(I5&gt;0,I21/I5,0)</x:f>
-        <x:v>34.74701558518518</x:v>
+        <x:v>40.67294151111111</x:v>
       </x:c>
       <x:c r="J22" s="19" t="n">
         <x:f>IF(J5&gt;0,J21/J5,0)</x:f>
-        <x:v>34.74701558518518</x:v>
+        <x:v>40.67294151111111</x:v>
       </x:c>
       <x:c r="K22" s="19" t="n">
         <x:f>IF(K5&gt;0,K21/K5,0)</x:f>
-        <x:v>34.74701558518518</x:v>
+        <x:v>40.67294151111111</x:v>
       </x:c>
       <x:c r="L22" s="19" t="n">
         <x:f>IF(L5&gt;0,L21/L5,0)</x:f>
-        <x:v>34.74701558518518</x:v>
+        <x:v>40.67294151111111</x:v>
       </x:c>
       <x:c r="M22" s="19" t="n">
         <x:f>IF(M5&gt;0,M21/M5,0)</x:f>
-        <x:v>34.74701558518518</x:v>
+        <x:v>40.67294151111111</x:v>
       </x:c>
       <x:c r="N22" s="19" t="n">
         <x:f>IF(N5&gt;0,N21/N5,0)</x:f>
-        <x:v>24.72760817777778</x:v>
+        <x:v>28.283163733333335</x:v>
       </x:c>
       <x:c r="O22" s="19" t="n">
         <x:f>IF(O5&gt;0,O21/O5,0)</x:f>
-        <x:v>24.72760817777778</x:v>
+        <x:v>28.283163733333335</x:v>
       </x:c>
       <x:c r="P22" s="19" t="n">
         <x:f>IF(P5&gt;0,P21/P5,0)</x:f>
-        <x:v>24.72760817777778</x:v>
+        <x:v>28.283163733333335</x:v>
       </x:c>
       <x:c r="Q22" s="19" t="n">
         <x:f>IF(Q5&gt;0,Q21/Q5,0)</x:f>
-        <x:v>24.72760817777778</x:v>
+        <x:v>28.283163733333335</x:v>
       </x:c>
       <x:c r="R22" s="19" t="n">
         <x:f>IF(R5&gt;0,R21/R5,0)</x:f>
-        <x:v>24.72760817777778</x:v>
+        <x:v>28.283163733333335</x:v>
       </x:c>
       <x:c r="S22" s="19" t="n">
         <x:f>IF(S5&gt;0,S21/S5,0)</x:f>
-        <x:v>24.72760817777778</x:v>
+        <x:v>28.283163733333335</x:v>
       </x:c>
       <x:c r="T22" s="19" t="n">
         <x:f>IF(T5&gt;0,T21/T5,0)</x:f>
-        <x:v>24.72760817777778</x:v>
+        <x:v>28.283163733333335</x:v>
       </x:c>
       <x:c r="U22" s="19" t="n">
         <x:f>IF(U5&gt;0,U21/U5,0)</x:f>
-        <x:v>24.72760817777778</x:v>
+        <x:v>28.283163733333335</x:v>
       </x:c>
       <x:c r="V22" s="19" t="n">
         <x:f>IF(V5&gt;0,V21/V5,0)</x:f>
-        <x:v>24.72760817777778</x:v>
+        <x:v>28.283163733333335</x:v>
       </x:c>
       <x:c r="W22" s="19" t="n">
         <x:f>IF(W5&gt;0,W21/W5,0)</x:f>
-        <x:v>24.72760817777778</x:v>
+        <x:v>28.283163733333335</x:v>
       </x:c>
       <x:c r="X22" s="19" t="n">
         <x:f>IF(X5&gt;0,X21/X5,0)</x:f>
-        <x:v>24.72760817777778</x:v>
+        <x:v>28.283163733333335</x:v>
       </x:c>
       <x:c r="Y22" s="19" t="n">
         <x:f>IF(Y5&gt;0,Y21/Y5,0)</x:f>
-        <x:v>24.72760817777778</x:v>
+        <x:v>28.283163733333335</x:v>
       </x:c>
       <x:c r="Z22" s="19" t="n">
         <x:f>IF(Z5&gt;0,Z21/Z5,0)</x:f>
-        <x:v>24.72760817777778</x:v>
+        <x:v>28.283163733333335</x:v>
       </x:c>
       <x:c r="AA22" s="19" t="n">
         <x:f>IF(AA5&gt;0,AA21/AA5,0)</x:f>
-        <x:v>24.72760817777778</x:v>
+        <x:v>28.283163733333335</x:v>
       </x:c>
       <x:c r="AB22" s="19" t="n">
         <x:f>IF(AB5&gt;0,AB21/AB5,0)</x:f>
-        <x:v>24.72760817777778</x:v>
+        <x:v>28.283163733333335</x:v>
       </x:c>
       <x:c r="AC22" s="19" t="n">
         <x:f>IF(AC5&gt;0,AC21/AC5,0)</x:f>
-        <x:v>24.72760817777778</x:v>
+        <x:v>28.283163733333335</x:v>
       </x:c>
       <x:c r="AD22" s="19" t="n">
         <x:f>IF(AD5&gt;0,AD21/AD5,0)</x:f>
-        <x:v>24.72760817777778</x:v>
+        <x:v>28.283163733333335</x:v>
       </x:c>
       <x:c r="AE22" s="19" t="n">
         <x:f>IF(AE5&gt;0,AE21/AE5,0)</x:f>
-        <x:v>24.72760817777778</x:v>
+        <x:v>28.283163733333335</x:v>
       </x:c>
       <x:c r="AF22" s="19" t="n">
         <x:f>IF(AF5&gt;0,AF21/AF5,0)</x:f>
-        <x:v>24.72760817777778</x:v>
+        <x:v>28.283163733333335</x:v>
       </x:c>
       <x:c r="AG22" s="19" t="n">
         <x:f>IF(AG5&gt;0,AG21/AG5,0)</x:f>
-        <x:v>24.72760817777778</x:v>
+        <x:v>28.283163733333335</x:v>
       </x:c>
       <x:c r="AH22" s="19" t="n">
         <x:f>IF(AH5&gt;0,AH21/AH5,0)</x:f>
-        <x:v>24.72760817777778</x:v>
+        <x:v>28.283163733333335</x:v>
       </x:c>
       <x:c r="AI22" s="19" t="n">
         <x:f>IF(AI5&gt;0,AI21/AI5,0)</x:f>
-        <x:v>24.72760817777778</x:v>
+        <x:v>28.283163733333335</x:v>
       </x:c>
       <x:c r="AJ22" s="19" t="n">
         <x:f>IF(AJ5&gt;0,AJ21/AJ5,0)</x:f>
-        <x:v>24.72760817777778</x:v>
+        <x:v>28.283163733333335</x:v>
       </x:c>
       <x:c r="AK22" s="19" t="n">
         <x:f>IF(AK5&gt;0,AK21/AK5,0)</x:f>
-        <x:v>24.72760817777778</x:v>
+        <x:v>28.283163733333335</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -5857,7 +5857,7 @@
       </x:c>
       <x:c r="B5" s="27" t="n">
         <x:f>SUM(B33:M33)</x:f>
-        <x:v>15500000</x:v>
+        <x:v>17500000</x:v>
       </x:c>
       <x:c r="C5" s="27" t="n">
         <x:f>SUM(N33:Y33)</x:f>
@@ -5869,7 +5869,7 @@
       </x:c>
       <x:c r="E5" s="28" t="n">
         <x:f>SUM(B5:D5)</x:f>
-        <x:v>15500000</x:v>
+        <x:v>17500000</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -5926,7 +5926,7 @@
       </x:c>
       <x:c r="B8" s="28" t="n">
         <x:f>SUM(B36:M36)</x:f>
-        <x:v>29222000</x:v>
+        <x:v>31222000</x:v>
       </x:c>
       <x:c r="C8" s="28" t="n">
         <x:f>SUM(N36:Y36)</x:f>
@@ -5938,7 +5938,7 @@
       </x:c>
       <x:c r="E8" s="28" t="n">
         <x:f>SUM(B8:D8)</x:f>
-        <x:v>80342000</x:v>
+        <x:v>82342000</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -5949,19 +5949,19 @@
       </x:c>
       <x:c r="B9" s="27" t="n">
         <x:f>SUM(B40:M40)</x:f>
-        <x:v>18173263.847771432</x:v>
+        <x:v>20848549.562057145</x:v>
       </x:c>
       <x:c r="C9" s="27" t="n">
         <x:f>SUM(N40:Y40)</x:f>
-        <x:v>17852908.416000005</x:v>
+        <x:v>19772908.416000005</x:v>
       </x:c>
       <x:c r="D9" s="27" t="n">
         <x:f>SUM(Z40:AK40)</x:f>
-        <x:v>13352908.416000003</x:v>
+        <x:v>15272908.416000003</x:v>
       </x:c>
       <x:c r="E9" s="28" t="n">
         <x:f>SUM(B9:D9)</x:f>
-        <x:v>49379080.67977144</x:v>
+        <x:v>55894366.39405715</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -5972,19 +5972,19 @@
       </x:c>
       <x:c r="B10" s="28" t="n">
         <x:f>SUM(B41:M41)</x:f>
-        <x:v>11048736.152228568</x:v>
+        <x:v>10373450.437942853</x:v>
       </x:c>
       <x:c r="C10" s="28" t="n">
         <x:f>SUM(N41:Y41)</x:f>
-        <x:v>12207091.583999997</x:v>
+        <x:v>10287091.583999999</x:v>
       </x:c>
       <x:c r="D10" s="28" t="n">
         <x:f>SUM(Z41:AK41)</x:f>
-        <x:v>7707091.584000002</x:v>
+        <x:v>5787091.584000002</x:v>
       </x:c>
       <x:c r="E10" s="28" t="n">
         <x:f>SUM(B10:D10)</x:f>
-        <x:v>30962919.320228565</x:v>
+        <x:v>26447633.605942857</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -5995,19 +5995,19 @@
       </x:c>
       <x:c r="B11" s="24" t="n">
         <x:f>IF(B8&gt;0,B10/B8,0)</x:f>
-        <x:v>0.37809650784438326</x:v>
+        <x:v>0.33224810831922535</x:v>
       </x:c>
       <x:c r="C11" s="24" t="n">
         <x:f>IF(C8&gt;0,C10/C8,0)</x:f>
-        <x:v>0.4060908710578841</x:v>
+        <x:v>0.34221861556886224</x:v>
       </x:c>
       <x:c r="D11" s="24" t="n">
         <x:f>IF(D8&gt;0,D10/D8,0)</x:f>
-        <x:v>0.36595876467236477</x:v>
+        <x:v>0.2747906735042736</x:v>
       </x:c>
       <x:c r="E11" s="29" t="n">
         <x:f>IF(E8&gt;0,E10/E8,0)</x:f>
-        <x:v>0.3853889537256798</x:v>
+        <x:v>0.3211925093626929</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -6044,7 +6044,7 @@
       </x:c>
       <x:c r="B15" s="20" t="n">
         <x:f>IF(B14&gt;0,B8/B14,0)</x:f>
-        <x:v>1082.2962962962963</x:v>
+        <x:v>1156.3703703703704</x:v>
       </x:c>
       <x:c r="C15" s="20" t="n">
         <x:f>IF(C14&gt;0,C8/C14,0)</x:f>
@@ -6063,7 +6063,7 @@
       </x:c>
       <x:c r="B16" s="30" t="n">
         <x:f>IF(B15&gt;0,B15/Assumptions!$B$9,0)</x:f>
-        <x:v>0.3279685746352413</x:v>
+        <x:v>0.3504152637485971</x:v>
       </x:c>
       <x:c r="C16" s="30" t="n">
         <x:f>IF(C15&gt;0,C15/Assumptions!$B$9,0)</x:f>
@@ -6104,7 +6104,7 @@
       </x:c>
       <x:c r="D19" s="31" t="n">
         <x:f>Run!AK22</x:f>
-        <x:v>24.72760817777778</x:v>
+        <x:v>28.283163733333335</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -6126,7 +6126,7 @@
       </x:c>
       <x:c r="D21" s="32" t="n">
         <x:f>Build!$E$31</x:f>
-        <x:v>15500000</x:v>
+        <x:v>17500000</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -6137,7 +6137,7 @@
       </x:c>
       <x:c r="C22" s="33" t="n">
         <x:f>Run!E21</x:f>
-        <x:v>743891.9648</x:v>
+        <x:v>903891.9648</x:v>
       </x:c>
       <x:c r="D22" s="20" t="n">
         <x:f>E34</x:f>
@@ -6576,15 +6576,15 @@
       </x:c>
       <x:c r="B33" s="20" t="n">
         <x:f>IF(B$30=1,0.3,IF(B$30=2,0.3,IF(B$30=3,0.4,0)))*Build!$E$31</x:f>
-        <x:v>4650000</x:v>
+        <x:v>5250000</x:v>
       </x:c>
       <x:c r="C33" s="20" t="n">
         <x:f>IF(C$30=1,0.3,IF(C$30=2,0.3,IF(C$30=3,0.4,0)))*Build!$E$31</x:f>
-        <x:v>4650000</x:v>
+        <x:v>5250000</x:v>
       </x:c>
       <x:c r="D33" s="20" t="n">
         <x:f>IF(D$30=1,0.3,IF(D$30=2,0.3,IF(D$30=3,0.4,0)))*Build!$E$31</x:f>
-        <x:v>6200000</x:v>
+        <x:v>7000000</x:v>
       </x:c>
       <x:c r="E33" s="20" t="n">
         <x:f>IF(E$30=1,0.3,IF(E$30=2,0.3,IF(E$30=3,0.4,0)))*Build!$E$31</x:f>
@@ -7029,15 +7029,15 @@
       </x:c>
       <x:c r="B36" s="22" t="n">
         <x:f>SUM(B33:B35)</x:f>
-        <x:v>4650000</x:v>
+        <x:v>5250000</x:v>
       </x:c>
       <x:c r="C36" s="22" t="n">
         <x:f>SUM(C33:C35)</x:f>
-        <x:v>4650000</x:v>
+        <x:v>5250000</x:v>
       </x:c>
       <x:c r="D36" s="22" t="n">
         <x:f>SUM(D33:D35)</x:f>
-        <x:v>6200000</x:v>
+        <x:v>7000000</x:v>
       </x:c>
       <x:c r="E36" s="22" t="n">
         <x:f>SUM(E33:E35)</x:f>
@@ -7180,15 +7180,15 @@
       </x:c>
       <x:c r="B37" s="20" t="n">
         <x:f>IF(B$30&lt;=3,Build!$D$28/3,0)</x:f>
-        <x:v>2437523.8095238097</x:v>
+        <x:v>2849285.7142857146</x:v>
       </x:c>
       <x:c r="C37" s="20" t="n">
         <x:f>IF(C$30&lt;=3,Build!$D$28/3,0)</x:f>
-        <x:v>2437523.8095238097</x:v>
+        <x:v>2849285.7142857146</x:v>
       </x:c>
       <x:c r="D37" s="20" t="n">
         <x:f>IF(D$30&lt;=3,Build!$D$28/3,0)</x:f>
-        <x:v>2437523.8095238097</x:v>
+        <x:v>2849285.7142857146</x:v>
       </x:c>
       <x:c r="E37" s="20" t="n">
         <x:f>IF(E$30&lt;=3,Build!$D$28/3,0)</x:f>
@@ -7343,135 +7343,135 @@
       </x:c>
       <x:c r="E38" s="33" t="n">
         <x:f>Run!E21</x:f>
-        <x:v>743891.9648</x:v>
+        <x:v>903891.9648</x:v>
       </x:c>
       <x:c r="F38" s="33" t="n">
         <x:f>Run!F21</x:f>
-        <x:v>743891.9648</x:v>
+        <x:v>903891.9648</x:v>
       </x:c>
       <x:c r="G38" s="33" t="n">
         <x:f>Run!G21</x:f>
-        <x:v>743891.9648</x:v>
+        <x:v>903891.9648</x:v>
       </x:c>
       <x:c r="H38" s="33" t="n">
         <x:f>Run!H21</x:f>
-        <x:v>938169.4208</x:v>
+        <x:v>1098169.4208</x:v>
       </x:c>
       <x:c r="I38" s="33" t="n">
         <x:f>Run!I21</x:f>
-        <x:v>938169.4208</x:v>
+        <x:v>1098169.4208</x:v>
       </x:c>
       <x:c r="J38" s="33" t="n">
         <x:f>Run!J21</x:f>
-        <x:v>938169.4208</x:v>
+        <x:v>1098169.4208</x:v>
       </x:c>
       <x:c r="K38" s="33" t="n">
         <x:f>Run!K21</x:f>
-        <x:v>938169.4208</x:v>
+        <x:v>1098169.4208</x:v>
       </x:c>
       <x:c r="L38" s="33" t="n">
         <x:f>Run!L21</x:f>
-        <x:v>938169.4208</x:v>
+        <x:v>1098169.4208</x:v>
       </x:c>
       <x:c r="M38" s="33" t="n">
         <x:f>Run!M21</x:f>
-        <x:v>938169.4208</x:v>
+        <x:v>1098169.4208</x:v>
       </x:c>
       <x:c r="N38" s="33" t="n">
         <x:f>Run!N21</x:f>
-        <x:v>1112742.368</x:v>
+        <x:v>1272742.368</x:v>
       </x:c>
       <x:c r="O38" s="33" t="n">
         <x:f>Run!O21</x:f>
-        <x:v>1112742.368</x:v>
+        <x:v>1272742.368</x:v>
       </x:c>
       <x:c r="P38" s="33" t="n">
         <x:f>Run!P21</x:f>
-        <x:v>1112742.368</x:v>
+        <x:v>1272742.368</x:v>
       </x:c>
       <x:c r="Q38" s="33" t="n">
         <x:f>Run!Q21</x:f>
-        <x:v>1112742.368</x:v>
+        <x:v>1272742.368</x:v>
       </x:c>
       <x:c r="R38" s="33" t="n">
         <x:f>Run!R21</x:f>
-        <x:v>1112742.368</x:v>
+        <x:v>1272742.368</x:v>
       </x:c>
       <x:c r="S38" s="33" t="n">
         <x:f>Run!S21</x:f>
-        <x:v>1112742.368</x:v>
+        <x:v>1272742.368</x:v>
       </x:c>
       <x:c r="T38" s="33" t="n">
         <x:f>Run!T21</x:f>
-        <x:v>1112742.368</x:v>
+        <x:v>1272742.368</x:v>
       </x:c>
       <x:c r="U38" s="33" t="n">
         <x:f>Run!U21</x:f>
-        <x:v>1112742.368</x:v>
+        <x:v>1272742.368</x:v>
       </x:c>
       <x:c r="V38" s="33" t="n">
         <x:f>Run!V21</x:f>
-        <x:v>1112742.368</x:v>
+        <x:v>1272742.368</x:v>
       </x:c>
       <x:c r="W38" s="33" t="n">
         <x:f>Run!W21</x:f>
-        <x:v>1112742.368</x:v>
+        <x:v>1272742.368</x:v>
       </x:c>
       <x:c r="X38" s="33" t="n">
         <x:f>Run!X21</x:f>
-        <x:v>1112742.368</x:v>
+        <x:v>1272742.368</x:v>
       </x:c>
       <x:c r="Y38" s="33" t="n">
         <x:f>Run!Y21</x:f>
-        <x:v>1112742.368</x:v>
+        <x:v>1272742.368</x:v>
       </x:c>
       <x:c r="Z38" s="33" t="n">
         <x:f>Run!Z21</x:f>
-        <x:v>1112742.368</x:v>
+        <x:v>1272742.368</x:v>
       </x:c>
       <x:c r="AA38" s="33" t="n">
         <x:f>Run!AA21</x:f>
-        <x:v>1112742.368</x:v>
+        <x:v>1272742.368</x:v>
       </x:c>
       <x:c r="AB38" s="33" t="n">
         <x:f>Run!AB21</x:f>
-        <x:v>1112742.368</x:v>
+        <x:v>1272742.368</x:v>
       </x:c>
       <x:c r="AC38" s="33" t="n">
         <x:f>Run!AC21</x:f>
-        <x:v>1112742.368</x:v>
+        <x:v>1272742.368</x:v>
       </x:c>
       <x:c r="AD38" s="33" t="n">
         <x:f>Run!AD21</x:f>
-        <x:v>1112742.368</x:v>
+        <x:v>1272742.368</x:v>
       </x:c>
       <x:c r="AE38" s="33" t="n">
         <x:f>Run!AE21</x:f>
-        <x:v>1112742.368</x:v>
+        <x:v>1272742.368</x:v>
       </x:c>
       <x:c r="AF38" s="33" t="n">
         <x:f>Run!AF21</x:f>
-        <x:v>1112742.368</x:v>
+        <x:v>1272742.368</x:v>
       </x:c>
       <x:c r="AG38" s="33" t="n">
         <x:f>Run!AG21</x:f>
-        <x:v>1112742.368</x:v>
+        <x:v>1272742.368</x:v>
       </x:c>
       <x:c r="AH38" s="33" t="n">
         <x:f>Run!AH21</x:f>
-        <x:v>1112742.368</x:v>
+        <x:v>1272742.368</x:v>
       </x:c>
       <x:c r="AI38" s="33" t="n">
         <x:f>Run!AI21</x:f>
-        <x:v>1112742.368</x:v>
+        <x:v>1272742.368</x:v>
       </x:c>
       <x:c r="AJ38" s="33" t="n">
         <x:f>Run!AJ21</x:f>
-        <x:v>1112742.368</x:v>
+        <x:v>1272742.368</x:v>
       </x:c>
       <x:c r="AK38" s="33" t="n">
         <x:f>Run!AK21</x:f>
-        <x:v>1112742.368</x:v>
+        <x:v>1272742.368</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
@@ -7633,147 +7633,147 @@
       </x:c>
       <x:c r="B40" s="20" t="n">
         <x:f>SUM(B37:B39)</x:f>
-        <x:v>2437523.8095238097</x:v>
+        <x:v>2849285.7142857146</x:v>
       </x:c>
       <x:c r="C40" s="20" t="n">
         <x:f>SUM(C37:C39)</x:f>
-        <x:v>2437523.8095238097</x:v>
+        <x:v>2849285.7142857146</x:v>
       </x:c>
       <x:c r="D40" s="20" t="n">
         <x:f>SUM(D37:D39)</x:f>
-        <x:v>2437523.8095238097</x:v>
+        <x:v>2849285.7142857146</x:v>
       </x:c>
       <x:c r="E40" s="20" t="n">
         <x:f>SUM(E37:E39)</x:f>
-        <x:v>743891.9648</x:v>
+        <x:v>903891.9648</x:v>
       </x:c>
       <x:c r="F40" s="20" t="n">
         <x:f>SUM(F37:F39)</x:f>
-        <x:v>743891.9648</x:v>
+        <x:v>903891.9648</x:v>
       </x:c>
       <x:c r="G40" s="20" t="n">
         <x:f>SUM(G37:G39)</x:f>
-        <x:v>743891.9648</x:v>
+        <x:v>903891.9648</x:v>
       </x:c>
       <x:c r="H40" s="20" t="n">
         <x:f>SUM(H37:H39)</x:f>
-        <x:v>3938169.4208</x:v>
+        <x:v>4098169.4208</x:v>
       </x:c>
       <x:c r="I40" s="20" t="n">
         <x:f>SUM(I37:I39)</x:f>
-        <x:v>938169.4208</x:v>
+        <x:v>1098169.4208</x:v>
       </x:c>
       <x:c r="J40" s="20" t="n">
         <x:f>SUM(J37:J39)</x:f>
-        <x:v>938169.4208</x:v>
+        <x:v>1098169.4208</x:v>
       </x:c>
       <x:c r="K40" s="20" t="n">
         <x:f>SUM(K37:K39)</x:f>
-        <x:v>938169.4208</x:v>
+        <x:v>1098169.4208</x:v>
       </x:c>
       <x:c r="L40" s="20" t="n">
         <x:f>SUM(L37:L39)</x:f>
-        <x:v>938169.4208</x:v>
+        <x:v>1098169.4208</x:v>
       </x:c>
       <x:c r="M40" s="20" t="n">
         <x:f>SUM(M37:M39)</x:f>
-        <x:v>938169.4208</x:v>
+        <x:v>1098169.4208</x:v>
       </x:c>
       <x:c r="N40" s="20" t="n">
         <x:f>SUM(N37:N39)</x:f>
-        <x:v>5612742.368</x:v>
+        <x:v>5772742.368</x:v>
       </x:c>
       <x:c r="O40" s="20" t="n">
         <x:f>SUM(O37:O39)</x:f>
-        <x:v>1112742.368</x:v>
+        <x:v>1272742.368</x:v>
       </x:c>
       <x:c r="P40" s="20" t="n">
         <x:f>SUM(P37:P39)</x:f>
-        <x:v>1112742.368</x:v>
+        <x:v>1272742.368</x:v>
       </x:c>
       <x:c r="Q40" s="20" t="n">
         <x:f>SUM(Q37:Q39)</x:f>
-        <x:v>1112742.368</x:v>
+        <x:v>1272742.368</x:v>
       </x:c>
       <x:c r="R40" s="20" t="n">
         <x:f>SUM(R37:R39)</x:f>
-        <x:v>1112742.368</x:v>
+        <x:v>1272742.368</x:v>
       </x:c>
       <x:c r="S40" s="20" t="n">
         <x:f>SUM(S37:S39)</x:f>
-        <x:v>1112742.368</x:v>
+        <x:v>1272742.368</x:v>
       </x:c>
       <x:c r="T40" s="20" t="n">
         <x:f>SUM(T37:T39)</x:f>
-        <x:v>1112742.368</x:v>
+        <x:v>1272742.368</x:v>
       </x:c>
       <x:c r="U40" s="20" t="n">
         <x:f>SUM(U37:U39)</x:f>
-        <x:v>1112742.368</x:v>
+        <x:v>1272742.368</x:v>
       </x:c>
       <x:c r="V40" s="20" t="n">
         <x:f>SUM(V37:V39)</x:f>
-        <x:v>1112742.368</x:v>
+        <x:v>1272742.368</x:v>
       </x:c>
       <x:c r="W40" s="20" t="n">
         <x:f>SUM(W37:W39)</x:f>
-        <x:v>1112742.368</x:v>
+        <x:v>1272742.368</x:v>
       </x:c>
       <x:c r="X40" s="20" t="n">
         <x:f>SUM(X37:X39)</x:f>
-        <x:v>1112742.368</x:v>
+        <x:v>1272742.368</x:v>
       </x:c>
       <x:c r="Y40" s="20" t="n">
         <x:f>SUM(Y37:Y39)</x:f>
-        <x:v>1112742.368</x:v>
+        <x:v>1272742.368</x:v>
       </x:c>
       <x:c r="Z40" s="20" t="n">
         <x:f>SUM(Z37:Z39)</x:f>
-        <x:v>1112742.368</x:v>
+        <x:v>1272742.368</x:v>
       </x:c>
       <x:c r="AA40" s="20" t="n">
         <x:f>SUM(AA37:AA39)</x:f>
-        <x:v>1112742.368</x:v>
+        <x:v>1272742.368</x:v>
       </x:c>
       <x:c r="AB40" s="20" t="n">
         <x:f>SUM(AB37:AB39)</x:f>
-        <x:v>1112742.368</x:v>
+        <x:v>1272742.368</x:v>
       </x:c>
       <x:c r="AC40" s="20" t="n">
         <x:f>SUM(AC37:AC39)</x:f>
-        <x:v>1112742.368</x:v>
+        <x:v>1272742.368</x:v>
       </x:c>
       <x:c r="AD40" s="20" t="n">
         <x:f>SUM(AD37:AD39)</x:f>
-        <x:v>1112742.368</x:v>
+        <x:v>1272742.368</x:v>
       </x:c>
       <x:c r="AE40" s="20" t="n">
         <x:f>SUM(AE37:AE39)</x:f>
-        <x:v>1112742.368</x:v>
+        <x:v>1272742.368</x:v>
       </x:c>
       <x:c r="AF40" s="20" t="n">
         <x:f>SUM(AF37:AF39)</x:f>
-        <x:v>1112742.368</x:v>
+        <x:v>1272742.368</x:v>
       </x:c>
       <x:c r="AG40" s="20" t="n">
         <x:f>SUM(AG37:AG39)</x:f>
-        <x:v>1112742.368</x:v>
+        <x:v>1272742.368</x:v>
       </x:c>
       <x:c r="AH40" s="20" t="n">
         <x:f>SUM(AH37:AH39)</x:f>
-        <x:v>1112742.368</x:v>
+        <x:v>1272742.368</x:v>
       </x:c>
       <x:c r="AI40" s="20" t="n">
         <x:f>SUM(AI37:AI39)</x:f>
-        <x:v>1112742.368</x:v>
+        <x:v>1272742.368</x:v>
       </x:c>
       <x:c r="AJ40" s="20" t="n">
         <x:f>SUM(AJ37:AJ39)</x:f>
-        <x:v>1112742.368</x:v>
+        <x:v>1272742.368</x:v>
       </x:c>
       <x:c r="AK40" s="20" t="n">
         <x:f>SUM(AK37:AK39)</x:f>
-        <x:v>1112742.368</x:v>
+        <x:v>1272742.368</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
@@ -7784,147 +7784,147 @@
       </x:c>
       <x:c r="B41" s="22" t="n">
         <x:f>B36-B40</x:f>
-        <x:v>2212476.1904761903</x:v>
+        <x:v>2400714.2857142854</x:v>
       </x:c>
       <x:c r="C41" s="22" t="n">
         <x:f>C36-C40</x:f>
-        <x:v>2212476.1904761903</x:v>
+        <x:v>2400714.2857142854</x:v>
       </x:c>
       <x:c r="D41" s="22" t="n">
         <x:f>D36-D40</x:f>
-        <x:v>3762476.1904761903</x:v>
+        <x:v>4150714.2857142854</x:v>
       </x:c>
       <x:c r="E41" s="22" t="n">
         <x:f>E36-E40</x:f>
-        <x:v>-275891.96479999996</x:v>
+        <x:v>-435891.96479999996</x:v>
       </x:c>
       <x:c r="F41" s="22" t="n">
         <x:f>F36-F40</x:f>
-        <x:v>-275891.96479999996</x:v>
+        <x:v>-435891.96479999996</x:v>
       </x:c>
       <x:c r="G41" s="22" t="n">
         <x:f>G36-G40</x:f>
-        <x:v>-275891.96479999996</x:v>
+        <x:v>-435891.96479999996</x:v>
       </x:c>
       <x:c r="H41" s="22" t="n">
         <x:f>H36-H40</x:f>
-        <x:v>3114830.5792</x:v>
+        <x:v>2954830.5792</x:v>
       </x:c>
       <x:c r="I41" s="22" t="n">
         <x:f>I36-I40</x:f>
-        <x:v>114830.57920000004</x:v>
+        <x:v>-45169.42079999996</x:v>
       </x:c>
       <x:c r="J41" s="22" t="n">
         <x:f>J36-J40</x:f>
-        <x:v>114830.57920000004</x:v>
+        <x:v>-45169.42079999996</x:v>
       </x:c>
       <x:c r="K41" s="22" t="n">
         <x:f>K36-K40</x:f>
-        <x:v>114830.57920000004</x:v>
+        <x:v>-45169.42079999996</x:v>
       </x:c>
       <x:c r="L41" s="22" t="n">
         <x:f>L36-L40</x:f>
-        <x:v>114830.57920000004</x:v>
+        <x:v>-45169.42079999996</x:v>
       </x:c>
       <x:c r="M41" s="22" t="n">
         <x:f>M36-M40</x:f>
-        <x:v>114830.57920000004</x:v>
+        <x:v>-45169.42079999996</x:v>
       </x:c>
       <x:c r="N41" s="22" t="n">
         <x:f>N36-N40</x:f>
-        <x:v>5142257.632</x:v>
+        <x:v>4982257.632</x:v>
       </x:c>
       <x:c r="O41" s="22" t="n">
         <x:f>O36-O40</x:f>
-        <x:v>642257.632</x:v>
+        <x:v>482257.632</x:v>
       </x:c>
       <x:c r="P41" s="22" t="n">
         <x:f>P36-P40</x:f>
-        <x:v>642257.632</x:v>
+        <x:v>482257.632</x:v>
       </x:c>
       <x:c r="Q41" s="22" t="n">
         <x:f>Q36-Q40</x:f>
-        <x:v>642257.632</x:v>
+        <x:v>482257.632</x:v>
       </x:c>
       <x:c r="R41" s="22" t="n">
         <x:f>R36-R40</x:f>
-        <x:v>642257.632</x:v>
+        <x:v>482257.632</x:v>
       </x:c>
       <x:c r="S41" s="22" t="n">
         <x:f>S36-S40</x:f>
-        <x:v>642257.632</x:v>
+        <x:v>482257.632</x:v>
       </x:c>
       <x:c r="T41" s="22" t="n">
         <x:f>T36-T40</x:f>
-        <x:v>642257.632</x:v>
+        <x:v>482257.632</x:v>
       </x:c>
       <x:c r="U41" s="22" t="n">
         <x:f>U36-U40</x:f>
-        <x:v>642257.632</x:v>
+        <x:v>482257.632</x:v>
       </x:c>
       <x:c r="V41" s="22" t="n">
         <x:f>V36-V40</x:f>
-        <x:v>642257.632</x:v>
+        <x:v>482257.632</x:v>
       </x:c>
       <x:c r="W41" s="22" t="n">
         <x:f>W36-W40</x:f>
-        <x:v>642257.632</x:v>
+        <x:v>482257.632</x:v>
       </x:c>
       <x:c r="X41" s="22" t="n">
         <x:f>X36-X40</x:f>
-        <x:v>642257.632</x:v>
+        <x:v>482257.632</x:v>
       </x:c>
       <x:c r="Y41" s="22" t="n">
         <x:f>Y36-Y40</x:f>
-        <x:v>642257.632</x:v>
+        <x:v>482257.632</x:v>
       </x:c>
       <x:c r="Z41" s="22" t="n">
         <x:f>Z36-Z40</x:f>
-        <x:v>642257.632</x:v>
+        <x:v>482257.632</x:v>
       </x:c>
       <x:c r="AA41" s="22" t="n">
         <x:f>AA36-AA40</x:f>
-        <x:v>642257.632</x:v>
+        <x:v>482257.632</x:v>
       </x:c>
       <x:c r="AB41" s="22" t="n">
         <x:f>AB36-AB40</x:f>
-        <x:v>642257.632</x:v>
+        <x:v>482257.632</x:v>
       </x:c>
       <x:c r="AC41" s="22" t="n">
         <x:f>AC36-AC40</x:f>
-        <x:v>642257.632</x:v>
+        <x:v>482257.632</x:v>
       </x:c>
       <x:c r="AD41" s="22" t="n">
         <x:f>AD36-AD40</x:f>
-        <x:v>642257.632</x:v>
+        <x:v>482257.632</x:v>
       </x:c>
       <x:c r="AE41" s="22" t="n">
         <x:f>AE36-AE40</x:f>
-        <x:v>642257.632</x:v>
+        <x:v>482257.632</x:v>
       </x:c>
       <x:c r="AF41" s="22" t="n">
         <x:f>AF36-AF40</x:f>
-        <x:v>642257.632</x:v>
+        <x:v>482257.632</x:v>
       </x:c>
       <x:c r="AG41" s="22" t="n">
         <x:f>AG36-AG40</x:f>
-        <x:v>642257.632</x:v>
+        <x:v>482257.632</x:v>
       </x:c>
       <x:c r="AH41" s="22" t="n">
         <x:f>AH36-AH40</x:f>
-        <x:v>642257.632</x:v>
+        <x:v>482257.632</x:v>
       </x:c>
       <x:c r="AI41" s="22" t="n">
         <x:f>AI36-AI40</x:f>
-        <x:v>642257.632</x:v>
+        <x:v>482257.632</x:v>
       </x:c>
       <x:c r="AJ41" s="22" t="n">
         <x:f>AJ36-AJ40</x:f>
-        <x:v>642257.632</x:v>
+        <x:v>482257.632</x:v>
       </x:c>
       <x:c r="AK41" s="22" t="n">
         <x:f>AK36-AK40</x:f>
-        <x:v>642257.632</x:v>
+        <x:v>482257.632</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -8061,11 +8061,11 @@
       </x:c>
       <x:c r="B10" s="30" t="n">
         <x:f>B9/(Run!AK21*12)</x:f>
-        <x:v>0.10067420925236126</x:v>
+        <x:v>0.08801817305417146</x:v>
       </x:c>
       <x:c r="C10" s="30" t="n">
         <x:f>C9/(Run!AK21*12-B9+C9)</x:f>
-        <x:v>0.18056048836338598</x:v>
+        <x:v>0.1596444667636109</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -8195,11 +8195,11 @@
         </x:is>
       </x:c>
       <x:c r="B9" s="15" t="n">
-        <x:v>0.12</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="D9" s="10" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">percentage points; assumption</x:t>
+          <x:t xml:space="preserve">percentage points; conservative assumption</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -8226,7 +8226,7 @@
       </x:c>
       <x:c r="C11" s="22" t="n">
         <x:f>B8*B9*B10</x:f>
-        <x:v>14400000</x:v>
+        <x:v>6000000</x:v>
       </x:c>
       <x:c r="D11" s="10" t="inlineStr">
         <x:is>
@@ -8368,7 +8368,7 @@
       </x:c>
       <x:c r="C21" s="23" t="n">
         <x:f>C7+C11+C15+C18+C19</x:f>
-        <x:v>53250000</x:v>
+        <x:v>44850000</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -8390,7 +8390,7 @@
       </x:c>
       <x:c r="C23" s="34" t="n">
         <x:f>IF(C22&gt;0,C21/C22,0)</x:f>
-        <x:v>2.5284900284900287</x:v>
+        <x:v>2.1296296296296298</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -8411,7 +8411,7 @@
       </x:c>
       <x:c r="C26" s="20" t="n">
         <x:f>B26*$C$21</x:f>
-        <x:v>7987500</x:v>
+        <x:v>6727500</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -8425,7 +8425,7 @@
       </x:c>
       <x:c r="C27" s="20" t="n">
         <x:f>B27*$C$21</x:f>
-        <x:v>31950000</x:v>
+        <x:v>26910000</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -8439,7 +8439,7 @@
       </x:c>
       <x:c r="C28" s="20" t="n">
         <x:f>B28*$C$21</x:f>
-        <x:v>53250000</x:v>
+        <x:v>44850000</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
@@ -8450,7 +8450,7 @@
       </x:c>
       <x:c r="C29" s="22" t="n">
         <x:f>SUM(C26:C28)</x:f>
-        <x:v>93187500</x:v>
+        <x:v>78487500</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
@@ -8461,7 +8461,7 @@
       </x:c>
       <x:c r="C30" s="33" t="n">
         <x:f>'Pricing &amp; P&amp;L'!E8</x:f>
-        <x:v>80342000</x:v>
+        <x:v>82342000</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
@@ -8472,7 +8472,7 @@
       </x:c>
       <x:c r="C31" s="35" t="n">
         <x:f>IF(C30&gt;0,C29/C30,0)</x:f>
-        <x:v>1.1598852405964502</x:v>
+        <x:v>0.9531891379854752</x:v>
       </x:c>
     </x:row>
     <x:row r="33">

--- a/model/cost-model.xlsx
+++ b/model/cost-model.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="Re9c139b4f32b44dd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="2" r:id="R69b77b7fb6f24567"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Build" sheetId="3" r:id="Rb078780495aa4f74"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Run" sheetId="4" r:id="R50ba5a332b474f76"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pricing &amp; P&amp;L" sheetId="5" r:id="Rf66f3c0446054034"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AI Cost" sheetId="6" r:id="R3f0891b51cad4e2f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Value" sheetId="7" r:id="R60f3f89586a54148"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="Ra60ce345716c4b80"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="2" r:id="R58f0a5cbce18427b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Build" sheetId="3" r:id="Rb8e6fae0dc7b4c1b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Run" sheetId="4" r:id="R5a736c7c28bb4382"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pricing &amp; P&amp;L" sheetId="5" r:id="Rfcdb21b4062f4009"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AI Cost" sheetId="6" r:id="Rf36a430eb1884d8a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Value" sheetId="7" r:id="R63593f9597a4418b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -608,7 +608,7 @@
     <x:row r="7">
       <x:c r="A7" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Model prices: Anthropic list prices (Oct 2026). Running on Vertex AI (Singapore) or Bedrock uses partner pricing; the 30% LLM contingency covers the difference.</x:t>
+          <x:t xml:space="preserve">Model prices: DeepSeek API list prices (Oct 2026), at peak rates for daytime coaching. Hosting DeepSeek in an approved region through a cloud provider is priced differently; the 30% LLM contingency covers the difference.</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -976,7 +976,7 @@
       </x:c>
       <x:c r="D21" s="10" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Initial + one refresh; overnight Batch API.</x:t>
+          <x:t xml:space="preserve">Initial + one refresh; generated overnight at off-peak rates.</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -1183,7 +1183,7 @@
     <x:row r="32">
       <x:c r="A32" s="5" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Model prices (Anthropic list, USD per 1M tokens, Oct 2026)</x:t>
+          <x:t xml:space="preserve">Model prices (DeepSeek API list, USD per 1M tokens, Oct 2026)</x:t>
         </x:is>
       </x:c>
       <x:c r="B32" s="6" t="n"/>
@@ -1193,11 +1193,11 @@
     <x:row r="33">
       <x:c r="A33" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Coach model input (Sonnet 5.5)</x:t>
+          <x:t xml:space="preserve">Coach model input (DeepSeek V4.1 Flash, peak)</x:t>
         </x:is>
       </x:c>
       <x:c r="B33" s="13" t="n">
-        <x:v>2</x:v>
+        <x:v>0.3</x:v>
       </x:c>
       <x:c r="C33" s="9" t="inlineStr">
         <x:is>
@@ -1206,18 +1206,18 @@
       </x:c>
       <x:c r="D33" s="10" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Production coach on Sonnet 5.5 if it passes the eval gate; live prototype runs SEA-LION v4 (Workers AI, free).</x:t>
+          <x:t xml:space="preserve">Production coach on DeepSeek V4.1 Flash (deepseek-flash) if it passes the eval gate. Peak rate: DeepSeek peak hours (01:00-04:00 and 06:00-10:00 UTC, weekdays) are Thai working hours. The live prototype run used SEA-LION v4 (Workers AI, free).</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Coach model output (Sonnet 5.5)</x:t>
+          <x:t xml:space="preserve">Coach model output (DeepSeek V4.1 Flash, peak)</x:t>
         </x:is>
       </x:c>
       <x:c r="B34" s="13" t="n">
-        <x:v>10</x:v>
+        <x:v>1.2</x:v>
       </x:c>
       <x:c r="C34" s="9" t="inlineStr">
         <x:is>
@@ -1233,11 +1233,11 @@
     <x:row r="35">
       <x:c r="A35" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Coach model cache read</x:t>
+          <x:t xml:space="preserve">Coach model cache read (DeepSeek V4.1 Flash, peak)</x:t>
         </x:is>
       </x:c>
       <x:c r="B35" s="14" t="n">
-        <x:v>0.2</x:v>
+        <x:v>0.006</x:v>
       </x:c>
       <x:c r="C35" s="9" t="inlineStr">
         <x:is>
@@ -1246,18 +1246,18 @@
       </x:c>
       <x:c r="D35" s="10" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">Cache-hit input price.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Opus 5.5 input (scenario)</x:t>
+          <x:t xml:space="preserve">Claude Sonnet 5.5 input (scenario)</x:t>
         </x:is>
       </x:c>
       <x:c r="B36" s="14" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C36" s="9" t="inlineStr">
         <x:is>
@@ -1266,18 +1266,18 @@
       </x:c>
       <x:c r="D36" s="10" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Used for the Opus scenario on the AI Cost sheet.</x:t>
+          <x:t xml:space="preserve">Comparison scenario on the AI Cost sheet (Anthropic list price); the fallback if Flash fails the Thai quality gate.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Opus 5.5 output (scenario)</x:t>
+          <x:t xml:space="preserve">Claude Sonnet 5.5 output (scenario)</x:t>
         </x:is>
       </x:c>
       <x:c r="B37" s="14" t="n">
-        <x:v>20</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C37" s="9" t="inlineStr">
         <x:is>
@@ -1293,11 +1293,11 @@
     <x:row r="38">
       <x:c r="A38" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Haiku 5.5 input (classifier, nudges)</x:t>
+          <x:t xml:space="preserve">Claude Sonnet 5.5 cache read (scenario)</x:t>
         </x:is>
       </x:c>
       <x:c r="B38" s="14" t="n">
-        <x:v>0.1</x:v>
+        <x:v>0.2</x:v>
       </x:c>
       <x:c r="C38" s="9" t="inlineStr">
         <x:is>
@@ -1313,11 +1313,11 @@
     <x:row r="39">
       <x:c r="A39" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Haiku 5.5 output</x:t>
+          <x:t xml:space="preserve">Classifier and nudge model input (DeepSeek Flash, peak)</x:t>
         </x:is>
       </x:c>
       <x:c r="B39" s="14" t="n">
-        <x:v>0.5</x:v>
+        <x:v>0.3</x:v>
       </x:c>
       <x:c r="C39" s="9" t="inlineStr">
         <x:is>
@@ -1333,181 +1333,181 @@
     <x:row r="40">
       <x:c r="A40" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Batch API discount</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B40" s="15" t="n">
-        <x:v>0.5</x:v>
+          <x:t xml:space="preserve">Classifier and nudge model output (DeepSeek Flash, peak)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B40" s="14" t="n">
+        <x:v>1.2</x:v>
       </x:c>
       <x:c r="C40" s="9" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">USD / 1M</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D40" s="10" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
-      <x:c r="D40" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">50% off for overnight path generation.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="7" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">Off-peak discount (overnight path generation)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B41" s="15" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="C41" s="9" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="D41" s="10" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">DeepSeek off-peak rates are half the peak rates; paths are generated overnight Bangkok time.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" s="7" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">LLM contingency</x:t>
         </x:is>
       </x:c>
-      <x:c r="B41" s="15" t="n">
+      <x:c r="B42" s="15" t="n">
         <x:v>0.3</x:v>
       </x:c>
-      <x:c r="C41" s="9" t="inlineStr">
+      <x:c r="C42" s="9" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
-      <x:c r="D41" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Partner pricing on Vertex/Bedrock differs from list, plus retries and growth.</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="42">
-      <x:c r="A42" s="5" t="inlineStr">
+      <x:c r="D42" s="10" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Retries, growth, price changes, and in-region hosting through a cloud provider priced differently from the DeepSeek API.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" s="5" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Platform run costs</x:t>
         </x:is>
       </x:c>
-      <x:c r="B42" s="6" t="n"/>
-      <x:c r="C42" s="6" t="n"/>
-      <x:c r="D42" s="6" t="n"/>
-    </x:row>
-    <x:row r="43">
-      <x:c r="A43" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Cloud infrastructure, fixed</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B43" s="8" t="n">
-        <x:v>70000</x:v>
-      </x:c>
-      <x:c r="C43" s="9" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">THB / month</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D43" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Dedicated tenant in a Thailand region: app, Postgres + pgvector, Redis, storage, WAF, logs, non-prod.</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="B43" s="6" t="n"/>
+      <x:c r="C43" s="6" t="n"/>
+      <x:c r="D43" s="6" t="n"/>
     </x:row>
     <x:row r="44">
       <x:c r="A44" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Cloud infrastructure, variable</x:t>
+          <x:t xml:space="preserve">Cloud infrastructure, fixed</x:t>
         </x:is>
       </x:c>
       <x:c r="B44" s="8" t="n">
-        <x:v>1.8</x:v>
+        <x:v>70000</x:v>
       </x:c>
       <x:c r="C44" s="9" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">THB / employee / mo</x:t>
+          <x:t xml:space="preserve">THB / month</x:t>
         </x:is>
       </x:c>
       <x:c r="D44" s="10" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Assumption.</x:t>
+          <x:t xml:space="preserve">Dedicated tenant in a Thailand region: app, Postgres + pgvector, Redis, storage, WAF, logs, non-prod.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="45">
       <x:c r="A45" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">LINE OA Pro plan</x:t>
+          <x:t xml:space="preserve">Cloud infrastructure, variable</x:t>
         </x:is>
       </x:c>
       <x:c r="B45" s="8" t="n">
-        <x:v>1780</x:v>
+        <x:v>1.8</x:v>
       </x:c>
       <x:c r="C45" s="9" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">THB / month</x:t>
+          <x:t xml:space="preserve">THB / employee / mo</x:t>
         </x:is>
       </x:c>
       <x:c r="D45" s="10" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">LINE for Business TH price list (excl. VAT): 35,000 messages included.</x:t>
+          <x:t xml:space="preserve">Assumption.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="46">
       <x:c r="A46" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">LINE messages included</x:t>
+          <x:t xml:space="preserve">LINE OA Pro plan</x:t>
         </x:is>
       </x:c>
       <x:c r="B46" s="8" t="n">
-        <x:v>35000</x:v>
+        <x:v>1780</x:v>
       </x:c>
       <x:c r="C46" s="9" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">messages</x:t>
+          <x:t xml:space="preserve">THB / month</x:t>
         </x:is>
       </x:c>
       <x:c r="D46" s="10" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">LINE for Business TH price list (excl. VAT): 35,000 messages included.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="47">
       <x:c r="A47" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">LINE extra message</x:t>
+          <x:t xml:space="preserve">LINE messages included</x:t>
         </x:is>
       </x:c>
       <x:c r="B47" s="8" t="n">
-        <x:v>0.06</x:v>
+        <x:v>35000</x:v>
       </x:c>
       <x:c r="C47" s="9" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">THB / message</x:t>
+          <x:t xml:space="preserve">messages</x:t>
         </x:is>
       </x:c>
       <x:c r="D47" s="10" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Pro plan extra rate.</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="48">
       <x:c r="A48" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Frontline share</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B48" s="15" t="n">
-        <x:v>0.6</x:v>
+          <x:t xml:space="preserve">LINE extra message</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B48" s="8" t="n">
+        <x:v>0.06</x:v>
       </x:c>
       <x:c r="C48" s="9" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">THB / message</x:t>
         </x:is>
       </x:c>
       <x:c r="D48" s="10" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Brief: ~60% frontline, mostly mobile.</x:t>
+          <x:t xml:space="preserve">Pro plan extra rate.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="49">
       <x:c r="A49" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Frontline users needing SMS OTP per month</x:t>
+          <x:t xml:space="preserve">Frontline share</x:t>
         </x:is>
       </x:c>
       <x:c r="B49" s="15" t="n">
-        <x:v>0.1</x:v>
+        <x:v>0.6</x:v>
       </x:c>
       <x:c r="C49" s="9" t="inlineStr">
         <x:is>
@@ -1516,62 +1516,62 @@
       </x:c>
       <x:c r="D49" s="10" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Fallback for staff without corporate SSO; LINE Login is primary.</x:t>
+          <x:t xml:space="preserve">Brief: ~60% frontline, mostly mobile.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="50">
       <x:c r="A50" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SMS OTP cost</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B50" s="8" t="n">
-        <x:v>0.5</x:v>
+          <x:t xml:space="preserve">Frontline users needing SMS OTP per month</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B50" s="15" t="n">
+        <x:v>0.1</x:v>
       </x:c>
       <x:c r="C50" s="9" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">THB / SMS</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="D50" s="10" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Assumption; confirm with the client's SMS gateway.</x:t>
+          <x:t xml:space="preserve">Fallback for staff without corporate SSO; LINE Login is primary.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="51">
       <x:c r="A51" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Tooling (monitoring, LRS, security scanning)</x:t>
+          <x:t xml:space="preserve">SMS OTP cost</x:t>
         </x:is>
       </x:c>
       <x:c r="B51" s="8" t="n">
-        <x:v>30000</x:v>
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="C51" s="9" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">THB / month</x:t>
+          <x:t xml:space="preserve">THB / SMS</x:t>
         </x:is>
       </x:c>
       <x:c r="D51" s="10" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">Assumption; confirm with the client's SMS gateway.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="52">
       <x:c r="A52" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Tooling, variable</x:t>
+          <x:t xml:space="preserve">Tooling (monitoring, LRS, security scanning)</x:t>
         </x:is>
       </x:c>
       <x:c r="B52" s="8" t="n">
-        <x:v>0.25</x:v>
+        <x:v>30000</x:v>
       </x:c>
       <x:c r="C52" s="9" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">THB / employee / mo</x:t>
+          <x:t xml:space="preserve">THB / month</x:t>
         </x:is>
       </x:c>
       <x:c r="D52" s="10" t="inlineStr">
@@ -1583,81 +1583,81 @@
     <x:row r="53">
       <x:c r="A53" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Annual penetration test</x:t>
+          <x:t xml:space="preserve">Tooling, variable</x:t>
         </x:is>
       </x:c>
       <x:c r="B53" s="8" t="n">
-        <x:v>400000</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="C53" s="9" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">THB / yr</x:t>
+          <x:t xml:space="preserve">THB / employee / mo</x:t>
         </x:is>
       </x:c>
       <x:c r="D53" s="10" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Also one at go-live (Build sheet).</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="54">
       <x:c r="A54" s="7" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">Annual penetration test</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B54" s="8" t="n">
+        <x:v>400000</x:v>
+      </x:c>
+      <x:c r="C54" s="9" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">THB / yr</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D54" s="10" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Also one at go-live (Build sheet).</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="55">
+      <x:c r="A55" s="7" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">DPIA refresh and compliance audit</x:t>
         </x:is>
       </x:c>
-      <x:c r="B54" s="8" t="n">
+      <x:c r="B55" s="8" t="n">
         <x:v>200000</x:v>
       </x:c>
-      <x:c r="C54" s="9" t="inlineStr">
+      <x:c r="C55" s="9" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">THB / yr</x:t>
         </x:is>
       </x:c>
-      <x:c r="D54" s="10" t="inlineStr">
+      <x:c r="D55" s="10" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">PDPA; PDPC AI guidance expects DPIA for high-risk AI.</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="55">
-      <x:c r="A55" s="5" t="inlineStr">
+    <x:row r="56">
+      <x:c r="A56" s="5" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Run team (client-dedicated + platform)</x:t>
         </x:is>
       </x:c>
-      <x:c r="B55" s="6" t="n"/>
-      <x:c r="C55" s="6" t="n"/>
-      <x:c r="D55" s="6" t="n"/>
-    </x:row>
-    <x:row r="56">
-      <x:c r="A56" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Customer success / product owner</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B56" s="8" t="n">
-        <x:v>0.5</x:v>
-      </x:c>
-      <x:c r="C56" s="9" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">FTE</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D56" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
+      <x:c r="B56" s="6" t="n"/>
+      <x:c r="C56" s="6" t="n"/>
+      <x:c r="D56" s="6" t="n"/>
     </x:row>
     <x:row r="57">
       <x:c r="A57" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Skills &amp; content analysts, base</x:t>
+          <x:t xml:space="preserve">Customer success / product owner</x:t>
         </x:is>
       </x:c>
       <x:c r="B57" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="C57" s="9" t="inlineStr">
         <x:is>
@@ -1666,38 +1666,38 @@
       </x:c>
       <x:c r="D57" s="10" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Maintain frameworks, tag new content, review flagged answers.</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="58">
       <x:c r="A58" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Employees per extra analyst</x:t>
+          <x:t xml:space="preserve">Skills &amp; content analysts, base</x:t>
         </x:is>
       </x:c>
       <x:c r="B58" s="8" t="n">
-        <x:v>30000</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C58" s="9" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">people</x:t>
+          <x:t xml:space="preserve">FTE</x:t>
         </x:is>
       </x:c>
       <x:c r="D58" s="10" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">Maintain frameworks, tag new content, review flagged answers.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="59">
       <x:c r="A59" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Employees per L2 support analyst</x:t>
+          <x:t xml:space="preserve">Employees per extra analyst</x:t>
         </x:is>
       </x:c>
       <x:c r="B59" s="8" t="n">
-        <x:v>25000</x:v>
+        <x:v>30000</x:v>
       </x:c>
       <x:c r="C59" s="9" t="inlineStr">
         <x:is>
@@ -1706,148 +1706,148 @@
       </x:c>
       <x:c r="D59" s="10" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">L1 stays with the client's HR helpdesk.</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="60">
       <x:c r="A60" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Platform team up to 20k employees</x:t>
+          <x:t xml:space="preserve">Employees per L2 support analyst</x:t>
         </x:is>
       </x:c>
       <x:c r="B60" s="8" t="n">
-        <x:v>2.5</x:v>
+        <x:v>25000</x:v>
       </x:c>
       <x:c r="C60" s="9" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">FTE</x:t>
+          <x:t xml:space="preserve">people</x:t>
         </x:is>
       </x:c>
       <x:c r="D60" s="10" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Engineering, AI ops and security on call. Dedicated: this is the platform's first client, so no cost is shared yet.</x:t>
+          <x:t xml:space="preserve">L1 stays with the client's HR helpdesk.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="61">
       <x:c r="A61" s="7" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">Platform team up to 20k employees</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B61" s="8" t="n">
+        <x:v>2.5</x:v>
+      </x:c>
+      <x:c r="C61" s="9" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">FTE</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D61" s="10" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Engineering, AI ops and security on call. Dedicated: this is the platform's first client, so no cost is shared yet.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="62">
+      <x:c r="A62" s="7" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">Platform team above 20k employees</x:t>
         </x:is>
       </x:c>
-      <x:c r="B61" s="8" t="n">
+      <x:c r="B62" s="8" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C61" s="9" t="inlineStr">
+      <x:c r="C62" s="9" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">FTE</x:t>
         </x:is>
       </x:c>
-      <x:c r="D61" s="10" t="inlineStr">
+      <x:c r="D62" s="10" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Adds wave 2-3 integrations and the ASEAN languages.</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="62">
-      <x:c r="A62" s="5" t="inlineStr">
+    <x:row r="63">
+      <x:c r="A63" s="5" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Pricing (levers)</x:t>
         </x:is>
       </x:c>
-      <x:c r="B62" s="6" t="n"/>
-      <x:c r="C62" s="6" t="n"/>
-      <x:c r="D62" s="6" t="n"/>
-    </x:row>
-    <x:row r="63">
-      <x:c r="A63" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Subscription price per enrolled employee per month</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B63" s="16" t="n">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C63" s="9" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">THB</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D63" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Includes platform, hosting, AI coach (fair use), L2 support, framework upkeep.</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="B63" s="6" t="n"/>
+      <x:c r="C63" s="6" t="n"/>
+      <x:c r="D63" s="6" t="n"/>
     </x:row>
     <x:row r="64">
       <x:c r="A64" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Minimum committed employees from wave 2</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B64" s="17" t="n">
-        <x:v>20000</x:v>
+          <x:t xml:space="preserve">Subscription price per enrolled employee per month</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B64" s="16" t="n">
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C64" s="9" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">people</x:t>
+          <x:t xml:space="preserve">THB</x:t>
         </x:is>
       </x:c>
       <x:c r="D64" s="10" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Protects unit economics while waves ramp.</x:t>
+          <x:t xml:space="preserve">Includes platform, hosting, AI coach (fair use), L2 support, framework upkeep.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="65">
       <x:c r="A65" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Fixed-date risk premium on implementation</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B65" s="11" t="n">
-        <x:v>0.1</x:v>
+          <x:t xml:space="preserve">Minimum committed employees from wave 2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B65" s="17" t="n">
+        <x:v>20000</x:v>
       </x:c>
       <x:c r="C65" s="9" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">people</x:t>
         </x:is>
       </x:c>
       <x:c r="D65" s="10" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">IRIS carries schedule risk on a fixed fee.</x:t>
+          <x:t xml:space="preserve">Protects unit economics while waves ramp.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="66">
       <x:c r="A66" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Wave 2 rollout services (fixed)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B66" s="17" t="n">
-        <x:v>6000000</x:v>
+          <x:t xml:space="preserve">Fixed-date risk premium on implementation</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B66" s="11" t="n">
+        <x:v>0.1</x:v>
       </x:c>
       <x:c r="C66" s="9" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">THB</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="D66" s="10" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Frameworks for new role families, integrations, change.</x:t>
+          <x:t xml:space="preserve">IRIS carries schedule risk on a fixed fee.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="67">
       <x:c r="A67" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Wave 3 rollout services (fixed, incl. ASEAN localisation)</x:t>
+          <x:t xml:space="preserve">Wave 2 rollout services (fixed)</x:t>
         </x:is>
       </x:c>
       <x:c r="B67" s="17" t="n">
-        <x:v>9000000</x:v>
+        <x:v>6000000</x:v>
       </x:c>
       <x:c r="C67" s="9" t="inlineStr">
         <x:is>
@@ -1856,160 +1856,167 @@
       </x:c>
       <x:c r="D67" s="10" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">3 languages, local data rules, local content.</x:t>
+          <x:t xml:space="preserve">Frameworks for new role families, integrations, change.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="68">
       <x:c r="A68" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Wave services delivery cost ratio</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B68" s="15" t="n">
-        <x:v>0.5</x:v>
+          <x:t xml:space="preserve">Wave 3 rollout services (fixed, incl. ASEAN localisation)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B68" s="17" t="n">
+        <x:v>9000000</x:v>
       </x:c>
       <x:c r="C68" s="9" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">of fee</x:t>
+          <x:t xml:space="preserve">THB</x:t>
         </x:is>
       </x:c>
       <x:c r="D68" s="10" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">3 languages, local data rules, local content.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="69">
       <x:c r="A69" s="7" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">Wave services delivery cost ratio</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B69" s="15" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="C69" s="9" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">of fee</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D69" s="10" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="70">
+      <x:c r="A70" s="7" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">Share of subscription at risk on adoption KPIs</x:t>
         </x:is>
       </x:c>
-      <x:c r="B69" s="15" t="n">
+      <x:c r="B70" s="15" t="n">
         <x:v>0.1</x:v>
       </x:c>
-      <x:c r="C69" s="9" t="inlineStr">
+      <x:c r="C70" s="9" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
-      <x:c r="D69" s="10" t="inlineStr">
+      <x:c r="D70" s="10" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Credited back if adoption KPIs are missed. Base case assumes met.</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="70">
-      <x:c r="A70" s="5" t="inlineStr">
+    <x:row r="71">
+      <x:c r="A71" s="5" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Rate card (THB)</x:t>
         </x:is>
       </x:c>
-      <x:c r="B70" s="6" t="n"/>
-      <x:c r="C70" s="6" t="n"/>
-      <x:c r="D70" s="6" t="n"/>
-    </x:row>
-    <x:row r="71">
-      <x:c r="A71" s="18" t="inlineStr">
+      <x:c r="B71" s="6" t="n"/>
+      <x:c r="C71" s="6" t="n"/>
+      <x:c r="D71" s="6" t="n"/>
+    </x:row>
+    <x:row r="72">
+      <x:c r="A72" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Role</x:t>
         </x:is>
       </x:c>
-      <x:c r="B71" s="18" t="inlineStr">
+      <x:c r="B72" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Cost / month</x:t>
         </x:is>
       </x:c>
-      <x:c r="C71" s="18" t="inlineStr">
+      <x:c r="C72" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Bill / day</x:t>
         </x:is>
       </x:c>
-      <x:c r="D71" s="18" t="inlineStr">
+      <x:c r="D72" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Note</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="72">
-      <x:c r="A72" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Product &amp; delivery lead</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B72" s="17" t="n">
-        <x:v>260000</x:v>
-      </x:c>
-      <x:c r="C72" s="17" t="n">
-        <x:v>28000</x:v>
-      </x:c>
-      <x:c r="D72" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Cost = fully loaded monthly cost to IRIS (assumption). Bill rates are about 2x the Thai public-sector consultant reference (PDMO FY2026: developer 3,700-4,960 THB/day, senior consultant 8,410, PM 12,120) and below global-SI rates.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="73">
       <x:c r="A73" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Solution architect</x:t>
+          <x:t xml:space="preserve">Product &amp; delivery lead</x:t>
         </x:is>
       </x:c>
       <x:c r="B73" s="17" t="n">
-        <x:v>200000</x:v>
+        <x:v>260000</x:v>
       </x:c>
       <x:c r="C73" s="17" t="n">
-        <x:v>22000</x:v>
+        <x:v>28000</x:v>
+      </x:c>
+      <x:c r="D73" s="10" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Cost = fully loaded monthly cost to IRIS (assumption). Bill rates are about 2x the Thai public-sector consultant reference (PDMO FY2026: developer 3,700-4,960 THB/day, senior consultant 8,410, PM 12,120) and below global-SI rates.</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="74">
       <x:c r="A74" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Senior engineer</x:t>
+          <x:t xml:space="preserve">Solution architect</x:t>
         </x:is>
       </x:c>
       <x:c r="B74" s="17" t="n">
-        <x:v>160000</x:v>
+        <x:v>200000</x:v>
       </x:c>
       <x:c r="C74" s="17" t="n">
-        <x:v>16000</x:v>
+        <x:v>22000</x:v>
       </x:c>
     </x:row>
     <x:row r="75">
       <x:c r="A75" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Engineer</x:t>
+          <x:t xml:space="preserve">Senior engineer</x:t>
         </x:is>
       </x:c>
       <x:c r="B75" s="17" t="n">
-        <x:v>90000</x:v>
+        <x:v>160000</x:v>
       </x:c>
       <x:c r="C75" s="17" t="n">
-        <x:v>9500</x:v>
+        <x:v>16000</x:v>
       </x:c>
     </x:row>
     <x:row r="76">
       <x:c r="A76" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">AI engineer</x:t>
+          <x:t xml:space="preserve">Engineer</x:t>
         </x:is>
       </x:c>
       <x:c r="B76" s="17" t="n">
-        <x:v>160000</x:v>
+        <x:v>90000</x:v>
       </x:c>
       <x:c r="C76" s="17" t="n">
-        <x:v>16000</x:v>
+        <x:v>9500</x:v>
       </x:c>
     </x:row>
     <x:row r="77">
       <x:c r="A77" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Data &amp; integration engineer</x:t>
+          <x:t xml:space="preserve">AI engineer</x:t>
         </x:is>
       </x:c>
       <x:c r="B77" s="17" t="n">
-        <x:v>150000</x:v>
+        <x:v>160000</x:v>
       </x:c>
       <x:c r="C77" s="17" t="n">
         <x:v>16000</x:v>
@@ -2018,104 +2025,117 @@
     <x:row r="78">
       <x:c r="A78" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">QA engineer</x:t>
+          <x:t xml:space="preserve">Data &amp; integration engineer</x:t>
         </x:is>
       </x:c>
       <x:c r="B78" s="17" t="n">
-        <x:v>80000</x:v>
+        <x:v>150000</x:v>
       </x:c>
       <x:c r="C78" s="17" t="n">
-        <x:v>8500</x:v>
+        <x:v>16000</x:v>
       </x:c>
     </x:row>
     <x:row r="79">
       <x:c r="A79" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">UX/UI designer</x:t>
+          <x:t xml:space="preserve">QA engineer</x:t>
         </x:is>
       </x:c>
       <x:c r="B79" s="17" t="n">
-        <x:v>110000</x:v>
+        <x:v>80000</x:v>
       </x:c>
       <x:c r="C79" s="17" t="n">
-        <x:v>12000</x:v>
+        <x:v>8500</x:v>
       </x:c>
     </x:row>
     <x:row r="80">
       <x:c r="A80" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">DevSecOps engineer</x:t>
+          <x:t xml:space="preserve">UX/UI designer</x:t>
         </x:is>
       </x:c>
       <x:c r="B80" s="17" t="n">
-        <x:v>160000</x:v>
+        <x:v>110000</x:v>
       </x:c>
       <x:c r="C80" s="17" t="n">
-        <x:v>16000</x:v>
+        <x:v>12000</x:v>
       </x:c>
     </x:row>
     <x:row r="81">
       <x:c r="A81" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Skills methodology lead</x:t>
+          <x:t xml:space="preserve">DevSecOps engineer</x:t>
         </x:is>
       </x:c>
       <x:c r="B81" s="17" t="n">
-        <x:v>200000</x:v>
+        <x:v>160000</x:v>
       </x:c>
       <x:c r="C81" s="17" t="n">
-        <x:v>22000</x:v>
+        <x:v>16000</x:v>
       </x:c>
     </x:row>
     <x:row r="82">
       <x:c r="A82" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Skills consultant</x:t>
+          <x:t xml:space="preserve">Skills methodology lead</x:t>
         </x:is>
       </x:c>
       <x:c r="B82" s="17" t="n">
-        <x:v>140000</x:v>
+        <x:v>200000</x:v>
       </x:c>
       <x:c r="C82" s="17" t="n">
-        <x:v>15000</x:v>
+        <x:v>22000</x:v>
       </x:c>
     </x:row>
     <x:row r="83">
       <x:c r="A83" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Content analyst</x:t>
+          <x:t xml:space="preserve">Skills consultant</x:t>
         </x:is>
       </x:c>
       <x:c r="B83" s="17" t="n">
-        <x:v>70000</x:v>
+        <x:v>140000</x:v>
       </x:c>
       <x:c r="C83" s="17" t="n">
-        <x:v>7000</x:v>
+        <x:v>15000</x:v>
       </x:c>
     </x:row>
     <x:row r="84">
       <x:c r="A84" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Change &amp; adoption consultant</x:t>
+          <x:t xml:space="preserve">Content analyst</x:t>
         </x:is>
       </x:c>
       <x:c r="B84" s="17" t="n">
-        <x:v>140000</x:v>
+        <x:v>70000</x:v>
       </x:c>
       <x:c r="C84" s="17" t="n">
-        <x:v>15000</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="85">
       <x:c r="A85" s="7" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">Change &amp; adoption consultant</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B85" s="17" t="n">
+        <x:v>140000</x:v>
+      </x:c>
+      <x:c r="C85" s="17" t="n">
+        <x:v>15000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86">
+      <x:c r="A86" s="7" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">Support analyst</x:t>
         </x:is>
       </x:c>
-      <x:c r="B85" s="17" t="n">
+      <x:c r="B86" s="17" t="n">
         <x:v>60000</x:v>
       </x:c>
-      <x:c r="C85" s="17" t="n">
+      <x:c r="C86" s="17" t="n">
         <x:v>6000</x:v>
       </x:c>
     </x:row>
@@ -2196,11 +2216,11 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="D5" s="20" t="n">
-        <x:f>C5*Assumptions!$B$72/Assumptions!$B$7</x:f>
+        <x:f>C5*Assumptions!$B$73/Assumptions!$B$7</x:f>
         <x:v>742857.1428571428</x:v>
       </x:c>
       <x:c r="E5" s="20" t="n">
-        <x:f>C5*Assumptions!$C$72</x:f>
+        <x:f>C5*Assumptions!$C$73</x:f>
         <x:v>1680000</x:v>
       </x:c>
       <x:c r="F5" s="10" t="inlineStr">
@@ -2223,11 +2243,11 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="D6" s="20" t="n">
-        <x:f>C6*Assumptions!$B$73/Assumptions!$B$7</x:f>
+        <x:f>C6*Assumptions!$B$74/Assumptions!$B$7</x:f>
         <x:v>571428.5714285715</x:v>
       </x:c>
       <x:c r="E6" s="20" t="n">
-        <x:f>C6*Assumptions!$C$73</x:f>
+        <x:f>C6*Assumptions!$C$74</x:f>
         <x:v>1320000</x:v>
       </x:c>
       <x:c r="F6" s="10" t="inlineStr">
@@ -2250,11 +2270,11 @@
         <x:v>120</x:v>
       </x:c>
       <x:c r="D7" s="20" t="n">
-        <x:f>C7*Assumptions!$B$74/Assumptions!$B$7</x:f>
+        <x:f>C7*Assumptions!$B$75/Assumptions!$B$7</x:f>
         <x:v>914285.7142857143</x:v>
       </x:c>
       <x:c r="E7" s="20" t="n">
-        <x:f>C7*Assumptions!$C$74</x:f>
+        <x:f>C7*Assumptions!$C$75</x:f>
         <x:v>1920000</x:v>
       </x:c>
       <x:c r="F7" s="10" t="inlineStr">
@@ -2277,11 +2297,11 @@
         <x:v>120</x:v>
       </x:c>
       <x:c r="D8" s="20" t="n">
-        <x:f>C8*Assumptions!$B$75/Assumptions!$B$7</x:f>
+        <x:f>C8*Assumptions!$B$76/Assumptions!$B$7</x:f>
         <x:v>514285.71428571426</x:v>
       </x:c>
       <x:c r="E8" s="20" t="n">
-        <x:f>C8*Assumptions!$C$75</x:f>
+        <x:f>C8*Assumptions!$C$76</x:f>
         <x:v>1140000</x:v>
       </x:c>
       <x:c r="F8" s="10" t="inlineStr">
@@ -2304,11 +2324,11 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="D9" s="20" t="n">
-        <x:f>C9*Assumptions!$B$76/Assumptions!$B$7</x:f>
+        <x:f>C9*Assumptions!$B$77/Assumptions!$B$7</x:f>
         <x:v>457142.85714285716</x:v>
       </x:c>
       <x:c r="E9" s="20" t="n">
-        <x:f>C9*Assumptions!$C$76</x:f>
+        <x:f>C9*Assumptions!$C$77</x:f>
         <x:v>960000</x:v>
       </x:c>
       <x:c r="F9" s="10" t="inlineStr">
@@ -2331,11 +2351,11 @@
         <x:v>120</x:v>
       </x:c>
       <x:c r="D10" s="20" t="n">
-        <x:f>C10*Assumptions!$B$77/Assumptions!$B$7</x:f>
+        <x:f>C10*Assumptions!$B$78/Assumptions!$B$7</x:f>
         <x:v>857142.8571428572</x:v>
       </x:c>
       <x:c r="E10" s="20" t="n">
-        <x:f>C10*Assumptions!$C$77</x:f>
+        <x:f>C10*Assumptions!$C$78</x:f>
         <x:v>1920000</x:v>
       </x:c>
       <x:c r="F10" s="10" t="inlineStr">
@@ -2358,11 +2378,11 @@
         <x:v>90</x:v>
       </x:c>
       <x:c r="D11" s="20" t="n">
-        <x:f>C11*Assumptions!$B$78/Assumptions!$B$7</x:f>
+        <x:f>C11*Assumptions!$B$79/Assumptions!$B$7</x:f>
         <x:v>342857.14285714284</x:v>
       </x:c>
       <x:c r="E11" s="20" t="n">
-        <x:f>C11*Assumptions!$C$78</x:f>
+        <x:f>C11*Assumptions!$C$79</x:f>
         <x:v>765000</x:v>
       </x:c>
       <x:c r="F11" s="10" t="inlineStr">
@@ -2385,11 +2405,11 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="D12" s="20" t="n">
-        <x:f>C12*Assumptions!$B$79/Assumptions!$B$7</x:f>
+        <x:f>C12*Assumptions!$B$80/Assumptions!$B$7</x:f>
         <x:v>220000</x:v>
       </x:c>
       <x:c r="E12" s="20" t="n">
-        <x:f>C12*Assumptions!$C$79</x:f>
+        <x:f>C12*Assumptions!$C$80</x:f>
         <x:v>504000</x:v>
       </x:c>
       <x:c r="F12" s="10" t="inlineStr">
@@ -2412,11 +2432,11 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="D13" s="20" t="n">
-        <x:f>C13*Assumptions!$B$80/Assumptions!$B$7</x:f>
+        <x:f>C13*Assumptions!$B$81/Assumptions!$B$7</x:f>
         <x:v>457142.85714285716</x:v>
       </x:c>
       <x:c r="E13" s="20" t="n">
-        <x:f>C13*Assumptions!$C$80</x:f>
+        <x:f>C13*Assumptions!$C$81</x:f>
         <x:v>960000</x:v>
       </x:c>
       <x:c r="F13" s="10" t="inlineStr">
@@ -2439,11 +2459,11 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="D14" s="20" t="n">
-        <x:f>C14*Assumptions!$B$81/Assumptions!$B$7</x:f>
+        <x:f>C14*Assumptions!$B$82/Assumptions!$B$7</x:f>
         <x:v>571428.5714285715</x:v>
       </x:c>
       <x:c r="E14" s="20" t="n">
-        <x:f>C14*Assumptions!$C$81</x:f>
+        <x:f>C14*Assumptions!$C$82</x:f>
         <x:v>1320000</x:v>
       </x:c>
       <x:c r="F14" s="10" t="inlineStr">
@@ -2466,11 +2486,11 @@
         <x:v>84</x:v>
       </x:c>
       <x:c r="D15" s="20" t="n">
-        <x:f>C15*Assumptions!$B$82/Assumptions!$B$7</x:f>
+        <x:f>C15*Assumptions!$B$83/Assumptions!$B$7</x:f>
         <x:v>560000</x:v>
       </x:c>
       <x:c r="E15" s="20" t="n">
-        <x:f>C15*Assumptions!$C$82</x:f>
+        <x:f>C15*Assumptions!$C$83</x:f>
         <x:v>1260000</x:v>
       </x:c>
       <x:c r="F15" s="10" t="inlineStr">
@@ -2493,11 +2513,11 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="D16" s="20" t="n">
-        <x:f>C16*Assumptions!$B$83/Assumptions!$B$7</x:f>
+        <x:f>C16*Assumptions!$B$84/Assumptions!$B$7</x:f>
         <x:v>200000</x:v>
       </x:c>
       <x:c r="E16" s="20" t="n">
-        <x:f>C16*Assumptions!$C$83</x:f>
+        <x:f>C16*Assumptions!$C$84</x:f>
         <x:v>420000</x:v>
       </x:c>
       <x:c r="F16" s="10" t="inlineStr">
@@ -2520,11 +2540,11 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D17" s="20" t="n">
-        <x:f>C17*Assumptions!$B$84/Assumptions!$B$7</x:f>
+        <x:f>C17*Assumptions!$B$85/Assumptions!$B$7</x:f>
         <x:v>320000</x:v>
       </x:c>
       <x:c r="E17" s="20" t="n">
-        <x:f>C17*Assumptions!$C$84</x:f>
+        <x:f>C17*Assumptions!$C$85</x:f>
         <x:v>720000</x:v>
       </x:c>
       <x:c r="F17" s="10" t="inlineStr">
@@ -2674,7 +2694,7 @@
         </x:is>
       </x:c>
       <x:c r="E30" s="20" t="n">
-        <x:f>E29*Assumptions!$B$65</x:f>
+        <x:f>E29*Assumptions!$B$66</x:f>
         <x:v>1569900</x:v>
       </x:c>
     </x:row>
@@ -3364,135 +3384,135 @@
       </x:c>
       <x:c r="E8" s="26" t="n">
         <x:f>E7*(Assumptions!$B$22*Assumptions!$B$33+Assumptions!$B$23*Assumptions!$B$35+Assumptions!$B$24*Assumptions!$B$34)/1000000</x:f>
-        <x:v>670.032</x:v>
+        <x:v>89.89056</x:v>
       </x:c>
       <x:c r="F8" s="26" t="n">
         <x:f>F7*(Assumptions!$B$22*Assumptions!$B$33+Assumptions!$B$23*Assumptions!$B$35+Assumptions!$B$24*Assumptions!$B$34)/1000000</x:f>
-        <x:v>670.032</x:v>
+        <x:v>89.89056</x:v>
       </x:c>
       <x:c r="G8" s="26" t="n">
         <x:f>G7*(Assumptions!$B$22*Assumptions!$B$33+Assumptions!$B$23*Assumptions!$B$35+Assumptions!$B$24*Assumptions!$B$34)/1000000</x:f>
-        <x:v>670.032</x:v>
+        <x:v>89.89056</x:v>
       </x:c>
       <x:c r="H8" s="26" t="n">
         <x:f>H7*(Assumptions!$B$22*Assumptions!$B$33+Assumptions!$B$23*Assumptions!$B$35+Assumptions!$B$24*Assumptions!$B$34)/1000000</x:f>
-        <x:v>1507.572</x:v>
+        <x:v>202.25376</x:v>
       </x:c>
       <x:c r="I8" s="26" t="n">
         <x:f>I7*(Assumptions!$B$22*Assumptions!$B$33+Assumptions!$B$23*Assumptions!$B$35+Assumptions!$B$24*Assumptions!$B$34)/1000000</x:f>
-        <x:v>1507.572</x:v>
+        <x:v>202.25376</x:v>
       </x:c>
       <x:c r="J8" s="26" t="n">
         <x:f>J7*(Assumptions!$B$22*Assumptions!$B$33+Assumptions!$B$23*Assumptions!$B$35+Assumptions!$B$24*Assumptions!$B$34)/1000000</x:f>
-        <x:v>1507.572</x:v>
+        <x:v>202.25376</x:v>
       </x:c>
       <x:c r="K8" s="26" t="n">
         <x:f>K7*(Assumptions!$B$22*Assumptions!$B$33+Assumptions!$B$23*Assumptions!$B$35+Assumptions!$B$24*Assumptions!$B$34)/1000000</x:f>
-        <x:v>1507.572</x:v>
+        <x:v>202.25376</x:v>
       </x:c>
       <x:c r="L8" s="26" t="n">
         <x:f>L7*(Assumptions!$B$22*Assumptions!$B$33+Assumptions!$B$23*Assumptions!$B$35+Assumptions!$B$24*Assumptions!$B$34)/1000000</x:f>
-        <x:v>1507.572</x:v>
+        <x:v>202.25376</x:v>
       </x:c>
       <x:c r="M8" s="26" t="n">
         <x:f>M7*(Assumptions!$B$22*Assumptions!$B$33+Assumptions!$B$23*Assumptions!$B$35+Assumptions!$B$24*Assumptions!$B$34)/1000000</x:f>
-        <x:v>1507.572</x:v>
+        <x:v>202.25376</x:v>
       </x:c>
       <x:c r="N8" s="26" t="n">
         <x:f>N7*(Assumptions!$B$22*Assumptions!$B$33+Assumptions!$B$23*Assumptions!$B$35+Assumptions!$B$24*Assumptions!$B$34)/1000000</x:f>
-        <x:v>2512.62</x:v>
+        <x:v>337.0896</x:v>
       </x:c>
       <x:c r="O8" s="26" t="n">
         <x:f>O7*(Assumptions!$B$22*Assumptions!$B$33+Assumptions!$B$23*Assumptions!$B$35+Assumptions!$B$24*Assumptions!$B$34)/1000000</x:f>
-        <x:v>2512.62</x:v>
+        <x:v>337.0896</x:v>
       </x:c>
       <x:c r="P8" s="26" t="n">
         <x:f>P7*(Assumptions!$B$22*Assumptions!$B$33+Assumptions!$B$23*Assumptions!$B$35+Assumptions!$B$24*Assumptions!$B$34)/1000000</x:f>
-        <x:v>2512.62</x:v>
+        <x:v>337.0896</x:v>
       </x:c>
       <x:c r="Q8" s="26" t="n">
         <x:f>Q7*(Assumptions!$B$22*Assumptions!$B$33+Assumptions!$B$23*Assumptions!$B$35+Assumptions!$B$24*Assumptions!$B$34)/1000000</x:f>
-        <x:v>2512.62</x:v>
+        <x:v>337.0896</x:v>
       </x:c>
       <x:c r="R8" s="26" t="n">
         <x:f>R7*(Assumptions!$B$22*Assumptions!$B$33+Assumptions!$B$23*Assumptions!$B$35+Assumptions!$B$24*Assumptions!$B$34)/1000000</x:f>
-        <x:v>2512.62</x:v>
+        <x:v>337.0896</x:v>
       </x:c>
       <x:c r="S8" s="26" t="n">
         <x:f>S7*(Assumptions!$B$22*Assumptions!$B$33+Assumptions!$B$23*Assumptions!$B$35+Assumptions!$B$24*Assumptions!$B$34)/1000000</x:f>
-        <x:v>2512.62</x:v>
+        <x:v>337.0896</x:v>
       </x:c>
       <x:c r="T8" s="26" t="n">
         <x:f>T7*(Assumptions!$B$22*Assumptions!$B$33+Assumptions!$B$23*Assumptions!$B$35+Assumptions!$B$24*Assumptions!$B$34)/1000000</x:f>
-        <x:v>2512.62</x:v>
+        <x:v>337.0896</x:v>
       </x:c>
       <x:c r="U8" s="26" t="n">
         <x:f>U7*(Assumptions!$B$22*Assumptions!$B$33+Assumptions!$B$23*Assumptions!$B$35+Assumptions!$B$24*Assumptions!$B$34)/1000000</x:f>
-        <x:v>2512.62</x:v>
+        <x:v>337.0896</x:v>
       </x:c>
       <x:c r="V8" s="26" t="n">
         <x:f>V7*(Assumptions!$B$22*Assumptions!$B$33+Assumptions!$B$23*Assumptions!$B$35+Assumptions!$B$24*Assumptions!$B$34)/1000000</x:f>
-        <x:v>2512.62</x:v>
+        <x:v>337.0896</x:v>
       </x:c>
       <x:c r="W8" s="26" t="n">
         <x:f>W7*(Assumptions!$B$22*Assumptions!$B$33+Assumptions!$B$23*Assumptions!$B$35+Assumptions!$B$24*Assumptions!$B$34)/1000000</x:f>
-        <x:v>2512.62</x:v>
+        <x:v>337.0896</x:v>
       </x:c>
       <x:c r="X8" s="26" t="n">
         <x:f>X7*(Assumptions!$B$22*Assumptions!$B$33+Assumptions!$B$23*Assumptions!$B$35+Assumptions!$B$24*Assumptions!$B$34)/1000000</x:f>
-        <x:v>2512.62</x:v>
+        <x:v>337.0896</x:v>
       </x:c>
       <x:c r="Y8" s="26" t="n">
         <x:f>Y7*(Assumptions!$B$22*Assumptions!$B$33+Assumptions!$B$23*Assumptions!$B$35+Assumptions!$B$24*Assumptions!$B$34)/1000000</x:f>
-        <x:v>2512.62</x:v>
+        <x:v>337.0896</x:v>
       </x:c>
       <x:c r="Z8" s="26" t="n">
         <x:f>Z7*(Assumptions!$B$22*Assumptions!$B$33+Assumptions!$B$23*Assumptions!$B$35+Assumptions!$B$24*Assumptions!$B$34)/1000000</x:f>
-        <x:v>2512.62</x:v>
+        <x:v>337.0896</x:v>
       </x:c>
       <x:c r="AA8" s="26" t="n">
         <x:f>AA7*(Assumptions!$B$22*Assumptions!$B$33+Assumptions!$B$23*Assumptions!$B$35+Assumptions!$B$24*Assumptions!$B$34)/1000000</x:f>
-        <x:v>2512.62</x:v>
+        <x:v>337.0896</x:v>
       </x:c>
       <x:c r="AB8" s="26" t="n">
         <x:f>AB7*(Assumptions!$B$22*Assumptions!$B$33+Assumptions!$B$23*Assumptions!$B$35+Assumptions!$B$24*Assumptions!$B$34)/1000000</x:f>
-        <x:v>2512.62</x:v>
+        <x:v>337.0896</x:v>
       </x:c>
       <x:c r="AC8" s="26" t="n">
         <x:f>AC7*(Assumptions!$B$22*Assumptions!$B$33+Assumptions!$B$23*Assumptions!$B$35+Assumptions!$B$24*Assumptions!$B$34)/1000000</x:f>
-        <x:v>2512.62</x:v>
+        <x:v>337.0896</x:v>
       </x:c>
       <x:c r="AD8" s="26" t="n">
         <x:f>AD7*(Assumptions!$B$22*Assumptions!$B$33+Assumptions!$B$23*Assumptions!$B$35+Assumptions!$B$24*Assumptions!$B$34)/1000000</x:f>
-        <x:v>2512.62</x:v>
+        <x:v>337.0896</x:v>
       </x:c>
       <x:c r="AE8" s="26" t="n">
         <x:f>AE7*(Assumptions!$B$22*Assumptions!$B$33+Assumptions!$B$23*Assumptions!$B$35+Assumptions!$B$24*Assumptions!$B$34)/1000000</x:f>
-        <x:v>2512.62</x:v>
+        <x:v>337.0896</x:v>
       </x:c>
       <x:c r="AF8" s="26" t="n">
         <x:f>AF7*(Assumptions!$B$22*Assumptions!$B$33+Assumptions!$B$23*Assumptions!$B$35+Assumptions!$B$24*Assumptions!$B$34)/1000000</x:f>
-        <x:v>2512.62</x:v>
+        <x:v>337.0896</x:v>
       </x:c>
       <x:c r="AG8" s="26" t="n">
         <x:f>AG7*(Assumptions!$B$22*Assumptions!$B$33+Assumptions!$B$23*Assumptions!$B$35+Assumptions!$B$24*Assumptions!$B$34)/1000000</x:f>
-        <x:v>2512.62</x:v>
+        <x:v>337.0896</x:v>
       </x:c>
       <x:c r="AH8" s="26" t="n">
         <x:f>AH7*(Assumptions!$B$22*Assumptions!$B$33+Assumptions!$B$23*Assumptions!$B$35+Assumptions!$B$24*Assumptions!$B$34)/1000000</x:f>
-        <x:v>2512.62</x:v>
+        <x:v>337.0896</x:v>
       </x:c>
       <x:c r="AI8" s="26" t="n">
         <x:f>AI7*(Assumptions!$B$22*Assumptions!$B$33+Assumptions!$B$23*Assumptions!$B$35+Assumptions!$B$24*Assumptions!$B$34)/1000000</x:f>
-        <x:v>2512.62</x:v>
+        <x:v>337.0896</x:v>
       </x:c>
       <x:c r="AJ8" s="26" t="n">
         <x:f>AJ7*(Assumptions!$B$22*Assumptions!$B$33+Assumptions!$B$23*Assumptions!$B$35+Assumptions!$B$24*Assumptions!$B$34)/1000000</x:f>
-        <x:v>2512.62</x:v>
+        <x:v>337.0896</x:v>
       </x:c>
       <x:c r="AK8" s="26" t="n">
         <x:f>AK7*(Assumptions!$B$22*Assumptions!$B$33+Assumptions!$B$23*Assumptions!$B$35+Assumptions!$B$24*Assumptions!$B$34)/1000000</x:f>
-        <x:v>2512.62</x:v>
+        <x:v>337.0896</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -3502,148 +3522,148 @@
         </x:is>
       </x:c>
       <x:c r="B9" s="26" t="n">
-        <x:f>B7*(Assumptions!$B$25*Assumptions!$B$38+Assumptions!$B$26*Assumptions!$B$39)/1000000</x:f>
+        <x:f>B7*(Assumptions!$B$25*Assumptions!$B$39+Assumptions!$B$26*Assumptions!$B$40)/1000000</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C9" s="26" t="n">
-        <x:f>C7*(Assumptions!$B$25*Assumptions!$B$38+Assumptions!$B$26*Assumptions!$B$39)/1000000</x:f>
+        <x:f>C7*(Assumptions!$B$25*Assumptions!$B$39+Assumptions!$B$26*Assumptions!$B$40)/1000000</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D9" s="26" t="n">
-        <x:f>D7*(Assumptions!$B$25*Assumptions!$B$38+Assumptions!$B$26*Assumptions!$B$39)/1000000</x:f>
+        <x:f>D7*(Assumptions!$B$25*Assumptions!$B$39+Assumptions!$B$26*Assumptions!$B$40)/1000000</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="E9" s="26" t="n">
-        <x:f>E7*(Assumptions!$B$25*Assumptions!$B$38+Assumptions!$B$26*Assumptions!$B$39)/1000000</x:f>
-        <x:v>5.832</x:v>
+        <x:f>E7*(Assumptions!$B$25*Assumptions!$B$39+Assumptions!$B$26*Assumptions!$B$40)/1000000</x:f>
+        <x:v>15.9408</x:v>
       </x:c>
       <x:c r="F9" s="26" t="n">
-        <x:f>F7*(Assumptions!$B$25*Assumptions!$B$38+Assumptions!$B$26*Assumptions!$B$39)/1000000</x:f>
-        <x:v>5.832</x:v>
+        <x:f>F7*(Assumptions!$B$25*Assumptions!$B$39+Assumptions!$B$26*Assumptions!$B$40)/1000000</x:f>
+        <x:v>15.9408</x:v>
       </x:c>
       <x:c r="G9" s="26" t="n">
-        <x:f>G7*(Assumptions!$B$25*Assumptions!$B$38+Assumptions!$B$26*Assumptions!$B$39)/1000000</x:f>
-        <x:v>5.832</x:v>
+        <x:f>G7*(Assumptions!$B$25*Assumptions!$B$39+Assumptions!$B$26*Assumptions!$B$40)/1000000</x:f>
+        <x:v>15.9408</x:v>
       </x:c>
       <x:c r="H9" s="26" t="n">
-        <x:f>H7*(Assumptions!$B$25*Assumptions!$B$38+Assumptions!$B$26*Assumptions!$B$39)/1000000</x:f>
-        <x:v>13.122</x:v>
+        <x:f>H7*(Assumptions!$B$25*Assumptions!$B$39+Assumptions!$B$26*Assumptions!$B$40)/1000000</x:f>
+        <x:v>35.8668</x:v>
       </x:c>
       <x:c r="I9" s="26" t="n">
-        <x:f>I7*(Assumptions!$B$25*Assumptions!$B$38+Assumptions!$B$26*Assumptions!$B$39)/1000000</x:f>
-        <x:v>13.122</x:v>
+        <x:f>I7*(Assumptions!$B$25*Assumptions!$B$39+Assumptions!$B$26*Assumptions!$B$40)/1000000</x:f>
+        <x:v>35.8668</x:v>
       </x:c>
       <x:c r="J9" s="26" t="n">
-        <x:f>J7*(Assumptions!$B$25*Assumptions!$B$38+Assumptions!$B$26*Assumptions!$B$39)/1000000</x:f>
-        <x:v>13.122</x:v>
+        <x:f>J7*(Assumptions!$B$25*Assumptions!$B$39+Assumptions!$B$26*Assumptions!$B$40)/1000000</x:f>
+        <x:v>35.8668</x:v>
       </x:c>
       <x:c r="K9" s="26" t="n">
-        <x:f>K7*(Assumptions!$B$25*Assumptions!$B$38+Assumptions!$B$26*Assumptions!$B$39)/1000000</x:f>
-        <x:v>13.122</x:v>
+        <x:f>K7*(Assumptions!$B$25*Assumptions!$B$39+Assumptions!$B$26*Assumptions!$B$40)/1000000</x:f>
+        <x:v>35.8668</x:v>
       </x:c>
       <x:c r="L9" s="26" t="n">
-        <x:f>L7*(Assumptions!$B$25*Assumptions!$B$38+Assumptions!$B$26*Assumptions!$B$39)/1000000</x:f>
-        <x:v>13.122</x:v>
+        <x:f>L7*(Assumptions!$B$25*Assumptions!$B$39+Assumptions!$B$26*Assumptions!$B$40)/1000000</x:f>
+        <x:v>35.8668</x:v>
       </x:c>
       <x:c r="M9" s="26" t="n">
-        <x:f>M7*(Assumptions!$B$25*Assumptions!$B$38+Assumptions!$B$26*Assumptions!$B$39)/1000000</x:f>
-        <x:v>13.122</x:v>
+        <x:f>M7*(Assumptions!$B$25*Assumptions!$B$39+Assumptions!$B$26*Assumptions!$B$40)/1000000</x:f>
+        <x:v>35.8668</x:v>
       </x:c>
       <x:c r="N9" s="26" t="n">
-        <x:f>N7*(Assumptions!$B$25*Assumptions!$B$38+Assumptions!$B$26*Assumptions!$B$39)/1000000</x:f>
-        <x:v>21.87</x:v>
+        <x:f>N7*(Assumptions!$B$25*Assumptions!$B$39+Assumptions!$B$26*Assumptions!$B$40)/1000000</x:f>
+        <x:v>59.778</x:v>
       </x:c>
       <x:c r="O9" s="26" t="n">
-        <x:f>O7*(Assumptions!$B$25*Assumptions!$B$38+Assumptions!$B$26*Assumptions!$B$39)/1000000</x:f>
-        <x:v>21.87</x:v>
+        <x:f>O7*(Assumptions!$B$25*Assumptions!$B$39+Assumptions!$B$26*Assumptions!$B$40)/1000000</x:f>
+        <x:v>59.778</x:v>
       </x:c>
       <x:c r="P9" s="26" t="n">
-        <x:f>P7*(Assumptions!$B$25*Assumptions!$B$38+Assumptions!$B$26*Assumptions!$B$39)/1000000</x:f>
-        <x:v>21.87</x:v>
+        <x:f>P7*(Assumptions!$B$25*Assumptions!$B$39+Assumptions!$B$26*Assumptions!$B$40)/1000000</x:f>
+        <x:v>59.778</x:v>
       </x:c>
       <x:c r="Q9" s="26" t="n">
-        <x:f>Q7*(Assumptions!$B$25*Assumptions!$B$38+Assumptions!$B$26*Assumptions!$B$39)/1000000</x:f>
-        <x:v>21.87</x:v>
+        <x:f>Q7*(Assumptions!$B$25*Assumptions!$B$39+Assumptions!$B$26*Assumptions!$B$40)/1000000</x:f>
+        <x:v>59.778</x:v>
       </x:c>
       <x:c r="R9" s="26" t="n">
-        <x:f>R7*(Assumptions!$B$25*Assumptions!$B$38+Assumptions!$B$26*Assumptions!$B$39)/1000000</x:f>
-        <x:v>21.87</x:v>
+        <x:f>R7*(Assumptions!$B$25*Assumptions!$B$39+Assumptions!$B$26*Assumptions!$B$40)/1000000</x:f>
+        <x:v>59.778</x:v>
       </x:c>
       <x:c r="S9" s="26" t="n">
-        <x:f>S7*(Assumptions!$B$25*Assumptions!$B$38+Assumptions!$B$26*Assumptions!$B$39)/1000000</x:f>
-        <x:v>21.87</x:v>
+        <x:f>S7*(Assumptions!$B$25*Assumptions!$B$39+Assumptions!$B$26*Assumptions!$B$40)/1000000</x:f>
+        <x:v>59.778</x:v>
       </x:c>
       <x:c r="T9" s="26" t="n">
-        <x:f>T7*(Assumptions!$B$25*Assumptions!$B$38+Assumptions!$B$26*Assumptions!$B$39)/1000000</x:f>
-        <x:v>21.87</x:v>
+        <x:f>T7*(Assumptions!$B$25*Assumptions!$B$39+Assumptions!$B$26*Assumptions!$B$40)/1000000</x:f>
+        <x:v>59.778</x:v>
       </x:c>
       <x:c r="U9" s="26" t="n">
-        <x:f>U7*(Assumptions!$B$25*Assumptions!$B$38+Assumptions!$B$26*Assumptions!$B$39)/1000000</x:f>
-        <x:v>21.87</x:v>
+        <x:f>U7*(Assumptions!$B$25*Assumptions!$B$39+Assumptions!$B$26*Assumptions!$B$40)/1000000</x:f>
+        <x:v>59.778</x:v>
       </x:c>
       <x:c r="V9" s="26" t="n">
-        <x:f>V7*(Assumptions!$B$25*Assumptions!$B$38+Assumptions!$B$26*Assumptions!$B$39)/1000000</x:f>
-        <x:v>21.87</x:v>
+        <x:f>V7*(Assumptions!$B$25*Assumptions!$B$39+Assumptions!$B$26*Assumptions!$B$40)/1000000</x:f>
+        <x:v>59.778</x:v>
       </x:c>
       <x:c r="W9" s="26" t="n">
-        <x:f>W7*(Assumptions!$B$25*Assumptions!$B$38+Assumptions!$B$26*Assumptions!$B$39)/1000000</x:f>
-        <x:v>21.87</x:v>
+        <x:f>W7*(Assumptions!$B$25*Assumptions!$B$39+Assumptions!$B$26*Assumptions!$B$40)/1000000</x:f>
+        <x:v>59.778</x:v>
       </x:c>
       <x:c r="X9" s="26" t="n">
-        <x:f>X7*(Assumptions!$B$25*Assumptions!$B$38+Assumptions!$B$26*Assumptions!$B$39)/1000000</x:f>
-        <x:v>21.87</x:v>
+        <x:f>X7*(Assumptions!$B$25*Assumptions!$B$39+Assumptions!$B$26*Assumptions!$B$40)/1000000</x:f>
+        <x:v>59.778</x:v>
       </x:c>
       <x:c r="Y9" s="26" t="n">
-        <x:f>Y7*(Assumptions!$B$25*Assumptions!$B$38+Assumptions!$B$26*Assumptions!$B$39)/1000000</x:f>
-        <x:v>21.87</x:v>
+        <x:f>Y7*(Assumptions!$B$25*Assumptions!$B$39+Assumptions!$B$26*Assumptions!$B$40)/1000000</x:f>
+        <x:v>59.778</x:v>
       </x:c>
       <x:c r="Z9" s="26" t="n">
-        <x:f>Z7*(Assumptions!$B$25*Assumptions!$B$38+Assumptions!$B$26*Assumptions!$B$39)/1000000</x:f>
-        <x:v>21.87</x:v>
+        <x:f>Z7*(Assumptions!$B$25*Assumptions!$B$39+Assumptions!$B$26*Assumptions!$B$40)/1000000</x:f>
+        <x:v>59.778</x:v>
       </x:c>
       <x:c r="AA9" s="26" t="n">
-        <x:f>AA7*(Assumptions!$B$25*Assumptions!$B$38+Assumptions!$B$26*Assumptions!$B$39)/1000000</x:f>
-        <x:v>21.87</x:v>
+        <x:f>AA7*(Assumptions!$B$25*Assumptions!$B$39+Assumptions!$B$26*Assumptions!$B$40)/1000000</x:f>
+        <x:v>59.778</x:v>
       </x:c>
       <x:c r="AB9" s="26" t="n">
-        <x:f>AB7*(Assumptions!$B$25*Assumptions!$B$38+Assumptions!$B$26*Assumptions!$B$39)/1000000</x:f>
-        <x:v>21.87</x:v>
+        <x:f>AB7*(Assumptions!$B$25*Assumptions!$B$39+Assumptions!$B$26*Assumptions!$B$40)/1000000</x:f>
+        <x:v>59.778</x:v>
       </x:c>
       <x:c r="AC9" s="26" t="n">
-        <x:f>AC7*(Assumptions!$B$25*Assumptions!$B$38+Assumptions!$B$26*Assumptions!$B$39)/1000000</x:f>
-        <x:v>21.87</x:v>
+        <x:f>AC7*(Assumptions!$B$25*Assumptions!$B$39+Assumptions!$B$26*Assumptions!$B$40)/1000000</x:f>
+        <x:v>59.778</x:v>
       </x:c>
       <x:c r="AD9" s="26" t="n">
-        <x:f>AD7*(Assumptions!$B$25*Assumptions!$B$38+Assumptions!$B$26*Assumptions!$B$39)/1000000</x:f>
-        <x:v>21.87</x:v>
+        <x:f>AD7*(Assumptions!$B$25*Assumptions!$B$39+Assumptions!$B$26*Assumptions!$B$40)/1000000</x:f>
+        <x:v>59.778</x:v>
       </x:c>
       <x:c r="AE9" s="26" t="n">
-        <x:f>AE7*(Assumptions!$B$25*Assumptions!$B$38+Assumptions!$B$26*Assumptions!$B$39)/1000000</x:f>
-        <x:v>21.87</x:v>
+        <x:f>AE7*(Assumptions!$B$25*Assumptions!$B$39+Assumptions!$B$26*Assumptions!$B$40)/1000000</x:f>
+        <x:v>59.778</x:v>
       </x:c>
       <x:c r="AF9" s="26" t="n">
-        <x:f>AF7*(Assumptions!$B$25*Assumptions!$B$38+Assumptions!$B$26*Assumptions!$B$39)/1000000</x:f>
-        <x:v>21.87</x:v>
+        <x:f>AF7*(Assumptions!$B$25*Assumptions!$B$39+Assumptions!$B$26*Assumptions!$B$40)/1000000</x:f>
+        <x:v>59.778</x:v>
       </x:c>
       <x:c r="AG9" s="26" t="n">
-        <x:f>AG7*(Assumptions!$B$25*Assumptions!$B$38+Assumptions!$B$26*Assumptions!$B$39)/1000000</x:f>
-        <x:v>21.87</x:v>
+        <x:f>AG7*(Assumptions!$B$25*Assumptions!$B$39+Assumptions!$B$26*Assumptions!$B$40)/1000000</x:f>
+        <x:v>59.778</x:v>
       </x:c>
       <x:c r="AH9" s="26" t="n">
-        <x:f>AH7*(Assumptions!$B$25*Assumptions!$B$38+Assumptions!$B$26*Assumptions!$B$39)/1000000</x:f>
-        <x:v>21.87</x:v>
+        <x:f>AH7*(Assumptions!$B$25*Assumptions!$B$39+Assumptions!$B$26*Assumptions!$B$40)/1000000</x:f>
+        <x:v>59.778</x:v>
       </x:c>
       <x:c r="AI9" s="26" t="n">
-        <x:f>AI7*(Assumptions!$B$25*Assumptions!$B$38+Assumptions!$B$26*Assumptions!$B$39)/1000000</x:f>
-        <x:v>21.87</x:v>
+        <x:f>AI7*(Assumptions!$B$25*Assumptions!$B$39+Assumptions!$B$26*Assumptions!$B$40)/1000000</x:f>
+        <x:v>59.778</x:v>
       </x:c>
       <x:c r="AJ9" s="26" t="n">
-        <x:f>AJ7*(Assumptions!$B$25*Assumptions!$B$38+Assumptions!$B$26*Assumptions!$B$39)/1000000</x:f>
-        <x:v>21.87</x:v>
+        <x:f>AJ7*(Assumptions!$B$25*Assumptions!$B$39+Assumptions!$B$26*Assumptions!$B$40)/1000000</x:f>
+        <x:v>59.778</x:v>
       </x:c>
       <x:c r="AK9" s="26" t="n">
-        <x:f>AK7*(Assumptions!$B$25*Assumptions!$B$38+Assumptions!$B$26*Assumptions!$B$39)/1000000</x:f>
-        <x:v>21.87</x:v>
+        <x:f>AK7*(Assumptions!$B$25*Assumptions!$B$39+Assumptions!$B$26*Assumptions!$B$40)/1000000</x:f>
+        <x:v>59.778</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -3653,299 +3673,299 @@
         </x:is>
       </x:c>
       <x:c r="B10" s="26" t="n">
-        <x:f>B5*Assumptions!$B$20*(Assumptions!$B$27*Assumptions!$B$38+Assumptions!$B$28*Assumptions!$B$39)/1000000</x:f>
+        <x:f>B5*Assumptions!$B$20*(Assumptions!$B$27*Assumptions!$B$39+Assumptions!$B$28*Assumptions!$B$40)/1000000</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C10" s="26" t="n">
-        <x:f>C5*Assumptions!$B$20*(Assumptions!$B$27*Assumptions!$B$38+Assumptions!$B$28*Assumptions!$B$39)/1000000</x:f>
+        <x:f>C5*Assumptions!$B$20*(Assumptions!$B$27*Assumptions!$B$39+Assumptions!$B$28*Assumptions!$B$40)/1000000</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D10" s="26" t="n">
-        <x:f>D5*Assumptions!$B$20*(Assumptions!$B$27*Assumptions!$B$38+Assumptions!$B$28*Assumptions!$B$39)/1000000</x:f>
+        <x:f>D5*Assumptions!$B$20*(Assumptions!$B$27*Assumptions!$B$39+Assumptions!$B$28*Assumptions!$B$40)/1000000</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="E10" s="26" t="n">
-        <x:f>E5*Assumptions!$B$20*(Assumptions!$B$27*Assumptions!$B$38+Assumptions!$B$28*Assumptions!$B$39)/1000000</x:f>
-        <x:v>5.28</x:v>
+        <x:f>E5*Assumptions!$B$20*(Assumptions!$B$27*Assumptions!$B$39+Assumptions!$B$28*Assumptions!$B$40)/1000000</x:f>
+        <x:v>14.4</x:v>
       </x:c>
       <x:c r="F10" s="26" t="n">
-        <x:f>F5*Assumptions!$B$20*(Assumptions!$B$27*Assumptions!$B$38+Assumptions!$B$28*Assumptions!$B$39)/1000000</x:f>
-        <x:v>5.28</x:v>
+        <x:f>F5*Assumptions!$B$20*(Assumptions!$B$27*Assumptions!$B$39+Assumptions!$B$28*Assumptions!$B$40)/1000000</x:f>
+        <x:v>14.4</x:v>
       </x:c>
       <x:c r="G10" s="26" t="n">
-        <x:f>G5*Assumptions!$B$20*(Assumptions!$B$27*Assumptions!$B$38+Assumptions!$B$28*Assumptions!$B$39)/1000000</x:f>
-        <x:v>5.28</x:v>
+        <x:f>G5*Assumptions!$B$20*(Assumptions!$B$27*Assumptions!$B$39+Assumptions!$B$28*Assumptions!$B$40)/1000000</x:f>
+        <x:v>14.4</x:v>
       </x:c>
       <x:c r="H10" s="26" t="n">
-        <x:f>H5*Assumptions!$B$20*(Assumptions!$B$27*Assumptions!$B$38+Assumptions!$B$28*Assumptions!$B$39)/1000000</x:f>
-        <x:v>11.88</x:v>
+        <x:f>H5*Assumptions!$B$20*(Assumptions!$B$27*Assumptions!$B$39+Assumptions!$B$28*Assumptions!$B$40)/1000000</x:f>
+        <x:v>32.4</x:v>
       </x:c>
       <x:c r="I10" s="26" t="n">
-        <x:f>I5*Assumptions!$B$20*(Assumptions!$B$27*Assumptions!$B$38+Assumptions!$B$28*Assumptions!$B$39)/1000000</x:f>
-        <x:v>11.88</x:v>
+        <x:f>I5*Assumptions!$B$20*(Assumptions!$B$27*Assumptions!$B$39+Assumptions!$B$28*Assumptions!$B$40)/1000000</x:f>
+        <x:v>32.4</x:v>
       </x:c>
       <x:c r="J10" s="26" t="n">
-        <x:f>J5*Assumptions!$B$20*(Assumptions!$B$27*Assumptions!$B$38+Assumptions!$B$28*Assumptions!$B$39)/1000000</x:f>
-        <x:v>11.88</x:v>
+        <x:f>J5*Assumptions!$B$20*(Assumptions!$B$27*Assumptions!$B$39+Assumptions!$B$28*Assumptions!$B$40)/1000000</x:f>
+        <x:v>32.4</x:v>
       </x:c>
       <x:c r="K10" s="26" t="n">
-        <x:f>K5*Assumptions!$B$20*(Assumptions!$B$27*Assumptions!$B$38+Assumptions!$B$28*Assumptions!$B$39)/1000000</x:f>
-        <x:v>11.88</x:v>
+        <x:f>K5*Assumptions!$B$20*(Assumptions!$B$27*Assumptions!$B$39+Assumptions!$B$28*Assumptions!$B$40)/1000000</x:f>
+        <x:v>32.4</x:v>
       </x:c>
       <x:c r="L10" s="26" t="n">
-        <x:f>L5*Assumptions!$B$20*(Assumptions!$B$27*Assumptions!$B$38+Assumptions!$B$28*Assumptions!$B$39)/1000000</x:f>
-        <x:v>11.88</x:v>
+        <x:f>L5*Assumptions!$B$20*(Assumptions!$B$27*Assumptions!$B$39+Assumptions!$B$28*Assumptions!$B$40)/1000000</x:f>
+        <x:v>32.4</x:v>
       </x:c>
       <x:c r="M10" s="26" t="n">
-        <x:f>M5*Assumptions!$B$20*(Assumptions!$B$27*Assumptions!$B$38+Assumptions!$B$28*Assumptions!$B$39)/1000000</x:f>
-        <x:v>11.88</x:v>
+        <x:f>M5*Assumptions!$B$20*(Assumptions!$B$27*Assumptions!$B$39+Assumptions!$B$28*Assumptions!$B$40)/1000000</x:f>
+        <x:v>32.4</x:v>
       </x:c>
       <x:c r="N10" s="26" t="n">
-        <x:f>N5*Assumptions!$B$20*(Assumptions!$B$27*Assumptions!$B$38+Assumptions!$B$28*Assumptions!$B$39)/1000000</x:f>
-        <x:v>19.8</x:v>
+        <x:f>N5*Assumptions!$B$20*(Assumptions!$B$27*Assumptions!$B$39+Assumptions!$B$28*Assumptions!$B$40)/1000000</x:f>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="O10" s="26" t="n">
-        <x:f>O5*Assumptions!$B$20*(Assumptions!$B$27*Assumptions!$B$38+Assumptions!$B$28*Assumptions!$B$39)/1000000</x:f>
-        <x:v>19.8</x:v>
+        <x:f>O5*Assumptions!$B$20*(Assumptions!$B$27*Assumptions!$B$39+Assumptions!$B$28*Assumptions!$B$40)/1000000</x:f>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="P10" s="26" t="n">
-        <x:f>P5*Assumptions!$B$20*(Assumptions!$B$27*Assumptions!$B$38+Assumptions!$B$28*Assumptions!$B$39)/1000000</x:f>
-        <x:v>19.8</x:v>
+        <x:f>P5*Assumptions!$B$20*(Assumptions!$B$27*Assumptions!$B$39+Assumptions!$B$28*Assumptions!$B$40)/1000000</x:f>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="Q10" s="26" t="n">
-        <x:f>Q5*Assumptions!$B$20*(Assumptions!$B$27*Assumptions!$B$38+Assumptions!$B$28*Assumptions!$B$39)/1000000</x:f>
-        <x:v>19.8</x:v>
+        <x:f>Q5*Assumptions!$B$20*(Assumptions!$B$27*Assumptions!$B$39+Assumptions!$B$28*Assumptions!$B$40)/1000000</x:f>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="R10" s="26" t="n">
-        <x:f>R5*Assumptions!$B$20*(Assumptions!$B$27*Assumptions!$B$38+Assumptions!$B$28*Assumptions!$B$39)/1000000</x:f>
-        <x:v>19.8</x:v>
+        <x:f>R5*Assumptions!$B$20*(Assumptions!$B$27*Assumptions!$B$39+Assumptions!$B$28*Assumptions!$B$40)/1000000</x:f>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="S10" s="26" t="n">
-        <x:f>S5*Assumptions!$B$20*(Assumptions!$B$27*Assumptions!$B$38+Assumptions!$B$28*Assumptions!$B$39)/1000000</x:f>
-        <x:v>19.8</x:v>
+        <x:f>S5*Assumptions!$B$20*(Assumptions!$B$27*Assumptions!$B$39+Assumptions!$B$28*Assumptions!$B$40)/1000000</x:f>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="T10" s="26" t="n">
-        <x:f>T5*Assumptions!$B$20*(Assumptions!$B$27*Assumptions!$B$38+Assumptions!$B$28*Assumptions!$B$39)/1000000</x:f>
-        <x:v>19.8</x:v>
+        <x:f>T5*Assumptions!$B$20*(Assumptions!$B$27*Assumptions!$B$39+Assumptions!$B$28*Assumptions!$B$40)/1000000</x:f>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="U10" s="26" t="n">
-        <x:f>U5*Assumptions!$B$20*(Assumptions!$B$27*Assumptions!$B$38+Assumptions!$B$28*Assumptions!$B$39)/1000000</x:f>
-        <x:v>19.8</x:v>
+        <x:f>U5*Assumptions!$B$20*(Assumptions!$B$27*Assumptions!$B$39+Assumptions!$B$28*Assumptions!$B$40)/1000000</x:f>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="V10" s="26" t="n">
-        <x:f>V5*Assumptions!$B$20*(Assumptions!$B$27*Assumptions!$B$38+Assumptions!$B$28*Assumptions!$B$39)/1000000</x:f>
-        <x:v>19.8</x:v>
+        <x:f>V5*Assumptions!$B$20*(Assumptions!$B$27*Assumptions!$B$39+Assumptions!$B$28*Assumptions!$B$40)/1000000</x:f>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="W10" s="26" t="n">
-        <x:f>W5*Assumptions!$B$20*(Assumptions!$B$27*Assumptions!$B$38+Assumptions!$B$28*Assumptions!$B$39)/1000000</x:f>
-        <x:v>19.8</x:v>
+        <x:f>W5*Assumptions!$B$20*(Assumptions!$B$27*Assumptions!$B$39+Assumptions!$B$28*Assumptions!$B$40)/1000000</x:f>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="X10" s="26" t="n">
-        <x:f>X5*Assumptions!$B$20*(Assumptions!$B$27*Assumptions!$B$38+Assumptions!$B$28*Assumptions!$B$39)/1000000</x:f>
-        <x:v>19.8</x:v>
+        <x:f>X5*Assumptions!$B$20*(Assumptions!$B$27*Assumptions!$B$39+Assumptions!$B$28*Assumptions!$B$40)/1000000</x:f>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="Y10" s="26" t="n">
-        <x:f>Y5*Assumptions!$B$20*(Assumptions!$B$27*Assumptions!$B$38+Assumptions!$B$28*Assumptions!$B$39)/1000000</x:f>
-        <x:v>19.8</x:v>
+        <x:f>Y5*Assumptions!$B$20*(Assumptions!$B$27*Assumptions!$B$39+Assumptions!$B$28*Assumptions!$B$40)/1000000</x:f>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="Z10" s="26" t="n">
-        <x:f>Z5*Assumptions!$B$20*(Assumptions!$B$27*Assumptions!$B$38+Assumptions!$B$28*Assumptions!$B$39)/1000000</x:f>
-        <x:v>19.8</x:v>
+        <x:f>Z5*Assumptions!$B$20*(Assumptions!$B$27*Assumptions!$B$39+Assumptions!$B$28*Assumptions!$B$40)/1000000</x:f>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AA10" s="26" t="n">
-        <x:f>AA5*Assumptions!$B$20*(Assumptions!$B$27*Assumptions!$B$38+Assumptions!$B$28*Assumptions!$B$39)/1000000</x:f>
-        <x:v>19.8</x:v>
+        <x:f>AA5*Assumptions!$B$20*(Assumptions!$B$27*Assumptions!$B$39+Assumptions!$B$28*Assumptions!$B$40)/1000000</x:f>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AB10" s="26" t="n">
-        <x:f>AB5*Assumptions!$B$20*(Assumptions!$B$27*Assumptions!$B$38+Assumptions!$B$28*Assumptions!$B$39)/1000000</x:f>
-        <x:v>19.8</x:v>
+        <x:f>AB5*Assumptions!$B$20*(Assumptions!$B$27*Assumptions!$B$39+Assumptions!$B$28*Assumptions!$B$40)/1000000</x:f>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AC10" s="26" t="n">
-        <x:f>AC5*Assumptions!$B$20*(Assumptions!$B$27*Assumptions!$B$38+Assumptions!$B$28*Assumptions!$B$39)/1000000</x:f>
-        <x:v>19.8</x:v>
+        <x:f>AC5*Assumptions!$B$20*(Assumptions!$B$27*Assumptions!$B$39+Assumptions!$B$28*Assumptions!$B$40)/1000000</x:f>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AD10" s="26" t="n">
-        <x:f>AD5*Assumptions!$B$20*(Assumptions!$B$27*Assumptions!$B$38+Assumptions!$B$28*Assumptions!$B$39)/1000000</x:f>
-        <x:v>19.8</x:v>
+        <x:f>AD5*Assumptions!$B$20*(Assumptions!$B$27*Assumptions!$B$39+Assumptions!$B$28*Assumptions!$B$40)/1000000</x:f>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AE10" s="26" t="n">
-        <x:f>AE5*Assumptions!$B$20*(Assumptions!$B$27*Assumptions!$B$38+Assumptions!$B$28*Assumptions!$B$39)/1000000</x:f>
-        <x:v>19.8</x:v>
+        <x:f>AE5*Assumptions!$B$20*(Assumptions!$B$27*Assumptions!$B$39+Assumptions!$B$28*Assumptions!$B$40)/1000000</x:f>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AF10" s="26" t="n">
-        <x:f>AF5*Assumptions!$B$20*(Assumptions!$B$27*Assumptions!$B$38+Assumptions!$B$28*Assumptions!$B$39)/1000000</x:f>
-        <x:v>19.8</x:v>
+        <x:f>AF5*Assumptions!$B$20*(Assumptions!$B$27*Assumptions!$B$39+Assumptions!$B$28*Assumptions!$B$40)/1000000</x:f>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AG10" s="26" t="n">
-        <x:f>AG5*Assumptions!$B$20*(Assumptions!$B$27*Assumptions!$B$38+Assumptions!$B$28*Assumptions!$B$39)/1000000</x:f>
-        <x:v>19.8</x:v>
+        <x:f>AG5*Assumptions!$B$20*(Assumptions!$B$27*Assumptions!$B$39+Assumptions!$B$28*Assumptions!$B$40)/1000000</x:f>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AH10" s="26" t="n">
-        <x:f>AH5*Assumptions!$B$20*(Assumptions!$B$27*Assumptions!$B$38+Assumptions!$B$28*Assumptions!$B$39)/1000000</x:f>
-        <x:v>19.8</x:v>
+        <x:f>AH5*Assumptions!$B$20*(Assumptions!$B$27*Assumptions!$B$39+Assumptions!$B$28*Assumptions!$B$40)/1000000</x:f>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AI10" s="26" t="n">
-        <x:f>AI5*Assumptions!$B$20*(Assumptions!$B$27*Assumptions!$B$38+Assumptions!$B$28*Assumptions!$B$39)/1000000</x:f>
-        <x:v>19.8</x:v>
+        <x:f>AI5*Assumptions!$B$20*(Assumptions!$B$27*Assumptions!$B$39+Assumptions!$B$28*Assumptions!$B$40)/1000000</x:f>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AJ10" s="26" t="n">
-        <x:f>AJ5*Assumptions!$B$20*(Assumptions!$B$27*Assumptions!$B$38+Assumptions!$B$28*Assumptions!$B$39)/1000000</x:f>
-        <x:v>19.8</x:v>
+        <x:f>AJ5*Assumptions!$B$20*(Assumptions!$B$27*Assumptions!$B$39+Assumptions!$B$28*Assumptions!$B$40)/1000000</x:f>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AK10" s="26" t="n">
-        <x:f>AK5*Assumptions!$B$20*(Assumptions!$B$27*Assumptions!$B$38+Assumptions!$B$28*Assumptions!$B$39)/1000000</x:f>
-        <x:v>19.8</x:v>
+        <x:f>AK5*Assumptions!$B$20*(Assumptions!$B$27*Assumptions!$B$39+Assumptions!$B$28*Assumptions!$B$40)/1000000</x:f>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Path generation LLM, batch (USD)</x:t>
+          <x:t xml:space="preserve">Path generation LLM, off-peak (USD)</x:t>
         </x:is>
       </x:c>
       <x:c r="B11" s="26" t="n">
-        <x:f>B5*Assumptions!$B$21/12*(Assumptions!$B$29*Assumptions!$B$33+Assumptions!$B$30*Assumptions!$B$34)/1000000*(1-Assumptions!$B$40)</x:f>
+        <x:f>B5*Assumptions!$B$21/12*(Assumptions!$B$29*Assumptions!$B$33+Assumptions!$B$30*Assumptions!$B$34)/1000000*(1-Assumptions!$B$41)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C11" s="26" t="n">
-        <x:f>C5*Assumptions!$B$21/12*(Assumptions!$B$29*Assumptions!$B$33+Assumptions!$B$30*Assumptions!$B$34)/1000000*(1-Assumptions!$B$40)</x:f>
+        <x:f>C5*Assumptions!$B$21/12*(Assumptions!$B$29*Assumptions!$B$33+Assumptions!$B$30*Assumptions!$B$34)/1000000*(1-Assumptions!$B$41)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D11" s="26" t="n">
-        <x:f>D5*Assumptions!$B$21/12*(Assumptions!$B$29*Assumptions!$B$33+Assumptions!$B$30*Assumptions!$B$34)/1000000*(1-Assumptions!$B$40)</x:f>
+        <x:f>D5*Assumptions!$B$21/12*(Assumptions!$B$29*Assumptions!$B$33+Assumptions!$B$30*Assumptions!$B$34)/1000000*(1-Assumptions!$B$41)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="E11" s="26" t="n">
-        <x:f>E5*Assumptions!$B$21/12*(Assumptions!$B$29*Assumptions!$B$33+Assumptions!$B$30*Assumptions!$B$34)/1000000*(1-Assumptions!$B$40)</x:f>
-        <x:v>37</x:v>
+        <x:f>E5*Assumptions!$B$21/12*(Assumptions!$B$29*Assumptions!$B$33+Assumptions!$B$30*Assumptions!$B$34)/1000000*(1-Assumptions!$B$41)</x:f>
+        <x:v>4.8</x:v>
       </x:c>
       <x:c r="F11" s="26" t="n">
-        <x:f>F5*Assumptions!$B$21/12*(Assumptions!$B$29*Assumptions!$B$33+Assumptions!$B$30*Assumptions!$B$34)/1000000*(1-Assumptions!$B$40)</x:f>
-        <x:v>37</x:v>
+        <x:f>F5*Assumptions!$B$21/12*(Assumptions!$B$29*Assumptions!$B$33+Assumptions!$B$30*Assumptions!$B$34)/1000000*(1-Assumptions!$B$41)</x:f>
+        <x:v>4.8</x:v>
       </x:c>
       <x:c r="G11" s="26" t="n">
-        <x:f>G5*Assumptions!$B$21/12*(Assumptions!$B$29*Assumptions!$B$33+Assumptions!$B$30*Assumptions!$B$34)/1000000*(1-Assumptions!$B$40)</x:f>
-        <x:v>37</x:v>
+        <x:f>G5*Assumptions!$B$21/12*(Assumptions!$B$29*Assumptions!$B$33+Assumptions!$B$30*Assumptions!$B$34)/1000000*(1-Assumptions!$B$41)</x:f>
+        <x:v>4.8</x:v>
       </x:c>
       <x:c r="H11" s="26" t="n">
-        <x:f>H5*Assumptions!$B$21/12*(Assumptions!$B$29*Assumptions!$B$33+Assumptions!$B$30*Assumptions!$B$34)/1000000*(1-Assumptions!$B$40)</x:f>
-        <x:v>83.25</x:v>
+        <x:f>H5*Assumptions!$B$21/12*(Assumptions!$B$29*Assumptions!$B$33+Assumptions!$B$30*Assumptions!$B$34)/1000000*(1-Assumptions!$B$41)</x:f>
+        <x:v>10.8</x:v>
       </x:c>
       <x:c r="I11" s="26" t="n">
-        <x:f>I5*Assumptions!$B$21/12*(Assumptions!$B$29*Assumptions!$B$33+Assumptions!$B$30*Assumptions!$B$34)/1000000*(1-Assumptions!$B$40)</x:f>
-        <x:v>83.25</x:v>
+        <x:f>I5*Assumptions!$B$21/12*(Assumptions!$B$29*Assumptions!$B$33+Assumptions!$B$30*Assumptions!$B$34)/1000000*(1-Assumptions!$B$41)</x:f>
+        <x:v>10.8</x:v>
       </x:c>
       <x:c r="J11" s="26" t="n">
-        <x:f>J5*Assumptions!$B$21/12*(Assumptions!$B$29*Assumptions!$B$33+Assumptions!$B$30*Assumptions!$B$34)/1000000*(1-Assumptions!$B$40)</x:f>
-        <x:v>83.25</x:v>
+        <x:f>J5*Assumptions!$B$21/12*(Assumptions!$B$29*Assumptions!$B$33+Assumptions!$B$30*Assumptions!$B$34)/1000000*(1-Assumptions!$B$41)</x:f>
+        <x:v>10.8</x:v>
       </x:c>
       <x:c r="K11" s="26" t="n">
-        <x:f>K5*Assumptions!$B$21/12*(Assumptions!$B$29*Assumptions!$B$33+Assumptions!$B$30*Assumptions!$B$34)/1000000*(1-Assumptions!$B$40)</x:f>
-        <x:v>83.25</x:v>
+        <x:f>K5*Assumptions!$B$21/12*(Assumptions!$B$29*Assumptions!$B$33+Assumptions!$B$30*Assumptions!$B$34)/1000000*(1-Assumptions!$B$41)</x:f>
+        <x:v>10.8</x:v>
       </x:c>
       <x:c r="L11" s="26" t="n">
-        <x:f>L5*Assumptions!$B$21/12*(Assumptions!$B$29*Assumptions!$B$33+Assumptions!$B$30*Assumptions!$B$34)/1000000*(1-Assumptions!$B$40)</x:f>
-        <x:v>83.25</x:v>
+        <x:f>L5*Assumptions!$B$21/12*(Assumptions!$B$29*Assumptions!$B$33+Assumptions!$B$30*Assumptions!$B$34)/1000000*(1-Assumptions!$B$41)</x:f>
+        <x:v>10.8</x:v>
       </x:c>
       <x:c r="M11" s="26" t="n">
-        <x:f>M5*Assumptions!$B$21/12*(Assumptions!$B$29*Assumptions!$B$33+Assumptions!$B$30*Assumptions!$B$34)/1000000*(1-Assumptions!$B$40)</x:f>
-        <x:v>83.25</x:v>
+        <x:f>M5*Assumptions!$B$21/12*(Assumptions!$B$29*Assumptions!$B$33+Assumptions!$B$30*Assumptions!$B$34)/1000000*(1-Assumptions!$B$41)</x:f>
+        <x:v>10.8</x:v>
       </x:c>
       <x:c r="N11" s="26" t="n">
-        <x:f>N5*Assumptions!$B$21/12*(Assumptions!$B$29*Assumptions!$B$33+Assumptions!$B$30*Assumptions!$B$34)/1000000*(1-Assumptions!$B$40)</x:f>
-        <x:v>138.75</x:v>
+        <x:f>N5*Assumptions!$B$21/12*(Assumptions!$B$29*Assumptions!$B$33+Assumptions!$B$30*Assumptions!$B$34)/1000000*(1-Assumptions!$B$41)</x:f>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="O11" s="26" t="n">
-        <x:f>O5*Assumptions!$B$21/12*(Assumptions!$B$29*Assumptions!$B$33+Assumptions!$B$30*Assumptions!$B$34)/1000000*(1-Assumptions!$B$40)</x:f>
-        <x:v>138.75</x:v>
+        <x:f>O5*Assumptions!$B$21/12*(Assumptions!$B$29*Assumptions!$B$33+Assumptions!$B$30*Assumptions!$B$34)/1000000*(1-Assumptions!$B$41)</x:f>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="P11" s="26" t="n">
-        <x:f>P5*Assumptions!$B$21/12*(Assumptions!$B$29*Assumptions!$B$33+Assumptions!$B$30*Assumptions!$B$34)/1000000*(1-Assumptions!$B$40)</x:f>
-        <x:v>138.75</x:v>
+        <x:f>P5*Assumptions!$B$21/12*(Assumptions!$B$29*Assumptions!$B$33+Assumptions!$B$30*Assumptions!$B$34)/1000000*(1-Assumptions!$B$41)</x:f>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="Q11" s="26" t="n">
-        <x:f>Q5*Assumptions!$B$21/12*(Assumptions!$B$29*Assumptions!$B$33+Assumptions!$B$30*Assumptions!$B$34)/1000000*(1-Assumptions!$B$40)</x:f>
-        <x:v>138.75</x:v>
+        <x:f>Q5*Assumptions!$B$21/12*(Assumptions!$B$29*Assumptions!$B$33+Assumptions!$B$30*Assumptions!$B$34)/1000000*(1-Assumptions!$B$41)</x:f>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="R11" s="26" t="n">
-        <x:f>R5*Assumptions!$B$21/12*(Assumptions!$B$29*Assumptions!$B$33+Assumptions!$B$30*Assumptions!$B$34)/1000000*(1-Assumptions!$B$40)</x:f>
-        <x:v>138.75</x:v>
+        <x:f>R5*Assumptions!$B$21/12*(Assumptions!$B$29*Assumptions!$B$33+Assumptions!$B$30*Assumptions!$B$34)/1000000*(1-Assumptions!$B$41)</x:f>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="S11" s="26" t="n">
-        <x:f>S5*Assumptions!$B$21/12*(Assumptions!$B$29*Assumptions!$B$33+Assumptions!$B$30*Assumptions!$B$34)/1000000*(1-Assumptions!$B$40)</x:f>
-        <x:v>138.75</x:v>
+        <x:f>S5*Assumptions!$B$21/12*(Assumptions!$B$29*Assumptions!$B$33+Assumptions!$B$30*Assumptions!$B$34)/1000000*(1-Assumptions!$B$41)</x:f>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="T11" s="26" t="n">
-        <x:f>T5*Assumptions!$B$21/12*(Assumptions!$B$29*Assumptions!$B$33+Assumptions!$B$30*Assumptions!$B$34)/1000000*(1-Assumptions!$B$40)</x:f>
-        <x:v>138.75</x:v>
+        <x:f>T5*Assumptions!$B$21/12*(Assumptions!$B$29*Assumptions!$B$33+Assumptions!$B$30*Assumptions!$B$34)/1000000*(1-Assumptions!$B$41)</x:f>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="U11" s="26" t="n">
-        <x:f>U5*Assumptions!$B$21/12*(Assumptions!$B$29*Assumptions!$B$33+Assumptions!$B$30*Assumptions!$B$34)/1000000*(1-Assumptions!$B$40)</x:f>
-        <x:v>138.75</x:v>
+        <x:f>U5*Assumptions!$B$21/12*(Assumptions!$B$29*Assumptions!$B$33+Assumptions!$B$30*Assumptions!$B$34)/1000000*(1-Assumptions!$B$41)</x:f>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="V11" s="26" t="n">
-        <x:f>V5*Assumptions!$B$21/12*(Assumptions!$B$29*Assumptions!$B$33+Assumptions!$B$30*Assumptions!$B$34)/1000000*(1-Assumptions!$B$40)</x:f>
-        <x:v>138.75</x:v>
+        <x:f>V5*Assumptions!$B$21/12*(Assumptions!$B$29*Assumptions!$B$33+Assumptions!$B$30*Assumptions!$B$34)/1000000*(1-Assumptions!$B$41)</x:f>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="W11" s="26" t="n">
-        <x:f>W5*Assumptions!$B$21/12*(Assumptions!$B$29*Assumptions!$B$33+Assumptions!$B$30*Assumptions!$B$34)/1000000*(1-Assumptions!$B$40)</x:f>
-        <x:v>138.75</x:v>
+        <x:f>W5*Assumptions!$B$21/12*(Assumptions!$B$29*Assumptions!$B$33+Assumptions!$B$30*Assumptions!$B$34)/1000000*(1-Assumptions!$B$41)</x:f>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="X11" s="26" t="n">
-        <x:f>X5*Assumptions!$B$21/12*(Assumptions!$B$29*Assumptions!$B$33+Assumptions!$B$30*Assumptions!$B$34)/1000000*(1-Assumptions!$B$40)</x:f>
-        <x:v>138.75</x:v>
+        <x:f>X5*Assumptions!$B$21/12*(Assumptions!$B$29*Assumptions!$B$33+Assumptions!$B$30*Assumptions!$B$34)/1000000*(1-Assumptions!$B$41)</x:f>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="Y11" s="26" t="n">
-        <x:f>Y5*Assumptions!$B$21/12*(Assumptions!$B$29*Assumptions!$B$33+Assumptions!$B$30*Assumptions!$B$34)/1000000*(1-Assumptions!$B$40)</x:f>
-        <x:v>138.75</x:v>
+        <x:f>Y5*Assumptions!$B$21/12*(Assumptions!$B$29*Assumptions!$B$33+Assumptions!$B$30*Assumptions!$B$34)/1000000*(1-Assumptions!$B$41)</x:f>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="Z11" s="26" t="n">
-        <x:f>Z5*Assumptions!$B$21/12*(Assumptions!$B$29*Assumptions!$B$33+Assumptions!$B$30*Assumptions!$B$34)/1000000*(1-Assumptions!$B$40)</x:f>
-        <x:v>138.75</x:v>
+        <x:f>Z5*Assumptions!$B$21/12*(Assumptions!$B$29*Assumptions!$B$33+Assumptions!$B$30*Assumptions!$B$34)/1000000*(1-Assumptions!$B$41)</x:f>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="AA11" s="26" t="n">
-        <x:f>AA5*Assumptions!$B$21/12*(Assumptions!$B$29*Assumptions!$B$33+Assumptions!$B$30*Assumptions!$B$34)/1000000*(1-Assumptions!$B$40)</x:f>
-        <x:v>138.75</x:v>
+        <x:f>AA5*Assumptions!$B$21/12*(Assumptions!$B$29*Assumptions!$B$33+Assumptions!$B$30*Assumptions!$B$34)/1000000*(1-Assumptions!$B$41)</x:f>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="AB11" s="26" t="n">
-        <x:f>AB5*Assumptions!$B$21/12*(Assumptions!$B$29*Assumptions!$B$33+Assumptions!$B$30*Assumptions!$B$34)/1000000*(1-Assumptions!$B$40)</x:f>
-        <x:v>138.75</x:v>
+        <x:f>AB5*Assumptions!$B$21/12*(Assumptions!$B$29*Assumptions!$B$33+Assumptions!$B$30*Assumptions!$B$34)/1000000*(1-Assumptions!$B$41)</x:f>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="AC11" s="26" t="n">
-        <x:f>AC5*Assumptions!$B$21/12*(Assumptions!$B$29*Assumptions!$B$33+Assumptions!$B$30*Assumptions!$B$34)/1000000*(1-Assumptions!$B$40)</x:f>
-        <x:v>138.75</x:v>
+        <x:f>AC5*Assumptions!$B$21/12*(Assumptions!$B$29*Assumptions!$B$33+Assumptions!$B$30*Assumptions!$B$34)/1000000*(1-Assumptions!$B$41)</x:f>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="AD11" s="26" t="n">
-        <x:f>AD5*Assumptions!$B$21/12*(Assumptions!$B$29*Assumptions!$B$33+Assumptions!$B$30*Assumptions!$B$34)/1000000*(1-Assumptions!$B$40)</x:f>
-        <x:v>138.75</x:v>
+        <x:f>AD5*Assumptions!$B$21/12*(Assumptions!$B$29*Assumptions!$B$33+Assumptions!$B$30*Assumptions!$B$34)/1000000*(1-Assumptions!$B$41)</x:f>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="AE11" s="26" t="n">
-        <x:f>AE5*Assumptions!$B$21/12*(Assumptions!$B$29*Assumptions!$B$33+Assumptions!$B$30*Assumptions!$B$34)/1000000*(1-Assumptions!$B$40)</x:f>
-        <x:v>138.75</x:v>
+        <x:f>AE5*Assumptions!$B$21/12*(Assumptions!$B$29*Assumptions!$B$33+Assumptions!$B$30*Assumptions!$B$34)/1000000*(1-Assumptions!$B$41)</x:f>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="AF11" s="26" t="n">
-        <x:f>AF5*Assumptions!$B$21/12*(Assumptions!$B$29*Assumptions!$B$33+Assumptions!$B$30*Assumptions!$B$34)/1000000*(1-Assumptions!$B$40)</x:f>
-        <x:v>138.75</x:v>
+        <x:f>AF5*Assumptions!$B$21/12*(Assumptions!$B$29*Assumptions!$B$33+Assumptions!$B$30*Assumptions!$B$34)/1000000*(1-Assumptions!$B$41)</x:f>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="AG11" s="26" t="n">
-        <x:f>AG5*Assumptions!$B$21/12*(Assumptions!$B$29*Assumptions!$B$33+Assumptions!$B$30*Assumptions!$B$34)/1000000*(1-Assumptions!$B$40)</x:f>
-        <x:v>138.75</x:v>
+        <x:f>AG5*Assumptions!$B$21/12*(Assumptions!$B$29*Assumptions!$B$33+Assumptions!$B$30*Assumptions!$B$34)/1000000*(1-Assumptions!$B$41)</x:f>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="AH11" s="26" t="n">
-        <x:f>AH5*Assumptions!$B$21/12*(Assumptions!$B$29*Assumptions!$B$33+Assumptions!$B$30*Assumptions!$B$34)/1000000*(1-Assumptions!$B$40)</x:f>
-        <x:v>138.75</x:v>
+        <x:f>AH5*Assumptions!$B$21/12*(Assumptions!$B$29*Assumptions!$B$33+Assumptions!$B$30*Assumptions!$B$34)/1000000*(1-Assumptions!$B$41)</x:f>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="AI11" s="26" t="n">
-        <x:f>AI5*Assumptions!$B$21/12*(Assumptions!$B$29*Assumptions!$B$33+Assumptions!$B$30*Assumptions!$B$34)/1000000*(1-Assumptions!$B$40)</x:f>
-        <x:v>138.75</x:v>
+        <x:f>AI5*Assumptions!$B$21/12*(Assumptions!$B$29*Assumptions!$B$33+Assumptions!$B$30*Assumptions!$B$34)/1000000*(1-Assumptions!$B$41)</x:f>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="AJ11" s="26" t="n">
-        <x:f>AJ5*Assumptions!$B$21/12*(Assumptions!$B$29*Assumptions!$B$33+Assumptions!$B$30*Assumptions!$B$34)/1000000*(1-Assumptions!$B$40)</x:f>
-        <x:v>138.75</x:v>
+        <x:f>AJ5*Assumptions!$B$21/12*(Assumptions!$B$29*Assumptions!$B$33+Assumptions!$B$30*Assumptions!$B$34)/1000000*(1-Assumptions!$B$41)</x:f>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="AK11" s="26" t="n">
-        <x:f>AK5*Assumptions!$B$21/12*(Assumptions!$B$29*Assumptions!$B$33+Assumptions!$B$30*Assumptions!$B$34)/1000000*(1-Assumptions!$B$40)</x:f>
-        <x:v>138.75</x:v>
+        <x:f>AK5*Assumptions!$B$21/12*(Assumptions!$B$29*Assumptions!$B$33+Assumptions!$B$30*Assumptions!$B$34)/1000000*(1-Assumptions!$B$41)</x:f>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -4106,148 +4126,148 @@
         </x:is>
       </x:c>
       <x:c r="B13" s="20" t="n">
-        <x:f>SUM(B8:B12)*(1+Assumptions!$B$41)*Assumptions!$B$6</x:f>
+        <x:f>SUM(B8:B12)*(1+Assumptions!$B$42)*Assumptions!$B$6</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C13" s="20" t="n">
-        <x:f>SUM(C8:C12)*(1+Assumptions!$B$41)*Assumptions!$B$6</x:f>
+        <x:f>SUM(C8:C12)*(1+Assumptions!$B$42)*Assumptions!$B$6</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D13" s="20" t="n">
-        <x:f>SUM(D8:D12)*(1+Assumptions!$B$41)*Assumptions!$B$6</x:f>
+        <x:f>SUM(D8:D12)*(1+Assumptions!$B$42)*Assumptions!$B$6</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="E13" s="20" t="n">
-        <x:f>SUM(E8:E12)*(1+Assumptions!$B$41)*Assumptions!$B$6</x:f>
-        <x:v>38371.9648</x:v>
+        <x:f>SUM(E8:E12)*(1+Assumptions!$B$42)*Assumptions!$B$6</x:f>
+        <x:v>12156.386112</x:v>
       </x:c>
       <x:c r="F13" s="20" t="n">
-        <x:f>SUM(F8:F12)*(1+Assumptions!$B$41)*Assumptions!$B$6</x:f>
-        <x:v>38371.9648</x:v>
+        <x:f>SUM(F8:F12)*(1+Assumptions!$B$42)*Assumptions!$B$6</x:f>
+        <x:v>12156.386112</x:v>
       </x:c>
       <x:c r="G13" s="20" t="n">
-        <x:f>SUM(G8:G12)*(1+Assumptions!$B$41)*Assumptions!$B$6</x:f>
-        <x:v>38371.9648</x:v>
+        <x:f>SUM(G8:G12)*(1+Assumptions!$B$42)*Assumptions!$B$6</x:f>
+        <x:v>12156.386112</x:v>
       </x:c>
       <x:c r="H13" s="20" t="n">
-        <x:f>SUM(H8:H12)*(1+Assumptions!$B$41)*Assumptions!$B$6</x:f>
-        <x:v>78049.4208</x:v>
+        <x:f>SUM(H8:H12)*(1+Assumptions!$B$42)*Assumptions!$B$6</x:f>
+        <x:v>19064.368752</x:v>
       </x:c>
       <x:c r="I13" s="20" t="n">
-        <x:f>SUM(I8:I12)*(1+Assumptions!$B$41)*Assumptions!$B$6</x:f>
-        <x:v>78049.4208</x:v>
+        <x:f>SUM(I8:I12)*(1+Assumptions!$B$42)*Assumptions!$B$6</x:f>
+        <x:v>19064.368752</x:v>
       </x:c>
       <x:c r="J13" s="20" t="n">
-        <x:f>SUM(J8:J12)*(1+Assumptions!$B$41)*Assumptions!$B$6</x:f>
-        <x:v>78049.4208</x:v>
+        <x:f>SUM(J8:J12)*(1+Assumptions!$B$42)*Assumptions!$B$6</x:f>
+        <x:v>19064.368752</x:v>
       </x:c>
       <x:c r="K13" s="20" t="n">
-        <x:f>SUM(K8:K12)*(1+Assumptions!$B$41)*Assumptions!$B$6</x:f>
-        <x:v>78049.4208</x:v>
+        <x:f>SUM(K8:K12)*(1+Assumptions!$B$42)*Assumptions!$B$6</x:f>
+        <x:v>19064.368752</x:v>
       </x:c>
       <x:c r="L13" s="20" t="n">
-        <x:f>SUM(L8:L12)*(1+Assumptions!$B$41)*Assumptions!$B$6</x:f>
-        <x:v>78049.4208</x:v>
+        <x:f>SUM(L8:L12)*(1+Assumptions!$B$42)*Assumptions!$B$6</x:f>
+        <x:v>19064.368752</x:v>
       </x:c>
       <x:c r="M13" s="20" t="n">
-        <x:f>SUM(M8:M12)*(1+Assumptions!$B$41)*Assumptions!$B$6</x:f>
-        <x:v>78049.4208</x:v>
+        <x:f>SUM(M8:M12)*(1+Assumptions!$B$42)*Assumptions!$B$6</x:f>
+        <x:v>19064.368752</x:v>
       </x:c>
       <x:c r="N13" s="20" t="n">
-        <x:f>SUM(N8:N12)*(1+Assumptions!$B$41)*Assumptions!$B$6</x:f>
-        <x:v>125662.368</x:v>
+        <x:f>SUM(N8:N12)*(1+Assumptions!$B$42)*Assumptions!$B$6</x:f>
+        <x:v>27353.947920000002</x:v>
       </x:c>
       <x:c r="O13" s="20" t="n">
-        <x:f>SUM(O8:O12)*(1+Assumptions!$B$41)*Assumptions!$B$6</x:f>
-        <x:v>125662.368</x:v>
+        <x:f>SUM(O8:O12)*(1+Assumptions!$B$42)*Assumptions!$B$6</x:f>
+        <x:v>27353.947920000002</x:v>
       </x:c>
       <x:c r="P13" s="20" t="n">
-        <x:f>SUM(P8:P12)*(1+Assumptions!$B$41)*Assumptions!$B$6</x:f>
-        <x:v>125662.368</x:v>
+        <x:f>SUM(P8:P12)*(1+Assumptions!$B$42)*Assumptions!$B$6</x:f>
+        <x:v>27353.947920000002</x:v>
       </x:c>
       <x:c r="Q13" s="20" t="n">
-        <x:f>SUM(Q8:Q12)*(1+Assumptions!$B$41)*Assumptions!$B$6</x:f>
-        <x:v>125662.368</x:v>
+        <x:f>SUM(Q8:Q12)*(1+Assumptions!$B$42)*Assumptions!$B$6</x:f>
+        <x:v>27353.947920000002</x:v>
       </x:c>
       <x:c r="R13" s="20" t="n">
-        <x:f>SUM(R8:R12)*(1+Assumptions!$B$41)*Assumptions!$B$6</x:f>
-        <x:v>125662.368</x:v>
+        <x:f>SUM(R8:R12)*(1+Assumptions!$B$42)*Assumptions!$B$6</x:f>
+        <x:v>27353.947920000002</x:v>
       </x:c>
       <x:c r="S13" s="20" t="n">
-        <x:f>SUM(S8:S12)*(1+Assumptions!$B$41)*Assumptions!$B$6</x:f>
-        <x:v>125662.368</x:v>
+        <x:f>SUM(S8:S12)*(1+Assumptions!$B$42)*Assumptions!$B$6</x:f>
+        <x:v>27353.947920000002</x:v>
       </x:c>
       <x:c r="T13" s="20" t="n">
-        <x:f>SUM(T8:T12)*(1+Assumptions!$B$41)*Assumptions!$B$6</x:f>
-        <x:v>125662.368</x:v>
+        <x:f>SUM(T8:T12)*(1+Assumptions!$B$42)*Assumptions!$B$6</x:f>
+        <x:v>27353.947920000002</x:v>
       </x:c>
       <x:c r="U13" s="20" t="n">
-        <x:f>SUM(U8:U12)*(1+Assumptions!$B$41)*Assumptions!$B$6</x:f>
-        <x:v>125662.368</x:v>
+        <x:f>SUM(U8:U12)*(1+Assumptions!$B$42)*Assumptions!$B$6</x:f>
+        <x:v>27353.947920000002</x:v>
       </x:c>
       <x:c r="V13" s="20" t="n">
-        <x:f>SUM(V8:V12)*(1+Assumptions!$B$41)*Assumptions!$B$6</x:f>
-        <x:v>125662.368</x:v>
+        <x:f>SUM(V8:V12)*(1+Assumptions!$B$42)*Assumptions!$B$6</x:f>
+        <x:v>27353.947920000002</x:v>
       </x:c>
       <x:c r="W13" s="20" t="n">
-        <x:f>SUM(W8:W12)*(1+Assumptions!$B$41)*Assumptions!$B$6</x:f>
-        <x:v>125662.368</x:v>
+        <x:f>SUM(W8:W12)*(1+Assumptions!$B$42)*Assumptions!$B$6</x:f>
+        <x:v>27353.947920000002</x:v>
       </x:c>
       <x:c r="X13" s="20" t="n">
-        <x:f>SUM(X8:X12)*(1+Assumptions!$B$41)*Assumptions!$B$6</x:f>
-        <x:v>125662.368</x:v>
+        <x:f>SUM(X8:X12)*(1+Assumptions!$B$42)*Assumptions!$B$6</x:f>
+        <x:v>27353.947920000002</x:v>
       </x:c>
       <x:c r="Y13" s="20" t="n">
-        <x:f>SUM(Y8:Y12)*(1+Assumptions!$B$41)*Assumptions!$B$6</x:f>
-        <x:v>125662.368</x:v>
+        <x:f>SUM(Y8:Y12)*(1+Assumptions!$B$42)*Assumptions!$B$6</x:f>
+        <x:v>27353.947920000002</x:v>
       </x:c>
       <x:c r="Z13" s="20" t="n">
-        <x:f>SUM(Z8:Z12)*(1+Assumptions!$B$41)*Assumptions!$B$6</x:f>
-        <x:v>125662.368</x:v>
+        <x:f>SUM(Z8:Z12)*(1+Assumptions!$B$42)*Assumptions!$B$6</x:f>
+        <x:v>27353.947920000002</x:v>
       </x:c>
       <x:c r="AA13" s="20" t="n">
-        <x:f>SUM(AA8:AA12)*(1+Assumptions!$B$41)*Assumptions!$B$6</x:f>
-        <x:v>125662.368</x:v>
+        <x:f>SUM(AA8:AA12)*(1+Assumptions!$B$42)*Assumptions!$B$6</x:f>
+        <x:v>27353.947920000002</x:v>
       </x:c>
       <x:c r="AB13" s="20" t="n">
-        <x:f>SUM(AB8:AB12)*(1+Assumptions!$B$41)*Assumptions!$B$6</x:f>
-        <x:v>125662.368</x:v>
+        <x:f>SUM(AB8:AB12)*(1+Assumptions!$B$42)*Assumptions!$B$6</x:f>
+        <x:v>27353.947920000002</x:v>
       </x:c>
       <x:c r="AC13" s="20" t="n">
-        <x:f>SUM(AC8:AC12)*(1+Assumptions!$B$41)*Assumptions!$B$6</x:f>
-        <x:v>125662.368</x:v>
+        <x:f>SUM(AC8:AC12)*(1+Assumptions!$B$42)*Assumptions!$B$6</x:f>
+        <x:v>27353.947920000002</x:v>
       </x:c>
       <x:c r="AD13" s="20" t="n">
-        <x:f>SUM(AD8:AD12)*(1+Assumptions!$B$41)*Assumptions!$B$6</x:f>
-        <x:v>125662.368</x:v>
+        <x:f>SUM(AD8:AD12)*(1+Assumptions!$B$42)*Assumptions!$B$6</x:f>
+        <x:v>27353.947920000002</x:v>
       </x:c>
       <x:c r="AE13" s="20" t="n">
-        <x:f>SUM(AE8:AE12)*(1+Assumptions!$B$41)*Assumptions!$B$6</x:f>
-        <x:v>125662.368</x:v>
+        <x:f>SUM(AE8:AE12)*(1+Assumptions!$B$42)*Assumptions!$B$6</x:f>
+        <x:v>27353.947920000002</x:v>
       </x:c>
       <x:c r="AF13" s="20" t="n">
-        <x:f>SUM(AF8:AF12)*(1+Assumptions!$B$41)*Assumptions!$B$6</x:f>
-        <x:v>125662.368</x:v>
+        <x:f>SUM(AF8:AF12)*(1+Assumptions!$B$42)*Assumptions!$B$6</x:f>
+        <x:v>27353.947920000002</x:v>
       </x:c>
       <x:c r="AG13" s="20" t="n">
-        <x:f>SUM(AG8:AG12)*(1+Assumptions!$B$41)*Assumptions!$B$6</x:f>
-        <x:v>125662.368</x:v>
+        <x:f>SUM(AG8:AG12)*(1+Assumptions!$B$42)*Assumptions!$B$6</x:f>
+        <x:v>27353.947920000002</x:v>
       </x:c>
       <x:c r="AH13" s="20" t="n">
-        <x:f>SUM(AH8:AH12)*(1+Assumptions!$B$41)*Assumptions!$B$6</x:f>
-        <x:v>125662.368</x:v>
+        <x:f>SUM(AH8:AH12)*(1+Assumptions!$B$42)*Assumptions!$B$6</x:f>
+        <x:v>27353.947920000002</x:v>
       </x:c>
       <x:c r="AI13" s="20" t="n">
-        <x:f>SUM(AI8:AI12)*(1+Assumptions!$B$41)*Assumptions!$B$6</x:f>
-        <x:v>125662.368</x:v>
+        <x:f>SUM(AI8:AI12)*(1+Assumptions!$B$42)*Assumptions!$B$6</x:f>
+        <x:v>27353.947920000002</x:v>
       </x:c>
       <x:c r="AJ13" s="20" t="n">
-        <x:f>SUM(AJ8:AJ12)*(1+Assumptions!$B$41)*Assumptions!$B$6</x:f>
-        <x:v>125662.368</x:v>
+        <x:f>SUM(AJ8:AJ12)*(1+Assumptions!$B$42)*Assumptions!$B$6</x:f>
+        <x:v>27353.947920000002</x:v>
       </x:c>
       <x:c r="AK13" s="20" t="n">
-        <x:f>SUM(AK8:AK12)*(1+Assumptions!$B$41)*Assumptions!$B$6</x:f>
-        <x:v>125662.368</x:v>
+        <x:f>SUM(AK8:AK12)*(1+Assumptions!$B$42)*Assumptions!$B$6</x:f>
+        <x:v>27353.947920000002</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -4257,147 +4277,147 @@
         </x:is>
       </x:c>
       <x:c r="B14" s="20" t="n">
-        <x:f>IF(B5&gt;0,Assumptions!$B$43+Assumptions!$B$44*B5,0)</x:f>
+        <x:f>IF(B5&gt;0,Assumptions!$B$44+Assumptions!$B$45*B5,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C14" s="20" t="n">
-        <x:f>IF(C5&gt;0,Assumptions!$B$43+Assumptions!$B$44*C5,0)</x:f>
+        <x:f>IF(C5&gt;0,Assumptions!$B$44+Assumptions!$B$45*C5,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D14" s="20" t="n">
-        <x:f>IF(D5&gt;0,Assumptions!$B$43+Assumptions!$B$44*D5,0)</x:f>
+        <x:f>IF(D5&gt;0,Assumptions!$B$44+Assumptions!$B$45*D5,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="E14" s="20" t="n">
-        <x:f>IF(E5&gt;0,Assumptions!$B$43+Assumptions!$B$44*E5,0)</x:f>
+        <x:f>IF(E5&gt;0,Assumptions!$B$44+Assumptions!$B$45*E5,0)</x:f>
         <x:v>91600</x:v>
       </x:c>
       <x:c r="F14" s="20" t="n">
-        <x:f>IF(F5&gt;0,Assumptions!$B$43+Assumptions!$B$44*F5,0)</x:f>
+        <x:f>IF(F5&gt;0,Assumptions!$B$44+Assumptions!$B$45*F5,0)</x:f>
         <x:v>91600</x:v>
       </x:c>
       <x:c r="G14" s="20" t="n">
-        <x:f>IF(G5&gt;0,Assumptions!$B$43+Assumptions!$B$44*G5,0)</x:f>
+        <x:f>IF(G5&gt;0,Assumptions!$B$44+Assumptions!$B$45*G5,0)</x:f>
         <x:v>91600</x:v>
       </x:c>
       <x:c r="H14" s="20" t="n">
-        <x:f>IF(H5&gt;0,Assumptions!$B$43+Assumptions!$B$44*H5,0)</x:f>
+        <x:f>IF(H5&gt;0,Assumptions!$B$44+Assumptions!$B$45*H5,0)</x:f>
         <x:v>118600</x:v>
       </x:c>
       <x:c r="I14" s="20" t="n">
-        <x:f>IF(I5&gt;0,Assumptions!$B$43+Assumptions!$B$44*I5,0)</x:f>
+        <x:f>IF(I5&gt;0,Assumptions!$B$44+Assumptions!$B$45*I5,0)</x:f>
         <x:v>118600</x:v>
       </x:c>
       <x:c r="J14" s="20" t="n">
-        <x:f>IF(J5&gt;0,Assumptions!$B$43+Assumptions!$B$44*J5,0)</x:f>
+        <x:f>IF(J5&gt;0,Assumptions!$B$44+Assumptions!$B$45*J5,0)</x:f>
         <x:v>118600</x:v>
       </x:c>
       <x:c r="K14" s="20" t="n">
-        <x:f>IF(K5&gt;0,Assumptions!$B$43+Assumptions!$B$44*K5,0)</x:f>
+        <x:f>IF(K5&gt;0,Assumptions!$B$44+Assumptions!$B$45*K5,0)</x:f>
         <x:v>118600</x:v>
       </x:c>
       <x:c r="L14" s="20" t="n">
-        <x:f>IF(L5&gt;0,Assumptions!$B$43+Assumptions!$B$44*L5,0)</x:f>
+        <x:f>IF(L5&gt;0,Assumptions!$B$44+Assumptions!$B$45*L5,0)</x:f>
         <x:v>118600</x:v>
       </x:c>
       <x:c r="M14" s="20" t="n">
-        <x:f>IF(M5&gt;0,Assumptions!$B$43+Assumptions!$B$44*M5,0)</x:f>
+        <x:f>IF(M5&gt;0,Assumptions!$B$44+Assumptions!$B$45*M5,0)</x:f>
         <x:v>118600</x:v>
       </x:c>
       <x:c r="N14" s="20" t="n">
-        <x:f>IF(N5&gt;0,Assumptions!$B$43+Assumptions!$B$44*N5,0)</x:f>
+        <x:f>IF(N5&gt;0,Assumptions!$B$44+Assumptions!$B$45*N5,0)</x:f>
         <x:v>151000</x:v>
       </x:c>
       <x:c r="O14" s="20" t="n">
-        <x:f>IF(O5&gt;0,Assumptions!$B$43+Assumptions!$B$44*O5,0)</x:f>
+        <x:f>IF(O5&gt;0,Assumptions!$B$44+Assumptions!$B$45*O5,0)</x:f>
         <x:v>151000</x:v>
       </x:c>
       <x:c r="P14" s="20" t="n">
-        <x:f>IF(P5&gt;0,Assumptions!$B$43+Assumptions!$B$44*P5,0)</x:f>
+        <x:f>IF(P5&gt;0,Assumptions!$B$44+Assumptions!$B$45*P5,0)</x:f>
         <x:v>151000</x:v>
       </x:c>
       <x:c r="Q14" s="20" t="n">
-        <x:f>IF(Q5&gt;0,Assumptions!$B$43+Assumptions!$B$44*Q5,0)</x:f>
+        <x:f>IF(Q5&gt;0,Assumptions!$B$44+Assumptions!$B$45*Q5,0)</x:f>
         <x:v>151000</x:v>
       </x:c>
       <x:c r="R14" s="20" t="n">
-        <x:f>IF(R5&gt;0,Assumptions!$B$43+Assumptions!$B$44*R5,0)</x:f>
+        <x:f>IF(R5&gt;0,Assumptions!$B$44+Assumptions!$B$45*R5,0)</x:f>
         <x:v>151000</x:v>
       </x:c>
       <x:c r="S14" s="20" t="n">
-        <x:f>IF(S5&gt;0,Assumptions!$B$43+Assumptions!$B$44*S5,0)</x:f>
+        <x:f>IF(S5&gt;0,Assumptions!$B$44+Assumptions!$B$45*S5,0)</x:f>
         <x:v>151000</x:v>
       </x:c>
       <x:c r="T14" s="20" t="n">
-        <x:f>IF(T5&gt;0,Assumptions!$B$43+Assumptions!$B$44*T5,0)</x:f>
+        <x:f>IF(T5&gt;0,Assumptions!$B$44+Assumptions!$B$45*T5,0)</x:f>
         <x:v>151000</x:v>
       </x:c>
       <x:c r="U14" s="20" t="n">
-        <x:f>IF(U5&gt;0,Assumptions!$B$43+Assumptions!$B$44*U5,0)</x:f>
+        <x:f>IF(U5&gt;0,Assumptions!$B$44+Assumptions!$B$45*U5,0)</x:f>
         <x:v>151000</x:v>
       </x:c>
       <x:c r="V14" s="20" t="n">
-        <x:f>IF(V5&gt;0,Assumptions!$B$43+Assumptions!$B$44*V5,0)</x:f>
+        <x:f>IF(V5&gt;0,Assumptions!$B$44+Assumptions!$B$45*V5,0)</x:f>
         <x:v>151000</x:v>
       </x:c>
       <x:c r="W14" s="20" t="n">
-        <x:f>IF(W5&gt;0,Assumptions!$B$43+Assumptions!$B$44*W5,0)</x:f>
+        <x:f>IF(W5&gt;0,Assumptions!$B$44+Assumptions!$B$45*W5,0)</x:f>
         <x:v>151000</x:v>
       </x:c>
       <x:c r="X14" s="20" t="n">
-        <x:f>IF(X5&gt;0,Assumptions!$B$43+Assumptions!$B$44*X5,0)</x:f>
+        <x:f>IF(X5&gt;0,Assumptions!$B$44+Assumptions!$B$45*X5,0)</x:f>
         <x:v>151000</x:v>
       </x:c>
       <x:c r="Y14" s="20" t="n">
-        <x:f>IF(Y5&gt;0,Assumptions!$B$43+Assumptions!$B$44*Y5,0)</x:f>
+        <x:f>IF(Y5&gt;0,Assumptions!$B$44+Assumptions!$B$45*Y5,0)</x:f>
         <x:v>151000</x:v>
       </x:c>
       <x:c r="Z14" s="20" t="n">
-        <x:f>IF(Z5&gt;0,Assumptions!$B$43+Assumptions!$B$44*Z5,0)</x:f>
+        <x:f>IF(Z5&gt;0,Assumptions!$B$44+Assumptions!$B$45*Z5,0)</x:f>
         <x:v>151000</x:v>
       </x:c>
       <x:c r="AA14" s="20" t="n">
-        <x:f>IF(AA5&gt;0,Assumptions!$B$43+Assumptions!$B$44*AA5,0)</x:f>
+        <x:f>IF(AA5&gt;0,Assumptions!$B$44+Assumptions!$B$45*AA5,0)</x:f>
         <x:v>151000</x:v>
       </x:c>
       <x:c r="AB14" s="20" t="n">
-        <x:f>IF(AB5&gt;0,Assumptions!$B$43+Assumptions!$B$44*AB5,0)</x:f>
+        <x:f>IF(AB5&gt;0,Assumptions!$B$44+Assumptions!$B$45*AB5,0)</x:f>
         <x:v>151000</x:v>
       </x:c>
       <x:c r="AC14" s="20" t="n">
-        <x:f>IF(AC5&gt;0,Assumptions!$B$43+Assumptions!$B$44*AC5,0)</x:f>
+        <x:f>IF(AC5&gt;0,Assumptions!$B$44+Assumptions!$B$45*AC5,0)</x:f>
         <x:v>151000</x:v>
       </x:c>
       <x:c r="AD14" s="20" t="n">
-        <x:f>IF(AD5&gt;0,Assumptions!$B$43+Assumptions!$B$44*AD5,0)</x:f>
+        <x:f>IF(AD5&gt;0,Assumptions!$B$44+Assumptions!$B$45*AD5,0)</x:f>
         <x:v>151000</x:v>
       </x:c>
       <x:c r="AE14" s="20" t="n">
-        <x:f>IF(AE5&gt;0,Assumptions!$B$43+Assumptions!$B$44*AE5,0)</x:f>
+        <x:f>IF(AE5&gt;0,Assumptions!$B$44+Assumptions!$B$45*AE5,0)</x:f>
         <x:v>151000</x:v>
       </x:c>
       <x:c r="AF14" s="20" t="n">
-        <x:f>IF(AF5&gt;0,Assumptions!$B$43+Assumptions!$B$44*AF5,0)</x:f>
+        <x:f>IF(AF5&gt;0,Assumptions!$B$44+Assumptions!$B$45*AF5,0)</x:f>
         <x:v>151000</x:v>
       </x:c>
       <x:c r="AG14" s="20" t="n">
-        <x:f>IF(AG5&gt;0,Assumptions!$B$43+Assumptions!$B$44*AG5,0)</x:f>
+        <x:f>IF(AG5&gt;0,Assumptions!$B$44+Assumptions!$B$45*AG5,0)</x:f>
         <x:v>151000</x:v>
       </x:c>
       <x:c r="AH14" s="20" t="n">
-        <x:f>IF(AH5&gt;0,Assumptions!$B$43+Assumptions!$B$44*AH5,0)</x:f>
+        <x:f>IF(AH5&gt;0,Assumptions!$B$44+Assumptions!$B$45*AH5,0)</x:f>
         <x:v>151000</x:v>
       </x:c>
       <x:c r="AI14" s="20" t="n">
-        <x:f>IF(AI5&gt;0,Assumptions!$B$43+Assumptions!$B$44*AI5,0)</x:f>
+        <x:f>IF(AI5&gt;0,Assumptions!$B$44+Assumptions!$B$45*AI5,0)</x:f>
         <x:v>151000</x:v>
       </x:c>
       <x:c r="AJ14" s="20" t="n">
-        <x:f>IF(AJ5&gt;0,Assumptions!$B$43+Assumptions!$B$44*AJ5,0)</x:f>
+        <x:f>IF(AJ5&gt;0,Assumptions!$B$44+Assumptions!$B$45*AJ5,0)</x:f>
         <x:v>151000</x:v>
       </x:c>
       <x:c r="AK14" s="20" t="n">
-        <x:f>IF(AK5&gt;0,Assumptions!$B$43+Assumptions!$B$44*AK5,0)</x:f>
+        <x:f>IF(AK5&gt;0,Assumptions!$B$44+Assumptions!$B$45*AK5,0)</x:f>
         <x:v>151000</x:v>
       </x:c>
     </x:row>
@@ -4408,147 +4428,147 @@
         </x:is>
       </x:c>
       <x:c r="B15" s="20" t="n">
-        <x:f>IF(B5&gt;0,Assumptions!$B$45+MAX(0,B5*Assumptions!$B$20-Assumptions!$B$46)*Assumptions!$B$47,0)</x:f>
+        <x:f>IF(B5&gt;0,Assumptions!$B$46+MAX(0,B5*Assumptions!$B$20-Assumptions!$B$47)*Assumptions!$B$48,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C15" s="20" t="n">
-        <x:f>IF(C5&gt;0,Assumptions!$B$45+MAX(0,C5*Assumptions!$B$20-Assumptions!$B$46)*Assumptions!$B$47,0)</x:f>
+        <x:f>IF(C5&gt;0,Assumptions!$B$46+MAX(0,C5*Assumptions!$B$20-Assumptions!$B$47)*Assumptions!$B$48,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D15" s="20" t="n">
-        <x:f>IF(D5&gt;0,Assumptions!$B$45+MAX(0,D5*Assumptions!$B$20-Assumptions!$B$46)*Assumptions!$B$47,0)</x:f>
+        <x:f>IF(D5&gt;0,Assumptions!$B$46+MAX(0,D5*Assumptions!$B$20-Assumptions!$B$47)*Assumptions!$B$48,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="E15" s="20" t="n">
-        <x:f>IF(E5&gt;0,Assumptions!$B$45+MAX(0,E5*Assumptions!$B$20-Assumptions!$B$46)*Assumptions!$B$47,0)</x:f>
+        <x:f>IF(E5&gt;0,Assumptions!$B$46+MAX(0,E5*Assumptions!$B$20-Assumptions!$B$47)*Assumptions!$B$48,0)</x:f>
         <x:v>2560</x:v>
       </x:c>
       <x:c r="F15" s="20" t="n">
-        <x:f>IF(F5&gt;0,Assumptions!$B$45+MAX(0,F5*Assumptions!$B$20-Assumptions!$B$46)*Assumptions!$B$47,0)</x:f>
+        <x:f>IF(F5&gt;0,Assumptions!$B$46+MAX(0,F5*Assumptions!$B$20-Assumptions!$B$47)*Assumptions!$B$48,0)</x:f>
         <x:v>2560</x:v>
       </x:c>
       <x:c r="G15" s="20" t="n">
-        <x:f>IF(G5&gt;0,Assumptions!$B$45+MAX(0,G5*Assumptions!$B$20-Assumptions!$B$46)*Assumptions!$B$47,0)</x:f>
+        <x:f>IF(G5&gt;0,Assumptions!$B$46+MAX(0,G5*Assumptions!$B$20-Assumptions!$B$47)*Assumptions!$B$48,0)</x:f>
         <x:v>2560</x:v>
       </x:c>
       <x:c r="H15" s="20" t="n">
-        <x:f>IF(H5&gt;0,Assumptions!$B$45+MAX(0,H5*Assumptions!$B$20-Assumptions!$B$46)*Assumptions!$B$47,0)</x:f>
+        <x:f>IF(H5&gt;0,Assumptions!$B$46+MAX(0,H5*Assumptions!$B$20-Assumptions!$B$47)*Assumptions!$B$48,0)</x:f>
         <x:v>6160</x:v>
       </x:c>
       <x:c r="I15" s="20" t="n">
-        <x:f>IF(I5&gt;0,Assumptions!$B$45+MAX(0,I5*Assumptions!$B$20-Assumptions!$B$46)*Assumptions!$B$47,0)</x:f>
+        <x:f>IF(I5&gt;0,Assumptions!$B$46+MAX(0,I5*Assumptions!$B$20-Assumptions!$B$47)*Assumptions!$B$48,0)</x:f>
         <x:v>6160</x:v>
       </x:c>
       <x:c r="J15" s="20" t="n">
-        <x:f>IF(J5&gt;0,Assumptions!$B$45+MAX(0,J5*Assumptions!$B$20-Assumptions!$B$46)*Assumptions!$B$47,0)</x:f>
+        <x:f>IF(J5&gt;0,Assumptions!$B$46+MAX(0,J5*Assumptions!$B$20-Assumptions!$B$47)*Assumptions!$B$48,0)</x:f>
         <x:v>6160</x:v>
       </x:c>
       <x:c r="K15" s="20" t="n">
-        <x:f>IF(K5&gt;0,Assumptions!$B$45+MAX(0,K5*Assumptions!$B$20-Assumptions!$B$46)*Assumptions!$B$47,0)</x:f>
+        <x:f>IF(K5&gt;0,Assumptions!$B$46+MAX(0,K5*Assumptions!$B$20-Assumptions!$B$47)*Assumptions!$B$48,0)</x:f>
         <x:v>6160</x:v>
       </x:c>
       <x:c r="L15" s="20" t="n">
-        <x:f>IF(L5&gt;0,Assumptions!$B$45+MAX(0,L5*Assumptions!$B$20-Assumptions!$B$46)*Assumptions!$B$47,0)</x:f>
+        <x:f>IF(L5&gt;0,Assumptions!$B$46+MAX(0,L5*Assumptions!$B$20-Assumptions!$B$47)*Assumptions!$B$48,0)</x:f>
         <x:v>6160</x:v>
       </x:c>
       <x:c r="M15" s="20" t="n">
-        <x:f>IF(M5&gt;0,Assumptions!$B$45+MAX(0,M5*Assumptions!$B$20-Assumptions!$B$46)*Assumptions!$B$47,0)</x:f>
+        <x:f>IF(M5&gt;0,Assumptions!$B$46+MAX(0,M5*Assumptions!$B$20-Assumptions!$B$47)*Assumptions!$B$48,0)</x:f>
         <x:v>6160</x:v>
       </x:c>
       <x:c r="N15" s="20" t="n">
-        <x:f>IF(N5&gt;0,Assumptions!$B$45+MAX(0,N5*Assumptions!$B$20-Assumptions!$B$46)*Assumptions!$B$47,0)</x:f>
+        <x:f>IF(N5&gt;0,Assumptions!$B$46+MAX(0,N5*Assumptions!$B$20-Assumptions!$B$47)*Assumptions!$B$48,0)</x:f>
         <x:v>10480</x:v>
       </x:c>
       <x:c r="O15" s="20" t="n">
-        <x:f>IF(O5&gt;0,Assumptions!$B$45+MAX(0,O5*Assumptions!$B$20-Assumptions!$B$46)*Assumptions!$B$47,0)</x:f>
+        <x:f>IF(O5&gt;0,Assumptions!$B$46+MAX(0,O5*Assumptions!$B$20-Assumptions!$B$47)*Assumptions!$B$48,0)</x:f>
         <x:v>10480</x:v>
       </x:c>
       <x:c r="P15" s="20" t="n">
-        <x:f>IF(P5&gt;0,Assumptions!$B$45+MAX(0,P5*Assumptions!$B$20-Assumptions!$B$46)*Assumptions!$B$47,0)</x:f>
+        <x:f>IF(P5&gt;0,Assumptions!$B$46+MAX(0,P5*Assumptions!$B$20-Assumptions!$B$47)*Assumptions!$B$48,0)</x:f>
         <x:v>10480</x:v>
       </x:c>
       <x:c r="Q15" s="20" t="n">
-        <x:f>IF(Q5&gt;0,Assumptions!$B$45+MAX(0,Q5*Assumptions!$B$20-Assumptions!$B$46)*Assumptions!$B$47,0)</x:f>
+        <x:f>IF(Q5&gt;0,Assumptions!$B$46+MAX(0,Q5*Assumptions!$B$20-Assumptions!$B$47)*Assumptions!$B$48,0)</x:f>
         <x:v>10480</x:v>
       </x:c>
       <x:c r="R15" s="20" t="n">
-        <x:f>IF(R5&gt;0,Assumptions!$B$45+MAX(0,R5*Assumptions!$B$20-Assumptions!$B$46)*Assumptions!$B$47,0)</x:f>
+        <x:f>IF(R5&gt;0,Assumptions!$B$46+MAX(0,R5*Assumptions!$B$20-Assumptions!$B$47)*Assumptions!$B$48,0)</x:f>
         <x:v>10480</x:v>
       </x:c>
       <x:c r="S15" s="20" t="n">
-        <x:f>IF(S5&gt;0,Assumptions!$B$45+MAX(0,S5*Assumptions!$B$20-Assumptions!$B$46)*Assumptions!$B$47,0)</x:f>
+        <x:f>IF(S5&gt;0,Assumptions!$B$46+MAX(0,S5*Assumptions!$B$20-Assumptions!$B$47)*Assumptions!$B$48,0)</x:f>
         <x:v>10480</x:v>
       </x:c>
       <x:c r="T15" s="20" t="n">
-        <x:f>IF(T5&gt;0,Assumptions!$B$45+MAX(0,T5*Assumptions!$B$20-Assumptions!$B$46)*Assumptions!$B$47,0)</x:f>
+        <x:f>IF(T5&gt;0,Assumptions!$B$46+MAX(0,T5*Assumptions!$B$20-Assumptions!$B$47)*Assumptions!$B$48,0)</x:f>
         <x:v>10480</x:v>
       </x:c>
       <x:c r="U15" s="20" t="n">
-        <x:f>IF(U5&gt;0,Assumptions!$B$45+MAX(0,U5*Assumptions!$B$20-Assumptions!$B$46)*Assumptions!$B$47,0)</x:f>
+        <x:f>IF(U5&gt;0,Assumptions!$B$46+MAX(0,U5*Assumptions!$B$20-Assumptions!$B$47)*Assumptions!$B$48,0)</x:f>
         <x:v>10480</x:v>
       </x:c>
       <x:c r="V15" s="20" t="n">
-        <x:f>IF(V5&gt;0,Assumptions!$B$45+MAX(0,V5*Assumptions!$B$20-Assumptions!$B$46)*Assumptions!$B$47,0)</x:f>
+        <x:f>IF(V5&gt;0,Assumptions!$B$46+MAX(0,V5*Assumptions!$B$20-Assumptions!$B$47)*Assumptions!$B$48,0)</x:f>
         <x:v>10480</x:v>
       </x:c>
       <x:c r="W15" s="20" t="n">
-        <x:f>IF(W5&gt;0,Assumptions!$B$45+MAX(0,W5*Assumptions!$B$20-Assumptions!$B$46)*Assumptions!$B$47,0)</x:f>
+        <x:f>IF(W5&gt;0,Assumptions!$B$46+MAX(0,W5*Assumptions!$B$20-Assumptions!$B$47)*Assumptions!$B$48,0)</x:f>
         <x:v>10480</x:v>
       </x:c>
       <x:c r="X15" s="20" t="n">
-        <x:f>IF(X5&gt;0,Assumptions!$B$45+MAX(0,X5*Assumptions!$B$20-Assumptions!$B$46)*Assumptions!$B$47,0)</x:f>
+        <x:f>IF(X5&gt;0,Assumptions!$B$46+MAX(0,X5*Assumptions!$B$20-Assumptions!$B$47)*Assumptions!$B$48,0)</x:f>
         <x:v>10480</x:v>
       </x:c>
       <x:c r="Y15" s="20" t="n">
-        <x:f>IF(Y5&gt;0,Assumptions!$B$45+MAX(0,Y5*Assumptions!$B$20-Assumptions!$B$46)*Assumptions!$B$47,0)</x:f>
+        <x:f>IF(Y5&gt;0,Assumptions!$B$46+MAX(0,Y5*Assumptions!$B$20-Assumptions!$B$47)*Assumptions!$B$48,0)</x:f>
         <x:v>10480</x:v>
       </x:c>
       <x:c r="Z15" s="20" t="n">
-        <x:f>IF(Z5&gt;0,Assumptions!$B$45+MAX(0,Z5*Assumptions!$B$20-Assumptions!$B$46)*Assumptions!$B$47,0)</x:f>
+        <x:f>IF(Z5&gt;0,Assumptions!$B$46+MAX(0,Z5*Assumptions!$B$20-Assumptions!$B$47)*Assumptions!$B$48,0)</x:f>
         <x:v>10480</x:v>
       </x:c>
       <x:c r="AA15" s="20" t="n">
-        <x:f>IF(AA5&gt;0,Assumptions!$B$45+MAX(0,AA5*Assumptions!$B$20-Assumptions!$B$46)*Assumptions!$B$47,0)</x:f>
+        <x:f>IF(AA5&gt;0,Assumptions!$B$46+MAX(0,AA5*Assumptions!$B$20-Assumptions!$B$47)*Assumptions!$B$48,0)</x:f>
         <x:v>10480</x:v>
       </x:c>
       <x:c r="AB15" s="20" t="n">
-        <x:f>IF(AB5&gt;0,Assumptions!$B$45+MAX(0,AB5*Assumptions!$B$20-Assumptions!$B$46)*Assumptions!$B$47,0)</x:f>
+        <x:f>IF(AB5&gt;0,Assumptions!$B$46+MAX(0,AB5*Assumptions!$B$20-Assumptions!$B$47)*Assumptions!$B$48,0)</x:f>
         <x:v>10480</x:v>
       </x:c>
       <x:c r="AC15" s="20" t="n">
-        <x:f>IF(AC5&gt;0,Assumptions!$B$45+MAX(0,AC5*Assumptions!$B$20-Assumptions!$B$46)*Assumptions!$B$47,0)</x:f>
+        <x:f>IF(AC5&gt;0,Assumptions!$B$46+MAX(0,AC5*Assumptions!$B$20-Assumptions!$B$47)*Assumptions!$B$48,0)</x:f>
         <x:v>10480</x:v>
       </x:c>
       <x:c r="AD15" s="20" t="n">
-        <x:f>IF(AD5&gt;0,Assumptions!$B$45+MAX(0,AD5*Assumptions!$B$20-Assumptions!$B$46)*Assumptions!$B$47,0)</x:f>
+        <x:f>IF(AD5&gt;0,Assumptions!$B$46+MAX(0,AD5*Assumptions!$B$20-Assumptions!$B$47)*Assumptions!$B$48,0)</x:f>
         <x:v>10480</x:v>
       </x:c>
       <x:c r="AE15" s="20" t="n">
-        <x:f>IF(AE5&gt;0,Assumptions!$B$45+MAX(0,AE5*Assumptions!$B$20-Assumptions!$B$46)*Assumptions!$B$47,0)</x:f>
+        <x:f>IF(AE5&gt;0,Assumptions!$B$46+MAX(0,AE5*Assumptions!$B$20-Assumptions!$B$47)*Assumptions!$B$48,0)</x:f>
         <x:v>10480</x:v>
       </x:c>
       <x:c r="AF15" s="20" t="n">
-        <x:f>IF(AF5&gt;0,Assumptions!$B$45+MAX(0,AF5*Assumptions!$B$20-Assumptions!$B$46)*Assumptions!$B$47,0)</x:f>
+        <x:f>IF(AF5&gt;0,Assumptions!$B$46+MAX(0,AF5*Assumptions!$B$20-Assumptions!$B$47)*Assumptions!$B$48,0)</x:f>
         <x:v>10480</x:v>
       </x:c>
       <x:c r="AG15" s="20" t="n">
-        <x:f>IF(AG5&gt;0,Assumptions!$B$45+MAX(0,AG5*Assumptions!$B$20-Assumptions!$B$46)*Assumptions!$B$47,0)</x:f>
+        <x:f>IF(AG5&gt;0,Assumptions!$B$46+MAX(0,AG5*Assumptions!$B$20-Assumptions!$B$47)*Assumptions!$B$48,0)</x:f>
         <x:v>10480</x:v>
       </x:c>
       <x:c r="AH15" s="20" t="n">
-        <x:f>IF(AH5&gt;0,Assumptions!$B$45+MAX(0,AH5*Assumptions!$B$20-Assumptions!$B$46)*Assumptions!$B$47,0)</x:f>
+        <x:f>IF(AH5&gt;0,Assumptions!$B$46+MAX(0,AH5*Assumptions!$B$20-Assumptions!$B$47)*Assumptions!$B$48,0)</x:f>
         <x:v>10480</x:v>
       </x:c>
       <x:c r="AI15" s="20" t="n">
-        <x:f>IF(AI5&gt;0,Assumptions!$B$45+MAX(0,AI5*Assumptions!$B$20-Assumptions!$B$46)*Assumptions!$B$47,0)</x:f>
+        <x:f>IF(AI5&gt;0,Assumptions!$B$46+MAX(0,AI5*Assumptions!$B$20-Assumptions!$B$47)*Assumptions!$B$48,0)</x:f>
         <x:v>10480</x:v>
       </x:c>
       <x:c r="AJ15" s="20" t="n">
-        <x:f>IF(AJ5&gt;0,Assumptions!$B$45+MAX(0,AJ5*Assumptions!$B$20-Assumptions!$B$46)*Assumptions!$B$47,0)</x:f>
+        <x:f>IF(AJ5&gt;0,Assumptions!$B$46+MAX(0,AJ5*Assumptions!$B$20-Assumptions!$B$47)*Assumptions!$B$48,0)</x:f>
         <x:v>10480</x:v>
       </x:c>
       <x:c r="AK15" s="20" t="n">
-        <x:f>IF(AK5&gt;0,Assumptions!$B$45+MAX(0,AK5*Assumptions!$B$20-Assumptions!$B$46)*Assumptions!$B$47,0)</x:f>
+        <x:f>IF(AK5&gt;0,Assumptions!$B$46+MAX(0,AK5*Assumptions!$B$20-Assumptions!$B$47)*Assumptions!$B$48,0)</x:f>
         <x:v>10480</x:v>
       </x:c>
     </x:row>
@@ -4559,147 +4579,147 @@
         </x:is>
       </x:c>
       <x:c r="B16" s="20" t="n">
-        <x:f>B5*Assumptions!$B$48*Assumptions!$B$49*Assumptions!$B$50</x:f>
+        <x:f>B5*Assumptions!$B$49*Assumptions!$B$50*Assumptions!$B$51</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C16" s="20" t="n">
-        <x:f>C5*Assumptions!$B$48*Assumptions!$B$49*Assumptions!$B$50</x:f>
+        <x:f>C5*Assumptions!$B$49*Assumptions!$B$50*Assumptions!$B$51</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D16" s="20" t="n">
-        <x:f>D5*Assumptions!$B$48*Assumptions!$B$49*Assumptions!$B$50</x:f>
+        <x:f>D5*Assumptions!$B$49*Assumptions!$B$50*Assumptions!$B$51</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="E16" s="20" t="n">
-        <x:f>E5*Assumptions!$B$48*Assumptions!$B$49*Assumptions!$B$50</x:f>
+        <x:f>E5*Assumptions!$B$49*Assumptions!$B$50*Assumptions!$B$51</x:f>
         <x:v>360</x:v>
       </x:c>
       <x:c r="F16" s="20" t="n">
-        <x:f>F5*Assumptions!$B$48*Assumptions!$B$49*Assumptions!$B$50</x:f>
+        <x:f>F5*Assumptions!$B$49*Assumptions!$B$50*Assumptions!$B$51</x:f>
         <x:v>360</x:v>
       </x:c>
       <x:c r="G16" s="20" t="n">
-        <x:f>G5*Assumptions!$B$48*Assumptions!$B$49*Assumptions!$B$50</x:f>
+        <x:f>G5*Assumptions!$B$49*Assumptions!$B$50*Assumptions!$B$51</x:f>
         <x:v>360</x:v>
       </x:c>
       <x:c r="H16" s="20" t="n">
-        <x:f>H5*Assumptions!$B$48*Assumptions!$B$49*Assumptions!$B$50</x:f>
+        <x:f>H5*Assumptions!$B$49*Assumptions!$B$50*Assumptions!$B$51</x:f>
         <x:v>810</x:v>
       </x:c>
       <x:c r="I16" s="20" t="n">
-        <x:f>I5*Assumptions!$B$48*Assumptions!$B$49*Assumptions!$B$50</x:f>
+        <x:f>I5*Assumptions!$B$49*Assumptions!$B$50*Assumptions!$B$51</x:f>
         <x:v>810</x:v>
       </x:c>
       <x:c r="J16" s="20" t="n">
-        <x:f>J5*Assumptions!$B$48*Assumptions!$B$49*Assumptions!$B$50</x:f>
+        <x:f>J5*Assumptions!$B$49*Assumptions!$B$50*Assumptions!$B$51</x:f>
         <x:v>810</x:v>
       </x:c>
       <x:c r="K16" s="20" t="n">
-        <x:f>K5*Assumptions!$B$48*Assumptions!$B$49*Assumptions!$B$50</x:f>
+        <x:f>K5*Assumptions!$B$49*Assumptions!$B$50*Assumptions!$B$51</x:f>
         <x:v>810</x:v>
       </x:c>
       <x:c r="L16" s="20" t="n">
-        <x:f>L5*Assumptions!$B$48*Assumptions!$B$49*Assumptions!$B$50</x:f>
+        <x:f>L5*Assumptions!$B$49*Assumptions!$B$50*Assumptions!$B$51</x:f>
         <x:v>810</x:v>
       </x:c>
       <x:c r="M16" s="20" t="n">
-        <x:f>M5*Assumptions!$B$48*Assumptions!$B$49*Assumptions!$B$50</x:f>
+        <x:f>M5*Assumptions!$B$49*Assumptions!$B$50*Assumptions!$B$51</x:f>
         <x:v>810</x:v>
       </x:c>
       <x:c r="N16" s="20" t="n">
-        <x:f>N5*Assumptions!$B$48*Assumptions!$B$49*Assumptions!$B$50</x:f>
+        <x:f>N5*Assumptions!$B$49*Assumptions!$B$50*Assumptions!$B$51</x:f>
         <x:v>1350</x:v>
       </x:c>
       <x:c r="O16" s="20" t="n">
-        <x:f>O5*Assumptions!$B$48*Assumptions!$B$49*Assumptions!$B$50</x:f>
+        <x:f>O5*Assumptions!$B$49*Assumptions!$B$50*Assumptions!$B$51</x:f>
         <x:v>1350</x:v>
       </x:c>
       <x:c r="P16" s="20" t="n">
-        <x:f>P5*Assumptions!$B$48*Assumptions!$B$49*Assumptions!$B$50</x:f>
+        <x:f>P5*Assumptions!$B$49*Assumptions!$B$50*Assumptions!$B$51</x:f>
         <x:v>1350</x:v>
       </x:c>
       <x:c r="Q16" s="20" t="n">
-        <x:f>Q5*Assumptions!$B$48*Assumptions!$B$49*Assumptions!$B$50</x:f>
+        <x:f>Q5*Assumptions!$B$49*Assumptions!$B$50*Assumptions!$B$51</x:f>
         <x:v>1350</x:v>
       </x:c>
       <x:c r="R16" s="20" t="n">
-        <x:f>R5*Assumptions!$B$48*Assumptions!$B$49*Assumptions!$B$50</x:f>
+        <x:f>R5*Assumptions!$B$49*Assumptions!$B$50*Assumptions!$B$51</x:f>
         <x:v>1350</x:v>
       </x:c>
       <x:c r="S16" s="20" t="n">
-        <x:f>S5*Assumptions!$B$48*Assumptions!$B$49*Assumptions!$B$50</x:f>
+        <x:f>S5*Assumptions!$B$49*Assumptions!$B$50*Assumptions!$B$51</x:f>
         <x:v>1350</x:v>
       </x:c>
       <x:c r="T16" s="20" t="n">
-        <x:f>T5*Assumptions!$B$48*Assumptions!$B$49*Assumptions!$B$50</x:f>
+        <x:f>T5*Assumptions!$B$49*Assumptions!$B$50*Assumptions!$B$51</x:f>
         <x:v>1350</x:v>
       </x:c>
       <x:c r="U16" s="20" t="n">
-        <x:f>U5*Assumptions!$B$48*Assumptions!$B$49*Assumptions!$B$50</x:f>
+        <x:f>U5*Assumptions!$B$49*Assumptions!$B$50*Assumptions!$B$51</x:f>
         <x:v>1350</x:v>
       </x:c>
       <x:c r="V16" s="20" t="n">
-        <x:f>V5*Assumptions!$B$48*Assumptions!$B$49*Assumptions!$B$50</x:f>
+        <x:f>V5*Assumptions!$B$49*Assumptions!$B$50*Assumptions!$B$51</x:f>
         <x:v>1350</x:v>
       </x:c>
       <x:c r="W16" s="20" t="n">
-        <x:f>W5*Assumptions!$B$48*Assumptions!$B$49*Assumptions!$B$50</x:f>
+        <x:f>W5*Assumptions!$B$49*Assumptions!$B$50*Assumptions!$B$51</x:f>
         <x:v>1350</x:v>
       </x:c>
       <x:c r="X16" s="20" t="n">
-        <x:f>X5*Assumptions!$B$48*Assumptions!$B$49*Assumptions!$B$50</x:f>
+        <x:f>X5*Assumptions!$B$49*Assumptions!$B$50*Assumptions!$B$51</x:f>
         <x:v>1350</x:v>
       </x:c>
       <x:c r="Y16" s="20" t="n">
-        <x:f>Y5*Assumptions!$B$48*Assumptions!$B$49*Assumptions!$B$50</x:f>
+        <x:f>Y5*Assumptions!$B$49*Assumptions!$B$50*Assumptions!$B$51</x:f>
         <x:v>1350</x:v>
       </x:c>
       <x:c r="Z16" s="20" t="n">
-        <x:f>Z5*Assumptions!$B$48*Assumptions!$B$49*Assumptions!$B$50</x:f>
+        <x:f>Z5*Assumptions!$B$49*Assumptions!$B$50*Assumptions!$B$51</x:f>
         <x:v>1350</x:v>
       </x:c>
       <x:c r="AA16" s="20" t="n">
-        <x:f>AA5*Assumptions!$B$48*Assumptions!$B$49*Assumptions!$B$50</x:f>
+        <x:f>AA5*Assumptions!$B$49*Assumptions!$B$50*Assumptions!$B$51</x:f>
         <x:v>1350</x:v>
       </x:c>
       <x:c r="AB16" s="20" t="n">
-        <x:f>AB5*Assumptions!$B$48*Assumptions!$B$49*Assumptions!$B$50</x:f>
+        <x:f>AB5*Assumptions!$B$49*Assumptions!$B$50*Assumptions!$B$51</x:f>
         <x:v>1350</x:v>
       </x:c>
       <x:c r="AC16" s="20" t="n">
-        <x:f>AC5*Assumptions!$B$48*Assumptions!$B$49*Assumptions!$B$50</x:f>
+        <x:f>AC5*Assumptions!$B$49*Assumptions!$B$50*Assumptions!$B$51</x:f>
         <x:v>1350</x:v>
       </x:c>
       <x:c r="AD16" s="20" t="n">
-        <x:f>AD5*Assumptions!$B$48*Assumptions!$B$49*Assumptions!$B$50</x:f>
+        <x:f>AD5*Assumptions!$B$49*Assumptions!$B$50*Assumptions!$B$51</x:f>
         <x:v>1350</x:v>
       </x:c>
       <x:c r="AE16" s="20" t="n">
-        <x:f>AE5*Assumptions!$B$48*Assumptions!$B$49*Assumptions!$B$50</x:f>
+        <x:f>AE5*Assumptions!$B$49*Assumptions!$B$50*Assumptions!$B$51</x:f>
         <x:v>1350</x:v>
       </x:c>
       <x:c r="AF16" s="20" t="n">
-        <x:f>AF5*Assumptions!$B$48*Assumptions!$B$49*Assumptions!$B$50</x:f>
+        <x:f>AF5*Assumptions!$B$49*Assumptions!$B$50*Assumptions!$B$51</x:f>
         <x:v>1350</x:v>
       </x:c>
       <x:c r="AG16" s="20" t="n">
-        <x:f>AG5*Assumptions!$B$48*Assumptions!$B$49*Assumptions!$B$50</x:f>
+        <x:f>AG5*Assumptions!$B$49*Assumptions!$B$50*Assumptions!$B$51</x:f>
         <x:v>1350</x:v>
       </x:c>
       <x:c r="AH16" s="20" t="n">
-        <x:f>AH5*Assumptions!$B$48*Assumptions!$B$49*Assumptions!$B$50</x:f>
+        <x:f>AH5*Assumptions!$B$49*Assumptions!$B$50*Assumptions!$B$51</x:f>
         <x:v>1350</x:v>
       </x:c>
       <x:c r="AI16" s="20" t="n">
-        <x:f>AI5*Assumptions!$B$48*Assumptions!$B$49*Assumptions!$B$50</x:f>
+        <x:f>AI5*Assumptions!$B$49*Assumptions!$B$50*Assumptions!$B$51</x:f>
         <x:v>1350</x:v>
       </x:c>
       <x:c r="AJ16" s="20" t="n">
-        <x:f>AJ5*Assumptions!$B$48*Assumptions!$B$49*Assumptions!$B$50</x:f>
+        <x:f>AJ5*Assumptions!$B$49*Assumptions!$B$50*Assumptions!$B$51</x:f>
         <x:v>1350</x:v>
       </x:c>
       <x:c r="AK16" s="20" t="n">
-        <x:f>AK5*Assumptions!$B$48*Assumptions!$B$49*Assumptions!$B$50</x:f>
+        <x:f>AK5*Assumptions!$B$49*Assumptions!$B$50*Assumptions!$B$51</x:f>
         <x:v>1350</x:v>
       </x:c>
     </x:row>
@@ -4710,147 +4730,147 @@
         </x:is>
       </x:c>
       <x:c r="B17" s="20" t="n">
-        <x:f>IF(B5&gt;0,Assumptions!$B$51+Assumptions!$B$52*B5,0)</x:f>
+        <x:f>IF(B5&gt;0,Assumptions!$B$52+Assumptions!$B$53*B5,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C17" s="20" t="n">
-        <x:f>IF(C5&gt;0,Assumptions!$B$51+Assumptions!$B$52*C5,0)</x:f>
+        <x:f>IF(C5&gt;0,Assumptions!$B$52+Assumptions!$B$53*C5,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D17" s="20" t="n">
-        <x:f>IF(D5&gt;0,Assumptions!$B$51+Assumptions!$B$52*D5,0)</x:f>
+        <x:f>IF(D5&gt;0,Assumptions!$B$52+Assumptions!$B$53*D5,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="E17" s="20" t="n">
-        <x:f>IF(E5&gt;0,Assumptions!$B$51+Assumptions!$B$52*E5,0)</x:f>
+        <x:f>IF(E5&gt;0,Assumptions!$B$52+Assumptions!$B$53*E5,0)</x:f>
         <x:v>33000</x:v>
       </x:c>
       <x:c r="F17" s="20" t="n">
-        <x:f>IF(F5&gt;0,Assumptions!$B$51+Assumptions!$B$52*F5,0)</x:f>
+        <x:f>IF(F5&gt;0,Assumptions!$B$52+Assumptions!$B$53*F5,0)</x:f>
         <x:v>33000</x:v>
       </x:c>
       <x:c r="G17" s="20" t="n">
-        <x:f>IF(G5&gt;0,Assumptions!$B$51+Assumptions!$B$52*G5,0)</x:f>
+        <x:f>IF(G5&gt;0,Assumptions!$B$52+Assumptions!$B$53*G5,0)</x:f>
         <x:v>33000</x:v>
       </x:c>
       <x:c r="H17" s="20" t="n">
-        <x:f>IF(H5&gt;0,Assumptions!$B$51+Assumptions!$B$52*H5,0)</x:f>
+        <x:f>IF(H5&gt;0,Assumptions!$B$52+Assumptions!$B$53*H5,0)</x:f>
         <x:v>36750</x:v>
       </x:c>
       <x:c r="I17" s="20" t="n">
-        <x:f>IF(I5&gt;0,Assumptions!$B$51+Assumptions!$B$52*I5,0)</x:f>
+        <x:f>IF(I5&gt;0,Assumptions!$B$52+Assumptions!$B$53*I5,0)</x:f>
         <x:v>36750</x:v>
       </x:c>
       <x:c r="J17" s="20" t="n">
-        <x:f>IF(J5&gt;0,Assumptions!$B$51+Assumptions!$B$52*J5,0)</x:f>
+        <x:f>IF(J5&gt;0,Assumptions!$B$52+Assumptions!$B$53*J5,0)</x:f>
         <x:v>36750</x:v>
       </x:c>
       <x:c r="K17" s="20" t="n">
-        <x:f>IF(K5&gt;0,Assumptions!$B$51+Assumptions!$B$52*K5,0)</x:f>
+        <x:f>IF(K5&gt;0,Assumptions!$B$52+Assumptions!$B$53*K5,0)</x:f>
         <x:v>36750</x:v>
       </x:c>
       <x:c r="L17" s="20" t="n">
-        <x:f>IF(L5&gt;0,Assumptions!$B$51+Assumptions!$B$52*L5,0)</x:f>
+        <x:f>IF(L5&gt;0,Assumptions!$B$52+Assumptions!$B$53*L5,0)</x:f>
         <x:v>36750</x:v>
       </x:c>
       <x:c r="M17" s="20" t="n">
-        <x:f>IF(M5&gt;0,Assumptions!$B$51+Assumptions!$B$52*M5,0)</x:f>
+        <x:f>IF(M5&gt;0,Assumptions!$B$52+Assumptions!$B$53*M5,0)</x:f>
         <x:v>36750</x:v>
       </x:c>
       <x:c r="N17" s="20" t="n">
-        <x:f>IF(N5&gt;0,Assumptions!$B$51+Assumptions!$B$52*N5,0)</x:f>
+        <x:f>IF(N5&gt;0,Assumptions!$B$52+Assumptions!$B$53*N5,0)</x:f>
         <x:v>41250</x:v>
       </x:c>
       <x:c r="O17" s="20" t="n">
-        <x:f>IF(O5&gt;0,Assumptions!$B$51+Assumptions!$B$52*O5,0)</x:f>
+        <x:f>IF(O5&gt;0,Assumptions!$B$52+Assumptions!$B$53*O5,0)</x:f>
         <x:v>41250</x:v>
       </x:c>
       <x:c r="P17" s="20" t="n">
-        <x:f>IF(P5&gt;0,Assumptions!$B$51+Assumptions!$B$52*P5,0)</x:f>
+        <x:f>IF(P5&gt;0,Assumptions!$B$52+Assumptions!$B$53*P5,0)</x:f>
         <x:v>41250</x:v>
       </x:c>
       <x:c r="Q17" s="20" t="n">
-        <x:f>IF(Q5&gt;0,Assumptions!$B$51+Assumptions!$B$52*Q5,0)</x:f>
+        <x:f>IF(Q5&gt;0,Assumptions!$B$52+Assumptions!$B$53*Q5,0)</x:f>
         <x:v>41250</x:v>
       </x:c>
       <x:c r="R17" s="20" t="n">
-        <x:f>IF(R5&gt;0,Assumptions!$B$51+Assumptions!$B$52*R5,0)</x:f>
+        <x:f>IF(R5&gt;0,Assumptions!$B$52+Assumptions!$B$53*R5,0)</x:f>
         <x:v>41250</x:v>
       </x:c>
       <x:c r="S17" s="20" t="n">
-        <x:f>IF(S5&gt;0,Assumptions!$B$51+Assumptions!$B$52*S5,0)</x:f>
+        <x:f>IF(S5&gt;0,Assumptions!$B$52+Assumptions!$B$53*S5,0)</x:f>
         <x:v>41250</x:v>
       </x:c>
       <x:c r="T17" s="20" t="n">
-        <x:f>IF(T5&gt;0,Assumptions!$B$51+Assumptions!$B$52*T5,0)</x:f>
+        <x:f>IF(T5&gt;0,Assumptions!$B$52+Assumptions!$B$53*T5,0)</x:f>
         <x:v>41250</x:v>
       </x:c>
       <x:c r="U17" s="20" t="n">
-        <x:f>IF(U5&gt;0,Assumptions!$B$51+Assumptions!$B$52*U5,0)</x:f>
+        <x:f>IF(U5&gt;0,Assumptions!$B$52+Assumptions!$B$53*U5,0)</x:f>
         <x:v>41250</x:v>
       </x:c>
       <x:c r="V17" s="20" t="n">
-        <x:f>IF(V5&gt;0,Assumptions!$B$51+Assumptions!$B$52*V5,0)</x:f>
+        <x:f>IF(V5&gt;0,Assumptions!$B$52+Assumptions!$B$53*V5,0)</x:f>
         <x:v>41250</x:v>
       </x:c>
       <x:c r="W17" s="20" t="n">
-        <x:f>IF(W5&gt;0,Assumptions!$B$51+Assumptions!$B$52*W5,0)</x:f>
+        <x:f>IF(W5&gt;0,Assumptions!$B$52+Assumptions!$B$53*W5,0)</x:f>
         <x:v>41250</x:v>
       </x:c>
       <x:c r="X17" s="20" t="n">
-        <x:f>IF(X5&gt;0,Assumptions!$B$51+Assumptions!$B$52*X5,0)</x:f>
+        <x:f>IF(X5&gt;0,Assumptions!$B$52+Assumptions!$B$53*X5,0)</x:f>
         <x:v>41250</x:v>
       </x:c>
       <x:c r="Y17" s="20" t="n">
-        <x:f>IF(Y5&gt;0,Assumptions!$B$51+Assumptions!$B$52*Y5,0)</x:f>
+        <x:f>IF(Y5&gt;0,Assumptions!$B$52+Assumptions!$B$53*Y5,0)</x:f>
         <x:v>41250</x:v>
       </x:c>
       <x:c r="Z17" s="20" t="n">
-        <x:f>IF(Z5&gt;0,Assumptions!$B$51+Assumptions!$B$52*Z5,0)</x:f>
+        <x:f>IF(Z5&gt;0,Assumptions!$B$52+Assumptions!$B$53*Z5,0)</x:f>
         <x:v>41250</x:v>
       </x:c>
       <x:c r="AA17" s="20" t="n">
-        <x:f>IF(AA5&gt;0,Assumptions!$B$51+Assumptions!$B$52*AA5,0)</x:f>
+        <x:f>IF(AA5&gt;0,Assumptions!$B$52+Assumptions!$B$53*AA5,0)</x:f>
         <x:v>41250</x:v>
       </x:c>
       <x:c r="AB17" s="20" t="n">
-        <x:f>IF(AB5&gt;0,Assumptions!$B$51+Assumptions!$B$52*AB5,0)</x:f>
+        <x:f>IF(AB5&gt;0,Assumptions!$B$52+Assumptions!$B$53*AB5,0)</x:f>
         <x:v>41250</x:v>
       </x:c>
       <x:c r="AC17" s="20" t="n">
-        <x:f>IF(AC5&gt;0,Assumptions!$B$51+Assumptions!$B$52*AC5,0)</x:f>
+        <x:f>IF(AC5&gt;0,Assumptions!$B$52+Assumptions!$B$53*AC5,0)</x:f>
         <x:v>41250</x:v>
       </x:c>
       <x:c r="AD17" s="20" t="n">
-        <x:f>IF(AD5&gt;0,Assumptions!$B$51+Assumptions!$B$52*AD5,0)</x:f>
+        <x:f>IF(AD5&gt;0,Assumptions!$B$52+Assumptions!$B$53*AD5,0)</x:f>
         <x:v>41250</x:v>
       </x:c>
       <x:c r="AE17" s="20" t="n">
-        <x:f>IF(AE5&gt;0,Assumptions!$B$51+Assumptions!$B$52*AE5,0)</x:f>
+        <x:f>IF(AE5&gt;0,Assumptions!$B$52+Assumptions!$B$53*AE5,0)</x:f>
         <x:v>41250</x:v>
       </x:c>
       <x:c r="AF17" s="20" t="n">
-        <x:f>IF(AF5&gt;0,Assumptions!$B$51+Assumptions!$B$52*AF5,0)</x:f>
+        <x:f>IF(AF5&gt;0,Assumptions!$B$52+Assumptions!$B$53*AF5,0)</x:f>
         <x:v>41250</x:v>
       </x:c>
       <x:c r="AG17" s="20" t="n">
-        <x:f>IF(AG5&gt;0,Assumptions!$B$51+Assumptions!$B$52*AG5,0)</x:f>
+        <x:f>IF(AG5&gt;0,Assumptions!$B$52+Assumptions!$B$53*AG5,0)</x:f>
         <x:v>41250</x:v>
       </x:c>
       <x:c r="AH17" s="20" t="n">
-        <x:f>IF(AH5&gt;0,Assumptions!$B$51+Assumptions!$B$52*AH5,0)</x:f>
+        <x:f>IF(AH5&gt;0,Assumptions!$B$52+Assumptions!$B$53*AH5,0)</x:f>
         <x:v>41250</x:v>
       </x:c>
       <x:c r="AI17" s="20" t="n">
-        <x:f>IF(AI5&gt;0,Assumptions!$B$51+Assumptions!$B$52*AI5,0)</x:f>
+        <x:f>IF(AI5&gt;0,Assumptions!$B$52+Assumptions!$B$53*AI5,0)</x:f>
         <x:v>41250</x:v>
       </x:c>
       <x:c r="AJ17" s="20" t="n">
-        <x:f>IF(AJ5&gt;0,Assumptions!$B$51+Assumptions!$B$52*AJ5,0)</x:f>
+        <x:f>IF(AJ5&gt;0,Assumptions!$B$52+Assumptions!$B$53*AJ5,0)</x:f>
         <x:v>41250</x:v>
       </x:c>
       <x:c r="AK17" s="20" t="n">
-        <x:f>IF(AK5&gt;0,Assumptions!$B$51+Assumptions!$B$52*AK5,0)</x:f>
+        <x:f>IF(AK5&gt;0,Assumptions!$B$52+Assumptions!$B$53*AK5,0)</x:f>
         <x:v>41250</x:v>
       </x:c>
     </x:row>
@@ -4861,147 +4881,147 @@
         </x:is>
       </x:c>
       <x:c r="B18" s="20" t="n">
-        <x:f>IF(B5&gt;0,(Assumptions!$B$53+Assumptions!$B$54)/12,0)</x:f>
+        <x:f>IF(B5&gt;0,(Assumptions!$B$54+Assumptions!$B$55)/12,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C18" s="20" t="n">
-        <x:f>IF(C5&gt;0,(Assumptions!$B$53+Assumptions!$B$54)/12,0)</x:f>
+        <x:f>IF(C5&gt;0,(Assumptions!$B$54+Assumptions!$B$55)/12,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D18" s="20" t="n">
-        <x:f>IF(D5&gt;0,(Assumptions!$B$53+Assumptions!$B$54)/12,0)</x:f>
+        <x:f>IF(D5&gt;0,(Assumptions!$B$54+Assumptions!$B$55)/12,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="E18" s="20" t="n">
-        <x:f>IF(E5&gt;0,(Assumptions!$B$53+Assumptions!$B$54)/12,0)</x:f>
+        <x:f>IF(E5&gt;0,(Assumptions!$B$54+Assumptions!$B$55)/12,0)</x:f>
         <x:v>50000</x:v>
       </x:c>
       <x:c r="F18" s="20" t="n">
-        <x:f>IF(F5&gt;0,(Assumptions!$B$53+Assumptions!$B$54)/12,0)</x:f>
+        <x:f>IF(F5&gt;0,(Assumptions!$B$54+Assumptions!$B$55)/12,0)</x:f>
         <x:v>50000</x:v>
       </x:c>
       <x:c r="G18" s="20" t="n">
-        <x:f>IF(G5&gt;0,(Assumptions!$B$53+Assumptions!$B$54)/12,0)</x:f>
+        <x:f>IF(G5&gt;0,(Assumptions!$B$54+Assumptions!$B$55)/12,0)</x:f>
         <x:v>50000</x:v>
       </x:c>
       <x:c r="H18" s="20" t="n">
-        <x:f>IF(H5&gt;0,(Assumptions!$B$53+Assumptions!$B$54)/12,0)</x:f>
+        <x:f>IF(H5&gt;0,(Assumptions!$B$54+Assumptions!$B$55)/12,0)</x:f>
         <x:v>50000</x:v>
       </x:c>
       <x:c r="I18" s="20" t="n">
-        <x:f>IF(I5&gt;0,(Assumptions!$B$53+Assumptions!$B$54)/12,0)</x:f>
+        <x:f>IF(I5&gt;0,(Assumptions!$B$54+Assumptions!$B$55)/12,0)</x:f>
         <x:v>50000</x:v>
       </x:c>
       <x:c r="J18" s="20" t="n">
-        <x:f>IF(J5&gt;0,(Assumptions!$B$53+Assumptions!$B$54)/12,0)</x:f>
+        <x:f>IF(J5&gt;0,(Assumptions!$B$54+Assumptions!$B$55)/12,0)</x:f>
         <x:v>50000</x:v>
       </x:c>
       <x:c r="K18" s="20" t="n">
-        <x:f>IF(K5&gt;0,(Assumptions!$B$53+Assumptions!$B$54)/12,0)</x:f>
+        <x:f>IF(K5&gt;0,(Assumptions!$B$54+Assumptions!$B$55)/12,0)</x:f>
         <x:v>50000</x:v>
       </x:c>
       <x:c r="L18" s="20" t="n">
-        <x:f>IF(L5&gt;0,(Assumptions!$B$53+Assumptions!$B$54)/12,0)</x:f>
+        <x:f>IF(L5&gt;0,(Assumptions!$B$54+Assumptions!$B$55)/12,0)</x:f>
         <x:v>50000</x:v>
       </x:c>
       <x:c r="M18" s="20" t="n">
-        <x:f>IF(M5&gt;0,(Assumptions!$B$53+Assumptions!$B$54)/12,0)</x:f>
+        <x:f>IF(M5&gt;0,(Assumptions!$B$54+Assumptions!$B$55)/12,0)</x:f>
         <x:v>50000</x:v>
       </x:c>
       <x:c r="N18" s="20" t="n">
-        <x:f>IF(N5&gt;0,(Assumptions!$B$53+Assumptions!$B$54)/12,0)</x:f>
+        <x:f>IF(N5&gt;0,(Assumptions!$B$54+Assumptions!$B$55)/12,0)</x:f>
         <x:v>50000</x:v>
       </x:c>
       <x:c r="O18" s="20" t="n">
-        <x:f>IF(O5&gt;0,(Assumptions!$B$53+Assumptions!$B$54)/12,0)</x:f>
+        <x:f>IF(O5&gt;0,(Assumptions!$B$54+Assumptions!$B$55)/12,0)</x:f>
         <x:v>50000</x:v>
       </x:c>
       <x:c r="P18" s="20" t="n">
-        <x:f>IF(P5&gt;0,(Assumptions!$B$53+Assumptions!$B$54)/12,0)</x:f>
+        <x:f>IF(P5&gt;0,(Assumptions!$B$54+Assumptions!$B$55)/12,0)</x:f>
         <x:v>50000</x:v>
       </x:c>
       <x:c r="Q18" s="20" t="n">
-        <x:f>IF(Q5&gt;0,(Assumptions!$B$53+Assumptions!$B$54)/12,0)</x:f>
+        <x:f>IF(Q5&gt;0,(Assumptions!$B$54+Assumptions!$B$55)/12,0)</x:f>
         <x:v>50000</x:v>
       </x:c>
       <x:c r="R18" s="20" t="n">
-        <x:f>IF(R5&gt;0,(Assumptions!$B$53+Assumptions!$B$54)/12,0)</x:f>
+        <x:f>IF(R5&gt;0,(Assumptions!$B$54+Assumptions!$B$55)/12,0)</x:f>
         <x:v>50000</x:v>
       </x:c>
       <x:c r="S18" s="20" t="n">
-        <x:f>IF(S5&gt;0,(Assumptions!$B$53+Assumptions!$B$54)/12,0)</x:f>
+        <x:f>IF(S5&gt;0,(Assumptions!$B$54+Assumptions!$B$55)/12,0)</x:f>
         <x:v>50000</x:v>
       </x:c>
       <x:c r="T18" s="20" t="n">
-        <x:f>IF(T5&gt;0,(Assumptions!$B$53+Assumptions!$B$54)/12,0)</x:f>
+        <x:f>IF(T5&gt;0,(Assumptions!$B$54+Assumptions!$B$55)/12,0)</x:f>
         <x:v>50000</x:v>
       </x:c>
       <x:c r="U18" s="20" t="n">
-        <x:f>IF(U5&gt;0,(Assumptions!$B$53+Assumptions!$B$54)/12,0)</x:f>
+        <x:f>IF(U5&gt;0,(Assumptions!$B$54+Assumptions!$B$55)/12,0)</x:f>
         <x:v>50000</x:v>
       </x:c>
       <x:c r="V18" s="20" t="n">
-        <x:f>IF(V5&gt;0,(Assumptions!$B$53+Assumptions!$B$54)/12,0)</x:f>
+        <x:f>IF(V5&gt;0,(Assumptions!$B$54+Assumptions!$B$55)/12,0)</x:f>
         <x:v>50000</x:v>
       </x:c>
       <x:c r="W18" s="20" t="n">
-        <x:f>IF(W5&gt;0,(Assumptions!$B$53+Assumptions!$B$54)/12,0)</x:f>
+        <x:f>IF(W5&gt;0,(Assumptions!$B$54+Assumptions!$B$55)/12,0)</x:f>
         <x:v>50000</x:v>
       </x:c>
       <x:c r="X18" s="20" t="n">
-        <x:f>IF(X5&gt;0,(Assumptions!$B$53+Assumptions!$B$54)/12,0)</x:f>
+        <x:f>IF(X5&gt;0,(Assumptions!$B$54+Assumptions!$B$55)/12,0)</x:f>
         <x:v>50000</x:v>
       </x:c>
       <x:c r="Y18" s="20" t="n">
-        <x:f>IF(Y5&gt;0,(Assumptions!$B$53+Assumptions!$B$54)/12,0)</x:f>
+        <x:f>IF(Y5&gt;0,(Assumptions!$B$54+Assumptions!$B$55)/12,0)</x:f>
         <x:v>50000</x:v>
       </x:c>
       <x:c r="Z18" s="20" t="n">
-        <x:f>IF(Z5&gt;0,(Assumptions!$B$53+Assumptions!$B$54)/12,0)</x:f>
+        <x:f>IF(Z5&gt;0,(Assumptions!$B$54+Assumptions!$B$55)/12,0)</x:f>
         <x:v>50000</x:v>
       </x:c>
       <x:c r="AA18" s="20" t="n">
-        <x:f>IF(AA5&gt;0,(Assumptions!$B$53+Assumptions!$B$54)/12,0)</x:f>
+        <x:f>IF(AA5&gt;0,(Assumptions!$B$54+Assumptions!$B$55)/12,0)</x:f>
         <x:v>50000</x:v>
       </x:c>
       <x:c r="AB18" s="20" t="n">
-        <x:f>IF(AB5&gt;0,(Assumptions!$B$53+Assumptions!$B$54)/12,0)</x:f>
+        <x:f>IF(AB5&gt;0,(Assumptions!$B$54+Assumptions!$B$55)/12,0)</x:f>
         <x:v>50000</x:v>
       </x:c>
       <x:c r="AC18" s="20" t="n">
-        <x:f>IF(AC5&gt;0,(Assumptions!$B$53+Assumptions!$B$54)/12,0)</x:f>
+        <x:f>IF(AC5&gt;0,(Assumptions!$B$54+Assumptions!$B$55)/12,0)</x:f>
         <x:v>50000</x:v>
       </x:c>
       <x:c r="AD18" s="20" t="n">
-        <x:f>IF(AD5&gt;0,(Assumptions!$B$53+Assumptions!$B$54)/12,0)</x:f>
+        <x:f>IF(AD5&gt;0,(Assumptions!$B$54+Assumptions!$B$55)/12,0)</x:f>
         <x:v>50000</x:v>
       </x:c>
       <x:c r="AE18" s="20" t="n">
-        <x:f>IF(AE5&gt;0,(Assumptions!$B$53+Assumptions!$B$54)/12,0)</x:f>
+        <x:f>IF(AE5&gt;0,(Assumptions!$B$54+Assumptions!$B$55)/12,0)</x:f>
         <x:v>50000</x:v>
       </x:c>
       <x:c r="AF18" s="20" t="n">
-        <x:f>IF(AF5&gt;0,(Assumptions!$B$53+Assumptions!$B$54)/12,0)</x:f>
+        <x:f>IF(AF5&gt;0,(Assumptions!$B$54+Assumptions!$B$55)/12,0)</x:f>
         <x:v>50000</x:v>
       </x:c>
       <x:c r="AG18" s="20" t="n">
-        <x:f>IF(AG5&gt;0,(Assumptions!$B$53+Assumptions!$B$54)/12,0)</x:f>
+        <x:f>IF(AG5&gt;0,(Assumptions!$B$54+Assumptions!$B$55)/12,0)</x:f>
         <x:v>50000</x:v>
       </x:c>
       <x:c r="AH18" s="20" t="n">
-        <x:f>IF(AH5&gt;0,(Assumptions!$B$53+Assumptions!$B$54)/12,0)</x:f>
+        <x:f>IF(AH5&gt;0,(Assumptions!$B$54+Assumptions!$B$55)/12,0)</x:f>
         <x:v>50000</x:v>
       </x:c>
       <x:c r="AI18" s="20" t="n">
-        <x:f>IF(AI5&gt;0,(Assumptions!$B$53+Assumptions!$B$54)/12,0)</x:f>
+        <x:f>IF(AI5&gt;0,(Assumptions!$B$54+Assumptions!$B$55)/12,0)</x:f>
         <x:v>50000</x:v>
       </x:c>
       <x:c r="AJ18" s="20" t="n">
-        <x:f>IF(AJ5&gt;0,(Assumptions!$B$53+Assumptions!$B$54)/12,0)</x:f>
+        <x:f>IF(AJ5&gt;0,(Assumptions!$B$54+Assumptions!$B$55)/12,0)</x:f>
         <x:v>50000</x:v>
       </x:c>
       <x:c r="AK18" s="20" t="n">
-        <x:f>IF(AK5&gt;0,(Assumptions!$B$53+Assumptions!$B$54)/12,0)</x:f>
+        <x:f>IF(AK5&gt;0,(Assumptions!$B$54+Assumptions!$B$55)/12,0)</x:f>
         <x:v>50000</x:v>
       </x:c>
     </x:row>
@@ -5012,147 +5032,147 @@
         </x:is>
       </x:c>
       <x:c r="B19" s="20" t="n">
-        <x:f>IF(B5&gt;0,Assumptions!$B$56*Assumptions!$B$72+(Assumptions!$B$57+B5/Assumptions!$B$58)*Assumptions!$B$83+MAX(1,B5/Assumptions!$B$59)*Assumptions!$B$85,0)</x:f>
+        <x:f>IF(B5&gt;0,Assumptions!$B$57*Assumptions!$B$73+(Assumptions!$B$58+B5/Assumptions!$B$59)*Assumptions!$B$84+MAX(1,B5/Assumptions!$B$60)*Assumptions!$B$86,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C19" s="20" t="n">
-        <x:f>IF(C5&gt;0,Assumptions!$B$56*Assumptions!$B$72+(Assumptions!$B$57+C5/Assumptions!$B$58)*Assumptions!$B$83+MAX(1,C5/Assumptions!$B$59)*Assumptions!$B$85,0)</x:f>
+        <x:f>IF(C5&gt;0,Assumptions!$B$57*Assumptions!$B$73+(Assumptions!$B$58+C5/Assumptions!$B$59)*Assumptions!$B$84+MAX(1,C5/Assumptions!$B$60)*Assumptions!$B$86,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D19" s="20" t="n">
-        <x:f>IF(D5&gt;0,Assumptions!$B$56*Assumptions!$B$72+(Assumptions!$B$57+D5/Assumptions!$B$58)*Assumptions!$B$83+MAX(1,D5/Assumptions!$B$59)*Assumptions!$B$85,0)</x:f>
+        <x:f>IF(D5&gt;0,Assumptions!$B$57*Assumptions!$B$73+(Assumptions!$B$58+D5/Assumptions!$B$59)*Assumptions!$B$84+MAX(1,D5/Assumptions!$B$60)*Assumptions!$B$86,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="E19" s="20" t="n">
-        <x:f>IF(E5&gt;0,Assumptions!$B$56*Assumptions!$B$72+(Assumptions!$B$57+E5/Assumptions!$B$58)*Assumptions!$B$83+MAX(1,E5/Assumptions!$B$59)*Assumptions!$B$85,0)</x:f>
+        <x:f>IF(E5&gt;0,Assumptions!$B$57*Assumptions!$B$73+(Assumptions!$B$58+E5/Assumptions!$B$59)*Assumptions!$B$84+MAX(1,E5/Assumptions!$B$60)*Assumptions!$B$86,0)</x:f>
         <x:v>288000</x:v>
       </x:c>
       <x:c r="F19" s="20" t="n">
-        <x:f>IF(F5&gt;0,Assumptions!$B$56*Assumptions!$B$72+(Assumptions!$B$57+F5/Assumptions!$B$58)*Assumptions!$B$83+MAX(1,F5/Assumptions!$B$59)*Assumptions!$B$85,0)</x:f>
+        <x:f>IF(F5&gt;0,Assumptions!$B$57*Assumptions!$B$73+(Assumptions!$B$58+F5/Assumptions!$B$59)*Assumptions!$B$84+MAX(1,F5/Assumptions!$B$60)*Assumptions!$B$86,0)</x:f>
         <x:v>288000</x:v>
       </x:c>
       <x:c r="G19" s="20" t="n">
-        <x:f>IF(G5&gt;0,Assumptions!$B$56*Assumptions!$B$72+(Assumptions!$B$57+G5/Assumptions!$B$58)*Assumptions!$B$83+MAX(1,G5/Assumptions!$B$59)*Assumptions!$B$85,0)</x:f>
+        <x:f>IF(G5&gt;0,Assumptions!$B$57*Assumptions!$B$73+(Assumptions!$B$58+G5/Assumptions!$B$59)*Assumptions!$B$84+MAX(1,G5/Assumptions!$B$60)*Assumptions!$B$86,0)</x:f>
         <x:v>288000</x:v>
       </x:c>
       <x:c r="H19" s="20" t="n">
-        <x:f>IF(H5&gt;0,Assumptions!$B$56*Assumptions!$B$72+(Assumptions!$B$57+H5/Assumptions!$B$58)*Assumptions!$B$83+MAX(1,H5/Assumptions!$B$59)*Assumptions!$B$85,0)</x:f>
+        <x:f>IF(H5&gt;0,Assumptions!$B$57*Assumptions!$B$73+(Assumptions!$B$58+H5/Assumptions!$B$59)*Assumptions!$B$84+MAX(1,H5/Assumptions!$B$60)*Assumptions!$B$86,0)</x:f>
         <x:v>327800</x:v>
       </x:c>
       <x:c r="I19" s="20" t="n">
-        <x:f>IF(I5&gt;0,Assumptions!$B$56*Assumptions!$B$72+(Assumptions!$B$57+I5/Assumptions!$B$58)*Assumptions!$B$83+MAX(1,I5/Assumptions!$B$59)*Assumptions!$B$85,0)</x:f>
+        <x:f>IF(I5&gt;0,Assumptions!$B$57*Assumptions!$B$73+(Assumptions!$B$58+I5/Assumptions!$B$59)*Assumptions!$B$84+MAX(1,I5/Assumptions!$B$60)*Assumptions!$B$86,0)</x:f>
         <x:v>327800</x:v>
       </x:c>
       <x:c r="J19" s="20" t="n">
-        <x:f>IF(J5&gt;0,Assumptions!$B$56*Assumptions!$B$72+(Assumptions!$B$57+J5/Assumptions!$B$58)*Assumptions!$B$83+MAX(1,J5/Assumptions!$B$59)*Assumptions!$B$85,0)</x:f>
+        <x:f>IF(J5&gt;0,Assumptions!$B$57*Assumptions!$B$73+(Assumptions!$B$58+J5/Assumptions!$B$59)*Assumptions!$B$84+MAX(1,J5/Assumptions!$B$60)*Assumptions!$B$86,0)</x:f>
         <x:v>327800</x:v>
       </x:c>
       <x:c r="K19" s="20" t="n">
-        <x:f>IF(K5&gt;0,Assumptions!$B$56*Assumptions!$B$72+(Assumptions!$B$57+K5/Assumptions!$B$58)*Assumptions!$B$83+MAX(1,K5/Assumptions!$B$59)*Assumptions!$B$85,0)</x:f>
+        <x:f>IF(K5&gt;0,Assumptions!$B$57*Assumptions!$B$73+(Assumptions!$B$58+K5/Assumptions!$B$59)*Assumptions!$B$84+MAX(1,K5/Assumptions!$B$60)*Assumptions!$B$86,0)</x:f>
         <x:v>327800</x:v>
       </x:c>
       <x:c r="L19" s="20" t="n">
-        <x:f>IF(L5&gt;0,Assumptions!$B$56*Assumptions!$B$72+(Assumptions!$B$57+L5/Assumptions!$B$58)*Assumptions!$B$83+MAX(1,L5/Assumptions!$B$59)*Assumptions!$B$85,0)</x:f>
+        <x:f>IF(L5&gt;0,Assumptions!$B$57*Assumptions!$B$73+(Assumptions!$B$58+L5/Assumptions!$B$59)*Assumptions!$B$84+MAX(1,L5/Assumptions!$B$60)*Assumptions!$B$86,0)</x:f>
         <x:v>327800</x:v>
       </x:c>
       <x:c r="M19" s="20" t="n">
-        <x:f>IF(M5&gt;0,Assumptions!$B$56*Assumptions!$B$72+(Assumptions!$B$57+M5/Assumptions!$B$58)*Assumptions!$B$83+MAX(1,M5/Assumptions!$B$59)*Assumptions!$B$85,0)</x:f>
+        <x:f>IF(M5&gt;0,Assumptions!$B$57*Assumptions!$B$73+(Assumptions!$B$58+M5/Assumptions!$B$59)*Assumptions!$B$84+MAX(1,M5/Assumptions!$B$60)*Assumptions!$B$86,0)</x:f>
         <x:v>327800</x:v>
       </x:c>
       <x:c r="N19" s="20" t="n">
-        <x:f>IF(N5&gt;0,Assumptions!$B$56*Assumptions!$B$72+(Assumptions!$B$57+N5/Assumptions!$B$58)*Assumptions!$B$83+MAX(1,N5/Assumptions!$B$59)*Assumptions!$B$85,0)</x:f>
+        <x:f>IF(N5&gt;0,Assumptions!$B$57*Assumptions!$B$73+(Assumptions!$B$58+N5/Assumptions!$B$59)*Assumptions!$B$84+MAX(1,N5/Assumptions!$B$60)*Assumptions!$B$86,0)</x:f>
         <x:v>413000</x:v>
       </x:c>
       <x:c r="O19" s="20" t="n">
-        <x:f>IF(O5&gt;0,Assumptions!$B$56*Assumptions!$B$72+(Assumptions!$B$57+O5/Assumptions!$B$58)*Assumptions!$B$83+MAX(1,O5/Assumptions!$B$59)*Assumptions!$B$85,0)</x:f>
+        <x:f>IF(O5&gt;0,Assumptions!$B$57*Assumptions!$B$73+(Assumptions!$B$58+O5/Assumptions!$B$59)*Assumptions!$B$84+MAX(1,O5/Assumptions!$B$60)*Assumptions!$B$86,0)</x:f>
         <x:v>413000</x:v>
       </x:c>
       <x:c r="P19" s="20" t="n">
-        <x:f>IF(P5&gt;0,Assumptions!$B$56*Assumptions!$B$72+(Assumptions!$B$57+P5/Assumptions!$B$58)*Assumptions!$B$83+MAX(1,P5/Assumptions!$B$59)*Assumptions!$B$85,0)</x:f>
+        <x:f>IF(P5&gt;0,Assumptions!$B$57*Assumptions!$B$73+(Assumptions!$B$58+P5/Assumptions!$B$59)*Assumptions!$B$84+MAX(1,P5/Assumptions!$B$60)*Assumptions!$B$86,0)</x:f>
         <x:v>413000</x:v>
       </x:c>
       <x:c r="Q19" s="20" t="n">
-        <x:f>IF(Q5&gt;0,Assumptions!$B$56*Assumptions!$B$72+(Assumptions!$B$57+Q5/Assumptions!$B$58)*Assumptions!$B$83+MAX(1,Q5/Assumptions!$B$59)*Assumptions!$B$85,0)</x:f>
+        <x:f>IF(Q5&gt;0,Assumptions!$B$57*Assumptions!$B$73+(Assumptions!$B$58+Q5/Assumptions!$B$59)*Assumptions!$B$84+MAX(1,Q5/Assumptions!$B$60)*Assumptions!$B$86,0)</x:f>
         <x:v>413000</x:v>
       </x:c>
       <x:c r="R19" s="20" t="n">
-        <x:f>IF(R5&gt;0,Assumptions!$B$56*Assumptions!$B$72+(Assumptions!$B$57+R5/Assumptions!$B$58)*Assumptions!$B$83+MAX(1,R5/Assumptions!$B$59)*Assumptions!$B$85,0)</x:f>
+        <x:f>IF(R5&gt;0,Assumptions!$B$57*Assumptions!$B$73+(Assumptions!$B$58+R5/Assumptions!$B$59)*Assumptions!$B$84+MAX(1,R5/Assumptions!$B$60)*Assumptions!$B$86,0)</x:f>
         <x:v>413000</x:v>
       </x:c>
       <x:c r="S19" s="20" t="n">
-        <x:f>IF(S5&gt;0,Assumptions!$B$56*Assumptions!$B$72+(Assumptions!$B$57+S5/Assumptions!$B$58)*Assumptions!$B$83+MAX(1,S5/Assumptions!$B$59)*Assumptions!$B$85,0)</x:f>
+        <x:f>IF(S5&gt;0,Assumptions!$B$57*Assumptions!$B$73+(Assumptions!$B$58+S5/Assumptions!$B$59)*Assumptions!$B$84+MAX(1,S5/Assumptions!$B$60)*Assumptions!$B$86,0)</x:f>
         <x:v>413000</x:v>
       </x:c>
       <x:c r="T19" s="20" t="n">
-        <x:f>IF(T5&gt;0,Assumptions!$B$56*Assumptions!$B$72+(Assumptions!$B$57+T5/Assumptions!$B$58)*Assumptions!$B$83+MAX(1,T5/Assumptions!$B$59)*Assumptions!$B$85,0)</x:f>
+        <x:f>IF(T5&gt;0,Assumptions!$B$57*Assumptions!$B$73+(Assumptions!$B$58+T5/Assumptions!$B$59)*Assumptions!$B$84+MAX(1,T5/Assumptions!$B$60)*Assumptions!$B$86,0)</x:f>
         <x:v>413000</x:v>
       </x:c>
       <x:c r="U19" s="20" t="n">
-        <x:f>IF(U5&gt;0,Assumptions!$B$56*Assumptions!$B$72+(Assumptions!$B$57+U5/Assumptions!$B$58)*Assumptions!$B$83+MAX(1,U5/Assumptions!$B$59)*Assumptions!$B$85,0)</x:f>
+        <x:f>IF(U5&gt;0,Assumptions!$B$57*Assumptions!$B$73+(Assumptions!$B$58+U5/Assumptions!$B$59)*Assumptions!$B$84+MAX(1,U5/Assumptions!$B$60)*Assumptions!$B$86,0)</x:f>
         <x:v>413000</x:v>
       </x:c>
       <x:c r="V19" s="20" t="n">
-        <x:f>IF(V5&gt;0,Assumptions!$B$56*Assumptions!$B$72+(Assumptions!$B$57+V5/Assumptions!$B$58)*Assumptions!$B$83+MAX(1,V5/Assumptions!$B$59)*Assumptions!$B$85,0)</x:f>
+        <x:f>IF(V5&gt;0,Assumptions!$B$57*Assumptions!$B$73+(Assumptions!$B$58+V5/Assumptions!$B$59)*Assumptions!$B$84+MAX(1,V5/Assumptions!$B$60)*Assumptions!$B$86,0)</x:f>
         <x:v>413000</x:v>
       </x:c>
       <x:c r="W19" s="20" t="n">
-        <x:f>IF(W5&gt;0,Assumptions!$B$56*Assumptions!$B$72+(Assumptions!$B$57+W5/Assumptions!$B$58)*Assumptions!$B$83+MAX(1,W5/Assumptions!$B$59)*Assumptions!$B$85,0)</x:f>
+        <x:f>IF(W5&gt;0,Assumptions!$B$57*Assumptions!$B$73+(Assumptions!$B$58+W5/Assumptions!$B$59)*Assumptions!$B$84+MAX(1,W5/Assumptions!$B$60)*Assumptions!$B$86,0)</x:f>
         <x:v>413000</x:v>
       </x:c>
       <x:c r="X19" s="20" t="n">
-        <x:f>IF(X5&gt;0,Assumptions!$B$56*Assumptions!$B$72+(Assumptions!$B$57+X5/Assumptions!$B$58)*Assumptions!$B$83+MAX(1,X5/Assumptions!$B$59)*Assumptions!$B$85,0)</x:f>
+        <x:f>IF(X5&gt;0,Assumptions!$B$57*Assumptions!$B$73+(Assumptions!$B$58+X5/Assumptions!$B$59)*Assumptions!$B$84+MAX(1,X5/Assumptions!$B$60)*Assumptions!$B$86,0)</x:f>
         <x:v>413000</x:v>
       </x:c>
       <x:c r="Y19" s="20" t="n">
-        <x:f>IF(Y5&gt;0,Assumptions!$B$56*Assumptions!$B$72+(Assumptions!$B$57+Y5/Assumptions!$B$58)*Assumptions!$B$83+MAX(1,Y5/Assumptions!$B$59)*Assumptions!$B$85,0)</x:f>
+        <x:f>IF(Y5&gt;0,Assumptions!$B$57*Assumptions!$B$73+(Assumptions!$B$58+Y5/Assumptions!$B$59)*Assumptions!$B$84+MAX(1,Y5/Assumptions!$B$60)*Assumptions!$B$86,0)</x:f>
         <x:v>413000</x:v>
       </x:c>
       <x:c r="Z19" s="20" t="n">
-        <x:f>IF(Z5&gt;0,Assumptions!$B$56*Assumptions!$B$72+(Assumptions!$B$57+Z5/Assumptions!$B$58)*Assumptions!$B$83+MAX(1,Z5/Assumptions!$B$59)*Assumptions!$B$85,0)</x:f>
+        <x:f>IF(Z5&gt;0,Assumptions!$B$57*Assumptions!$B$73+(Assumptions!$B$58+Z5/Assumptions!$B$59)*Assumptions!$B$84+MAX(1,Z5/Assumptions!$B$60)*Assumptions!$B$86,0)</x:f>
         <x:v>413000</x:v>
       </x:c>
       <x:c r="AA19" s="20" t="n">
-        <x:f>IF(AA5&gt;0,Assumptions!$B$56*Assumptions!$B$72+(Assumptions!$B$57+AA5/Assumptions!$B$58)*Assumptions!$B$83+MAX(1,AA5/Assumptions!$B$59)*Assumptions!$B$85,0)</x:f>
+        <x:f>IF(AA5&gt;0,Assumptions!$B$57*Assumptions!$B$73+(Assumptions!$B$58+AA5/Assumptions!$B$59)*Assumptions!$B$84+MAX(1,AA5/Assumptions!$B$60)*Assumptions!$B$86,0)</x:f>
         <x:v>413000</x:v>
       </x:c>
       <x:c r="AB19" s="20" t="n">
-        <x:f>IF(AB5&gt;0,Assumptions!$B$56*Assumptions!$B$72+(Assumptions!$B$57+AB5/Assumptions!$B$58)*Assumptions!$B$83+MAX(1,AB5/Assumptions!$B$59)*Assumptions!$B$85,0)</x:f>
+        <x:f>IF(AB5&gt;0,Assumptions!$B$57*Assumptions!$B$73+(Assumptions!$B$58+AB5/Assumptions!$B$59)*Assumptions!$B$84+MAX(1,AB5/Assumptions!$B$60)*Assumptions!$B$86,0)</x:f>
         <x:v>413000</x:v>
       </x:c>
       <x:c r="AC19" s="20" t="n">
-        <x:f>IF(AC5&gt;0,Assumptions!$B$56*Assumptions!$B$72+(Assumptions!$B$57+AC5/Assumptions!$B$58)*Assumptions!$B$83+MAX(1,AC5/Assumptions!$B$59)*Assumptions!$B$85,0)</x:f>
+        <x:f>IF(AC5&gt;0,Assumptions!$B$57*Assumptions!$B$73+(Assumptions!$B$58+AC5/Assumptions!$B$59)*Assumptions!$B$84+MAX(1,AC5/Assumptions!$B$60)*Assumptions!$B$86,0)</x:f>
         <x:v>413000</x:v>
       </x:c>
       <x:c r="AD19" s="20" t="n">
-        <x:f>IF(AD5&gt;0,Assumptions!$B$56*Assumptions!$B$72+(Assumptions!$B$57+AD5/Assumptions!$B$58)*Assumptions!$B$83+MAX(1,AD5/Assumptions!$B$59)*Assumptions!$B$85,0)</x:f>
+        <x:f>IF(AD5&gt;0,Assumptions!$B$57*Assumptions!$B$73+(Assumptions!$B$58+AD5/Assumptions!$B$59)*Assumptions!$B$84+MAX(1,AD5/Assumptions!$B$60)*Assumptions!$B$86,0)</x:f>
         <x:v>413000</x:v>
       </x:c>
       <x:c r="AE19" s="20" t="n">
-        <x:f>IF(AE5&gt;0,Assumptions!$B$56*Assumptions!$B$72+(Assumptions!$B$57+AE5/Assumptions!$B$58)*Assumptions!$B$83+MAX(1,AE5/Assumptions!$B$59)*Assumptions!$B$85,0)</x:f>
+        <x:f>IF(AE5&gt;0,Assumptions!$B$57*Assumptions!$B$73+(Assumptions!$B$58+AE5/Assumptions!$B$59)*Assumptions!$B$84+MAX(1,AE5/Assumptions!$B$60)*Assumptions!$B$86,0)</x:f>
         <x:v>413000</x:v>
       </x:c>
       <x:c r="AF19" s="20" t="n">
-        <x:f>IF(AF5&gt;0,Assumptions!$B$56*Assumptions!$B$72+(Assumptions!$B$57+AF5/Assumptions!$B$58)*Assumptions!$B$83+MAX(1,AF5/Assumptions!$B$59)*Assumptions!$B$85,0)</x:f>
+        <x:f>IF(AF5&gt;0,Assumptions!$B$57*Assumptions!$B$73+(Assumptions!$B$58+AF5/Assumptions!$B$59)*Assumptions!$B$84+MAX(1,AF5/Assumptions!$B$60)*Assumptions!$B$86,0)</x:f>
         <x:v>413000</x:v>
       </x:c>
       <x:c r="AG19" s="20" t="n">
-        <x:f>IF(AG5&gt;0,Assumptions!$B$56*Assumptions!$B$72+(Assumptions!$B$57+AG5/Assumptions!$B$58)*Assumptions!$B$83+MAX(1,AG5/Assumptions!$B$59)*Assumptions!$B$85,0)</x:f>
+        <x:f>IF(AG5&gt;0,Assumptions!$B$57*Assumptions!$B$73+(Assumptions!$B$58+AG5/Assumptions!$B$59)*Assumptions!$B$84+MAX(1,AG5/Assumptions!$B$60)*Assumptions!$B$86,0)</x:f>
         <x:v>413000</x:v>
       </x:c>
       <x:c r="AH19" s="20" t="n">
-        <x:f>IF(AH5&gt;0,Assumptions!$B$56*Assumptions!$B$72+(Assumptions!$B$57+AH5/Assumptions!$B$58)*Assumptions!$B$83+MAX(1,AH5/Assumptions!$B$59)*Assumptions!$B$85,0)</x:f>
+        <x:f>IF(AH5&gt;0,Assumptions!$B$57*Assumptions!$B$73+(Assumptions!$B$58+AH5/Assumptions!$B$59)*Assumptions!$B$84+MAX(1,AH5/Assumptions!$B$60)*Assumptions!$B$86,0)</x:f>
         <x:v>413000</x:v>
       </x:c>
       <x:c r="AI19" s="20" t="n">
-        <x:f>IF(AI5&gt;0,Assumptions!$B$56*Assumptions!$B$72+(Assumptions!$B$57+AI5/Assumptions!$B$58)*Assumptions!$B$83+MAX(1,AI5/Assumptions!$B$59)*Assumptions!$B$85,0)</x:f>
+        <x:f>IF(AI5&gt;0,Assumptions!$B$57*Assumptions!$B$73+(Assumptions!$B$58+AI5/Assumptions!$B$59)*Assumptions!$B$84+MAX(1,AI5/Assumptions!$B$60)*Assumptions!$B$86,0)</x:f>
         <x:v>413000</x:v>
       </x:c>
       <x:c r="AJ19" s="20" t="n">
-        <x:f>IF(AJ5&gt;0,Assumptions!$B$56*Assumptions!$B$72+(Assumptions!$B$57+AJ5/Assumptions!$B$58)*Assumptions!$B$83+MAX(1,AJ5/Assumptions!$B$59)*Assumptions!$B$85,0)</x:f>
+        <x:f>IF(AJ5&gt;0,Assumptions!$B$57*Assumptions!$B$73+(Assumptions!$B$58+AJ5/Assumptions!$B$59)*Assumptions!$B$84+MAX(1,AJ5/Assumptions!$B$60)*Assumptions!$B$86,0)</x:f>
         <x:v>413000</x:v>
       </x:c>
       <x:c r="AK19" s="20" t="n">
-        <x:f>IF(AK5&gt;0,Assumptions!$B$56*Assumptions!$B$72+(Assumptions!$B$57+AK5/Assumptions!$B$58)*Assumptions!$B$83+MAX(1,AK5/Assumptions!$B$59)*Assumptions!$B$85,0)</x:f>
+        <x:f>IF(AK5&gt;0,Assumptions!$B$57*Assumptions!$B$73+(Assumptions!$B$58+AK5/Assumptions!$B$59)*Assumptions!$B$84+MAX(1,AK5/Assumptions!$B$60)*Assumptions!$B$86,0)</x:f>
         <x:v>413000</x:v>
       </x:c>
     </x:row>
@@ -5163,147 +5183,147 @@
         </x:is>
       </x:c>
       <x:c r="B20" s="20" t="n">
-        <x:f>IF(B5&gt;0,IF(B5&gt;20000,Assumptions!$B$61,Assumptions!$B$60)*Assumptions!$B$74,0)</x:f>
+        <x:f>IF(B5&gt;0,IF(B5&gt;20000,Assumptions!$B$62,Assumptions!$B$61)*Assumptions!$B$75,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C20" s="20" t="n">
-        <x:f>IF(C5&gt;0,IF(C5&gt;20000,Assumptions!$B$61,Assumptions!$B$60)*Assumptions!$B$74,0)</x:f>
+        <x:f>IF(C5&gt;0,IF(C5&gt;20000,Assumptions!$B$62,Assumptions!$B$61)*Assumptions!$B$75,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D20" s="20" t="n">
-        <x:f>IF(D5&gt;0,IF(D5&gt;20000,Assumptions!$B$61,Assumptions!$B$60)*Assumptions!$B$74,0)</x:f>
+        <x:f>IF(D5&gt;0,IF(D5&gt;20000,Assumptions!$B$62,Assumptions!$B$61)*Assumptions!$B$75,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="E20" s="20" t="n">
-        <x:f>IF(E5&gt;0,IF(E5&gt;20000,Assumptions!$B$61,Assumptions!$B$60)*Assumptions!$B$74,0)</x:f>
+        <x:f>IF(E5&gt;0,IF(E5&gt;20000,Assumptions!$B$62,Assumptions!$B$61)*Assumptions!$B$75,0)</x:f>
         <x:v>400000</x:v>
       </x:c>
       <x:c r="F20" s="20" t="n">
-        <x:f>IF(F5&gt;0,IF(F5&gt;20000,Assumptions!$B$61,Assumptions!$B$60)*Assumptions!$B$74,0)</x:f>
+        <x:f>IF(F5&gt;0,IF(F5&gt;20000,Assumptions!$B$62,Assumptions!$B$61)*Assumptions!$B$75,0)</x:f>
         <x:v>400000</x:v>
       </x:c>
       <x:c r="G20" s="20" t="n">
-        <x:f>IF(G5&gt;0,IF(G5&gt;20000,Assumptions!$B$61,Assumptions!$B$60)*Assumptions!$B$74,0)</x:f>
+        <x:f>IF(G5&gt;0,IF(G5&gt;20000,Assumptions!$B$62,Assumptions!$B$61)*Assumptions!$B$75,0)</x:f>
         <x:v>400000</x:v>
       </x:c>
       <x:c r="H20" s="20" t="n">
-        <x:f>IF(H5&gt;0,IF(H5&gt;20000,Assumptions!$B$61,Assumptions!$B$60)*Assumptions!$B$74,0)</x:f>
+        <x:f>IF(H5&gt;0,IF(H5&gt;20000,Assumptions!$B$62,Assumptions!$B$61)*Assumptions!$B$75,0)</x:f>
         <x:v>480000</x:v>
       </x:c>
       <x:c r="I20" s="20" t="n">
-        <x:f>IF(I5&gt;0,IF(I5&gt;20000,Assumptions!$B$61,Assumptions!$B$60)*Assumptions!$B$74,0)</x:f>
+        <x:f>IF(I5&gt;0,IF(I5&gt;20000,Assumptions!$B$62,Assumptions!$B$61)*Assumptions!$B$75,0)</x:f>
         <x:v>480000</x:v>
       </x:c>
       <x:c r="J20" s="20" t="n">
-        <x:f>IF(J5&gt;0,IF(J5&gt;20000,Assumptions!$B$61,Assumptions!$B$60)*Assumptions!$B$74,0)</x:f>
+        <x:f>IF(J5&gt;0,IF(J5&gt;20000,Assumptions!$B$62,Assumptions!$B$61)*Assumptions!$B$75,0)</x:f>
         <x:v>480000</x:v>
       </x:c>
       <x:c r="K20" s="20" t="n">
-        <x:f>IF(K5&gt;0,IF(K5&gt;20000,Assumptions!$B$61,Assumptions!$B$60)*Assumptions!$B$74,0)</x:f>
+        <x:f>IF(K5&gt;0,IF(K5&gt;20000,Assumptions!$B$62,Assumptions!$B$61)*Assumptions!$B$75,0)</x:f>
         <x:v>480000</x:v>
       </x:c>
       <x:c r="L20" s="20" t="n">
-        <x:f>IF(L5&gt;0,IF(L5&gt;20000,Assumptions!$B$61,Assumptions!$B$60)*Assumptions!$B$74,0)</x:f>
+        <x:f>IF(L5&gt;0,IF(L5&gt;20000,Assumptions!$B$62,Assumptions!$B$61)*Assumptions!$B$75,0)</x:f>
         <x:v>480000</x:v>
       </x:c>
       <x:c r="M20" s="20" t="n">
-        <x:f>IF(M5&gt;0,IF(M5&gt;20000,Assumptions!$B$61,Assumptions!$B$60)*Assumptions!$B$74,0)</x:f>
+        <x:f>IF(M5&gt;0,IF(M5&gt;20000,Assumptions!$B$62,Assumptions!$B$61)*Assumptions!$B$75,0)</x:f>
         <x:v>480000</x:v>
       </x:c>
       <x:c r="N20" s="20" t="n">
-        <x:f>IF(N5&gt;0,IF(N5&gt;20000,Assumptions!$B$61,Assumptions!$B$60)*Assumptions!$B$74,0)</x:f>
+        <x:f>IF(N5&gt;0,IF(N5&gt;20000,Assumptions!$B$62,Assumptions!$B$61)*Assumptions!$B$75,0)</x:f>
         <x:v>480000</x:v>
       </x:c>
       <x:c r="O20" s="20" t="n">
-        <x:f>IF(O5&gt;0,IF(O5&gt;20000,Assumptions!$B$61,Assumptions!$B$60)*Assumptions!$B$74,0)</x:f>
+        <x:f>IF(O5&gt;0,IF(O5&gt;20000,Assumptions!$B$62,Assumptions!$B$61)*Assumptions!$B$75,0)</x:f>
         <x:v>480000</x:v>
       </x:c>
       <x:c r="P20" s="20" t="n">
-        <x:f>IF(P5&gt;0,IF(P5&gt;20000,Assumptions!$B$61,Assumptions!$B$60)*Assumptions!$B$74,0)</x:f>
+        <x:f>IF(P5&gt;0,IF(P5&gt;20000,Assumptions!$B$62,Assumptions!$B$61)*Assumptions!$B$75,0)</x:f>
         <x:v>480000</x:v>
       </x:c>
       <x:c r="Q20" s="20" t="n">
-        <x:f>IF(Q5&gt;0,IF(Q5&gt;20000,Assumptions!$B$61,Assumptions!$B$60)*Assumptions!$B$74,0)</x:f>
+        <x:f>IF(Q5&gt;0,IF(Q5&gt;20000,Assumptions!$B$62,Assumptions!$B$61)*Assumptions!$B$75,0)</x:f>
         <x:v>480000</x:v>
       </x:c>
       <x:c r="R20" s="20" t="n">
-        <x:f>IF(R5&gt;0,IF(R5&gt;20000,Assumptions!$B$61,Assumptions!$B$60)*Assumptions!$B$74,0)</x:f>
+        <x:f>IF(R5&gt;0,IF(R5&gt;20000,Assumptions!$B$62,Assumptions!$B$61)*Assumptions!$B$75,0)</x:f>
         <x:v>480000</x:v>
       </x:c>
       <x:c r="S20" s="20" t="n">
-        <x:f>IF(S5&gt;0,IF(S5&gt;20000,Assumptions!$B$61,Assumptions!$B$60)*Assumptions!$B$74,0)</x:f>
+        <x:f>IF(S5&gt;0,IF(S5&gt;20000,Assumptions!$B$62,Assumptions!$B$61)*Assumptions!$B$75,0)</x:f>
         <x:v>480000</x:v>
       </x:c>
       <x:c r="T20" s="20" t="n">
-        <x:f>IF(T5&gt;0,IF(T5&gt;20000,Assumptions!$B$61,Assumptions!$B$60)*Assumptions!$B$74,0)</x:f>
+        <x:f>IF(T5&gt;0,IF(T5&gt;20000,Assumptions!$B$62,Assumptions!$B$61)*Assumptions!$B$75,0)</x:f>
         <x:v>480000</x:v>
       </x:c>
       <x:c r="U20" s="20" t="n">
-        <x:f>IF(U5&gt;0,IF(U5&gt;20000,Assumptions!$B$61,Assumptions!$B$60)*Assumptions!$B$74,0)</x:f>
+        <x:f>IF(U5&gt;0,IF(U5&gt;20000,Assumptions!$B$62,Assumptions!$B$61)*Assumptions!$B$75,0)</x:f>
         <x:v>480000</x:v>
       </x:c>
       <x:c r="V20" s="20" t="n">
-        <x:f>IF(V5&gt;0,IF(V5&gt;20000,Assumptions!$B$61,Assumptions!$B$60)*Assumptions!$B$74,0)</x:f>
+        <x:f>IF(V5&gt;0,IF(V5&gt;20000,Assumptions!$B$62,Assumptions!$B$61)*Assumptions!$B$75,0)</x:f>
         <x:v>480000</x:v>
       </x:c>
       <x:c r="W20" s="20" t="n">
-        <x:f>IF(W5&gt;0,IF(W5&gt;20000,Assumptions!$B$61,Assumptions!$B$60)*Assumptions!$B$74,0)</x:f>
+        <x:f>IF(W5&gt;0,IF(W5&gt;20000,Assumptions!$B$62,Assumptions!$B$61)*Assumptions!$B$75,0)</x:f>
         <x:v>480000</x:v>
       </x:c>
       <x:c r="X20" s="20" t="n">
-        <x:f>IF(X5&gt;0,IF(X5&gt;20000,Assumptions!$B$61,Assumptions!$B$60)*Assumptions!$B$74,0)</x:f>
+        <x:f>IF(X5&gt;0,IF(X5&gt;20000,Assumptions!$B$62,Assumptions!$B$61)*Assumptions!$B$75,0)</x:f>
         <x:v>480000</x:v>
       </x:c>
       <x:c r="Y20" s="20" t="n">
-        <x:f>IF(Y5&gt;0,IF(Y5&gt;20000,Assumptions!$B$61,Assumptions!$B$60)*Assumptions!$B$74,0)</x:f>
+        <x:f>IF(Y5&gt;0,IF(Y5&gt;20000,Assumptions!$B$62,Assumptions!$B$61)*Assumptions!$B$75,0)</x:f>
         <x:v>480000</x:v>
       </x:c>
       <x:c r="Z20" s="20" t="n">
-        <x:f>IF(Z5&gt;0,IF(Z5&gt;20000,Assumptions!$B$61,Assumptions!$B$60)*Assumptions!$B$74,0)</x:f>
+        <x:f>IF(Z5&gt;0,IF(Z5&gt;20000,Assumptions!$B$62,Assumptions!$B$61)*Assumptions!$B$75,0)</x:f>
         <x:v>480000</x:v>
       </x:c>
       <x:c r="AA20" s="20" t="n">
-        <x:f>IF(AA5&gt;0,IF(AA5&gt;20000,Assumptions!$B$61,Assumptions!$B$60)*Assumptions!$B$74,0)</x:f>
+        <x:f>IF(AA5&gt;0,IF(AA5&gt;20000,Assumptions!$B$62,Assumptions!$B$61)*Assumptions!$B$75,0)</x:f>
         <x:v>480000</x:v>
       </x:c>
       <x:c r="AB20" s="20" t="n">
-        <x:f>IF(AB5&gt;0,IF(AB5&gt;20000,Assumptions!$B$61,Assumptions!$B$60)*Assumptions!$B$74,0)</x:f>
+        <x:f>IF(AB5&gt;0,IF(AB5&gt;20000,Assumptions!$B$62,Assumptions!$B$61)*Assumptions!$B$75,0)</x:f>
         <x:v>480000</x:v>
       </x:c>
       <x:c r="AC20" s="20" t="n">
-        <x:f>IF(AC5&gt;0,IF(AC5&gt;20000,Assumptions!$B$61,Assumptions!$B$60)*Assumptions!$B$74,0)</x:f>
+        <x:f>IF(AC5&gt;0,IF(AC5&gt;20000,Assumptions!$B$62,Assumptions!$B$61)*Assumptions!$B$75,0)</x:f>
         <x:v>480000</x:v>
       </x:c>
       <x:c r="AD20" s="20" t="n">
-        <x:f>IF(AD5&gt;0,IF(AD5&gt;20000,Assumptions!$B$61,Assumptions!$B$60)*Assumptions!$B$74,0)</x:f>
+        <x:f>IF(AD5&gt;0,IF(AD5&gt;20000,Assumptions!$B$62,Assumptions!$B$61)*Assumptions!$B$75,0)</x:f>
         <x:v>480000</x:v>
       </x:c>
       <x:c r="AE20" s="20" t="n">
-        <x:f>IF(AE5&gt;0,IF(AE5&gt;20000,Assumptions!$B$61,Assumptions!$B$60)*Assumptions!$B$74,0)</x:f>
+        <x:f>IF(AE5&gt;0,IF(AE5&gt;20000,Assumptions!$B$62,Assumptions!$B$61)*Assumptions!$B$75,0)</x:f>
         <x:v>480000</x:v>
       </x:c>
       <x:c r="AF20" s="20" t="n">
-        <x:f>IF(AF5&gt;0,IF(AF5&gt;20000,Assumptions!$B$61,Assumptions!$B$60)*Assumptions!$B$74,0)</x:f>
+        <x:f>IF(AF5&gt;0,IF(AF5&gt;20000,Assumptions!$B$62,Assumptions!$B$61)*Assumptions!$B$75,0)</x:f>
         <x:v>480000</x:v>
       </x:c>
       <x:c r="AG20" s="20" t="n">
-        <x:f>IF(AG5&gt;0,IF(AG5&gt;20000,Assumptions!$B$61,Assumptions!$B$60)*Assumptions!$B$74,0)</x:f>
+        <x:f>IF(AG5&gt;0,IF(AG5&gt;20000,Assumptions!$B$62,Assumptions!$B$61)*Assumptions!$B$75,0)</x:f>
         <x:v>480000</x:v>
       </x:c>
       <x:c r="AH20" s="20" t="n">
-        <x:f>IF(AH5&gt;0,IF(AH5&gt;20000,Assumptions!$B$61,Assumptions!$B$60)*Assumptions!$B$74,0)</x:f>
+        <x:f>IF(AH5&gt;0,IF(AH5&gt;20000,Assumptions!$B$62,Assumptions!$B$61)*Assumptions!$B$75,0)</x:f>
         <x:v>480000</x:v>
       </x:c>
       <x:c r="AI20" s="20" t="n">
-        <x:f>IF(AI5&gt;0,IF(AI5&gt;20000,Assumptions!$B$61,Assumptions!$B$60)*Assumptions!$B$74,0)</x:f>
+        <x:f>IF(AI5&gt;0,IF(AI5&gt;20000,Assumptions!$B$62,Assumptions!$B$61)*Assumptions!$B$75,0)</x:f>
         <x:v>480000</x:v>
       </x:c>
       <x:c r="AJ20" s="20" t="n">
-        <x:f>IF(AJ5&gt;0,IF(AJ5&gt;20000,Assumptions!$B$61,Assumptions!$B$60)*Assumptions!$B$74,0)</x:f>
+        <x:f>IF(AJ5&gt;0,IF(AJ5&gt;20000,Assumptions!$B$62,Assumptions!$B$61)*Assumptions!$B$75,0)</x:f>
         <x:v>480000</x:v>
       </x:c>
       <x:c r="AK20" s="20" t="n">
-        <x:f>IF(AK5&gt;0,IF(AK5&gt;20000,Assumptions!$B$61,Assumptions!$B$60)*Assumptions!$B$74,0)</x:f>
+        <x:f>IF(AK5&gt;0,IF(AK5&gt;20000,Assumptions!$B$62,Assumptions!$B$61)*Assumptions!$B$75,0)</x:f>
         <x:v>480000</x:v>
       </x:c>
     </x:row>
@@ -5327,135 +5347,135 @@
       </x:c>
       <x:c r="E21" s="22" t="n">
         <x:f>E13+SUM(E14:E20)</x:f>
-        <x:v>903891.9648</x:v>
+        <x:v>877676.386112</x:v>
       </x:c>
       <x:c r="F21" s="22" t="n">
         <x:f>F13+SUM(F14:F20)</x:f>
-        <x:v>903891.9648</x:v>
+        <x:v>877676.386112</x:v>
       </x:c>
       <x:c r="G21" s="22" t="n">
         <x:f>G13+SUM(G14:G20)</x:f>
-        <x:v>903891.9648</x:v>
+        <x:v>877676.386112</x:v>
       </x:c>
       <x:c r="H21" s="22" t="n">
         <x:f>H13+SUM(H14:H20)</x:f>
-        <x:v>1098169.4208</x:v>
+        <x:v>1039184.368752</x:v>
       </x:c>
       <x:c r="I21" s="22" t="n">
         <x:f>I13+SUM(I14:I20)</x:f>
-        <x:v>1098169.4208</x:v>
+        <x:v>1039184.368752</x:v>
       </x:c>
       <x:c r="J21" s="22" t="n">
         <x:f>J13+SUM(J14:J20)</x:f>
-        <x:v>1098169.4208</x:v>
+        <x:v>1039184.368752</x:v>
       </x:c>
       <x:c r="K21" s="22" t="n">
         <x:f>K13+SUM(K14:K20)</x:f>
-        <x:v>1098169.4208</x:v>
+        <x:v>1039184.368752</x:v>
       </x:c>
       <x:c r="L21" s="22" t="n">
         <x:f>L13+SUM(L14:L20)</x:f>
-        <x:v>1098169.4208</x:v>
+        <x:v>1039184.368752</x:v>
       </x:c>
       <x:c r="M21" s="22" t="n">
         <x:f>M13+SUM(M14:M20)</x:f>
-        <x:v>1098169.4208</x:v>
+        <x:v>1039184.368752</x:v>
       </x:c>
       <x:c r="N21" s="22" t="n">
         <x:f>N13+SUM(N14:N20)</x:f>
-        <x:v>1272742.368</x:v>
+        <x:v>1174433.94792</x:v>
       </x:c>
       <x:c r="O21" s="22" t="n">
         <x:f>O13+SUM(O14:O20)</x:f>
-        <x:v>1272742.368</x:v>
+        <x:v>1174433.94792</x:v>
       </x:c>
       <x:c r="P21" s="22" t="n">
         <x:f>P13+SUM(P14:P20)</x:f>
-        <x:v>1272742.368</x:v>
+        <x:v>1174433.94792</x:v>
       </x:c>
       <x:c r="Q21" s="22" t="n">
         <x:f>Q13+SUM(Q14:Q20)</x:f>
-        <x:v>1272742.368</x:v>
+        <x:v>1174433.94792</x:v>
       </x:c>
       <x:c r="R21" s="22" t="n">
         <x:f>R13+SUM(R14:R20)</x:f>
-        <x:v>1272742.368</x:v>
+        <x:v>1174433.94792</x:v>
       </x:c>
       <x:c r="S21" s="22" t="n">
         <x:f>S13+SUM(S14:S20)</x:f>
-        <x:v>1272742.368</x:v>
+        <x:v>1174433.94792</x:v>
       </x:c>
       <x:c r="T21" s="22" t="n">
         <x:f>T13+SUM(T14:T20)</x:f>
-        <x:v>1272742.368</x:v>
+        <x:v>1174433.94792</x:v>
       </x:c>
       <x:c r="U21" s="22" t="n">
         <x:f>U13+SUM(U14:U20)</x:f>
-        <x:v>1272742.368</x:v>
+        <x:v>1174433.94792</x:v>
       </x:c>
       <x:c r="V21" s="22" t="n">
         <x:f>V13+SUM(V14:V20)</x:f>
-        <x:v>1272742.368</x:v>
+        <x:v>1174433.94792</x:v>
       </x:c>
       <x:c r="W21" s="22" t="n">
         <x:f>W13+SUM(W14:W20)</x:f>
-        <x:v>1272742.368</x:v>
+        <x:v>1174433.94792</x:v>
       </x:c>
       <x:c r="X21" s="22" t="n">
         <x:f>X13+SUM(X14:X20)</x:f>
-        <x:v>1272742.368</x:v>
+        <x:v>1174433.94792</x:v>
       </x:c>
       <x:c r="Y21" s="22" t="n">
         <x:f>Y13+SUM(Y14:Y20)</x:f>
-        <x:v>1272742.368</x:v>
+        <x:v>1174433.94792</x:v>
       </x:c>
       <x:c r="Z21" s="22" t="n">
         <x:f>Z13+SUM(Z14:Z20)</x:f>
-        <x:v>1272742.368</x:v>
+        <x:v>1174433.94792</x:v>
       </x:c>
       <x:c r="AA21" s="22" t="n">
         <x:f>AA13+SUM(AA14:AA20)</x:f>
-        <x:v>1272742.368</x:v>
+        <x:v>1174433.94792</x:v>
       </x:c>
       <x:c r="AB21" s="22" t="n">
         <x:f>AB13+SUM(AB14:AB20)</x:f>
-        <x:v>1272742.368</x:v>
+        <x:v>1174433.94792</x:v>
       </x:c>
       <x:c r="AC21" s="22" t="n">
         <x:f>AC13+SUM(AC14:AC20)</x:f>
-        <x:v>1272742.368</x:v>
+        <x:v>1174433.94792</x:v>
       </x:c>
       <x:c r="AD21" s="22" t="n">
         <x:f>AD13+SUM(AD14:AD20)</x:f>
-        <x:v>1272742.368</x:v>
+        <x:v>1174433.94792</x:v>
       </x:c>
       <x:c r="AE21" s="22" t="n">
         <x:f>AE13+SUM(AE14:AE20)</x:f>
-        <x:v>1272742.368</x:v>
+        <x:v>1174433.94792</x:v>
       </x:c>
       <x:c r="AF21" s="22" t="n">
         <x:f>AF13+SUM(AF14:AF20)</x:f>
-        <x:v>1272742.368</x:v>
+        <x:v>1174433.94792</x:v>
       </x:c>
       <x:c r="AG21" s="22" t="n">
         <x:f>AG13+SUM(AG14:AG20)</x:f>
-        <x:v>1272742.368</x:v>
+        <x:v>1174433.94792</x:v>
       </x:c>
       <x:c r="AH21" s="22" t="n">
         <x:f>AH13+SUM(AH14:AH20)</x:f>
-        <x:v>1272742.368</x:v>
+        <x:v>1174433.94792</x:v>
       </x:c>
       <x:c r="AI21" s="22" t="n">
         <x:f>AI13+SUM(AI14:AI20)</x:f>
-        <x:v>1272742.368</x:v>
+        <x:v>1174433.94792</x:v>
       </x:c>
       <x:c r="AJ21" s="22" t="n">
         <x:f>AJ13+SUM(AJ14:AJ20)</x:f>
-        <x:v>1272742.368</x:v>
+        <x:v>1174433.94792</x:v>
       </x:c>
       <x:c r="AK21" s="22" t="n">
         <x:f>AK13+SUM(AK14:AK20)</x:f>
-        <x:v>1272742.368</x:v>
+        <x:v>1174433.94792</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -5478,135 +5498,135 @@
       </x:c>
       <x:c r="E22" s="19" t="n">
         <x:f>IF(E5&gt;0,E21/E5,0)</x:f>
-        <x:v>75.3243304</x:v>
+        <x:v>73.13969884266666</x:v>
       </x:c>
       <x:c r="F22" s="19" t="n">
         <x:f>IF(F5&gt;0,F21/F5,0)</x:f>
-        <x:v>75.3243304</x:v>
+        <x:v>73.13969884266666</x:v>
       </x:c>
       <x:c r="G22" s="19" t="n">
         <x:f>IF(G5&gt;0,G21/G5,0)</x:f>
-        <x:v>75.3243304</x:v>
+        <x:v>73.13969884266666</x:v>
       </x:c>
       <x:c r="H22" s="19" t="n">
         <x:f>IF(H5&gt;0,H21/H5,0)</x:f>
-        <x:v>40.67294151111111</x:v>
+        <x:v>38.48830995377778</x:v>
       </x:c>
       <x:c r="I22" s="19" t="n">
         <x:f>IF(I5&gt;0,I21/I5,0)</x:f>
-        <x:v>40.67294151111111</x:v>
+        <x:v>38.48830995377778</x:v>
       </x:c>
       <x:c r="J22" s="19" t="n">
         <x:f>IF(J5&gt;0,J21/J5,0)</x:f>
-        <x:v>40.67294151111111</x:v>
+        <x:v>38.48830995377778</x:v>
       </x:c>
       <x:c r="K22" s="19" t="n">
         <x:f>IF(K5&gt;0,K21/K5,0)</x:f>
-        <x:v>40.67294151111111</x:v>
+        <x:v>38.48830995377778</x:v>
       </x:c>
       <x:c r="L22" s="19" t="n">
         <x:f>IF(L5&gt;0,L21/L5,0)</x:f>
-        <x:v>40.67294151111111</x:v>
+        <x:v>38.48830995377778</x:v>
       </x:c>
       <x:c r="M22" s="19" t="n">
         <x:f>IF(M5&gt;0,M21/M5,0)</x:f>
-        <x:v>40.67294151111111</x:v>
+        <x:v>38.48830995377778</x:v>
       </x:c>
       <x:c r="N22" s="19" t="n">
         <x:f>IF(N5&gt;0,N21/N5,0)</x:f>
-        <x:v>28.283163733333335</x:v>
+        <x:v>26.098532176</x:v>
       </x:c>
       <x:c r="O22" s="19" t="n">
         <x:f>IF(O5&gt;0,O21/O5,0)</x:f>
-        <x:v>28.283163733333335</x:v>
+        <x:v>26.098532176</x:v>
       </x:c>
       <x:c r="P22" s="19" t="n">
         <x:f>IF(P5&gt;0,P21/P5,0)</x:f>
-        <x:v>28.283163733333335</x:v>
+        <x:v>26.098532176</x:v>
       </x:c>
       <x:c r="Q22" s="19" t="n">
         <x:f>IF(Q5&gt;0,Q21/Q5,0)</x:f>
-        <x:v>28.283163733333335</x:v>
+        <x:v>26.098532176</x:v>
       </x:c>
       <x:c r="R22" s="19" t="n">
         <x:f>IF(R5&gt;0,R21/R5,0)</x:f>
-        <x:v>28.283163733333335</x:v>
+        <x:v>26.098532176</x:v>
       </x:c>
       <x:c r="S22" s="19" t="n">
         <x:f>IF(S5&gt;0,S21/S5,0)</x:f>
-        <x:v>28.283163733333335</x:v>
+        <x:v>26.098532176</x:v>
       </x:c>
       <x:c r="T22" s="19" t="n">
         <x:f>IF(T5&gt;0,T21/T5,0)</x:f>
-        <x:v>28.283163733333335</x:v>
+        <x:v>26.098532176</x:v>
       </x:c>
       <x:c r="U22" s="19" t="n">
         <x:f>IF(U5&gt;0,U21/U5,0)</x:f>
-        <x:v>28.283163733333335</x:v>
+        <x:v>26.098532176</x:v>
       </x:c>
       <x:c r="V22" s="19" t="n">
         <x:f>IF(V5&gt;0,V21/V5,0)</x:f>
-        <x:v>28.283163733333335</x:v>
+        <x:v>26.098532176</x:v>
       </x:c>
       <x:c r="W22" s="19" t="n">
         <x:f>IF(W5&gt;0,W21/W5,0)</x:f>
-        <x:v>28.283163733333335</x:v>
+        <x:v>26.098532176</x:v>
       </x:c>
       <x:c r="X22" s="19" t="n">
         <x:f>IF(X5&gt;0,X21/X5,0)</x:f>
-        <x:v>28.283163733333335</x:v>
+        <x:v>26.098532176</x:v>
       </x:c>
       <x:c r="Y22" s="19" t="n">
         <x:f>IF(Y5&gt;0,Y21/Y5,0)</x:f>
-        <x:v>28.283163733333335</x:v>
+        <x:v>26.098532176</x:v>
       </x:c>
       <x:c r="Z22" s="19" t="n">
         <x:f>IF(Z5&gt;0,Z21/Z5,0)</x:f>
-        <x:v>28.283163733333335</x:v>
+        <x:v>26.098532176</x:v>
       </x:c>
       <x:c r="AA22" s="19" t="n">
         <x:f>IF(AA5&gt;0,AA21/AA5,0)</x:f>
-        <x:v>28.283163733333335</x:v>
+        <x:v>26.098532176</x:v>
       </x:c>
       <x:c r="AB22" s="19" t="n">
         <x:f>IF(AB5&gt;0,AB21/AB5,0)</x:f>
-        <x:v>28.283163733333335</x:v>
+        <x:v>26.098532176</x:v>
       </x:c>
       <x:c r="AC22" s="19" t="n">
         <x:f>IF(AC5&gt;0,AC21/AC5,0)</x:f>
-        <x:v>28.283163733333335</x:v>
+        <x:v>26.098532176</x:v>
       </x:c>
       <x:c r="AD22" s="19" t="n">
         <x:f>IF(AD5&gt;0,AD21/AD5,0)</x:f>
-        <x:v>28.283163733333335</x:v>
+        <x:v>26.098532176</x:v>
       </x:c>
       <x:c r="AE22" s="19" t="n">
         <x:f>IF(AE5&gt;0,AE21/AE5,0)</x:f>
-        <x:v>28.283163733333335</x:v>
+        <x:v>26.098532176</x:v>
       </x:c>
       <x:c r="AF22" s="19" t="n">
         <x:f>IF(AF5&gt;0,AF21/AF5,0)</x:f>
-        <x:v>28.283163733333335</x:v>
+        <x:v>26.098532176</x:v>
       </x:c>
       <x:c r="AG22" s="19" t="n">
         <x:f>IF(AG5&gt;0,AG21/AG5,0)</x:f>
-        <x:v>28.283163733333335</x:v>
+        <x:v>26.098532176</x:v>
       </x:c>
       <x:c r="AH22" s="19" t="n">
         <x:f>IF(AH5&gt;0,AH21/AH5,0)</x:f>
-        <x:v>28.283163733333335</x:v>
+        <x:v>26.098532176</x:v>
       </x:c>
       <x:c r="AI22" s="19" t="n">
         <x:f>IF(AI5&gt;0,AI21/AI5,0)</x:f>
-        <x:v>28.283163733333335</x:v>
+        <x:v>26.098532176</x:v>
       </x:c>
       <x:c r="AJ22" s="19" t="n">
         <x:f>IF(AJ5&gt;0,AJ21/AJ5,0)</x:f>
-        <x:v>28.283163733333335</x:v>
+        <x:v>26.098532176</x:v>
       </x:c>
       <x:c r="AK22" s="19" t="n">
         <x:f>IF(AK5&gt;0,AK21/AK5,0)</x:f>
-        <x:v>28.283163733333335</x:v>
+        <x:v>26.098532176</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -5629,135 +5649,135 @@
       </x:c>
       <x:c r="E23" s="19" t="n">
         <x:f>IF(E6&gt;0,E13/E6,0)</x:f>
-        <x:v>7.1059194074074075</x:v>
+        <x:v>2.2511826133333335</x:v>
       </x:c>
       <x:c r="F23" s="19" t="n">
         <x:f>IF(F6&gt;0,F13/F6,0)</x:f>
-        <x:v>7.1059194074074075</x:v>
+        <x:v>2.2511826133333335</x:v>
       </x:c>
       <x:c r="G23" s="19" t="n">
         <x:f>IF(G6&gt;0,G13/G6,0)</x:f>
-        <x:v>7.1059194074074075</x:v>
+        <x:v>2.2511826133333335</x:v>
       </x:c>
       <x:c r="H23" s="19" t="n">
         <x:f>IF(H6&gt;0,H13/H6,0)</x:f>
-        <x:v>6.423820641975309</x:v>
+        <x:v>1.5690838479012343</x:v>
       </x:c>
       <x:c r="I23" s="19" t="n">
         <x:f>IF(I6&gt;0,I13/I6,0)</x:f>
-        <x:v>6.423820641975309</x:v>
+        <x:v>1.5690838479012343</x:v>
       </x:c>
       <x:c r="J23" s="19" t="n">
         <x:f>IF(J6&gt;0,J13/J6,0)</x:f>
-        <x:v>6.423820641975309</x:v>
+        <x:v>1.5690838479012343</x:v>
       </x:c>
       <x:c r="K23" s="19" t="n">
         <x:f>IF(K6&gt;0,K13/K6,0)</x:f>
-        <x:v>6.423820641975309</x:v>
+        <x:v>1.5690838479012343</x:v>
       </x:c>
       <x:c r="L23" s="19" t="n">
         <x:f>IF(L6&gt;0,L13/L6,0)</x:f>
-        <x:v>6.423820641975309</x:v>
+        <x:v>1.5690838479012343</x:v>
       </x:c>
       <x:c r="M23" s="19" t="n">
         <x:f>IF(M6&gt;0,M13/M6,0)</x:f>
-        <x:v>6.423820641975309</x:v>
+        <x:v>1.5690838479012343</x:v>
       </x:c>
       <x:c r="N23" s="19" t="n">
         <x:f>IF(N6&gt;0,N13/N6,0)</x:f>
-        <x:v>6.205549037037037</x:v>
+        <x:v>1.350812242962963</x:v>
       </x:c>
       <x:c r="O23" s="19" t="n">
         <x:f>IF(O6&gt;0,O13/O6,0)</x:f>
-        <x:v>6.205549037037037</x:v>
+        <x:v>1.350812242962963</x:v>
       </x:c>
       <x:c r="P23" s="19" t="n">
         <x:f>IF(P6&gt;0,P13/P6,0)</x:f>
-        <x:v>6.205549037037037</x:v>
+        <x:v>1.350812242962963</x:v>
       </x:c>
       <x:c r="Q23" s="19" t="n">
         <x:f>IF(Q6&gt;0,Q13/Q6,0)</x:f>
-        <x:v>6.205549037037037</x:v>
+        <x:v>1.350812242962963</x:v>
       </x:c>
       <x:c r="R23" s="19" t="n">
         <x:f>IF(R6&gt;0,R13/R6,0)</x:f>
-        <x:v>6.205549037037037</x:v>
+        <x:v>1.350812242962963</x:v>
       </x:c>
       <x:c r="S23" s="19" t="n">
         <x:f>IF(S6&gt;0,S13/S6,0)</x:f>
-        <x:v>6.205549037037037</x:v>
+        <x:v>1.350812242962963</x:v>
       </x:c>
       <x:c r="T23" s="19" t="n">
         <x:f>IF(T6&gt;0,T13/T6,0)</x:f>
-        <x:v>6.205549037037037</x:v>
+        <x:v>1.350812242962963</x:v>
       </x:c>
       <x:c r="U23" s="19" t="n">
         <x:f>IF(U6&gt;0,U13/U6,0)</x:f>
-        <x:v>6.205549037037037</x:v>
+        <x:v>1.350812242962963</x:v>
       </x:c>
       <x:c r="V23" s="19" t="n">
         <x:f>IF(V6&gt;0,V13/V6,0)</x:f>
-        <x:v>6.205549037037037</x:v>
+        <x:v>1.350812242962963</x:v>
       </x:c>
       <x:c r="W23" s="19" t="n">
         <x:f>IF(W6&gt;0,W13/W6,0)</x:f>
-        <x:v>6.205549037037037</x:v>
+        <x:v>1.350812242962963</x:v>
       </x:c>
       <x:c r="X23" s="19" t="n">
         <x:f>IF(X6&gt;0,X13/X6,0)</x:f>
-        <x:v>6.205549037037037</x:v>
+        <x:v>1.350812242962963</x:v>
       </x:c>
       <x:c r="Y23" s="19" t="n">
         <x:f>IF(Y6&gt;0,Y13/Y6,0)</x:f>
-        <x:v>6.205549037037037</x:v>
+        <x:v>1.350812242962963</x:v>
       </x:c>
       <x:c r="Z23" s="19" t="n">
         <x:f>IF(Z6&gt;0,Z13/Z6,0)</x:f>
-        <x:v>6.205549037037037</x:v>
+        <x:v>1.350812242962963</x:v>
       </x:c>
       <x:c r="AA23" s="19" t="n">
         <x:f>IF(AA6&gt;0,AA13/AA6,0)</x:f>
-        <x:v>6.205549037037037</x:v>
+        <x:v>1.350812242962963</x:v>
       </x:c>
       <x:c r="AB23" s="19" t="n">
         <x:f>IF(AB6&gt;0,AB13/AB6,0)</x:f>
-        <x:v>6.205549037037037</x:v>
+        <x:v>1.350812242962963</x:v>
       </x:c>
       <x:c r="AC23" s="19" t="n">
         <x:f>IF(AC6&gt;0,AC13/AC6,0)</x:f>
-        <x:v>6.205549037037037</x:v>
+        <x:v>1.350812242962963</x:v>
       </x:c>
       <x:c r="AD23" s="19" t="n">
         <x:f>IF(AD6&gt;0,AD13/AD6,0)</x:f>
-        <x:v>6.205549037037037</x:v>
+        <x:v>1.350812242962963</x:v>
       </x:c>
       <x:c r="AE23" s="19" t="n">
         <x:f>IF(AE6&gt;0,AE13/AE6,0)</x:f>
-        <x:v>6.205549037037037</x:v>
+        <x:v>1.350812242962963</x:v>
       </x:c>
       <x:c r="AF23" s="19" t="n">
         <x:f>IF(AF6&gt;0,AF13/AF6,0)</x:f>
-        <x:v>6.205549037037037</x:v>
+        <x:v>1.350812242962963</x:v>
       </x:c>
       <x:c r="AG23" s="19" t="n">
         <x:f>IF(AG6&gt;0,AG13/AG6,0)</x:f>
-        <x:v>6.205549037037037</x:v>
+        <x:v>1.350812242962963</x:v>
       </x:c>
       <x:c r="AH23" s="19" t="n">
         <x:f>IF(AH6&gt;0,AH13/AH6,0)</x:f>
-        <x:v>6.205549037037037</x:v>
+        <x:v>1.350812242962963</x:v>
       </x:c>
       <x:c r="AI23" s="19" t="n">
         <x:f>IF(AI6&gt;0,AI13/AI6,0)</x:f>
-        <x:v>6.205549037037037</x:v>
+        <x:v>1.350812242962963</x:v>
       </x:c>
       <x:c r="AJ23" s="19" t="n">
         <x:f>IF(AJ6&gt;0,AJ13/AJ6,0)</x:f>
-        <x:v>6.205549037037037</x:v>
+        <x:v>1.350812242962963</x:v>
       </x:c>
       <x:c r="AK23" s="19" t="n">
         <x:f>IF(AK6&gt;0,AK13/AK6,0)</x:f>
-        <x:v>6.205549037037037</x:v>
+        <x:v>1.350812242962963</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -5949,19 +5969,19 @@
       </x:c>
       <x:c r="B9" s="27" t="n">
         <x:f>SUM(B40:M40)</x:f>
-        <x:v>20848549.562057145</x:v>
+        <x:v>20415992.513705146</x:v>
       </x:c>
       <x:c r="C9" s="27" t="n">
         <x:f>SUM(N40:Y40)</x:f>
-        <x:v>19772908.416000005</x:v>
+        <x:v>18593207.37504</x:v>
       </x:c>
       <x:c r="D9" s="27" t="n">
         <x:f>SUM(Z40:AK40)</x:f>
-        <x:v>15272908.416000003</x:v>
+        <x:v>14093207.37504</x:v>
       </x:c>
       <x:c r="E9" s="28" t="n">
         <x:f>SUM(B9:D9)</x:f>
-        <x:v>55894366.39405715</x:v>
+        <x:v>53102407.263785146</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -5972,19 +5992,19 @@
       </x:c>
       <x:c r="B10" s="28" t="n">
         <x:f>SUM(B41:M41)</x:f>
-        <x:v>10373450.437942853</x:v>
+        <x:v>10806007.486294853</x:v>
       </x:c>
       <x:c r="C10" s="28" t="n">
         <x:f>SUM(N41:Y41)</x:f>
-        <x:v>10287091.583999999</x:v>
+        <x:v>11466792.624959998</x:v>
       </x:c>
       <x:c r="D10" s="28" t="n">
         <x:f>SUM(Z41:AK41)</x:f>
-        <x:v>5787091.584000002</x:v>
+        <x:v>6966792.624959999</x:v>
       </x:c>
       <x:c r="E10" s="28" t="n">
         <x:f>SUM(B10:D10)</x:f>
-        <x:v>26447633.605942857</x:v>
+        <x:v>29239592.736214846</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -5995,19 +6015,19 @@
       </x:c>
       <x:c r="B11" s="24" t="n">
         <x:f>IF(B8&gt;0,B10/B8,0)</x:f>
-        <x:v>0.33224810831922535</x:v>
+        <x:v>0.34610234726458433</x:v>
       </x:c>
       <x:c r="C11" s="24" t="n">
         <x:f>IF(C8&gt;0,C10/C8,0)</x:f>
-        <x:v>0.34221861556886224</x:v>
+        <x:v>0.38146349384431133</x:v>
       </x:c>
       <x:c r="D11" s="24" t="n">
         <x:f>IF(D8&gt;0,D10/D8,0)</x:f>
-        <x:v>0.2747906735042736</x:v>
+        <x:v>0.3308068672820512</x:v>
       </x:c>
       <x:c r="E11" s="29" t="n">
         <x:f>IF(E8&gt;0,E10/E8,0)</x:f>
-        <x:v>0.3211925093626929</x:v>
+        <x:v>0.35509937499957306</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -6081,7 +6101,7 @@
         </x:is>
       </x:c>
       <x:c r="D17" s="27" t="n">
-        <x:f>(Assumptions!$B$11+Assumptions!$B$13+Assumptions!$B$15)*Assumptions!$B$63*12</x:f>
+        <x:f>(Assumptions!$B$11+Assumptions!$B$13+Assumptions!$B$15)*Assumptions!$B$64*12</x:f>
         <x:v>21060000</x:v>
       </x:c>
     </x:row>
@@ -6092,7 +6112,7 @@
         </x:is>
       </x:c>
       <x:c r="D18" s="27" t="n">
-        <x:f>D17*Assumptions!$B$69</x:f>
+        <x:f>D17*Assumptions!$B$70</x:f>
         <x:v>2106000</x:v>
       </x:c>
     </x:row>
@@ -6104,7 +6124,7 @@
       </x:c>
       <x:c r="D19" s="31" t="n">
         <x:f>Run!AK22</x:f>
-        <x:v>28.283163733333335</x:v>
+        <x:v>26.098532176</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -6115,7 +6135,7 @@
       </x:c>
       <x:c r="D20" s="31" t="n">
         <x:f>Run!AK23</x:f>
-        <x:v>6.205549037037037</x:v>
+        <x:v>1.350812242962963</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -6137,7 +6157,7 @@
       </x:c>
       <x:c r="C22" s="33" t="n">
         <x:f>Run!E21</x:f>
-        <x:v>903891.9648</x:v>
+        <x:v>877676.386112</x:v>
       </x:c>
       <x:c r="D22" s="20" t="n">
         <x:f>E34</x:f>
@@ -6424,147 +6444,147 @@
         </x:is>
       </x:c>
       <x:c r="B32" s="20" t="n">
-        <x:f>IF(B31&gt;0,MAX(B31,IF(B$30&gt;=Assumptions!$B$14,Assumptions!$B$64,0)),0)</x:f>
+        <x:f>IF(B31&gt;0,MAX(B31,IF(B$30&gt;=Assumptions!$B$14,Assumptions!$B$65,0)),0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C32" s="20" t="n">
-        <x:f>IF(C31&gt;0,MAX(C31,IF(C$30&gt;=Assumptions!$B$14,Assumptions!$B$64,0)),0)</x:f>
+        <x:f>IF(C31&gt;0,MAX(C31,IF(C$30&gt;=Assumptions!$B$14,Assumptions!$B$65,0)),0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D32" s="20" t="n">
-        <x:f>IF(D31&gt;0,MAX(D31,IF(D$30&gt;=Assumptions!$B$14,Assumptions!$B$64,0)),0)</x:f>
+        <x:f>IF(D31&gt;0,MAX(D31,IF(D$30&gt;=Assumptions!$B$14,Assumptions!$B$65,0)),0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="E32" s="20" t="n">
-        <x:f>IF(E31&gt;0,MAX(E31,IF(E$30&gt;=Assumptions!$B$14,Assumptions!$B$64,0)),0)</x:f>
+        <x:f>IF(E31&gt;0,MAX(E31,IF(E$30&gt;=Assumptions!$B$14,Assumptions!$B$65,0)),0)</x:f>
         <x:v>12000</x:v>
       </x:c>
       <x:c r="F32" s="20" t="n">
-        <x:f>IF(F31&gt;0,MAX(F31,IF(F$30&gt;=Assumptions!$B$14,Assumptions!$B$64,0)),0)</x:f>
+        <x:f>IF(F31&gt;0,MAX(F31,IF(F$30&gt;=Assumptions!$B$14,Assumptions!$B$65,0)),0)</x:f>
         <x:v>12000</x:v>
       </x:c>
       <x:c r="G32" s="20" t="n">
-        <x:f>IF(G31&gt;0,MAX(G31,IF(G$30&gt;=Assumptions!$B$14,Assumptions!$B$64,0)),0)</x:f>
+        <x:f>IF(G31&gt;0,MAX(G31,IF(G$30&gt;=Assumptions!$B$14,Assumptions!$B$65,0)),0)</x:f>
         <x:v>12000</x:v>
       </x:c>
       <x:c r="H32" s="20" t="n">
-        <x:f>IF(H31&gt;0,MAX(H31,IF(H$30&gt;=Assumptions!$B$14,Assumptions!$B$64,0)),0)</x:f>
+        <x:f>IF(H31&gt;0,MAX(H31,IF(H$30&gt;=Assumptions!$B$14,Assumptions!$B$65,0)),0)</x:f>
         <x:v>27000</x:v>
       </x:c>
       <x:c r="I32" s="20" t="n">
-        <x:f>IF(I31&gt;0,MAX(I31,IF(I$30&gt;=Assumptions!$B$14,Assumptions!$B$64,0)),0)</x:f>
+        <x:f>IF(I31&gt;0,MAX(I31,IF(I$30&gt;=Assumptions!$B$14,Assumptions!$B$65,0)),0)</x:f>
         <x:v>27000</x:v>
       </x:c>
       <x:c r="J32" s="20" t="n">
-        <x:f>IF(J31&gt;0,MAX(J31,IF(J$30&gt;=Assumptions!$B$14,Assumptions!$B$64,0)),0)</x:f>
+        <x:f>IF(J31&gt;0,MAX(J31,IF(J$30&gt;=Assumptions!$B$14,Assumptions!$B$65,0)),0)</x:f>
         <x:v>27000</x:v>
       </x:c>
       <x:c r="K32" s="20" t="n">
-        <x:f>IF(K31&gt;0,MAX(K31,IF(K$30&gt;=Assumptions!$B$14,Assumptions!$B$64,0)),0)</x:f>
+        <x:f>IF(K31&gt;0,MAX(K31,IF(K$30&gt;=Assumptions!$B$14,Assumptions!$B$65,0)),0)</x:f>
         <x:v>27000</x:v>
       </x:c>
       <x:c r="L32" s="20" t="n">
-        <x:f>IF(L31&gt;0,MAX(L31,IF(L$30&gt;=Assumptions!$B$14,Assumptions!$B$64,0)),0)</x:f>
+        <x:f>IF(L31&gt;0,MAX(L31,IF(L$30&gt;=Assumptions!$B$14,Assumptions!$B$65,0)),0)</x:f>
         <x:v>27000</x:v>
       </x:c>
       <x:c r="M32" s="20" t="n">
-        <x:f>IF(M31&gt;0,MAX(M31,IF(M$30&gt;=Assumptions!$B$14,Assumptions!$B$64,0)),0)</x:f>
+        <x:f>IF(M31&gt;0,MAX(M31,IF(M$30&gt;=Assumptions!$B$14,Assumptions!$B$65,0)),0)</x:f>
         <x:v>27000</x:v>
       </x:c>
       <x:c r="N32" s="20" t="n">
-        <x:f>IF(N31&gt;0,MAX(N31,IF(N$30&gt;=Assumptions!$B$14,Assumptions!$B$64,0)),0)</x:f>
+        <x:f>IF(N31&gt;0,MAX(N31,IF(N$30&gt;=Assumptions!$B$14,Assumptions!$B$65,0)),0)</x:f>
         <x:v>45000</x:v>
       </x:c>
       <x:c r="O32" s="20" t="n">
-        <x:f>IF(O31&gt;0,MAX(O31,IF(O$30&gt;=Assumptions!$B$14,Assumptions!$B$64,0)),0)</x:f>
+        <x:f>IF(O31&gt;0,MAX(O31,IF(O$30&gt;=Assumptions!$B$14,Assumptions!$B$65,0)),0)</x:f>
         <x:v>45000</x:v>
       </x:c>
       <x:c r="P32" s="20" t="n">
-        <x:f>IF(P31&gt;0,MAX(P31,IF(P$30&gt;=Assumptions!$B$14,Assumptions!$B$64,0)),0)</x:f>
+        <x:f>IF(P31&gt;0,MAX(P31,IF(P$30&gt;=Assumptions!$B$14,Assumptions!$B$65,0)),0)</x:f>
         <x:v>45000</x:v>
       </x:c>
       <x:c r="Q32" s="20" t="n">
-        <x:f>IF(Q31&gt;0,MAX(Q31,IF(Q$30&gt;=Assumptions!$B$14,Assumptions!$B$64,0)),0)</x:f>
+        <x:f>IF(Q31&gt;0,MAX(Q31,IF(Q$30&gt;=Assumptions!$B$14,Assumptions!$B$65,0)),0)</x:f>
         <x:v>45000</x:v>
       </x:c>
       <x:c r="R32" s="20" t="n">
-        <x:f>IF(R31&gt;0,MAX(R31,IF(R$30&gt;=Assumptions!$B$14,Assumptions!$B$64,0)),0)</x:f>
+        <x:f>IF(R31&gt;0,MAX(R31,IF(R$30&gt;=Assumptions!$B$14,Assumptions!$B$65,0)),0)</x:f>
         <x:v>45000</x:v>
       </x:c>
       <x:c r="S32" s="20" t="n">
-        <x:f>IF(S31&gt;0,MAX(S31,IF(S$30&gt;=Assumptions!$B$14,Assumptions!$B$64,0)),0)</x:f>
+        <x:f>IF(S31&gt;0,MAX(S31,IF(S$30&gt;=Assumptions!$B$14,Assumptions!$B$65,0)),0)</x:f>
         <x:v>45000</x:v>
       </x:c>
       <x:c r="T32" s="20" t="n">
-        <x:f>IF(T31&gt;0,MAX(T31,IF(T$30&gt;=Assumptions!$B$14,Assumptions!$B$64,0)),0)</x:f>
+        <x:f>IF(T31&gt;0,MAX(T31,IF(T$30&gt;=Assumptions!$B$14,Assumptions!$B$65,0)),0)</x:f>
         <x:v>45000</x:v>
       </x:c>
       <x:c r="U32" s="20" t="n">
-        <x:f>IF(U31&gt;0,MAX(U31,IF(U$30&gt;=Assumptions!$B$14,Assumptions!$B$64,0)),0)</x:f>
+        <x:f>IF(U31&gt;0,MAX(U31,IF(U$30&gt;=Assumptions!$B$14,Assumptions!$B$65,0)),0)</x:f>
         <x:v>45000</x:v>
       </x:c>
       <x:c r="V32" s="20" t="n">
-        <x:f>IF(V31&gt;0,MAX(V31,IF(V$30&gt;=Assumptions!$B$14,Assumptions!$B$64,0)),0)</x:f>
+        <x:f>IF(V31&gt;0,MAX(V31,IF(V$30&gt;=Assumptions!$B$14,Assumptions!$B$65,0)),0)</x:f>
         <x:v>45000</x:v>
       </x:c>
       <x:c r="W32" s="20" t="n">
-        <x:f>IF(W31&gt;0,MAX(W31,IF(W$30&gt;=Assumptions!$B$14,Assumptions!$B$64,0)),0)</x:f>
+        <x:f>IF(W31&gt;0,MAX(W31,IF(W$30&gt;=Assumptions!$B$14,Assumptions!$B$65,0)),0)</x:f>
         <x:v>45000</x:v>
       </x:c>
       <x:c r="X32" s="20" t="n">
-        <x:f>IF(X31&gt;0,MAX(X31,IF(X$30&gt;=Assumptions!$B$14,Assumptions!$B$64,0)),0)</x:f>
+        <x:f>IF(X31&gt;0,MAX(X31,IF(X$30&gt;=Assumptions!$B$14,Assumptions!$B$65,0)),0)</x:f>
         <x:v>45000</x:v>
       </x:c>
       <x:c r="Y32" s="20" t="n">
-        <x:f>IF(Y31&gt;0,MAX(Y31,IF(Y$30&gt;=Assumptions!$B$14,Assumptions!$B$64,0)),0)</x:f>
+        <x:f>IF(Y31&gt;0,MAX(Y31,IF(Y$30&gt;=Assumptions!$B$14,Assumptions!$B$65,0)),0)</x:f>
         <x:v>45000</x:v>
       </x:c>
       <x:c r="Z32" s="20" t="n">
-        <x:f>IF(Z31&gt;0,MAX(Z31,IF(Z$30&gt;=Assumptions!$B$14,Assumptions!$B$64,0)),0)</x:f>
+        <x:f>IF(Z31&gt;0,MAX(Z31,IF(Z$30&gt;=Assumptions!$B$14,Assumptions!$B$65,0)),0)</x:f>
         <x:v>45000</x:v>
       </x:c>
       <x:c r="AA32" s="20" t="n">
-        <x:f>IF(AA31&gt;0,MAX(AA31,IF(AA$30&gt;=Assumptions!$B$14,Assumptions!$B$64,0)),0)</x:f>
+        <x:f>IF(AA31&gt;0,MAX(AA31,IF(AA$30&gt;=Assumptions!$B$14,Assumptions!$B$65,0)),0)</x:f>
         <x:v>45000</x:v>
       </x:c>
       <x:c r="AB32" s="20" t="n">
-        <x:f>IF(AB31&gt;0,MAX(AB31,IF(AB$30&gt;=Assumptions!$B$14,Assumptions!$B$64,0)),0)</x:f>
+        <x:f>IF(AB31&gt;0,MAX(AB31,IF(AB$30&gt;=Assumptions!$B$14,Assumptions!$B$65,0)),0)</x:f>
         <x:v>45000</x:v>
       </x:c>
       <x:c r="AC32" s="20" t="n">
-        <x:f>IF(AC31&gt;0,MAX(AC31,IF(AC$30&gt;=Assumptions!$B$14,Assumptions!$B$64,0)),0)</x:f>
+        <x:f>IF(AC31&gt;0,MAX(AC31,IF(AC$30&gt;=Assumptions!$B$14,Assumptions!$B$65,0)),0)</x:f>
         <x:v>45000</x:v>
       </x:c>
       <x:c r="AD32" s="20" t="n">
-        <x:f>IF(AD31&gt;0,MAX(AD31,IF(AD$30&gt;=Assumptions!$B$14,Assumptions!$B$64,0)),0)</x:f>
+        <x:f>IF(AD31&gt;0,MAX(AD31,IF(AD$30&gt;=Assumptions!$B$14,Assumptions!$B$65,0)),0)</x:f>
         <x:v>45000</x:v>
       </x:c>
       <x:c r="AE32" s="20" t="n">
-        <x:f>IF(AE31&gt;0,MAX(AE31,IF(AE$30&gt;=Assumptions!$B$14,Assumptions!$B$64,0)),0)</x:f>
+        <x:f>IF(AE31&gt;0,MAX(AE31,IF(AE$30&gt;=Assumptions!$B$14,Assumptions!$B$65,0)),0)</x:f>
         <x:v>45000</x:v>
       </x:c>
       <x:c r="AF32" s="20" t="n">
-        <x:f>IF(AF31&gt;0,MAX(AF31,IF(AF$30&gt;=Assumptions!$B$14,Assumptions!$B$64,0)),0)</x:f>
+        <x:f>IF(AF31&gt;0,MAX(AF31,IF(AF$30&gt;=Assumptions!$B$14,Assumptions!$B$65,0)),0)</x:f>
         <x:v>45000</x:v>
       </x:c>
       <x:c r="AG32" s="20" t="n">
-        <x:f>IF(AG31&gt;0,MAX(AG31,IF(AG$30&gt;=Assumptions!$B$14,Assumptions!$B$64,0)),0)</x:f>
+        <x:f>IF(AG31&gt;0,MAX(AG31,IF(AG$30&gt;=Assumptions!$B$14,Assumptions!$B$65,0)),0)</x:f>
         <x:v>45000</x:v>
       </x:c>
       <x:c r="AH32" s="20" t="n">
-        <x:f>IF(AH31&gt;0,MAX(AH31,IF(AH$30&gt;=Assumptions!$B$14,Assumptions!$B$64,0)),0)</x:f>
+        <x:f>IF(AH31&gt;0,MAX(AH31,IF(AH$30&gt;=Assumptions!$B$14,Assumptions!$B$65,0)),0)</x:f>
         <x:v>45000</x:v>
       </x:c>
       <x:c r="AI32" s="20" t="n">
-        <x:f>IF(AI31&gt;0,MAX(AI31,IF(AI$30&gt;=Assumptions!$B$14,Assumptions!$B$64,0)),0)</x:f>
+        <x:f>IF(AI31&gt;0,MAX(AI31,IF(AI$30&gt;=Assumptions!$B$14,Assumptions!$B$65,0)),0)</x:f>
         <x:v>45000</x:v>
       </x:c>
       <x:c r="AJ32" s="20" t="n">
-        <x:f>IF(AJ31&gt;0,MAX(AJ31,IF(AJ$30&gt;=Assumptions!$B$14,Assumptions!$B$64,0)),0)</x:f>
+        <x:f>IF(AJ31&gt;0,MAX(AJ31,IF(AJ$30&gt;=Assumptions!$B$14,Assumptions!$B$65,0)),0)</x:f>
         <x:v>45000</x:v>
       </x:c>
       <x:c r="AK32" s="20" t="n">
-        <x:f>IF(AK31&gt;0,MAX(AK31,IF(AK$30&gt;=Assumptions!$B$14,Assumptions!$B$64,0)),0)</x:f>
+        <x:f>IF(AK31&gt;0,MAX(AK31,IF(AK$30&gt;=Assumptions!$B$14,Assumptions!$B$65,0)),0)</x:f>
         <x:v>45000</x:v>
       </x:c>
     </x:row>
@@ -6726,147 +6746,147 @@
         </x:is>
       </x:c>
       <x:c r="B34" s="20" t="n">
-        <x:f>B32*Assumptions!$B$63</x:f>
+        <x:f>B32*Assumptions!$B$64</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C34" s="20" t="n">
-        <x:f>C32*Assumptions!$B$63</x:f>
+        <x:f>C32*Assumptions!$B$64</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D34" s="20" t="n">
-        <x:f>D32*Assumptions!$B$63</x:f>
+        <x:f>D32*Assumptions!$B$64</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="E34" s="20" t="n">
-        <x:f>E32*Assumptions!$B$63</x:f>
+        <x:f>E32*Assumptions!$B$64</x:f>
         <x:v>468000</x:v>
       </x:c>
       <x:c r="F34" s="20" t="n">
-        <x:f>F32*Assumptions!$B$63</x:f>
+        <x:f>F32*Assumptions!$B$64</x:f>
         <x:v>468000</x:v>
       </x:c>
       <x:c r="G34" s="20" t="n">
-        <x:f>G32*Assumptions!$B$63</x:f>
+        <x:f>G32*Assumptions!$B$64</x:f>
         <x:v>468000</x:v>
       </x:c>
       <x:c r="H34" s="20" t="n">
-        <x:f>H32*Assumptions!$B$63</x:f>
+        <x:f>H32*Assumptions!$B$64</x:f>
         <x:v>1053000</x:v>
       </x:c>
       <x:c r="I34" s="20" t="n">
-        <x:f>I32*Assumptions!$B$63</x:f>
+        <x:f>I32*Assumptions!$B$64</x:f>
         <x:v>1053000</x:v>
       </x:c>
       <x:c r="J34" s="20" t="n">
-        <x:f>J32*Assumptions!$B$63</x:f>
+        <x:f>J32*Assumptions!$B$64</x:f>
         <x:v>1053000</x:v>
       </x:c>
       <x:c r="K34" s="20" t="n">
-        <x:f>K32*Assumptions!$B$63</x:f>
+        <x:f>K32*Assumptions!$B$64</x:f>
         <x:v>1053000</x:v>
       </x:c>
       <x:c r="L34" s="20" t="n">
-        <x:f>L32*Assumptions!$B$63</x:f>
+        <x:f>L32*Assumptions!$B$64</x:f>
         <x:v>1053000</x:v>
       </x:c>
       <x:c r="M34" s="20" t="n">
-        <x:f>M32*Assumptions!$B$63</x:f>
+        <x:f>M32*Assumptions!$B$64</x:f>
         <x:v>1053000</x:v>
       </x:c>
       <x:c r="N34" s="20" t="n">
-        <x:f>N32*Assumptions!$B$63</x:f>
+        <x:f>N32*Assumptions!$B$64</x:f>
         <x:v>1755000</x:v>
       </x:c>
       <x:c r="O34" s="20" t="n">
-        <x:f>O32*Assumptions!$B$63</x:f>
+        <x:f>O32*Assumptions!$B$64</x:f>
         <x:v>1755000</x:v>
       </x:c>
       <x:c r="P34" s="20" t="n">
-        <x:f>P32*Assumptions!$B$63</x:f>
+        <x:f>P32*Assumptions!$B$64</x:f>
         <x:v>1755000</x:v>
       </x:c>
       <x:c r="Q34" s="20" t="n">
-        <x:f>Q32*Assumptions!$B$63</x:f>
+        <x:f>Q32*Assumptions!$B$64</x:f>
         <x:v>1755000</x:v>
       </x:c>
       <x:c r="R34" s="20" t="n">
-        <x:f>R32*Assumptions!$B$63</x:f>
+        <x:f>R32*Assumptions!$B$64</x:f>
         <x:v>1755000</x:v>
       </x:c>
       <x:c r="S34" s="20" t="n">
-        <x:f>S32*Assumptions!$B$63</x:f>
+        <x:f>S32*Assumptions!$B$64</x:f>
         <x:v>1755000</x:v>
       </x:c>
       <x:c r="T34" s="20" t="n">
-        <x:f>T32*Assumptions!$B$63</x:f>
+        <x:f>T32*Assumptions!$B$64</x:f>
         <x:v>1755000</x:v>
       </x:c>
       <x:c r="U34" s="20" t="n">
-        <x:f>U32*Assumptions!$B$63</x:f>
+        <x:f>U32*Assumptions!$B$64</x:f>
         <x:v>1755000</x:v>
       </x:c>
       <x:c r="V34" s="20" t="n">
-        <x:f>V32*Assumptions!$B$63</x:f>
+        <x:f>V32*Assumptions!$B$64</x:f>
         <x:v>1755000</x:v>
       </x:c>
       <x:c r="W34" s="20" t="n">
-        <x:f>W32*Assumptions!$B$63</x:f>
+        <x:f>W32*Assumptions!$B$64</x:f>
         <x:v>1755000</x:v>
       </x:c>
       <x:c r="X34" s="20" t="n">
-        <x:f>X32*Assumptions!$B$63</x:f>
+        <x:f>X32*Assumptions!$B$64</x:f>
         <x:v>1755000</x:v>
       </x:c>
       <x:c r="Y34" s="20" t="n">
-        <x:f>Y32*Assumptions!$B$63</x:f>
+        <x:f>Y32*Assumptions!$B$64</x:f>
         <x:v>1755000</x:v>
       </x:c>
       <x:c r="Z34" s="20" t="n">
-        <x:f>Z32*Assumptions!$B$63</x:f>
+        <x:f>Z32*Assumptions!$B$64</x:f>
         <x:v>1755000</x:v>
       </x:c>
       <x:c r="AA34" s="20" t="n">
-        <x:f>AA32*Assumptions!$B$63</x:f>
+        <x:f>AA32*Assumptions!$B$64</x:f>
         <x:v>1755000</x:v>
       </x:c>
       <x:c r="AB34" s="20" t="n">
-        <x:f>AB32*Assumptions!$B$63</x:f>
+        <x:f>AB32*Assumptions!$B$64</x:f>
         <x:v>1755000</x:v>
       </x:c>
       <x:c r="AC34" s="20" t="n">
-        <x:f>AC32*Assumptions!$B$63</x:f>
+        <x:f>AC32*Assumptions!$B$64</x:f>
         <x:v>1755000</x:v>
       </x:c>
       <x:c r="AD34" s="20" t="n">
-        <x:f>AD32*Assumptions!$B$63</x:f>
+        <x:f>AD32*Assumptions!$B$64</x:f>
         <x:v>1755000</x:v>
       </x:c>
       <x:c r="AE34" s="20" t="n">
-        <x:f>AE32*Assumptions!$B$63</x:f>
+        <x:f>AE32*Assumptions!$B$64</x:f>
         <x:v>1755000</x:v>
       </x:c>
       <x:c r="AF34" s="20" t="n">
-        <x:f>AF32*Assumptions!$B$63</x:f>
+        <x:f>AF32*Assumptions!$B$64</x:f>
         <x:v>1755000</x:v>
       </x:c>
       <x:c r="AG34" s="20" t="n">
-        <x:f>AG32*Assumptions!$B$63</x:f>
+        <x:f>AG32*Assumptions!$B$64</x:f>
         <x:v>1755000</x:v>
       </x:c>
       <x:c r="AH34" s="20" t="n">
-        <x:f>AH32*Assumptions!$B$63</x:f>
+        <x:f>AH32*Assumptions!$B$64</x:f>
         <x:v>1755000</x:v>
       </x:c>
       <x:c r="AI34" s="20" t="n">
-        <x:f>AI32*Assumptions!$B$63</x:f>
+        <x:f>AI32*Assumptions!$B$64</x:f>
         <x:v>1755000</x:v>
       </x:c>
       <x:c r="AJ34" s="20" t="n">
-        <x:f>AJ32*Assumptions!$B$63</x:f>
+        <x:f>AJ32*Assumptions!$B$64</x:f>
         <x:v>1755000</x:v>
       </x:c>
       <x:c r="AK34" s="20" t="n">
-        <x:f>AK32*Assumptions!$B$63</x:f>
+        <x:f>AK32*Assumptions!$B$64</x:f>
         <x:v>1755000</x:v>
       </x:c>
     </x:row>
@@ -6877,147 +6897,147 @@
         </x:is>
       </x:c>
       <x:c r="B35" s="20" t="n">
-        <x:f>IF(B$30=Assumptions!$B$14,Assumptions!$B$66,0)+IF(B$30=Assumptions!$B$16,Assumptions!$B$67,0)</x:f>
+        <x:f>IF(B$30=Assumptions!$B$14,Assumptions!$B$67,0)+IF(B$30=Assumptions!$B$16,Assumptions!$B$68,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C35" s="20" t="n">
-        <x:f>IF(C$30=Assumptions!$B$14,Assumptions!$B$66,0)+IF(C$30=Assumptions!$B$16,Assumptions!$B$67,0)</x:f>
+        <x:f>IF(C$30=Assumptions!$B$14,Assumptions!$B$67,0)+IF(C$30=Assumptions!$B$16,Assumptions!$B$68,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D35" s="20" t="n">
-        <x:f>IF(D$30=Assumptions!$B$14,Assumptions!$B$66,0)+IF(D$30=Assumptions!$B$16,Assumptions!$B$67,0)</x:f>
+        <x:f>IF(D$30=Assumptions!$B$14,Assumptions!$B$67,0)+IF(D$30=Assumptions!$B$16,Assumptions!$B$68,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="E35" s="20" t="n">
-        <x:f>IF(E$30=Assumptions!$B$14,Assumptions!$B$66,0)+IF(E$30=Assumptions!$B$16,Assumptions!$B$67,0)</x:f>
+        <x:f>IF(E$30=Assumptions!$B$14,Assumptions!$B$67,0)+IF(E$30=Assumptions!$B$16,Assumptions!$B$68,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="F35" s="20" t="n">
-        <x:f>IF(F$30=Assumptions!$B$14,Assumptions!$B$66,0)+IF(F$30=Assumptions!$B$16,Assumptions!$B$67,0)</x:f>
+        <x:f>IF(F$30=Assumptions!$B$14,Assumptions!$B$67,0)+IF(F$30=Assumptions!$B$16,Assumptions!$B$68,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="G35" s="20" t="n">
-        <x:f>IF(G$30=Assumptions!$B$14,Assumptions!$B$66,0)+IF(G$30=Assumptions!$B$16,Assumptions!$B$67,0)</x:f>
+        <x:f>IF(G$30=Assumptions!$B$14,Assumptions!$B$67,0)+IF(G$30=Assumptions!$B$16,Assumptions!$B$68,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="H35" s="20" t="n">
-        <x:f>IF(H$30=Assumptions!$B$14,Assumptions!$B$66,0)+IF(H$30=Assumptions!$B$16,Assumptions!$B$67,0)</x:f>
+        <x:f>IF(H$30=Assumptions!$B$14,Assumptions!$B$67,0)+IF(H$30=Assumptions!$B$16,Assumptions!$B$68,0)</x:f>
         <x:v>6000000</x:v>
       </x:c>
       <x:c r="I35" s="20" t="n">
-        <x:f>IF(I$30=Assumptions!$B$14,Assumptions!$B$66,0)+IF(I$30=Assumptions!$B$16,Assumptions!$B$67,0)</x:f>
+        <x:f>IF(I$30=Assumptions!$B$14,Assumptions!$B$67,0)+IF(I$30=Assumptions!$B$16,Assumptions!$B$68,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J35" s="20" t="n">
-        <x:f>IF(J$30=Assumptions!$B$14,Assumptions!$B$66,0)+IF(J$30=Assumptions!$B$16,Assumptions!$B$67,0)</x:f>
+        <x:f>IF(J$30=Assumptions!$B$14,Assumptions!$B$67,0)+IF(J$30=Assumptions!$B$16,Assumptions!$B$68,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K35" s="20" t="n">
-        <x:f>IF(K$30=Assumptions!$B$14,Assumptions!$B$66,0)+IF(K$30=Assumptions!$B$16,Assumptions!$B$67,0)</x:f>
+        <x:f>IF(K$30=Assumptions!$B$14,Assumptions!$B$67,0)+IF(K$30=Assumptions!$B$16,Assumptions!$B$68,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="L35" s="20" t="n">
-        <x:f>IF(L$30=Assumptions!$B$14,Assumptions!$B$66,0)+IF(L$30=Assumptions!$B$16,Assumptions!$B$67,0)</x:f>
+        <x:f>IF(L$30=Assumptions!$B$14,Assumptions!$B$67,0)+IF(L$30=Assumptions!$B$16,Assumptions!$B$68,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M35" s="20" t="n">
-        <x:f>IF(M$30=Assumptions!$B$14,Assumptions!$B$66,0)+IF(M$30=Assumptions!$B$16,Assumptions!$B$67,0)</x:f>
+        <x:f>IF(M$30=Assumptions!$B$14,Assumptions!$B$67,0)+IF(M$30=Assumptions!$B$16,Assumptions!$B$68,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="N35" s="20" t="n">
-        <x:f>IF(N$30=Assumptions!$B$14,Assumptions!$B$66,0)+IF(N$30=Assumptions!$B$16,Assumptions!$B$67,0)</x:f>
+        <x:f>IF(N$30=Assumptions!$B$14,Assumptions!$B$67,0)+IF(N$30=Assumptions!$B$16,Assumptions!$B$68,0)</x:f>
         <x:v>9000000</x:v>
       </x:c>
       <x:c r="O35" s="20" t="n">
-        <x:f>IF(O$30=Assumptions!$B$14,Assumptions!$B$66,0)+IF(O$30=Assumptions!$B$16,Assumptions!$B$67,0)</x:f>
+        <x:f>IF(O$30=Assumptions!$B$14,Assumptions!$B$67,0)+IF(O$30=Assumptions!$B$16,Assumptions!$B$68,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="P35" s="20" t="n">
-        <x:f>IF(P$30=Assumptions!$B$14,Assumptions!$B$66,0)+IF(P$30=Assumptions!$B$16,Assumptions!$B$67,0)</x:f>
+        <x:f>IF(P$30=Assumptions!$B$14,Assumptions!$B$67,0)+IF(P$30=Assumptions!$B$16,Assumptions!$B$68,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q35" s="20" t="n">
-        <x:f>IF(Q$30=Assumptions!$B$14,Assumptions!$B$66,0)+IF(Q$30=Assumptions!$B$16,Assumptions!$B$67,0)</x:f>
+        <x:f>IF(Q$30=Assumptions!$B$14,Assumptions!$B$67,0)+IF(Q$30=Assumptions!$B$16,Assumptions!$B$68,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="R35" s="20" t="n">
-        <x:f>IF(R$30=Assumptions!$B$14,Assumptions!$B$66,0)+IF(R$30=Assumptions!$B$16,Assumptions!$B$67,0)</x:f>
+        <x:f>IF(R$30=Assumptions!$B$14,Assumptions!$B$67,0)+IF(R$30=Assumptions!$B$16,Assumptions!$B$68,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="S35" s="20" t="n">
-        <x:f>IF(S$30=Assumptions!$B$14,Assumptions!$B$66,0)+IF(S$30=Assumptions!$B$16,Assumptions!$B$67,0)</x:f>
+        <x:f>IF(S$30=Assumptions!$B$14,Assumptions!$B$67,0)+IF(S$30=Assumptions!$B$16,Assumptions!$B$68,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="T35" s="20" t="n">
-        <x:f>IF(T$30=Assumptions!$B$14,Assumptions!$B$66,0)+IF(T$30=Assumptions!$B$16,Assumptions!$B$67,0)</x:f>
+        <x:f>IF(T$30=Assumptions!$B$14,Assumptions!$B$67,0)+IF(T$30=Assumptions!$B$16,Assumptions!$B$68,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="U35" s="20" t="n">
-        <x:f>IF(U$30=Assumptions!$B$14,Assumptions!$B$66,0)+IF(U$30=Assumptions!$B$16,Assumptions!$B$67,0)</x:f>
+        <x:f>IF(U$30=Assumptions!$B$14,Assumptions!$B$67,0)+IF(U$30=Assumptions!$B$16,Assumptions!$B$68,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="V35" s="20" t="n">
-        <x:f>IF(V$30=Assumptions!$B$14,Assumptions!$B$66,0)+IF(V$30=Assumptions!$B$16,Assumptions!$B$67,0)</x:f>
+        <x:f>IF(V$30=Assumptions!$B$14,Assumptions!$B$67,0)+IF(V$30=Assumptions!$B$16,Assumptions!$B$68,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="W35" s="20" t="n">
-        <x:f>IF(W$30=Assumptions!$B$14,Assumptions!$B$66,0)+IF(W$30=Assumptions!$B$16,Assumptions!$B$67,0)</x:f>
+        <x:f>IF(W$30=Assumptions!$B$14,Assumptions!$B$67,0)+IF(W$30=Assumptions!$B$16,Assumptions!$B$68,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="X35" s="20" t="n">
-        <x:f>IF(X$30=Assumptions!$B$14,Assumptions!$B$66,0)+IF(X$30=Assumptions!$B$16,Assumptions!$B$67,0)</x:f>
+        <x:f>IF(X$30=Assumptions!$B$14,Assumptions!$B$67,0)+IF(X$30=Assumptions!$B$16,Assumptions!$B$68,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="Y35" s="20" t="n">
-        <x:f>IF(Y$30=Assumptions!$B$14,Assumptions!$B$66,0)+IF(Y$30=Assumptions!$B$16,Assumptions!$B$67,0)</x:f>
+        <x:f>IF(Y$30=Assumptions!$B$14,Assumptions!$B$67,0)+IF(Y$30=Assumptions!$B$16,Assumptions!$B$68,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="Z35" s="20" t="n">
-        <x:f>IF(Z$30=Assumptions!$B$14,Assumptions!$B$66,0)+IF(Z$30=Assumptions!$B$16,Assumptions!$B$67,0)</x:f>
+        <x:f>IF(Z$30=Assumptions!$B$14,Assumptions!$B$67,0)+IF(Z$30=Assumptions!$B$16,Assumptions!$B$68,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AA35" s="20" t="n">
-        <x:f>IF(AA$30=Assumptions!$B$14,Assumptions!$B$66,0)+IF(AA$30=Assumptions!$B$16,Assumptions!$B$67,0)</x:f>
+        <x:f>IF(AA$30=Assumptions!$B$14,Assumptions!$B$67,0)+IF(AA$30=Assumptions!$B$16,Assumptions!$B$68,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AB35" s="20" t="n">
-        <x:f>IF(AB$30=Assumptions!$B$14,Assumptions!$B$66,0)+IF(AB$30=Assumptions!$B$16,Assumptions!$B$67,0)</x:f>
+        <x:f>IF(AB$30=Assumptions!$B$14,Assumptions!$B$67,0)+IF(AB$30=Assumptions!$B$16,Assumptions!$B$68,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AC35" s="20" t="n">
-        <x:f>IF(AC$30=Assumptions!$B$14,Assumptions!$B$66,0)+IF(AC$30=Assumptions!$B$16,Assumptions!$B$67,0)</x:f>
+        <x:f>IF(AC$30=Assumptions!$B$14,Assumptions!$B$67,0)+IF(AC$30=Assumptions!$B$16,Assumptions!$B$68,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AD35" s="20" t="n">
-        <x:f>IF(AD$30=Assumptions!$B$14,Assumptions!$B$66,0)+IF(AD$30=Assumptions!$B$16,Assumptions!$B$67,0)</x:f>
+        <x:f>IF(AD$30=Assumptions!$B$14,Assumptions!$B$67,0)+IF(AD$30=Assumptions!$B$16,Assumptions!$B$68,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AE35" s="20" t="n">
-        <x:f>IF(AE$30=Assumptions!$B$14,Assumptions!$B$66,0)+IF(AE$30=Assumptions!$B$16,Assumptions!$B$67,0)</x:f>
+        <x:f>IF(AE$30=Assumptions!$B$14,Assumptions!$B$67,0)+IF(AE$30=Assumptions!$B$16,Assumptions!$B$68,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AF35" s="20" t="n">
-        <x:f>IF(AF$30=Assumptions!$B$14,Assumptions!$B$66,0)+IF(AF$30=Assumptions!$B$16,Assumptions!$B$67,0)</x:f>
+        <x:f>IF(AF$30=Assumptions!$B$14,Assumptions!$B$67,0)+IF(AF$30=Assumptions!$B$16,Assumptions!$B$68,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AG35" s="20" t="n">
-        <x:f>IF(AG$30=Assumptions!$B$14,Assumptions!$B$66,0)+IF(AG$30=Assumptions!$B$16,Assumptions!$B$67,0)</x:f>
+        <x:f>IF(AG$30=Assumptions!$B$14,Assumptions!$B$67,0)+IF(AG$30=Assumptions!$B$16,Assumptions!$B$68,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AH35" s="20" t="n">
-        <x:f>IF(AH$30=Assumptions!$B$14,Assumptions!$B$66,0)+IF(AH$30=Assumptions!$B$16,Assumptions!$B$67,0)</x:f>
+        <x:f>IF(AH$30=Assumptions!$B$14,Assumptions!$B$67,0)+IF(AH$30=Assumptions!$B$16,Assumptions!$B$68,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AI35" s="20" t="n">
-        <x:f>IF(AI$30=Assumptions!$B$14,Assumptions!$B$66,0)+IF(AI$30=Assumptions!$B$16,Assumptions!$B$67,0)</x:f>
+        <x:f>IF(AI$30=Assumptions!$B$14,Assumptions!$B$67,0)+IF(AI$30=Assumptions!$B$16,Assumptions!$B$68,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AJ35" s="20" t="n">
-        <x:f>IF(AJ$30=Assumptions!$B$14,Assumptions!$B$66,0)+IF(AJ$30=Assumptions!$B$16,Assumptions!$B$67,0)</x:f>
+        <x:f>IF(AJ$30=Assumptions!$B$14,Assumptions!$B$67,0)+IF(AJ$30=Assumptions!$B$16,Assumptions!$B$68,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AK35" s="20" t="n">
-        <x:f>IF(AK$30=Assumptions!$B$14,Assumptions!$B$66,0)+IF(AK$30=Assumptions!$B$16,Assumptions!$B$67,0)</x:f>
+        <x:f>IF(AK$30=Assumptions!$B$14,Assumptions!$B$67,0)+IF(AK$30=Assumptions!$B$16,Assumptions!$B$68,0)</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -7343,135 +7363,135 @@
       </x:c>
       <x:c r="E38" s="33" t="n">
         <x:f>Run!E21</x:f>
-        <x:v>903891.9648</x:v>
+        <x:v>877676.386112</x:v>
       </x:c>
       <x:c r="F38" s="33" t="n">
         <x:f>Run!F21</x:f>
-        <x:v>903891.9648</x:v>
+        <x:v>877676.386112</x:v>
       </x:c>
       <x:c r="G38" s="33" t="n">
         <x:f>Run!G21</x:f>
-        <x:v>903891.9648</x:v>
+        <x:v>877676.386112</x:v>
       </x:c>
       <x:c r="H38" s="33" t="n">
         <x:f>Run!H21</x:f>
-        <x:v>1098169.4208</x:v>
+        <x:v>1039184.368752</x:v>
       </x:c>
       <x:c r="I38" s="33" t="n">
         <x:f>Run!I21</x:f>
-        <x:v>1098169.4208</x:v>
+        <x:v>1039184.368752</x:v>
       </x:c>
       <x:c r="J38" s="33" t="n">
         <x:f>Run!J21</x:f>
-        <x:v>1098169.4208</x:v>
+        <x:v>1039184.368752</x:v>
       </x:c>
       <x:c r="K38" s="33" t="n">
         <x:f>Run!K21</x:f>
-        <x:v>1098169.4208</x:v>
+        <x:v>1039184.368752</x:v>
       </x:c>
       <x:c r="L38" s="33" t="n">
         <x:f>Run!L21</x:f>
-        <x:v>1098169.4208</x:v>
+        <x:v>1039184.368752</x:v>
       </x:c>
       <x:c r="M38" s="33" t="n">
         <x:f>Run!M21</x:f>
-        <x:v>1098169.4208</x:v>
+        <x:v>1039184.368752</x:v>
       </x:c>
       <x:c r="N38" s="33" t="n">
         <x:f>Run!N21</x:f>
-        <x:v>1272742.368</x:v>
+        <x:v>1174433.94792</x:v>
       </x:c>
       <x:c r="O38" s="33" t="n">
         <x:f>Run!O21</x:f>
-        <x:v>1272742.368</x:v>
+        <x:v>1174433.94792</x:v>
       </x:c>
       <x:c r="P38" s="33" t="n">
         <x:f>Run!P21</x:f>
-        <x:v>1272742.368</x:v>
+        <x:v>1174433.94792</x:v>
       </x:c>
       <x:c r="Q38" s="33" t="n">
         <x:f>Run!Q21</x:f>
-        <x:v>1272742.368</x:v>
+        <x:v>1174433.94792</x:v>
       </x:c>
       <x:c r="R38" s="33" t="n">
         <x:f>Run!R21</x:f>
-        <x:v>1272742.368</x:v>
+        <x:v>1174433.94792</x:v>
       </x:c>
       <x:c r="S38" s="33" t="n">
         <x:f>Run!S21</x:f>
-        <x:v>1272742.368</x:v>
+        <x:v>1174433.94792</x:v>
       </x:c>
       <x:c r="T38" s="33" t="n">
         <x:f>Run!T21</x:f>
-        <x:v>1272742.368</x:v>
+        <x:v>1174433.94792</x:v>
       </x:c>
       <x:c r="U38" s="33" t="n">
         <x:f>Run!U21</x:f>
-        <x:v>1272742.368</x:v>
+        <x:v>1174433.94792</x:v>
       </x:c>
       <x:c r="V38" s="33" t="n">
         <x:f>Run!V21</x:f>
-        <x:v>1272742.368</x:v>
+        <x:v>1174433.94792</x:v>
       </x:c>
       <x:c r="W38" s="33" t="n">
         <x:f>Run!W21</x:f>
-        <x:v>1272742.368</x:v>
+        <x:v>1174433.94792</x:v>
       </x:c>
       <x:c r="X38" s="33" t="n">
         <x:f>Run!X21</x:f>
-        <x:v>1272742.368</x:v>
+        <x:v>1174433.94792</x:v>
       </x:c>
       <x:c r="Y38" s="33" t="n">
         <x:f>Run!Y21</x:f>
-        <x:v>1272742.368</x:v>
+        <x:v>1174433.94792</x:v>
       </x:c>
       <x:c r="Z38" s="33" t="n">
         <x:f>Run!Z21</x:f>
-        <x:v>1272742.368</x:v>
+        <x:v>1174433.94792</x:v>
       </x:c>
       <x:c r="AA38" s="33" t="n">
         <x:f>Run!AA21</x:f>
-        <x:v>1272742.368</x:v>
+        <x:v>1174433.94792</x:v>
       </x:c>
       <x:c r="AB38" s="33" t="n">
         <x:f>Run!AB21</x:f>
-        <x:v>1272742.368</x:v>
+        <x:v>1174433.94792</x:v>
       </x:c>
       <x:c r="AC38" s="33" t="n">
         <x:f>Run!AC21</x:f>
-        <x:v>1272742.368</x:v>
+        <x:v>1174433.94792</x:v>
       </x:c>
       <x:c r="AD38" s="33" t="n">
         <x:f>Run!AD21</x:f>
-        <x:v>1272742.368</x:v>
+        <x:v>1174433.94792</x:v>
       </x:c>
       <x:c r="AE38" s="33" t="n">
         <x:f>Run!AE21</x:f>
-        <x:v>1272742.368</x:v>
+        <x:v>1174433.94792</x:v>
       </x:c>
       <x:c r="AF38" s="33" t="n">
         <x:f>Run!AF21</x:f>
-        <x:v>1272742.368</x:v>
+        <x:v>1174433.94792</x:v>
       </x:c>
       <x:c r="AG38" s="33" t="n">
         <x:f>Run!AG21</x:f>
-        <x:v>1272742.368</x:v>
+        <x:v>1174433.94792</x:v>
       </x:c>
       <x:c r="AH38" s="33" t="n">
         <x:f>Run!AH21</x:f>
-        <x:v>1272742.368</x:v>
+        <x:v>1174433.94792</x:v>
       </x:c>
       <x:c r="AI38" s="33" t="n">
         <x:f>Run!AI21</x:f>
-        <x:v>1272742.368</x:v>
+        <x:v>1174433.94792</x:v>
       </x:c>
       <x:c r="AJ38" s="33" t="n">
         <x:f>Run!AJ21</x:f>
-        <x:v>1272742.368</x:v>
+        <x:v>1174433.94792</x:v>
       </x:c>
       <x:c r="AK38" s="33" t="n">
         <x:f>Run!AK21</x:f>
-        <x:v>1272742.368</x:v>
+        <x:v>1174433.94792</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
@@ -7481,147 +7501,147 @@
         </x:is>
       </x:c>
       <x:c r="B39" s="20" t="n">
-        <x:f>B35*Assumptions!$B$68</x:f>
+        <x:f>B35*Assumptions!$B$69</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C39" s="20" t="n">
-        <x:f>C35*Assumptions!$B$68</x:f>
+        <x:f>C35*Assumptions!$B$69</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D39" s="20" t="n">
-        <x:f>D35*Assumptions!$B$68</x:f>
+        <x:f>D35*Assumptions!$B$69</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="E39" s="20" t="n">
-        <x:f>E35*Assumptions!$B$68</x:f>
+        <x:f>E35*Assumptions!$B$69</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="F39" s="20" t="n">
-        <x:f>F35*Assumptions!$B$68</x:f>
+        <x:f>F35*Assumptions!$B$69</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="G39" s="20" t="n">
-        <x:f>G35*Assumptions!$B$68</x:f>
+        <x:f>G35*Assumptions!$B$69</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="H39" s="20" t="n">
-        <x:f>H35*Assumptions!$B$68</x:f>
+        <x:f>H35*Assumptions!$B$69</x:f>
         <x:v>3000000</x:v>
       </x:c>
       <x:c r="I39" s="20" t="n">
-        <x:f>I35*Assumptions!$B$68</x:f>
+        <x:f>I35*Assumptions!$B$69</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J39" s="20" t="n">
-        <x:f>J35*Assumptions!$B$68</x:f>
+        <x:f>J35*Assumptions!$B$69</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K39" s="20" t="n">
-        <x:f>K35*Assumptions!$B$68</x:f>
+        <x:f>K35*Assumptions!$B$69</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="L39" s="20" t="n">
-        <x:f>L35*Assumptions!$B$68</x:f>
+        <x:f>L35*Assumptions!$B$69</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M39" s="20" t="n">
-        <x:f>M35*Assumptions!$B$68</x:f>
+        <x:f>M35*Assumptions!$B$69</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="N39" s="20" t="n">
-        <x:f>N35*Assumptions!$B$68</x:f>
+        <x:f>N35*Assumptions!$B$69</x:f>
         <x:v>4500000</x:v>
       </x:c>
       <x:c r="O39" s="20" t="n">
-        <x:f>O35*Assumptions!$B$68</x:f>
+        <x:f>O35*Assumptions!$B$69</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="P39" s="20" t="n">
-        <x:f>P35*Assumptions!$B$68</x:f>
+        <x:f>P35*Assumptions!$B$69</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q39" s="20" t="n">
-        <x:f>Q35*Assumptions!$B$68</x:f>
+        <x:f>Q35*Assumptions!$B$69</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="R39" s="20" t="n">
-        <x:f>R35*Assumptions!$B$68</x:f>
+        <x:f>R35*Assumptions!$B$69</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="S39" s="20" t="n">
-        <x:f>S35*Assumptions!$B$68</x:f>
+        <x:f>S35*Assumptions!$B$69</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="T39" s="20" t="n">
-        <x:f>T35*Assumptions!$B$68</x:f>
+        <x:f>T35*Assumptions!$B$69</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="U39" s="20" t="n">
-        <x:f>U35*Assumptions!$B$68</x:f>
+        <x:f>U35*Assumptions!$B$69</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="V39" s="20" t="n">
-        <x:f>V35*Assumptions!$B$68</x:f>
+        <x:f>V35*Assumptions!$B$69</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="W39" s="20" t="n">
-        <x:f>W35*Assumptions!$B$68</x:f>
+        <x:f>W35*Assumptions!$B$69</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="X39" s="20" t="n">
-        <x:f>X35*Assumptions!$B$68</x:f>
+        <x:f>X35*Assumptions!$B$69</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="Y39" s="20" t="n">
-        <x:f>Y35*Assumptions!$B$68</x:f>
+        <x:f>Y35*Assumptions!$B$69</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="Z39" s="20" t="n">
-        <x:f>Z35*Assumptions!$B$68</x:f>
+        <x:f>Z35*Assumptions!$B$69</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AA39" s="20" t="n">
-        <x:f>AA35*Assumptions!$B$68</x:f>
+        <x:f>AA35*Assumptions!$B$69</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AB39" s="20" t="n">
-        <x:f>AB35*Assumptions!$B$68</x:f>
+        <x:f>AB35*Assumptions!$B$69</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AC39" s="20" t="n">
-        <x:f>AC35*Assumptions!$B$68</x:f>
+        <x:f>AC35*Assumptions!$B$69</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AD39" s="20" t="n">
-        <x:f>AD35*Assumptions!$B$68</x:f>
+        <x:f>AD35*Assumptions!$B$69</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AE39" s="20" t="n">
-        <x:f>AE35*Assumptions!$B$68</x:f>
+        <x:f>AE35*Assumptions!$B$69</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AF39" s="20" t="n">
-        <x:f>AF35*Assumptions!$B$68</x:f>
+        <x:f>AF35*Assumptions!$B$69</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AG39" s="20" t="n">
-        <x:f>AG35*Assumptions!$B$68</x:f>
+        <x:f>AG35*Assumptions!$B$69</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AH39" s="20" t="n">
-        <x:f>AH35*Assumptions!$B$68</x:f>
+        <x:f>AH35*Assumptions!$B$69</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AI39" s="20" t="n">
-        <x:f>AI35*Assumptions!$B$68</x:f>
+        <x:f>AI35*Assumptions!$B$69</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AJ39" s="20" t="n">
-        <x:f>AJ35*Assumptions!$B$68</x:f>
+        <x:f>AJ35*Assumptions!$B$69</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AK39" s="20" t="n">
-        <x:f>AK35*Assumptions!$B$68</x:f>
+        <x:f>AK35*Assumptions!$B$69</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -7645,135 +7665,135 @@
       </x:c>
       <x:c r="E40" s="20" t="n">
         <x:f>SUM(E37:E39)</x:f>
-        <x:v>903891.9648</x:v>
+        <x:v>877676.386112</x:v>
       </x:c>
       <x:c r="F40" s="20" t="n">
         <x:f>SUM(F37:F39)</x:f>
-        <x:v>903891.9648</x:v>
+        <x:v>877676.386112</x:v>
       </x:c>
       <x:c r="G40" s="20" t="n">
         <x:f>SUM(G37:G39)</x:f>
-        <x:v>903891.9648</x:v>
+        <x:v>877676.386112</x:v>
       </x:c>
       <x:c r="H40" s="20" t="n">
         <x:f>SUM(H37:H39)</x:f>
-        <x:v>4098169.4208</x:v>
+        <x:v>4039184.368752</x:v>
       </x:c>
       <x:c r="I40" s="20" t="n">
         <x:f>SUM(I37:I39)</x:f>
-        <x:v>1098169.4208</x:v>
+        <x:v>1039184.368752</x:v>
       </x:c>
       <x:c r="J40" s="20" t="n">
         <x:f>SUM(J37:J39)</x:f>
-        <x:v>1098169.4208</x:v>
+        <x:v>1039184.368752</x:v>
       </x:c>
       <x:c r="K40" s="20" t="n">
         <x:f>SUM(K37:K39)</x:f>
-        <x:v>1098169.4208</x:v>
+        <x:v>1039184.368752</x:v>
       </x:c>
       <x:c r="L40" s="20" t="n">
         <x:f>SUM(L37:L39)</x:f>
-        <x:v>1098169.4208</x:v>
+        <x:v>1039184.368752</x:v>
       </x:c>
       <x:c r="M40" s="20" t="n">
         <x:f>SUM(M37:M39)</x:f>
-        <x:v>1098169.4208</x:v>
+        <x:v>1039184.368752</x:v>
       </x:c>
       <x:c r="N40" s="20" t="n">
         <x:f>SUM(N37:N39)</x:f>
-        <x:v>5772742.368</x:v>
+        <x:v>5674433.94792</x:v>
       </x:c>
       <x:c r="O40" s="20" t="n">
         <x:f>SUM(O37:O39)</x:f>
-        <x:v>1272742.368</x:v>
+        <x:v>1174433.94792</x:v>
       </x:c>
       <x:c r="P40" s="20" t="n">
         <x:f>SUM(P37:P39)</x:f>
-        <x:v>1272742.368</x:v>
+        <x:v>1174433.94792</x:v>
       </x:c>
       <x:c r="Q40" s="20" t="n">
         <x:f>SUM(Q37:Q39)</x:f>
-        <x:v>1272742.368</x:v>
+        <x:v>1174433.94792</x:v>
       </x:c>
       <x:c r="R40" s="20" t="n">
         <x:f>SUM(R37:R39)</x:f>
-        <x:v>1272742.368</x:v>
+        <x:v>1174433.94792</x:v>
       </x:c>
       <x:c r="S40" s="20" t="n">
         <x:f>SUM(S37:S39)</x:f>
-        <x:v>1272742.368</x:v>
+        <x:v>1174433.94792</x:v>
       </x:c>
       <x:c r="T40" s="20" t="n">
         <x:f>SUM(T37:T39)</x:f>
-        <x:v>1272742.368</x:v>
+        <x:v>1174433.94792</x:v>
       </x:c>
       <x:c r="U40" s="20" t="n">
         <x:f>SUM(U37:U39)</x:f>
-        <x:v>1272742.368</x:v>
+        <x:v>1174433.94792</x:v>
       </x:c>
       <x:c r="V40" s="20" t="n">
         <x:f>SUM(V37:V39)</x:f>
-        <x:v>1272742.368</x:v>
+        <x:v>1174433.94792</x:v>
       </x:c>
       <x:c r="W40" s="20" t="n">
         <x:f>SUM(W37:W39)</x:f>
-        <x:v>1272742.368</x:v>
+        <x:v>1174433.94792</x:v>
       </x:c>
       <x:c r="X40" s="20" t="n">
         <x:f>SUM(X37:X39)</x:f>
-        <x:v>1272742.368</x:v>
+        <x:v>1174433.94792</x:v>
       </x:c>
       <x:c r="Y40" s="20" t="n">
         <x:f>SUM(Y37:Y39)</x:f>
-        <x:v>1272742.368</x:v>
+        <x:v>1174433.94792</x:v>
       </x:c>
       <x:c r="Z40" s="20" t="n">
         <x:f>SUM(Z37:Z39)</x:f>
-        <x:v>1272742.368</x:v>
+        <x:v>1174433.94792</x:v>
       </x:c>
       <x:c r="AA40" s="20" t="n">
         <x:f>SUM(AA37:AA39)</x:f>
-        <x:v>1272742.368</x:v>
+        <x:v>1174433.94792</x:v>
       </x:c>
       <x:c r="AB40" s="20" t="n">
         <x:f>SUM(AB37:AB39)</x:f>
-        <x:v>1272742.368</x:v>
+        <x:v>1174433.94792</x:v>
       </x:c>
       <x:c r="AC40" s="20" t="n">
         <x:f>SUM(AC37:AC39)</x:f>
-        <x:v>1272742.368</x:v>
+        <x:v>1174433.94792</x:v>
       </x:c>
       <x:c r="AD40" s="20" t="n">
         <x:f>SUM(AD37:AD39)</x:f>
-        <x:v>1272742.368</x:v>
+        <x:v>1174433.94792</x:v>
       </x:c>
       <x:c r="AE40" s="20" t="n">
         <x:f>SUM(AE37:AE39)</x:f>
-        <x:v>1272742.368</x:v>
+        <x:v>1174433.94792</x:v>
       </x:c>
       <x:c r="AF40" s="20" t="n">
         <x:f>SUM(AF37:AF39)</x:f>
-        <x:v>1272742.368</x:v>
+        <x:v>1174433.94792</x:v>
       </x:c>
       <x:c r="AG40" s="20" t="n">
         <x:f>SUM(AG37:AG39)</x:f>
-        <x:v>1272742.368</x:v>
+        <x:v>1174433.94792</x:v>
       </x:c>
       <x:c r="AH40" s="20" t="n">
         <x:f>SUM(AH37:AH39)</x:f>
-        <x:v>1272742.368</x:v>
+        <x:v>1174433.94792</x:v>
       </x:c>
       <x:c r="AI40" s="20" t="n">
         <x:f>SUM(AI37:AI39)</x:f>
-        <x:v>1272742.368</x:v>
+        <x:v>1174433.94792</x:v>
       </x:c>
       <x:c r="AJ40" s="20" t="n">
         <x:f>SUM(AJ37:AJ39)</x:f>
-        <x:v>1272742.368</x:v>
+        <x:v>1174433.94792</x:v>
       </x:c>
       <x:c r="AK40" s="20" t="n">
         <x:f>SUM(AK37:AK39)</x:f>
-        <x:v>1272742.368</x:v>
+        <x:v>1174433.94792</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
@@ -7796,135 +7816,135 @@
       </x:c>
       <x:c r="E41" s="22" t="n">
         <x:f>E36-E40</x:f>
-        <x:v>-435891.96479999996</x:v>
+        <x:v>-409676.386112</x:v>
       </x:c>
       <x:c r="F41" s="22" t="n">
         <x:f>F36-F40</x:f>
-        <x:v>-435891.96479999996</x:v>
+        <x:v>-409676.386112</x:v>
       </x:c>
       <x:c r="G41" s="22" t="n">
         <x:f>G36-G40</x:f>
-        <x:v>-435891.96479999996</x:v>
+        <x:v>-409676.386112</x:v>
       </x:c>
       <x:c r="H41" s="22" t="n">
         <x:f>H36-H40</x:f>
-        <x:v>2954830.5792</x:v>
+        <x:v>3013815.631248</x:v>
       </x:c>
       <x:c r="I41" s="22" t="n">
         <x:f>I36-I40</x:f>
-        <x:v>-45169.42079999996</x:v>
+        <x:v>13815.631247999961</x:v>
       </x:c>
       <x:c r="J41" s="22" t="n">
         <x:f>J36-J40</x:f>
-        <x:v>-45169.42079999996</x:v>
+        <x:v>13815.631247999961</x:v>
       </x:c>
       <x:c r="K41" s="22" t="n">
         <x:f>K36-K40</x:f>
-        <x:v>-45169.42079999996</x:v>
+        <x:v>13815.631247999961</x:v>
       </x:c>
       <x:c r="L41" s="22" t="n">
         <x:f>L36-L40</x:f>
-        <x:v>-45169.42079999996</x:v>
+        <x:v>13815.631247999961</x:v>
       </x:c>
       <x:c r="M41" s="22" t="n">
         <x:f>M36-M40</x:f>
-        <x:v>-45169.42079999996</x:v>
+        <x:v>13815.631247999961</x:v>
       </x:c>
       <x:c r="N41" s="22" t="n">
         <x:f>N36-N40</x:f>
-        <x:v>4982257.632</x:v>
+        <x:v>5080566.05208</x:v>
       </x:c>
       <x:c r="O41" s="22" t="n">
         <x:f>O36-O40</x:f>
-        <x:v>482257.632</x:v>
+        <x:v>580566.05208</x:v>
       </x:c>
       <x:c r="P41" s="22" t="n">
         <x:f>P36-P40</x:f>
-        <x:v>482257.632</x:v>
+        <x:v>580566.05208</x:v>
       </x:c>
       <x:c r="Q41" s="22" t="n">
         <x:f>Q36-Q40</x:f>
-        <x:v>482257.632</x:v>
+        <x:v>580566.05208</x:v>
       </x:c>
       <x:c r="R41" s="22" t="n">
         <x:f>R36-R40</x:f>
-        <x:v>482257.632</x:v>
+        <x:v>580566.05208</x:v>
       </x:c>
       <x:c r="S41" s="22" t="n">
         <x:f>S36-S40</x:f>
-        <x:v>482257.632</x:v>
+        <x:v>580566.05208</x:v>
       </x:c>
       <x:c r="T41" s="22" t="n">
         <x:f>T36-T40</x:f>
-        <x:v>482257.632</x:v>
+        <x:v>580566.05208</x:v>
       </x:c>
       <x:c r="U41" s="22" t="n">
         <x:f>U36-U40</x:f>
-        <x:v>482257.632</x:v>
+        <x:v>580566.05208</x:v>
       </x:c>
       <x:c r="V41" s="22" t="n">
         <x:f>V36-V40</x:f>
-        <x:v>482257.632</x:v>
+        <x:v>580566.05208</x:v>
       </x:c>
       <x:c r="W41" s="22" t="n">
         <x:f>W36-W40</x:f>
-        <x:v>482257.632</x:v>
+        <x:v>580566.05208</x:v>
       </x:c>
       <x:c r="X41" s="22" t="n">
         <x:f>X36-X40</x:f>
-        <x:v>482257.632</x:v>
+        <x:v>580566.05208</x:v>
       </x:c>
       <x:c r="Y41" s="22" t="n">
         <x:f>Y36-Y40</x:f>
-        <x:v>482257.632</x:v>
+        <x:v>580566.05208</x:v>
       </x:c>
       <x:c r="Z41" s="22" t="n">
         <x:f>Z36-Z40</x:f>
-        <x:v>482257.632</x:v>
+        <x:v>580566.05208</x:v>
       </x:c>
       <x:c r="AA41" s="22" t="n">
         <x:f>AA36-AA40</x:f>
-        <x:v>482257.632</x:v>
+        <x:v>580566.05208</x:v>
       </x:c>
       <x:c r="AB41" s="22" t="n">
         <x:f>AB36-AB40</x:f>
-        <x:v>482257.632</x:v>
+        <x:v>580566.05208</x:v>
       </x:c>
       <x:c r="AC41" s="22" t="n">
         <x:f>AC36-AC40</x:f>
-        <x:v>482257.632</x:v>
+        <x:v>580566.05208</x:v>
       </x:c>
       <x:c r="AD41" s="22" t="n">
         <x:f>AD36-AD40</x:f>
-        <x:v>482257.632</x:v>
+        <x:v>580566.05208</x:v>
       </x:c>
       <x:c r="AE41" s="22" t="n">
         <x:f>AE36-AE40</x:f>
-        <x:v>482257.632</x:v>
+        <x:v>580566.05208</x:v>
       </x:c>
       <x:c r="AF41" s="22" t="n">
         <x:f>AF36-AF40</x:f>
-        <x:v>482257.632</x:v>
+        <x:v>580566.05208</x:v>
       </x:c>
       <x:c r="AG41" s="22" t="n">
         <x:f>AG36-AG40</x:f>
-        <x:v>482257.632</x:v>
+        <x:v>580566.05208</x:v>
       </x:c>
       <x:c r="AH41" s="22" t="n">
         <x:f>AH36-AH40</x:f>
-        <x:v>482257.632</x:v>
+        <x:v>580566.05208</x:v>
       </x:c>
       <x:c r="AI41" s="22" t="n">
         <x:f>AI36-AI40</x:f>
-        <x:v>482257.632</x:v>
+        <x:v>580566.05208</x:v>
       </x:c>
       <x:c r="AJ41" s="22" t="n">
         <x:f>AJ36-AJ40</x:f>
-        <x:v>482257.632</x:v>
+        <x:v>580566.05208</x:v>
       </x:c>
       <x:c r="AK41" s="22" t="n">
         <x:f>AK36-AK40</x:f>
-        <x:v>482257.632</x:v>
+        <x:v>580566.05208</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -7937,8 +7957,8 @@
   <x:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="44" customWidth="1"/>
-    <x:col min="2" max="2" width="22" customWidth="1"/>
-    <x:col min="3" max="3" width="22" customWidth="1"/>
+    <x:col min="2" max="2" width="28" customWidth="1"/>
+    <x:col min="3" max="3" width="30" customWidth="1"/>
     <x:col min="4" max="4" width="60" customWidth="1"/>
   </x:cols>
   <x:sheetData>
@@ -7964,12 +7984,12 @@
       </x:c>
       <x:c r="B4" s="4" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Sonnet 5.5 coach (base)</x:t>
+          <x:t xml:space="preserve">DeepSeek V4.1 Flash coach (base)</x:t>
         </x:is>
       </x:c>
       <x:c r="C4" s="4" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Opus 5.5 coach</x:t>
+          <x:t xml:space="preserve">Claude Sonnet 5.5 coach (scenario)</x:t>
         </x:is>
       </x:c>
       <x:c r="D4" s="4" t="inlineStr">
@@ -7986,11 +8006,11 @@
       </x:c>
       <x:c r="B5" s="26" t="n">
         <x:f>(Assumptions!$B$22*Assumptions!$B$33+Assumptions!$B$23*Assumptions!$B$35+Assumptions!$B$24*Assumptions!$B$34)/1000000</x:f>
+        <x:v>0.0013872</x:v>
+      </x:c>
+      <x:c r="C5" s="26" t="n">
+        <x:f>(Assumptions!$B$22*Assumptions!$B$36+Assumptions!$B$23*Assumptions!$B$38+Assumptions!$B$24*Assumptions!$B$37)/1000000</x:f>
         <x:v>0.01034</x:v>
-      </x:c>
-      <x:c r="C5" s="26" t="n">
-        <x:f>(Assumptions!$B$22*Assumptions!$B$36+Assumptions!$B$23*Assumptions!$B$35+Assumptions!$B$24*Assumptions!$B$37)/1000000</x:f>
-        <x:v>0.02044</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -8000,12 +8020,12 @@
         </x:is>
       </x:c>
       <x:c r="B6" s="26" t="n">
-        <x:f>(Assumptions!$B$25*Assumptions!$B$38+Assumptions!$B$26*Assumptions!$B$39)/1000000</x:f>
-        <x:v>0.00009</x:v>
+        <x:f>(Assumptions!$B$25*Assumptions!$B$39+Assumptions!$B$26*Assumptions!$B$40)/1000000</x:f>
+        <x:v>0.000246</x:v>
       </x:c>
       <x:c r="C6" s="26" t="n">
         <x:f>B6</x:f>
-        <x:v>0.00009</x:v>
+        <x:v>0.000246</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -8015,12 +8035,12 @@
         </x:is>
       </x:c>
       <x:c r="B7" s="19" t="n">
-        <x:f>(B5+B6)*Assumptions!$B$19*(1+Assumptions!$B$41)*Assumptions!$B$6</x:f>
-        <x:v>5.532071999999999</x:v>
+        <x:f>(B5+B6)*Assumptions!$B$19*(1+Assumptions!$B$42)*Assumptions!$B$6</x:f>
+        <x:v>0.8662492800000001</x:v>
       </x:c>
       <x:c r="C7" s="19" t="n">
-        <x:f>(C5+C6)*Assumptions!$B$19*(1+Assumptions!$B$41)*Assumptions!$B$6</x:f>
-        <x:v>10.889112</x:v>
+        <x:f>(C5+C6)*Assumptions!$B$19*(1+Assumptions!$B$42)*Assumptions!$B$6</x:f>
+        <x:v>5.614814400000001</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -8046,11 +8066,11 @@
       </x:c>
       <x:c r="B9" s="20" t="n">
         <x:f>B7*B8*12</x:f>
-        <x:v>1344293.4959999998</x:v>
+        <x:v>210498.57504000003</x:v>
       </x:c>
       <x:c r="C9" s="20" t="n">
         <x:f>C7*C8*12</x:f>
-        <x:v>2646054.216</x:v>
+        <x:v>1364399.8992000003</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -8061,11 +8081,11 @@
       </x:c>
       <x:c r="B10" s="30" t="n">
         <x:f>B9/(Run!AK21*12)</x:f>
-        <x:v>0.08801817305417146</x:v>
+        <x:v>0.014936172401238268</x:v>
       </x:c>
       <x:c r="C10" s="30" t="n">
         <x:f>C9/(Run!AK21*12-B9+C9)</x:f>
-        <x:v>0.1596444667636109</x:v>
+        <x:v>0.08948581177699541</x:v>
       </x:c>
     </x:row>
     <x:row r="12">

--- a/model/cost-model.xlsx
+++ b/model/cost-model.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="Ra60ce345716c4b80"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="2" r:id="R58f0a5cbce18427b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Build" sheetId="3" r:id="Rb8e6fae0dc7b4c1b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Run" sheetId="4" r:id="R5a736c7c28bb4382"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pricing &amp; P&amp;L" sheetId="5" r:id="Rfcdb21b4062f4009"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AI Cost" sheetId="6" r:id="Rf36a430eb1884d8a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Value" sheetId="7" r:id="R63593f9597a4418b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="Rfe2c898cdbfd408a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="2" r:id="Rf6f144d411214778"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Build" sheetId="3" r:id="R8fcf96f38c9e405b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Run" sheetId="4" r:id="R7bf43dc435b94ecd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pricing &amp; P&amp;L" sheetId="5" r:id="Rdb2520aa654243cb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AI Cost" sheetId="6" r:id="R51ac287b42ea4151"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Value" sheetId="7" r:id="R5f20650e059649e8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -619,6 +619,13 @@
         </x:is>
       </x:c>
     </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Team software subscriptions (Claude Max, GitHub, Jira, Figma) are IRIS costs on the Build and Run sheets and are not passed through. General office software, laptops and email sit in the loaded rate card.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -1393,7 +1400,7 @@
     <x:row r="43">
       <x:c r="A43" s="5" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Platform run costs</x:t>
+          <x:t xml:space="preserve">Platform run costs (cloud lines are planning estimates for a Thailand-region tenant)</x:t>
         </x:is>
       </x:c>
       <x:c r="B43" s="6" t="n"/>
@@ -1403,11 +1410,11 @@
     <x:row r="44">
       <x:c r="A44" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Cloud infrastructure, fixed</x:t>
+          <x:t xml:space="preserve">Cloud: app servers (containers, 2 availability zones)</x:t>
         </x:is>
       </x:c>
       <x:c r="B44" s="8" t="n">
-        <x:v>70000</x:v>
+        <x:v>20000</x:v>
       </x:c>
       <x:c r="C44" s="9" t="inlineStr">
         <x:is>
@@ -1416,38 +1423,38 @@
       </x:c>
       <x:c r="D44" s="10" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Dedicated tenant in a Thailand region: app, Postgres + pgvector, Redis, storage, WAF, logs, non-prod.</x:t>
+          <x:t xml:space="preserve">Web app, API and background jobs with autoscaling.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="45">
       <x:c r="A45" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Cloud infrastructure, variable</x:t>
+          <x:t xml:space="preserve">Cloud: managed Postgres + pgvector (high availability)</x:t>
         </x:is>
       </x:c>
       <x:c r="B45" s="8" t="n">
-        <x:v>1.8</x:v>
+        <x:v>18000</x:v>
       </x:c>
       <x:c r="C45" s="9" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">THB / employee / mo</x:t>
+          <x:t xml:space="preserve">THB / month</x:t>
         </x:is>
       </x:c>
       <x:c r="D45" s="10" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Assumption.</x:t>
+          <x:t xml:space="preserve">Primary and standby; learning records, audit log, retrieval index.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="46">
       <x:c r="A46" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">LINE OA Pro plan</x:t>
+          <x:t xml:space="preserve">Cloud: Redis cache</x:t>
         </x:is>
       </x:c>
       <x:c r="B46" s="8" t="n">
-        <x:v>1780</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="C46" s="9" t="inlineStr">
         <x:is>
@@ -1456,118 +1463,118 @@
       </x:c>
       <x:c r="D46" s="10" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">LINE for Business TH price list (excl. VAT): 35,000 messages included.</x:t>
+          <x:t xml:space="preserve">Sessions, rate limits, queues.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="47">
       <x:c r="A47" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">LINE messages included</x:t>
+          <x:t xml:space="preserve">Cloud: object storage and CDN</x:t>
         </x:is>
       </x:c>
       <x:c r="B47" s="8" t="n">
-        <x:v>35000</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="C47" s="9" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">messages</x:t>
+          <x:t xml:space="preserve">THB / month</x:t>
         </x:is>
       </x:c>
       <x:c r="D47" s="10" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">Lesson assets, exports; video stays in the client's LMS.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="48">
       <x:c r="A48" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">LINE extra message</x:t>
+          <x:t xml:space="preserve">Cloud: load balancer, WAF and DDoS protection</x:t>
         </x:is>
       </x:c>
       <x:c r="B48" s="8" t="n">
-        <x:v>0.06</x:v>
+        <x:v>8000</x:v>
       </x:c>
       <x:c r="C48" s="9" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">THB / message</x:t>
+          <x:t xml:space="preserve">THB / month</x:t>
         </x:is>
       </x:c>
       <x:c r="D48" s="10" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Pro plan extra rate.</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="49">
       <x:c r="A49" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Frontline share</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B49" s="15" t="n">
-        <x:v>0.6</x:v>
+          <x:t xml:space="preserve">Cloud: logs, metrics and audit-log retention</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B49" s="8" t="n">
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="C49" s="9" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">THB / month</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D49" s="10" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
-      <x:c r="D49" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Brief: ~60% frontline, mostly mobile.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="50">
       <x:c r="A50" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Frontline users needing SMS OTP per month</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B50" s="15" t="n">
-        <x:v>0.1</x:v>
+          <x:t xml:space="preserve">Cloud: backups and disaster-recovery copy</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B50" s="8" t="n">
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="C50" s="9" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">THB / month</x:t>
         </x:is>
       </x:c>
       <x:c r="D50" s="10" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Fallback for staff without corporate SSO; LINE Login is primary.</x:t>
+          <x:t xml:space="preserve">Daily backups, point-in-time recovery, copy in a second zone.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="51">
       <x:c r="A51" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SMS OTP cost</x:t>
+          <x:t xml:space="preserve">Cloud: non-production environments (dev, staging)</x:t>
         </x:is>
       </x:c>
       <x:c r="B51" s="8" t="n">
-        <x:v>0.5</x:v>
+        <x:v>6000</x:v>
       </x:c>
       <x:c r="C51" s="9" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">THB / SMS</x:t>
+          <x:t xml:space="preserve">THB / month</x:t>
         </x:is>
       </x:c>
       <x:c r="D51" s="10" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Assumption; confirm with the client's SMS gateway.</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="52">
       <x:c r="A52" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Tooling (monitoring, LRS, security scanning)</x:t>
+          <x:t xml:space="preserve">Cloud: DNS, TLS certificates and transactional email</x:t>
         </x:is>
       </x:c>
       <x:c r="B52" s="8" t="n">
-        <x:v>30000</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="C52" s="9" t="inlineStr">
         <x:is>
@@ -1583,11 +1590,11 @@
     <x:row r="53">
       <x:c r="A53" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Tooling, variable</x:t>
+          <x:t xml:space="preserve">Cloud infrastructure, variable</x:t>
         </x:is>
       </x:c>
       <x:c r="B53" s="8" t="n">
-        <x:v>0.25</x:v>
+        <x:v>1.8</x:v>
       </x:c>
       <x:c r="C53" s="9" t="inlineStr">
         <x:is>
@@ -1596,546 +1603,896 @@
       </x:c>
       <x:c r="D53" s="10" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">Assumption: compute, storage and traffic that grow with headcount.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="54">
       <x:c r="A54" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Annual penetration test</x:t>
+          <x:t xml:space="preserve">LINE OA Pro plan</x:t>
         </x:is>
       </x:c>
       <x:c r="B54" s="8" t="n">
-        <x:v>400000</x:v>
+        <x:v>1780</x:v>
       </x:c>
       <x:c r="C54" s="9" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">THB / yr</x:t>
+          <x:t xml:space="preserve">THB / month</x:t>
         </x:is>
       </x:c>
       <x:c r="D54" s="10" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Also one at go-live (Build sheet).</x:t>
+          <x:t xml:space="preserve">LINE for Business TH price list (excl. VAT): 35,000 messages included.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="55">
       <x:c r="A55" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">DPIA refresh and compliance audit</x:t>
+          <x:t xml:space="preserve">LINE messages included</x:t>
         </x:is>
       </x:c>
       <x:c r="B55" s="8" t="n">
-        <x:v>200000</x:v>
+        <x:v>35000</x:v>
       </x:c>
       <x:c r="C55" s="9" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">THB / yr</x:t>
+          <x:t xml:space="preserve">messages</x:t>
         </x:is>
       </x:c>
       <x:c r="D55" s="10" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">PDPA; PDPC AI guidance expects DPIA for high-risk AI.</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="56">
-      <x:c r="A56" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Run team (client-dedicated + platform)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B56" s="6" t="n"/>
-      <x:c r="C56" s="6" t="n"/>
-      <x:c r="D56" s="6" t="n"/>
+      <x:c r="A56" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">LINE extra message</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B56" s="8" t="n">
+        <x:v>0.06</x:v>
+      </x:c>
+      <x:c r="C56" s="9" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">THB / message</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D56" s="10" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Pro plan extra rate.</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="57">
       <x:c r="A57" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Customer success / product owner</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B57" s="8" t="n">
-        <x:v>0.5</x:v>
+          <x:t xml:space="preserve">Frontline share</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B57" s="15" t="n">
+        <x:v>0.6</x:v>
       </x:c>
       <x:c r="C57" s="9" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">FTE</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="D57" s="10" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">Brief: ~60% frontline, mostly mobile.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="58">
       <x:c r="A58" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Skills &amp; content analysts, base</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B58" s="8" t="n">
-        <x:v>1</x:v>
+          <x:t xml:space="preserve">Frontline users needing SMS OTP per month</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B58" s="15" t="n">
+        <x:v>0.1</x:v>
       </x:c>
       <x:c r="C58" s="9" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">FTE</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="D58" s="10" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Maintain frameworks, tag new content, review flagged answers.</x:t>
+          <x:t xml:space="preserve">Fallback for staff without corporate SSO; LINE Login is primary.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="59">
       <x:c r="A59" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Employees per extra analyst</x:t>
+          <x:t xml:space="preserve">SMS OTP cost</x:t>
         </x:is>
       </x:c>
       <x:c r="B59" s="8" t="n">
-        <x:v>30000</x:v>
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="C59" s="9" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">people</x:t>
+          <x:t xml:space="preserve">THB / SMS</x:t>
         </x:is>
       </x:c>
       <x:c r="D59" s="10" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">Assumption; confirm with the client's SMS gateway.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="60">
       <x:c r="A60" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Employees per L2 support analyst</x:t>
+          <x:t xml:space="preserve">Tooling (monitoring, LRS, security scanning)</x:t>
         </x:is>
       </x:c>
       <x:c r="B60" s="8" t="n">
-        <x:v>25000</x:v>
+        <x:v>30000</x:v>
       </x:c>
       <x:c r="C60" s="9" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">people</x:t>
+          <x:t xml:space="preserve">THB / month</x:t>
         </x:is>
       </x:c>
       <x:c r="D60" s="10" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">L1 stays with the client's HR helpdesk.</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="61">
       <x:c r="A61" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Platform team up to 20k employees</x:t>
+          <x:t xml:space="preserve">Tooling, variable</x:t>
         </x:is>
       </x:c>
       <x:c r="B61" s="8" t="n">
-        <x:v>2.5</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="C61" s="9" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">FTE</x:t>
+          <x:t xml:space="preserve">THB / employee / mo</x:t>
         </x:is>
       </x:c>
       <x:c r="D61" s="10" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Engineering, AI ops and security on call. Dedicated: this is the platform's first client, so no cost is shared yet.</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="62">
       <x:c r="A62" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Platform team above 20k employees</x:t>
+          <x:t xml:space="preserve">Annual penetration test</x:t>
         </x:is>
       </x:c>
       <x:c r="B62" s="8" t="n">
-        <x:v>3</x:v>
+        <x:v>400000</x:v>
       </x:c>
       <x:c r="C62" s="9" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">FTE</x:t>
+          <x:t xml:space="preserve">THB / yr</x:t>
         </x:is>
       </x:c>
       <x:c r="D62" s="10" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Adds wave 2-3 integrations and the ASEAN languages.</x:t>
+          <x:t xml:space="preserve">Also one at go-live (Build sheet).</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="63">
-      <x:c r="A63" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Pricing (levers)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B63" s="6" t="n"/>
-      <x:c r="C63" s="6" t="n"/>
-      <x:c r="D63" s="6" t="n"/>
+      <x:c r="A63" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">DPIA refresh and compliance audit</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B63" s="8" t="n">
+        <x:v>200000</x:v>
+      </x:c>
+      <x:c r="C63" s="9" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">THB / yr</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D63" s="10" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">PDPA; PDPC AI guidance expects DPIA for high-risk AI.</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="64">
-      <x:c r="A64" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Subscription price per enrolled employee per month</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B64" s="16" t="n">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C64" s="9" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">THB</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D64" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Includes platform, hosting, AI coach (fair use), L2 support, framework upkeep.</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="A64" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Team software subscriptions (USD per seat per month; IRIS cost, not passed through)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B64" s="6" t="n"/>
+      <x:c r="C64" s="6" t="n"/>
+      <x:c r="D64" s="6" t="n"/>
     </x:row>
     <x:row r="65">
       <x:c r="A65" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Minimum committed employees from wave 2</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B65" s="17" t="n">
-        <x:v>20000</x:v>
+          <x:t xml:space="preserve">Claude Max 20x seat (engineering roles)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B65" s="14" t="n">
+        <x:v>200</x:v>
       </x:c>
       <x:c r="C65" s="9" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">people</x:t>
+          <x:t xml:space="preserve">USD / seat / mo</x:t>
         </x:is>
       </x:c>
       <x:c r="D65" s="10" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Protects unit economics while waves ramp.</x:t>
+          <x:t xml:space="preserve">Anthropic list price (support.claude.com, Oct 2026); monthly billing only. Claude Code for build, test and operations work.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="66">
       <x:c r="A66" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Fixed-date risk premium on implementation</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B66" s="11" t="n">
-        <x:v>0.1</x:v>
+          <x:t xml:space="preserve">Claude Max 5x seat (other roles)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B66" s="14" t="n">
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C66" s="9" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">USD / seat / mo</x:t>
         </x:is>
       </x:c>
       <x:c r="D66" s="10" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">IRIS carries schedule risk on a fixed fee.</x:t>
+          <x:t xml:space="preserve">Anthropic list price (Oct 2026). Product, design, skills, content, change and support roles.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="67">
       <x:c r="A67" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Wave 2 rollout services (fixed)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B67" s="17" t="n">
-        <x:v>6000000</x:v>
+          <x:t xml:space="preserve">GitHub Team seat (engineering roles)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B67" s="14" t="n">
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C67" s="9" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">THB</x:t>
+          <x:t xml:space="preserve">USD / seat / mo</x:t>
         </x:is>
       </x:c>
       <x:c r="D67" s="10" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Frameworks for new role families, integrations, change.</x:t>
+          <x:t xml:space="preserve">Repositories, Actions CI and code review. Third-party pricing guides (Sep 2026); confirm on github.com/pricing.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="68">
       <x:c r="A68" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Wave 3 rollout services (fixed, incl. ASEAN localisation)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B68" s="17" t="n">
-        <x:v>9000000</x:v>
+          <x:t xml:space="preserve">Jira Standard seat (all roles)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B68" s="14" t="n">
+        <x:v>7.91</x:v>
       </x:c>
       <x:c r="C68" s="9" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">THB</x:t>
+          <x:t xml:space="preserve">USD / seat / mo</x:t>
         </x:is>
       </x:c>
       <x:c r="D68" s="10" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">3 languages, local data rules, local content.</x:t>
+          <x:t xml:space="preserve">Delivery tracking with the product council. Third-party guides citing Atlassian list (Jul 2026).</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="69">
       <x:c r="A69" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Wave services delivery cost ratio</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B69" s="15" t="n">
-        <x:v>0.5</x:v>
+          <x:t xml:space="preserve">Figma Professional full seat (build only)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B69" s="14" t="n">
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C69" s="9" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">of fee</x:t>
+          <x:t xml:space="preserve">USD / seat / mo</x:t>
         </x:is>
       </x:c>
       <x:c r="D69" s="10" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">Monthly billing. Third-party guides and Figma forum (2026).</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="70">
       <x:c r="A70" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Share of subscription at risk on adoption KPIs</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B70" s="15" t="n">
-        <x:v>0.1</x:v>
+          <x:t xml:space="preserve">Build seats, engineering roles</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B70" s="8" t="n">
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C70" s="9" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">seats</x:t>
         </x:is>
       </x:c>
       <x:c r="D70" s="10" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Credited back if adoption KPIs are missed. Base case assumes met.</x:t>
+          <x:t xml:space="preserve">Architect, 2 senior engineers, 2 engineers, AI engineer, 2 data engineers, 2 QA, DevSecOps.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="71">
-      <x:c r="A71" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Rate card (THB)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B71" s="6" t="n"/>
-      <x:c r="C71" s="6" t="n"/>
-      <x:c r="D71" s="6" t="n"/>
+      <x:c r="A71" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Build seats, other roles</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B71" s="8" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C71" s="9" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">seats</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D71" s="10" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Product lead, designer, skills lead, 2 skills consultants, content analyst, change consultant.</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="72">
-      <x:c r="A72" s="18" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Role</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B72" s="18" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Cost / month</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C72" s="18" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Bill / day</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D72" s="18" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Note</x:t>
+      <x:c r="A72" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Design tool seats during build</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B72" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C72" s="9" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">seats</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D72" s="10" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">UX/UI designer.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="73">
       <x:c r="A73" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Product &amp; delivery lead</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B73" s="17" t="n">
-        <x:v>260000</x:v>
-      </x:c>
-      <x:c r="C73" s="17" t="n">
-        <x:v>28000</x:v>
+          <x:t xml:space="preserve">Subscription months during build</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B73" s="8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C73" s="9" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">months</x:t>
+        </x:is>
       </x:c>
       <x:c r="D73" s="10" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Cost = fully loaded monthly cost to IRIS (assumption). Bill rates are about 2x the Thai public-sector consultant reference (PDMO FY2026: developer 3,700-4,960 THB/day, senior consultant 8,410, PM 12,120) and below global-SI rates.</x:t>
+          <x:t xml:space="preserve">12 weeks billed as 3 monthly cycles. Run seats follow the run team FTE, rounded up.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="74">
-      <x:c r="A74" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Solution architect</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B74" s="17" t="n">
-        <x:v>200000</x:v>
-      </x:c>
-      <x:c r="C74" s="17" t="n">
-        <x:v>22000</x:v>
-      </x:c>
+      <x:c r="A74" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Run team (client-dedicated + platform)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B74" s="6" t="n"/>
+      <x:c r="C74" s="6" t="n"/>
+      <x:c r="D74" s="6" t="n"/>
     </x:row>
     <x:row r="75">
       <x:c r="A75" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Senior engineer</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B75" s="17" t="n">
-        <x:v>160000</x:v>
-      </x:c>
-      <x:c r="C75" s="17" t="n">
-        <x:v>16000</x:v>
+          <x:t xml:space="preserve">Customer success / product owner</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B75" s="8" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="C75" s="9" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">FTE</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D75" s="10" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="76">
       <x:c r="A76" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Engineer</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B76" s="17" t="n">
-        <x:v>90000</x:v>
-      </x:c>
-      <x:c r="C76" s="17" t="n">
-        <x:v>9500</x:v>
+          <x:t xml:space="preserve">Skills &amp; content analysts, base</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B76" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C76" s="9" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">FTE</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D76" s="10" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Maintain frameworks, tag new content, review flagged answers.</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="77">
       <x:c r="A77" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">AI engineer</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B77" s="17" t="n">
-        <x:v>160000</x:v>
-      </x:c>
-      <x:c r="C77" s="17" t="n">
-        <x:v>16000</x:v>
+          <x:t xml:space="preserve">Employees per extra analyst</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B77" s="8" t="n">
+        <x:v>30000</x:v>
+      </x:c>
+      <x:c r="C77" s="9" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">people</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D77" s="10" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="78">
       <x:c r="A78" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Data &amp; integration engineer</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B78" s="17" t="n">
-        <x:v>150000</x:v>
-      </x:c>
-      <x:c r="C78" s="17" t="n">
-        <x:v>16000</x:v>
+          <x:t xml:space="preserve">Employees per L2 support analyst</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B78" s="8" t="n">
+        <x:v>25000</x:v>
+      </x:c>
+      <x:c r="C78" s="9" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">people</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D78" s="10" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">L1 stays with the client's HR helpdesk.</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="79">
       <x:c r="A79" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">QA engineer</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B79" s="17" t="n">
-        <x:v>80000</x:v>
-      </x:c>
-      <x:c r="C79" s="17" t="n">
-        <x:v>8500</x:v>
+          <x:t xml:space="preserve">Platform team up to 20k employees</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B79" s="8" t="n">
+        <x:v>2.5</x:v>
+      </x:c>
+      <x:c r="C79" s="9" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">FTE</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D79" s="10" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Engineering, AI ops and security on call. Dedicated: this is the platform's first client, so no cost is shared yet.</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="80">
       <x:c r="A80" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">UX/UI designer</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B80" s="17" t="n">
-        <x:v>110000</x:v>
-      </x:c>
-      <x:c r="C80" s="17" t="n">
-        <x:v>12000</x:v>
+          <x:t xml:space="preserve">Platform team above 20k employees</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B80" s="8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C80" s="9" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">FTE</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D80" s="10" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Adds wave 2-3 integrations and the ASEAN languages.</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="81">
-      <x:c r="A81" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">DevSecOps engineer</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B81" s="17" t="n">
-        <x:v>160000</x:v>
-      </x:c>
-      <x:c r="C81" s="17" t="n">
-        <x:v>16000</x:v>
-      </x:c>
+      <x:c r="A81" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Pricing (levers)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B81" s="6" t="n"/>
+      <x:c r="C81" s="6" t="n"/>
+      <x:c r="D81" s="6" t="n"/>
     </x:row>
     <x:row r="82">
       <x:c r="A82" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Skills methodology lead</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B82" s="17" t="n">
-        <x:v>200000</x:v>
-      </x:c>
-      <x:c r="C82" s="17" t="n">
-        <x:v>22000</x:v>
+          <x:t xml:space="preserve">Subscription price per enrolled employee per month</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B82" s="16" t="n">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C82" s="9" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">THB</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D82" s="10" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Includes platform, hosting, AI coach (fair use), L2 support, framework upkeep.</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="83">
       <x:c r="A83" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Skills consultant</x:t>
+          <x:t xml:space="preserve">Minimum committed employees from wave 2</x:t>
         </x:is>
       </x:c>
       <x:c r="B83" s="17" t="n">
-        <x:v>140000</x:v>
-      </x:c>
-      <x:c r="C83" s="17" t="n">
-        <x:v>15000</x:v>
+        <x:v>20000</x:v>
+      </x:c>
+      <x:c r="C83" s="9" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">people</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D83" s="10" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Protects unit economics while waves ramp.</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="84">
       <x:c r="A84" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Content analyst</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B84" s="17" t="n">
-        <x:v>70000</x:v>
-      </x:c>
-      <x:c r="C84" s="17" t="n">
-        <x:v>7000</x:v>
+          <x:t xml:space="preserve">Fixed-date risk premium on implementation</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B84" s="11" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="C84" s="9" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="D84" s="10" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">IRIS carries schedule risk on a fixed fee.</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="85">
       <x:c r="A85" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Change &amp; adoption consultant</x:t>
+          <x:t xml:space="preserve">Wave 2 rollout services (fixed)</x:t>
         </x:is>
       </x:c>
       <x:c r="B85" s="17" t="n">
-        <x:v>140000</x:v>
-      </x:c>
-      <x:c r="C85" s="17" t="n">
-        <x:v>15000</x:v>
+        <x:v>6000000</x:v>
+      </x:c>
+      <x:c r="C85" s="9" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">THB</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D85" s="10" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Frameworks for new role families, integrations, change.</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="86">
       <x:c r="A86" s="7" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">Wave 3 rollout services (fixed, incl. ASEAN localisation)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B86" s="17" t="n">
+        <x:v>9000000</x:v>
+      </x:c>
+      <x:c r="C86" s="9" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">THB</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D86" s="10" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">3 languages, local data rules, local content.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="87">
+      <x:c r="A87" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Wave services delivery cost ratio</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B87" s="15" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="C87" s="9" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">of fee</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D87" s="10" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="88">
+      <x:c r="A88" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Share of subscription at risk on adoption KPIs</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B88" s="15" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="C88" s="9" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="D88" s="10" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Credited back if adoption KPIs are missed. Base case assumes met.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="89">
+      <x:c r="A89" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Rate card (THB)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B89" s="6" t="n"/>
+      <x:c r="C89" s="6" t="n"/>
+      <x:c r="D89" s="6" t="n"/>
+    </x:row>
+    <x:row r="90">
+      <x:c r="A90" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Role</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B90" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Cost / month</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C90" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Bill / day</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D90" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Note</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="91">
+      <x:c r="A91" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Product &amp; delivery lead</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B91" s="17" t="n">
+        <x:v>260000</x:v>
+      </x:c>
+      <x:c r="C91" s="17" t="n">
+        <x:v>28000</x:v>
+      </x:c>
+      <x:c r="D91" s="10" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Cost = fully loaded monthly cost to IRIS (assumption). Bill rates are about 2x the Thai public-sector consultant reference (PDMO FY2026: developer 3,700-4,960 THB/day, senior consultant 8,410, PM 12,120) and below global-SI rates.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="92">
+      <x:c r="A92" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Solution architect</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B92" s="17" t="n">
+        <x:v>200000</x:v>
+      </x:c>
+      <x:c r="C92" s="17" t="n">
+        <x:v>22000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93">
+      <x:c r="A93" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Senior engineer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B93" s="17" t="n">
+        <x:v>160000</x:v>
+      </x:c>
+      <x:c r="C93" s="17" t="n">
+        <x:v>16000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94">
+      <x:c r="A94" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Engineer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B94" s="17" t="n">
+        <x:v>90000</x:v>
+      </x:c>
+      <x:c r="C94" s="17" t="n">
+        <x:v>9500</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95">
+      <x:c r="A95" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">AI engineer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B95" s="17" t="n">
+        <x:v>160000</x:v>
+      </x:c>
+      <x:c r="C95" s="17" t="n">
+        <x:v>16000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96">
+      <x:c r="A96" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Data &amp; integration engineer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B96" s="17" t="n">
+        <x:v>150000</x:v>
+      </x:c>
+      <x:c r="C96" s="17" t="n">
+        <x:v>16000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97">
+      <x:c r="A97" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">QA engineer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B97" s="17" t="n">
+        <x:v>80000</x:v>
+      </x:c>
+      <x:c r="C97" s="17" t="n">
+        <x:v>8500</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98">
+      <x:c r="A98" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">UX/UI designer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B98" s="17" t="n">
+        <x:v>110000</x:v>
+      </x:c>
+      <x:c r="C98" s="17" t="n">
+        <x:v>12000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99">
+      <x:c r="A99" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">DevSecOps engineer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B99" s="17" t="n">
+        <x:v>160000</x:v>
+      </x:c>
+      <x:c r="C99" s="17" t="n">
+        <x:v>16000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100">
+      <x:c r="A100" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Skills methodology lead</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B100" s="17" t="n">
+        <x:v>200000</x:v>
+      </x:c>
+      <x:c r="C100" s="17" t="n">
+        <x:v>22000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101">
+      <x:c r="A101" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Skills consultant</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B101" s="17" t="n">
+        <x:v>140000</x:v>
+      </x:c>
+      <x:c r="C101" s="17" t="n">
+        <x:v>15000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="102">
+      <x:c r="A102" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Content analyst</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B102" s="17" t="n">
+        <x:v>70000</x:v>
+      </x:c>
+      <x:c r="C102" s="17" t="n">
+        <x:v>7000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="103">
+      <x:c r="A103" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Change &amp; adoption consultant</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B103" s="17" t="n">
+        <x:v>140000</x:v>
+      </x:c>
+      <x:c r="C103" s="17" t="n">
+        <x:v>15000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104">
+      <x:c r="A104" s="7" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">Support analyst</x:t>
         </x:is>
       </x:c>
-      <x:c r="B86" s="17" t="n">
+      <x:c r="B104" s="17" t="n">
         <x:v>60000</x:v>
       </x:c>
-      <x:c r="C86" s="17" t="n">
+      <x:c r="C104" s="17" t="n">
         <x:v>6000</x:v>
       </x:c>
     </x:row>
@@ -2216,11 +2573,11 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="D5" s="20" t="n">
-        <x:f>C5*Assumptions!$B$73/Assumptions!$B$7</x:f>
+        <x:f>C5*Assumptions!$B$91/Assumptions!$B$7</x:f>
         <x:v>742857.1428571428</x:v>
       </x:c>
       <x:c r="E5" s="20" t="n">
-        <x:f>C5*Assumptions!$C$73</x:f>
+        <x:f>C5*Assumptions!$C$91</x:f>
         <x:v>1680000</x:v>
       </x:c>
       <x:c r="F5" s="10" t="inlineStr">
@@ -2243,11 +2600,11 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="D6" s="20" t="n">
-        <x:f>C6*Assumptions!$B$74/Assumptions!$B$7</x:f>
+        <x:f>C6*Assumptions!$B$92/Assumptions!$B$7</x:f>
         <x:v>571428.5714285715</x:v>
       </x:c>
       <x:c r="E6" s="20" t="n">
-        <x:f>C6*Assumptions!$C$74</x:f>
+        <x:f>C6*Assumptions!$C$92</x:f>
         <x:v>1320000</x:v>
       </x:c>
       <x:c r="F6" s="10" t="inlineStr">
@@ -2270,11 +2627,11 @@
         <x:v>120</x:v>
       </x:c>
       <x:c r="D7" s="20" t="n">
-        <x:f>C7*Assumptions!$B$75/Assumptions!$B$7</x:f>
+        <x:f>C7*Assumptions!$B$93/Assumptions!$B$7</x:f>
         <x:v>914285.7142857143</x:v>
       </x:c>
       <x:c r="E7" s="20" t="n">
-        <x:f>C7*Assumptions!$C$75</x:f>
+        <x:f>C7*Assumptions!$C$93</x:f>
         <x:v>1920000</x:v>
       </x:c>
       <x:c r="F7" s="10" t="inlineStr">
@@ -2297,11 +2654,11 @@
         <x:v>120</x:v>
       </x:c>
       <x:c r="D8" s="20" t="n">
-        <x:f>C8*Assumptions!$B$76/Assumptions!$B$7</x:f>
+        <x:f>C8*Assumptions!$B$94/Assumptions!$B$7</x:f>
         <x:v>514285.71428571426</x:v>
       </x:c>
       <x:c r="E8" s="20" t="n">
-        <x:f>C8*Assumptions!$C$76</x:f>
+        <x:f>C8*Assumptions!$C$94</x:f>
         <x:v>1140000</x:v>
       </x:c>
       <x:c r="F8" s="10" t="inlineStr">
@@ -2324,11 +2681,11 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="D9" s="20" t="n">
-        <x:f>C9*Assumptions!$B$77/Assumptions!$B$7</x:f>
+        <x:f>C9*Assumptions!$B$95/Assumptions!$B$7</x:f>
         <x:v>457142.85714285716</x:v>
       </x:c>
       <x:c r="E9" s="20" t="n">
-        <x:f>C9*Assumptions!$C$77</x:f>
+        <x:f>C9*Assumptions!$C$95</x:f>
         <x:v>960000</x:v>
       </x:c>
       <x:c r="F9" s="10" t="inlineStr">
@@ -2351,11 +2708,11 @@
         <x:v>120</x:v>
       </x:c>
       <x:c r="D10" s="20" t="n">
-        <x:f>C10*Assumptions!$B$78/Assumptions!$B$7</x:f>
+        <x:f>C10*Assumptions!$B$96/Assumptions!$B$7</x:f>
         <x:v>857142.8571428572</x:v>
       </x:c>
       <x:c r="E10" s="20" t="n">
-        <x:f>C10*Assumptions!$C$78</x:f>
+        <x:f>C10*Assumptions!$C$96</x:f>
         <x:v>1920000</x:v>
       </x:c>
       <x:c r="F10" s="10" t="inlineStr">
@@ -2378,11 +2735,11 @@
         <x:v>90</x:v>
       </x:c>
       <x:c r="D11" s="20" t="n">
-        <x:f>C11*Assumptions!$B$79/Assumptions!$B$7</x:f>
+        <x:f>C11*Assumptions!$B$97/Assumptions!$B$7</x:f>
         <x:v>342857.14285714284</x:v>
       </x:c>
       <x:c r="E11" s="20" t="n">
-        <x:f>C11*Assumptions!$C$79</x:f>
+        <x:f>C11*Assumptions!$C$97</x:f>
         <x:v>765000</x:v>
       </x:c>
       <x:c r="F11" s="10" t="inlineStr">
@@ -2405,11 +2762,11 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="D12" s="20" t="n">
-        <x:f>C12*Assumptions!$B$80/Assumptions!$B$7</x:f>
+        <x:f>C12*Assumptions!$B$98/Assumptions!$B$7</x:f>
         <x:v>220000</x:v>
       </x:c>
       <x:c r="E12" s="20" t="n">
-        <x:f>C12*Assumptions!$C$80</x:f>
+        <x:f>C12*Assumptions!$C$98</x:f>
         <x:v>504000</x:v>
       </x:c>
       <x:c r="F12" s="10" t="inlineStr">
@@ -2432,11 +2789,11 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="D13" s="20" t="n">
-        <x:f>C13*Assumptions!$B$81/Assumptions!$B$7</x:f>
+        <x:f>C13*Assumptions!$B$99/Assumptions!$B$7</x:f>
         <x:v>457142.85714285716</x:v>
       </x:c>
       <x:c r="E13" s="20" t="n">
-        <x:f>C13*Assumptions!$C$81</x:f>
+        <x:f>C13*Assumptions!$C$99</x:f>
         <x:v>960000</x:v>
       </x:c>
       <x:c r="F13" s="10" t="inlineStr">
@@ -2459,11 +2816,11 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="D14" s="20" t="n">
-        <x:f>C14*Assumptions!$B$82/Assumptions!$B$7</x:f>
+        <x:f>C14*Assumptions!$B$100/Assumptions!$B$7</x:f>
         <x:v>571428.5714285715</x:v>
       </x:c>
       <x:c r="E14" s="20" t="n">
-        <x:f>C14*Assumptions!$C$82</x:f>
+        <x:f>C14*Assumptions!$C$100</x:f>
         <x:v>1320000</x:v>
       </x:c>
       <x:c r="F14" s="10" t="inlineStr">
@@ -2486,11 +2843,11 @@
         <x:v>84</x:v>
       </x:c>
       <x:c r="D15" s="20" t="n">
-        <x:f>C15*Assumptions!$B$83/Assumptions!$B$7</x:f>
+        <x:f>C15*Assumptions!$B$101/Assumptions!$B$7</x:f>
         <x:v>560000</x:v>
       </x:c>
       <x:c r="E15" s="20" t="n">
-        <x:f>C15*Assumptions!$C$83</x:f>
+        <x:f>C15*Assumptions!$C$101</x:f>
         <x:v>1260000</x:v>
       </x:c>
       <x:c r="F15" s="10" t="inlineStr">
@@ -2513,11 +2870,11 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="D16" s="20" t="n">
-        <x:f>C16*Assumptions!$B$84/Assumptions!$B$7</x:f>
+        <x:f>C16*Assumptions!$B$102/Assumptions!$B$7</x:f>
         <x:v>200000</x:v>
       </x:c>
       <x:c r="E16" s="20" t="n">
-        <x:f>C16*Assumptions!$C$84</x:f>
+        <x:f>C16*Assumptions!$C$102</x:f>
         <x:v>420000</x:v>
       </x:c>
       <x:c r="F16" s="10" t="inlineStr">
@@ -2540,11 +2897,11 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D17" s="20" t="n">
-        <x:f>C17*Assumptions!$B$85/Assumptions!$B$7</x:f>
+        <x:f>C17*Assumptions!$B$103/Assumptions!$B$7</x:f>
         <x:v>320000</x:v>
       </x:c>
       <x:c r="E17" s="20" t="n">
-        <x:f>C17*Assumptions!$C$85</x:f>
+        <x:f>C17*Assumptions!$C$103</x:f>
         <x:v>720000</x:v>
       </x:c>
       <x:c r="F17" s="10" t="inlineStr">
@@ -2666,69 +3023,80 @@
       </x:c>
     </x:row>
     <x:row r="28">
-      <x:c r="A28" s="18" t="inlineStr">
+      <x:c r="A28" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Team software subscriptions: Claude Max, GitHub, Jira, Figma (IRIS cost, not passed through)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D28" s="20" t="n">
+        <x:f>(Assumptions!$B$70*(Assumptions!$B$65+Assumptions!$B$67+Assumptions!$B$68)+Assumptions!$B$71*(Assumptions!$B$66+Assumptions!$B$68)+Assumptions!$B$72*Assumptions!$B$69)*Assumptions!$B$73*Assumptions!$B$6</x:f>
+        <x:v>316850.76</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Total cost to IRIS</x:t>
         </x:is>
       </x:c>
-      <x:c r="D28" s="22" t="n">
-        <x:f>D18+D25+D27</x:f>
-        <x:v>8547857.142857144</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29">
-      <x:c r="A29" s="7" t="inlineStr">
+      <x:c r="D29" s="22" t="n">
+        <x:f>D18+D25+D27+D28</x:f>
+        <x:v>8864707.902857143</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Price before risk premium</x:t>
         </x:is>
       </x:c>
-      <x:c r="E29" s="20" t="n">
+      <x:c r="E30" s="20" t="n">
         <x:f>E18+E25</x:f>
         <x:v>15699000</x:v>
       </x:c>
     </x:row>
-    <x:row r="30">
-      <x:c r="A30" s="7" t="inlineStr">
+    <x:row r="31">
+      <x:c r="A31" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Fixed-date risk premium</x:t>
         </x:is>
       </x:c>
-      <x:c r="E30" s="20" t="n">
-        <x:f>E29*Assumptions!$B$66</x:f>
+      <x:c r="E31" s="20" t="n">
+        <x:f>E30*Assumptions!$B$84</x:f>
         <x:v>1569900</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31">
-      <x:c r="A31" s="18" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Implementation fee (rounded to 0.5M)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E31" s="23" t="n">
-        <x:f>ROUND((E29+E30)/500000,0)*500000</x:f>
-        <x:v>17500000</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="18" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">Implementation fee (rounded to 0.5M)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E32" s="23" t="n">
+        <x:f>ROUND((E30+E31)/500000,0)*500000</x:f>
+        <x:v>17500000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="18" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">Gross margin on implementation</x:t>
         </x:is>
       </x:c>
-      <x:c r="E32" s="24" t="n">
-        <x:f>(E31-D28)/E31</x:f>
-        <x:v>0.5115510204081632</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34">
-      <x:c r="A34" s="9" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Milestones: 30% at kick-off, 30% at week 6 (integrated demo), 40% at go-live acceptance.</x:t>
-        </x:is>
+      <x:c r="E33" s="24" t="n">
+        <x:f>(E32-D29)/E32</x:f>
+        <x:v>0.4934452626938775</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="9" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Milestones: 30% at kick-off, 30% at week 6 (integrated demo), 40% at go-live acceptance.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="9" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Client-side roles (not priced): HRIS owner, 2 LMS admins, IT security, DPO, 2 SMEs per BU, comms lead, ~60 champions.</x:t>
         </x:is>
@@ -4273,151 +4641,151 @@
     <x:row r="14">
       <x:c r="A14" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Cloud infrastructure</x:t>
+          <x:t xml:space="preserve">Cloud infrastructure (servers, database, storage, security)</x:t>
         </x:is>
       </x:c>
       <x:c r="B14" s="20" t="n">
-        <x:f>IF(B5&gt;0,Assumptions!$B$44+Assumptions!$B$45*B5,0)</x:f>
+        <x:f>IF(B5&gt;0,SUM(Assumptions!$B$44:$B$52)+Assumptions!$B$53*B5,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C14" s="20" t="n">
-        <x:f>IF(C5&gt;0,Assumptions!$B$44+Assumptions!$B$45*C5,0)</x:f>
+        <x:f>IF(C5&gt;0,SUM(Assumptions!$B$44:$B$52)+Assumptions!$B$53*C5,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D14" s="20" t="n">
-        <x:f>IF(D5&gt;0,Assumptions!$B$44+Assumptions!$B$45*D5,0)</x:f>
+        <x:f>IF(D5&gt;0,SUM(Assumptions!$B$44:$B$52)+Assumptions!$B$53*D5,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="E14" s="20" t="n">
-        <x:f>IF(E5&gt;0,Assumptions!$B$44+Assumptions!$B$45*E5,0)</x:f>
+        <x:f>IF(E5&gt;0,SUM(Assumptions!$B$44:$B$52)+Assumptions!$B$53*E5,0)</x:f>
         <x:v>91600</x:v>
       </x:c>
       <x:c r="F14" s="20" t="n">
-        <x:f>IF(F5&gt;0,Assumptions!$B$44+Assumptions!$B$45*F5,0)</x:f>
+        <x:f>IF(F5&gt;0,SUM(Assumptions!$B$44:$B$52)+Assumptions!$B$53*F5,0)</x:f>
         <x:v>91600</x:v>
       </x:c>
       <x:c r="G14" s="20" t="n">
-        <x:f>IF(G5&gt;0,Assumptions!$B$44+Assumptions!$B$45*G5,0)</x:f>
+        <x:f>IF(G5&gt;0,SUM(Assumptions!$B$44:$B$52)+Assumptions!$B$53*G5,0)</x:f>
         <x:v>91600</x:v>
       </x:c>
       <x:c r="H14" s="20" t="n">
-        <x:f>IF(H5&gt;0,Assumptions!$B$44+Assumptions!$B$45*H5,0)</x:f>
+        <x:f>IF(H5&gt;0,SUM(Assumptions!$B$44:$B$52)+Assumptions!$B$53*H5,0)</x:f>
         <x:v>118600</x:v>
       </x:c>
       <x:c r="I14" s="20" t="n">
-        <x:f>IF(I5&gt;0,Assumptions!$B$44+Assumptions!$B$45*I5,0)</x:f>
+        <x:f>IF(I5&gt;0,SUM(Assumptions!$B$44:$B$52)+Assumptions!$B$53*I5,0)</x:f>
         <x:v>118600</x:v>
       </x:c>
       <x:c r="J14" s="20" t="n">
-        <x:f>IF(J5&gt;0,Assumptions!$B$44+Assumptions!$B$45*J5,0)</x:f>
+        <x:f>IF(J5&gt;0,SUM(Assumptions!$B$44:$B$52)+Assumptions!$B$53*J5,0)</x:f>
         <x:v>118600</x:v>
       </x:c>
       <x:c r="K14" s="20" t="n">
-        <x:f>IF(K5&gt;0,Assumptions!$B$44+Assumptions!$B$45*K5,0)</x:f>
+        <x:f>IF(K5&gt;0,SUM(Assumptions!$B$44:$B$52)+Assumptions!$B$53*K5,0)</x:f>
         <x:v>118600</x:v>
       </x:c>
       <x:c r="L14" s="20" t="n">
-        <x:f>IF(L5&gt;0,Assumptions!$B$44+Assumptions!$B$45*L5,0)</x:f>
+        <x:f>IF(L5&gt;0,SUM(Assumptions!$B$44:$B$52)+Assumptions!$B$53*L5,0)</x:f>
         <x:v>118600</x:v>
       </x:c>
       <x:c r="M14" s="20" t="n">
-        <x:f>IF(M5&gt;0,Assumptions!$B$44+Assumptions!$B$45*M5,0)</x:f>
+        <x:f>IF(M5&gt;0,SUM(Assumptions!$B$44:$B$52)+Assumptions!$B$53*M5,0)</x:f>
         <x:v>118600</x:v>
       </x:c>
       <x:c r="N14" s="20" t="n">
-        <x:f>IF(N5&gt;0,Assumptions!$B$44+Assumptions!$B$45*N5,0)</x:f>
+        <x:f>IF(N5&gt;0,SUM(Assumptions!$B$44:$B$52)+Assumptions!$B$53*N5,0)</x:f>
         <x:v>151000</x:v>
       </x:c>
       <x:c r="O14" s="20" t="n">
-        <x:f>IF(O5&gt;0,Assumptions!$B$44+Assumptions!$B$45*O5,0)</x:f>
+        <x:f>IF(O5&gt;0,SUM(Assumptions!$B$44:$B$52)+Assumptions!$B$53*O5,0)</x:f>
         <x:v>151000</x:v>
       </x:c>
       <x:c r="P14" s="20" t="n">
-        <x:f>IF(P5&gt;0,Assumptions!$B$44+Assumptions!$B$45*P5,0)</x:f>
+        <x:f>IF(P5&gt;0,SUM(Assumptions!$B$44:$B$52)+Assumptions!$B$53*P5,0)</x:f>
         <x:v>151000</x:v>
       </x:c>
       <x:c r="Q14" s="20" t="n">
-        <x:f>IF(Q5&gt;0,Assumptions!$B$44+Assumptions!$B$45*Q5,0)</x:f>
+        <x:f>IF(Q5&gt;0,SUM(Assumptions!$B$44:$B$52)+Assumptions!$B$53*Q5,0)</x:f>
         <x:v>151000</x:v>
       </x:c>
       <x:c r="R14" s="20" t="n">
-        <x:f>IF(R5&gt;0,Assumptions!$B$44+Assumptions!$B$45*R5,0)</x:f>
+        <x:f>IF(R5&gt;0,SUM(Assumptions!$B$44:$B$52)+Assumptions!$B$53*R5,0)</x:f>
         <x:v>151000</x:v>
       </x:c>
       <x:c r="S14" s="20" t="n">
-        <x:f>IF(S5&gt;0,Assumptions!$B$44+Assumptions!$B$45*S5,0)</x:f>
+        <x:f>IF(S5&gt;0,SUM(Assumptions!$B$44:$B$52)+Assumptions!$B$53*S5,0)</x:f>
         <x:v>151000</x:v>
       </x:c>
       <x:c r="T14" s="20" t="n">
-        <x:f>IF(T5&gt;0,Assumptions!$B$44+Assumptions!$B$45*T5,0)</x:f>
+        <x:f>IF(T5&gt;0,SUM(Assumptions!$B$44:$B$52)+Assumptions!$B$53*T5,0)</x:f>
         <x:v>151000</x:v>
       </x:c>
       <x:c r="U14" s="20" t="n">
-        <x:f>IF(U5&gt;0,Assumptions!$B$44+Assumptions!$B$45*U5,0)</x:f>
+        <x:f>IF(U5&gt;0,SUM(Assumptions!$B$44:$B$52)+Assumptions!$B$53*U5,0)</x:f>
         <x:v>151000</x:v>
       </x:c>
       <x:c r="V14" s="20" t="n">
-        <x:f>IF(V5&gt;0,Assumptions!$B$44+Assumptions!$B$45*V5,0)</x:f>
+        <x:f>IF(V5&gt;0,SUM(Assumptions!$B$44:$B$52)+Assumptions!$B$53*V5,0)</x:f>
         <x:v>151000</x:v>
       </x:c>
       <x:c r="W14" s="20" t="n">
-        <x:f>IF(W5&gt;0,Assumptions!$B$44+Assumptions!$B$45*W5,0)</x:f>
+        <x:f>IF(W5&gt;0,SUM(Assumptions!$B$44:$B$52)+Assumptions!$B$53*W5,0)</x:f>
         <x:v>151000</x:v>
       </x:c>
       <x:c r="X14" s="20" t="n">
-        <x:f>IF(X5&gt;0,Assumptions!$B$44+Assumptions!$B$45*X5,0)</x:f>
+        <x:f>IF(X5&gt;0,SUM(Assumptions!$B$44:$B$52)+Assumptions!$B$53*X5,0)</x:f>
         <x:v>151000</x:v>
       </x:c>
       <x:c r="Y14" s="20" t="n">
-        <x:f>IF(Y5&gt;0,Assumptions!$B$44+Assumptions!$B$45*Y5,0)</x:f>
+        <x:f>IF(Y5&gt;0,SUM(Assumptions!$B$44:$B$52)+Assumptions!$B$53*Y5,0)</x:f>
         <x:v>151000</x:v>
       </x:c>
       <x:c r="Z14" s="20" t="n">
-        <x:f>IF(Z5&gt;0,Assumptions!$B$44+Assumptions!$B$45*Z5,0)</x:f>
+        <x:f>IF(Z5&gt;0,SUM(Assumptions!$B$44:$B$52)+Assumptions!$B$53*Z5,0)</x:f>
         <x:v>151000</x:v>
       </x:c>
       <x:c r="AA14" s="20" t="n">
-        <x:f>IF(AA5&gt;0,Assumptions!$B$44+Assumptions!$B$45*AA5,0)</x:f>
+        <x:f>IF(AA5&gt;0,SUM(Assumptions!$B$44:$B$52)+Assumptions!$B$53*AA5,0)</x:f>
         <x:v>151000</x:v>
       </x:c>
       <x:c r="AB14" s="20" t="n">
-        <x:f>IF(AB5&gt;0,Assumptions!$B$44+Assumptions!$B$45*AB5,0)</x:f>
+        <x:f>IF(AB5&gt;0,SUM(Assumptions!$B$44:$B$52)+Assumptions!$B$53*AB5,0)</x:f>
         <x:v>151000</x:v>
       </x:c>
       <x:c r="AC14" s="20" t="n">
-        <x:f>IF(AC5&gt;0,Assumptions!$B$44+Assumptions!$B$45*AC5,0)</x:f>
+        <x:f>IF(AC5&gt;0,SUM(Assumptions!$B$44:$B$52)+Assumptions!$B$53*AC5,0)</x:f>
         <x:v>151000</x:v>
       </x:c>
       <x:c r="AD14" s="20" t="n">
-        <x:f>IF(AD5&gt;0,Assumptions!$B$44+Assumptions!$B$45*AD5,0)</x:f>
+        <x:f>IF(AD5&gt;0,SUM(Assumptions!$B$44:$B$52)+Assumptions!$B$53*AD5,0)</x:f>
         <x:v>151000</x:v>
       </x:c>
       <x:c r="AE14" s="20" t="n">
-        <x:f>IF(AE5&gt;0,Assumptions!$B$44+Assumptions!$B$45*AE5,0)</x:f>
+        <x:f>IF(AE5&gt;0,SUM(Assumptions!$B$44:$B$52)+Assumptions!$B$53*AE5,0)</x:f>
         <x:v>151000</x:v>
       </x:c>
       <x:c r="AF14" s="20" t="n">
-        <x:f>IF(AF5&gt;0,Assumptions!$B$44+Assumptions!$B$45*AF5,0)</x:f>
+        <x:f>IF(AF5&gt;0,SUM(Assumptions!$B$44:$B$52)+Assumptions!$B$53*AF5,0)</x:f>
         <x:v>151000</x:v>
       </x:c>
       <x:c r="AG14" s="20" t="n">
-        <x:f>IF(AG5&gt;0,Assumptions!$B$44+Assumptions!$B$45*AG5,0)</x:f>
+        <x:f>IF(AG5&gt;0,SUM(Assumptions!$B$44:$B$52)+Assumptions!$B$53*AG5,0)</x:f>
         <x:v>151000</x:v>
       </x:c>
       <x:c r="AH14" s="20" t="n">
-        <x:f>IF(AH5&gt;0,Assumptions!$B$44+Assumptions!$B$45*AH5,0)</x:f>
+        <x:f>IF(AH5&gt;0,SUM(Assumptions!$B$44:$B$52)+Assumptions!$B$53*AH5,0)</x:f>
         <x:v>151000</x:v>
       </x:c>
       <x:c r="AI14" s="20" t="n">
-        <x:f>IF(AI5&gt;0,Assumptions!$B$44+Assumptions!$B$45*AI5,0)</x:f>
+        <x:f>IF(AI5&gt;0,SUM(Assumptions!$B$44:$B$52)+Assumptions!$B$53*AI5,0)</x:f>
         <x:v>151000</x:v>
       </x:c>
       <x:c r="AJ14" s="20" t="n">
-        <x:f>IF(AJ5&gt;0,Assumptions!$B$44+Assumptions!$B$45*AJ5,0)</x:f>
+        <x:f>IF(AJ5&gt;0,SUM(Assumptions!$B$44:$B$52)+Assumptions!$B$53*AJ5,0)</x:f>
         <x:v>151000</x:v>
       </x:c>
       <x:c r="AK14" s="20" t="n">
-        <x:f>IF(AK5&gt;0,Assumptions!$B$44+Assumptions!$B$45*AK5,0)</x:f>
+        <x:f>IF(AK5&gt;0,SUM(Assumptions!$B$44:$B$52)+Assumptions!$B$53*AK5,0)</x:f>
         <x:v>151000</x:v>
       </x:c>
     </x:row>
@@ -4428,147 +4796,147 @@
         </x:is>
       </x:c>
       <x:c r="B15" s="20" t="n">
-        <x:f>IF(B5&gt;0,Assumptions!$B$46+MAX(0,B5*Assumptions!$B$20-Assumptions!$B$47)*Assumptions!$B$48,0)</x:f>
+        <x:f>IF(B5&gt;0,Assumptions!$B$54+MAX(0,B5*Assumptions!$B$20-Assumptions!$B$55)*Assumptions!$B$56,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C15" s="20" t="n">
-        <x:f>IF(C5&gt;0,Assumptions!$B$46+MAX(0,C5*Assumptions!$B$20-Assumptions!$B$47)*Assumptions!$B$48,0)</x:f>
+        <x:f>IF(C5&gt;0,Assumptions!$B$54+MAX(0,C5*Assumptions!$B$20-Assumptions!$B$55)*Assumptions!$B$56,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D15" s="20" t="n">
-        <x:f>IF(D5&gt;0,Assumptions!$B$46+MAX(0,D5*Assumptions!$B$20-Assumptions!$B$47)*Assumptions!$B$48,0)</x:f>
+        <x:f>IF(D5&gt;0,Assumptions!$B$54+MAX(0,D5*Assumptions!$B$20-Assumptions!$B$55)*Assumptions!$B$56,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="E15" s="20" t="n">
-        <x:f>IF(E5&gt;0,Assumptions!$B$46+MAX(0,E5*Assumptions!$B$20-Assumptions!$B$47)*Assumptions!$B$48,0)</x:f>
+        <x:f>IF(E5&gt;0,Assumptions!$B$54+MAX(0,E5*Assumptions!$B$20-Assumptions!$B$55)*Assumptions!$B$56,0)</x:f>
         <x:v>2560</x:v>
       </x:c>
       <x:c r="F15" s="20" t="n">
-        <x:f>IF(F5&gt;0,Assumptions!$B$46+MAX(0,F5*Assumptions!$B$20-Assumptions!$B$47)*Assumptions!$B$48,0)</x:f>
+        <x:f>IF(F5&gt;0,Assumptions!$B$54+MAX(0,F5*Assumptions!$B$20-Assumptions!$B$55)*Assumptions!$B$56,0)</x:f>
         <x:v>2560</x:v>
       </x:c>
       <x:c r="G15" s="20" t="n">
-        <x:f>IF(G5&gt;0,Assumptions!$B$46+MAX(0,G5*Assumptions!$B$20-Assumptions!$B$47)*Assumptions!$B$48,0)</x:f>
+        <x:f>IF(G5&gt;0,Assumptions!$B$54+MAX(0,G5*Assumptions!$B$20-Assumptions!$B$55)*Assumptions!$B$56,0)</x:f>
         <x:v>2560</x:v>
       </x:c>
       <x:c r="H15" s="20" t="n">
-        <x:f>IF(H5&gt;0,Assumptions!$B$46+MAX(0,H5*Assumptions!$B$20-Assumptions!$B$47)*Assumptions!$B$48,0)</x:f>
+        <x:f>IF(H5&gt;0,Assumptions!$B$54+MAX(0,H5*Assumptions!$B$20-Assumptions!$B$55)*Assumptions!$B$56,0)</x:f>
         <x:v>6160</x:v>
       </x:c>
       <x:c r="I15" s="20" t="n">
-        <x:f>IF(I5&gt;0,Assumptions!$B$46+MAX(0,I5*Assumptions!$B$20-Assumptions!$B$47)*Assumptions!$B$48,0)</x:f>
+        <x:f>IF(I5&gt;0,Assumptions!$B$54+MAX(0,I5*Assumptions!$B$20-Assumptions!$B$55)*Assumptions!$B$56,0)</x:f>
         <x:v>6160</x:v>
       </x:c>
       <x:c r="J15" s="20" t="n">
-        <x:f>IF(J5&gt;0,Assumptions!$B$46+MAX(0,J5*Assumptions!$B$20-Assumptions!$B$47)*Assumptions!$B$48,0)</x:f>
+        <x:f>IF(J5&gt;0,Assumptions!$B$54+MAX(0,J5*Assumptions!$B$20-Assumptions!$B$55)*Assumptions!$B$56,0)</x:f>
         <x:v>6160</x:v>
       </x:c>
       <x:c r="K15" s="20" t="n">
-        <x:f>IF(K5&gt;0,Assumptions!$B$46+MAX(0,K5*Assumptions!$B$20-Assumptions!$B$47)*Assumptions!$B$48,0)</x:f>
+        <x:f>IF(K5&gt;0,Assumptions!$B$54+MAX(0,K5*Assumptions!$B$20-Assumptions!$B$55)*Assumptions!$B$56,0)</x:f>
         <x:v>6160</x:v>
       </x:c>
       <x:c r="L15" s="20" t="n">
-        <x:f>IF(L5&gt;0,Assumptions!$B$46+MAX(0,L5*Assumptions!$B$20-Assumptions!$B$47)*Assumptions!$B$48,0)</x:f>
+        <x:f>IF(L5&gt;0,Assumptions!$B$54+MAX(0,L5*Assumptions!$B$20-Assumptions!$B$55)*Assumptions!$B$56,0)</x:f>
         <x:v>6160</x:v>
       </x:c>
       <x:c r="M15" s="20" t="n">
-        <x:f>IF(M5&gt;0,Assumptions!$B$46+MAX(0,M5*Assumptions!$B$20-Assumptions!$B$47)*Assumptions!$B$48,0)</x:f>
+        <x:f>IF(M5&gt;0,Assumptions!$B$54+MAX(0,M5*Assumptions!$B$20-Assumptions!$B$55)*Assumptions!$B$56,0)</x:f>
         <x:v>6160</x:v>
       </x:c>
       <x:c r="N15" s="20" t="n">
-        <x:f>IF(N5&gt;0,Assumptions!$B$46+MAX(0,N5*Assumptions!$B$20-Assumptions!$B$47)*Assumptions!$B$48,0)</x:f>
+        <x:f>IF(N5&gt;0,Assumptions!$B$54+MAX(0,N5*Assumptions!$B$20-Assumptions!$B$55)*Assumptions!$B$56,0)</x:f>
         <x:v>10480</x:v>
       </x:c>
       <x:c r="O15" s="20" t="n">
-        <x:f>IF(O5&gt;0,Assumptions!$B$46+MAX(0,O5*Assumptions!$B$20-Assumptions!$B$47)*Assumptions!$B$48,0)</x:f>
+        <x:f>IF(O5&gt;0,Assumptions!$B$54+MAX(0,O5*Assumptions!$B$20-Assumptions!$B$55)*Assumptions!$B$56,0)</x:f>
         <x:v>10480</x:v>
       </x:c>
       <x:c r="P15" s="20" t="n">
-        <x:f>IF(P5&gt;0,Assumptions!$B$46+MAX(0,P5*Assumptions!$B$20-Assumptions!$B$47)*Assumptions!$B$48,0)</x:f>
+        <x:f>IF(P5&gt;0,Assumptions!$B$54+MAX(0,P5*Assumptions!$B$20-Assumptions!$B$55)*Assumptions!$B$56,0)</x:f>
         <x:v>10480</x:v>
       </x:c>
       <x:c r="Q15" s="20" t="n">
-        <x:f>IF(Q5&gt;0,Assumptions!$B$46+MAX(0,Q5*Assumptions!$B$20-Assumptions!$B$47)*Assumptions!$B$48,0)</x:f>
+        <x:f>IF(Q5&gt;0,Assumptions!$B$54+MAX(0,Q5*Assumptions!$B$20-Assumptions!$B$55)*Assumptions!$B$56,0)</x:f>
         <x:v>10480</x:v>
       </x:c>
       <x:c r="R15" s="20" t="n">
-        <x:f>IF(R5&gt;0,Assumptions!$B$46+MAX(0,R5*Assumptions!$B$20-Assumptions!$B$47)*Assumptions!$B$48,0)</x:f>
+        <x:f>IF(R5&gt;0,Assumptions!$B$54+MAX(0,R5*Assumptions!$B$20-Assumptions!$B$55)*Assumptions!$B$56,0)</x:f>
         <x:v>10480</x:v>
       </x:c>
       <x:c r="S15" s="20" t="n">
-        <x:f>IF(S5&gt;0,Assumptions!$B$46+MAX(0,S5*Assumptions!$B$20-Assumptions!$B$47)*Assumptions!$B$48,0)</x:f>
+        <x:f>IF(S5&gt;0,Assumptions!$B$54+MAX(0,S5*Assumptions!$B$20-Assumptions!$B$55)*Assumptions!$B$56,0)</x:f>
         <x:v>10480</x:v>
       </x:c>
       <x:c r="T15" s="20" t="n">
-        <x:f>IF(T5&gt;0,Assumptions!$B$46+MAX(0,T5*Assumptions!$B$20-Assumptions!$B$47)*Assumptions!$B$48,0)</x:f>
+        <x:f>IF(T5&gt;0,Assumptions!$B$54+MAX(0,T5*Assumptions!$B$20-Assumptions!$B$55)*Assumptions!$B$56,0)</x:f>
         <x:v>10480</x:v>
       </x:c>
       <x:c r="U15" s="20" t="n">
-        <x:f>IF(U5&gt;0,Assumptions!$B$46+MAX(0,U5*Assumptions!$B$20-Assumptions!$B$47)*Assumptions!$B$48,0)</x:f>
+        <x:f>IF(U5&gt;0,Assumptions!$B$54+MAX(0,U5*Assumptions!$B$20-Assumptions!$B$55)*Assumptions!$B$56,0)</x:f>
         <x:v>10480</x:v>
       </x:c>
       <x:c r="V15" s="20" t="n">
-        <x:f>IF(V5&gt;0,Assumptions!$B$46+MAX(0,V5*Assumptions!$B$20-Assumptions!$B$47)*Assumptions!$B$48,0)</x:f>
+        <x:f>IF(V5&gt;0,Assumptions!$B$54+MAX(0,V5*Assumptions!$B$20-Assumptions!$B$55)*Assumptions!$B$56,0)</x:f>
         <x:v>10480</x:v>
       </x:c>
       <x:c r="W15" s="20" t="n">
-        <x:f>IF(W5&gt;0,Assumptions!$B$46+MAX(0,W5*Assumptions!$B$20-Assumptions!$B$47)*Assumptions!$B$48,0)</x:f>
+        <x:f>IF(W5&gt;0,Assumptions!$B$54+MAX(0,W5*Assumptions!$B$20-Assumptions!$B$55)*Assumptions!$B$56,0)</x:f>
         <x:v>10480</x:v>
       </x:c>
       <x:c r="X15" s="20" t="n">
-        <x:f>IF(X5&gt;0,Assumptions!$B$46+MAX(0,X5*Assumptions!$B$20-Assumptions!$B$47)*Assumptions!$B$48,0)</x:f>
+        <x:f>IF(X5&gt;0,Assumptions!$B$54+MAX(0,X5*Assumptions!$B$20-Assumptions!$B$55)*Assumptions!$B$56,0)</x:f>
         <x:v>10480</x:v>
       </x:c>
       <x:c r="Y15" s="20" t="n">
-        <x:f>IF(Y5&gt;0,Assumptions!$B$46+MAX(0,Y5*Assumptions!$B$20-Assumptions!$B$47)*Assumptions!$B$48,0)</x:f>
+        <x:f>IF(Y5&gt;0,Assumptions!$B$54+MAX(0,Y5*Assumptions!$B$20-Assumptions!$B$55)*Assumptions!$B$56,0)</x:f>
         <x:v>10480</x:v>
       </x:c>
       <x:c r="Z15" s="20" t="n">
-        <x:f>IF(Z5&gt;0,Assumptions!$B$46+MAX(0,Z5*Assumptions!$B$20-Assumptions!$B$47)*Assumptions!$B$48,0)</x:f>
+        <x:f>IF(Z5&gt;0,Assumptions!$B$54+MAX(0,Z5*Assumptions!$B$20-Assumptions!$B$55)*Assumptions!$B$56,0)</x:f>
         <x:v>10480</x:v>
       </x:c>
       <x:c r="AA15" s="20" t="n">
-        <x:f>IF(AA5&gt;0,Assumptions!$B$46+MAX(0,AA5*Assumptions!$B$20-Assumptions!$B$47)*Assumptions!$B$48,0)</x:f>
+        <x:f>IF(AA5&gt;0,Assumptions!$B$54+MAX(0,AA5*Assumptions!$B$20-Assumptions!$B$55)*Assumptions!$B$56,0)</x:f>
         <x:v>10480</x:v>
       </x:c>
       <x:c r="AB15" s="20" t="n">
-        <x:f>IF(AB5&gt;0,Assumptions!$B$46+MAX(0,AB5*Assumptions!$B$20-Assumptions!$B$47)*Assumptions!$B$48,0)</x:f>
+        <x:f>IF(AB5&gt;0,Assumptions!$B$54+MAX(0,AB5*Assumptions!$B$20-Assumptions!$B$55)*Assumptions!$B$56,0)</x:f>
         <x:v>10480</x:v>
       </x:c>
       <x:c r="AC15" s="20" t="n">
-        <x:f>IF(AC5&gt;0,Assumptions!$B$46+MAX(0,AC5*Assumptions!$B$20-Assumptions!$B$47)*Assumptions!$B$48,0)</x:f>
+        <x:f>IF(AC5&gt;0,Assumptions!$B$54+MAX(0,AC5*Assumptions!$B$20-Assumptions!$B$55)*Assumptions!$B$56,0)</x:f>
         <x:v>10480</x:v>
       </x:c>
       <x:c r="AD15" s="20" t="n">
-        <x:f>IF(AD5&gt;0,Assumptions!$B$46+MAX(0,AD5*Assumptions!$B$20-Assumptions!$B$47)*Assumptions!$B$48,0)</x:f>
+        <x:f>IF(AD5&gt;0,Assumptions!$B$54+MAX(0,AD5*Assumptions!$B$20-Assumptions!$B$55)*Assumptions!$B$56,0)</x:f>
         <x:v>10480</x:v>
       </x:c>
       <x:c r="AE15" s="20" t="n">
-        <x:f>IF(AE5&gt;0,Assumptions!$B$46+MAX(0,AE5*Assumptions!$B$20-Assumptions!$B$47)*Assumptions!$B$48,0)</x:f>
+        <x:f>IF(AE5&gt;0,Assumptions!$B$54+MAX(0,AE5*Assumptions!$B$20-Assumptions!$B$55)*Assumptions!$B$56,0)</x:f>
         <x:v>10480</x:v>
       </x:c>
       <x:c r="AF15" s="20" t="n">
-        <x:f>IF(AF5&gt;0,Assumptions!$B$46+MAX(0,AF5*Assumptions!$B$20-Assumptions!$B$47)*Assumptions!$B$48,0)</x:f>
+        <x:f>IF(AF5&gt;0,Assumptions!$B$54+MAX(0,AF5*Assumptions!$B$20-Assumptions!$B$55)*Assumptions!$B$56,0)</x:f>
         <x:v>10480</x:v>
       </x:c>
       <x:c r="AG15" s="20" t="n">
-        <x:f>IF(AG5&gt;0,Assumptions!$B$46+MAX(0,AG5*Assumptions!$B$20-Assumptions!$B$47)*Assumptions!$B$48,0)</x:f>
+        <x:f>IF(AG5&gt;0,Assumptions!$B$54+MAX(0,AG5*Assumptions!$B$20-Assumptions!$B$55)*Assumptions!$B$56,0)</x:f>
         <x:v>10480</x:v>
       </x:c>
       <x:c r="AH15" s="20" t="n">
-        <x:f>IF(AH5&gt;0,Assumptions!$B$46+MAX(0,AH5*Assumptions!$B$20-Assumptions!$B$47)*Assumptions!$B$48,0)</x:f>
+        <x:f>IF(AH5&gt;0,Assumptions!$B$54+MAX(0,AH5*Assumptions!$B$20-Assumptions!$B$55)*Assumptions!$B$56,0)</x:f>
         <x:v>10480</x:v>
       </x:c>
       <x:c r="AI15" s="20" t="n">
-        <x:f>IF(AI5&gt;0,Assumptions!$B$46+MAX(0,AI5*Assumptions!$B$20-Assumptions!$B$47)*Assumptions!$B$48,0)</x:f>
+        <x:f>IF(AI5&gt;0,Assumptions!$B$54+MAX(0,AI5*Assumptions!$B$20-Assumptions!$B$55)*Assumptions!$B$56,0)</x:f>
         <x:v>10480</x:v>
       </x:c>
       <x:c r="AJ15" s="20" t="n">
-        <x:f>IF(AJ5&gt;0,Assumptions!$B$46+MAX(0,AJ5*Assumptions!$B$20-Assumptions!$B$47)*Assumptions!$B$48,0)</x:f>
+        <x:f>IF(AJ5&gt;0,Assumptions!$B$54+MAX(0,AJ5*Assumptions!$B$20-Assumptions!$B$55)*Assumptions!$B$56,0)</x:f>
         <x:v>10480</x:v>
       </x:c>
       <x:c r="AK15" s="20" t="n">
-        <x:f>IF(AK5&gt;0,Assumptions!$B$46+MAX(0,AK5*Assumptions!$B$20-Assumptions!$B$47)*Assumptions!$B$48,0)</x:f>
+        <x:f>IF(AK5&gt;0,Assumptions!$B$54+MAX(0,AK5*Assumptions!$B$20-Assumptions!$B$55)*Assumptions!$B$56,0)</x:f>
         <x:v>10480</x:v>
       </x:c>
     </x:row>
@@ -4579,147 +4947,147 @@
         </x:is>
       </x:c>
       <x:c r="B16" s="20" t="n">
-        <x:f>B5*Assumptions!$B$49*Assumptions!$B$50*Assumptions!$B$51</x:f>
+        <x:f>B5*Assumptions!$B$57*Assumptions!$B$58*Assumptions!$B$59</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C16" s="20" t="n">
-        <x:f>C5*Assumptions!$B$49*Assumptions!$B$50*Assumptions!$B$51</x:f>
+        <x:f>C5*Assumptions!$B$57*Assumptions!$B$58*Assumptions!$B$59</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D16" s="20" t="n">
-        <x:f>D5*Assumptions!$B$49*Assumptions!$B$50*Assumptions!$B$51</x:f>
+        <x:f>D5*Assumptions!$B$57*Assumptions!$B$58*Assumptions!$B$59</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="E16" s="20" t="n">
-        <x:f>E5*Assumptions!$B$49*Assumptions!$B$50*Assumptions!$B$51</x:f>
+        <x:f>E5*Assumptions!$B$57*Assumptions!$B$58*Assumptions!$B$59</x:f>
         <x:v>360</x:v>
       </x:c>
       <x:c r="F16" s="20" t="n">
-        <x:f>F5*Assumptions!$B$49*Assumptions!$B$50*Assumptions!$B$51</x:f>
+        <x:f>F5*Assumptions!$B$57*Assumptions!$B$58*Assumptions!$B$59</x:f>
         <x:v>360</x:v>
       </x:c>
       <x:c r="G16" s="20" t="n">
-        <x:f>G5*Assumptions!$B$49*Assumptions!$B$50*Assumptions!$B$51</x:f>
+        <x:f>G5*Assumptions!$B$57*Assumptions!$B$58*Assumptions!$B$59</x:f>
         <x:v>360</x:v>
       </x:c>
       <x:c r="H16" s="20" t="n">
-        <x:f>H5*Assumptions!$B$49*Assumptions!$B$50*Assumptions!$B$51</x:f>
+        <x:f>H5*Assumptions!$B$57*Assumptions!$B$58*Assumptions!$B$59</x:f>
         <x:v>810</x:v>
       </x:c>
       <x:c r="I16" s="20" t="n">
-        <x:f>I5*Assumptions!$B$49*Assumptions!$B$50*Assumptions!$B$51</x:f>
+        <x:f>I5*Assumptions!$B$57*Assumptions!$B$58*Assumptions!$B$59</x:f>
         <x:v>810</x:v>
       </x:c>
       <x:c r="J16" s="20" t="n">
-        <x:f>J5*Assumptions!$B$49*Assumptions!$B$50*Assumptions!$B$51</x:f>
+        <x:f>J5*Assumptions!$B$57*Assumptions!$B$58*Assumptions!$B$59</x:f>
         <x:v>810</x:v>
       </x:c>
       <x:c r="K16" s="20" t="n">
-        <x:f>K5*Assumptions!$B$49*Assumptions!$B$50*Assumptions!$B$51</x:f>
+        <x:f>K5*Assumptions!$B$57*Assumptions!$B$58*Assumptions!$B$59</x:f>
         <x:v>810</x:v>
       </x:c>
       <x:c r="L16" s="20" t="n">
-        <x:f>L5*Assumptions!$B$49*Assumptions!$B$50*Assumptions!$B$51</x:f>
+        <x:f>L5*Assumptions!$B$57*Assumptions!$B$58*Assumptions!$B$59</x:f>
         <x:v>810</x:v>
       </x:c>
       <x:c r="M16" s="20" t="n">
-        <x:f>M5*Assumptions!$B$49*Assumptions!$B$50*Assumptions!$B$51</x:f>
+        <x:f>M5*Assumptions!$B$57*Assumptions!$B$58*Assumptions!$B$59</x:f>
         <x:v>810</x:v>
       </x:c>
       <x:c r="N16" s="20" t="n">
-        <x:f>N5*Assumptions!$B$49*Assumptions!$B$50*Assumptions!$B$51</x:f>
+        <x:f>N5*Assumptions!$B$57*Assumptions!$B$58*Assumptions!$B$59</x:f>
         <x:v>1350</x:v>
       </x:c>
       <x:c r="O16" s="20" t="n">
-        <x:f>O5*Assumptions!$B$49*Assumptions!$B$50*Assumptions!$B$51</x:f>
+        <x:f>O5*Assumptions!$B$57*Assumptions!$B$58*Assumptions!$B$59</x:f>
         <x:v>1350</x:v>
       </x:c>
       <x:c r="P16" s="20" t="n">
-        <x:f>P5*Assumptions!$B$49*Assumptions!$B$50*Assumptions!$B$51</x:f>
+        <x:f>P5*Assumptions!$B$57*Assumptions!$B$58*Assumptions!$B$59</x:f>
         <x:v>1350</x:v>
       </x:c>
       <x:c r="Q16" s="20" t="n">
-        <x:f>Q5*Assumptions!$B$49*Assumptions!$B$50*Assumptions!$B$51</x:f>
+        <x:f>Q5*Assumptions!$B$57*Assumptions!$B$58*Assumptions!$B$59</x:f>
         <x:v>1350</x:v>
       </x:c>
       <x:c r="R16" s="20" t="n">
-        <x:f>R5*Assumptions!$B$49*Assumptions!$B$50*Assumptions!$B$51</x:f>
+        <x:f>R5*Assumptions!$B$57*Assumptions!$B$58*Assumptions!$B$59</x:f>
         <x:v>1350</x:v>
       </x:c>
       <x:c r="S16" s="20" t="n">
-        <x:f>S5*Assumptions!$B$49*Assumptions!$B$50*Assumptions!$B$51</x:f>
+        <x:f>S5*Assumptions!$B$57*Assumptions!$B$58*Assumptions!$B$59</x:f>
         <x:v>1350</x:v>
       </x:c>
       <x:c r="T16" s="20" t="n">
-        <x:f>T5*Assumptions!$B$49*Assumptions!$B$50*Assumptions!$B$51</x:f>
+        <x:f>T5*Assumptions!$B$57*Assumptions!$B$58*Assumptions!$B$59</x:f>
         <x:v>1350</x:v>
       </x:c>
       <x:c r="U16" s="20" t="n">
-        <x:f>U5*Assumptions!$B$49*Assumptions!$B$50*Assumptions!$B$51</x:f>
+        <x:f>U5*Assumptions!$B$57*Assumptions!$B$58*Assumptions!$B$59</x:f>
         <x:v>1350</x:v>
       </x:c>
       <x:c r="V16" s="20" t="n">
-        <x:f>V5*Assumptions!$B$49*Assumptions!$B$50*Assumptions!$B$51</x:f>
+        <x:f>V5*Assumptions!$B$57*Assumptions!$B$58*Assumptions!$B$59</x:f>
         <x:v>1350</x:v>
       </x:c>
       <x:c r="W16" s="20" t="n">
-        <x:f>W5*Assumptions!$B$49*Assumptions!$B$50*Assumptions!$B$51</x:f>
+        <x:f>W5*Assumptions!$B$57*Assumptions!$B$58*Assumptions!$B$59</x:f>
         <x:v>1350</x:v>
       </x:c>
       <x:c r="X16" s="20" t="n">
-        <x:f>X5*Assumptions!$B$49*Assumptions!$B$50*Assumptions!$B$51</x:f>
+        <x:f>X5*Assumptions!$B$57*Assumptions!$B$58*Assumptions!$B$59</x:f>
         <x:v>1350</x:v>
       </x:c>
       <x:c r="Y16" s="20" t="n">
-        <x:f>Y5*Assumptions!$B$49*Assumptions!$B$50*Assumptions!$B$51</x:f>
+        <x:f>Y5*Assumptions!$B$57*Assumptions!$B$58*Assumptions!$B$59</x:f>
         <x:v>1350</x:v>
       </x:c>
       <x:c r="Z16" s="20" t="n">
-        <x:f>Z5*Assumptions!$B$49*Assumptions!$B$50*Assumptions!$B$51</x:f>
+        <x:f>Z5*Assumptions!$B$57*Assumptions!$B$58*Assumptions!$B$59</x:f>
         <x:v>1350</x:v>
       </x:c>
       <x:c r="AA16" s="20" t="n">
-        <x:f>AA5*Assumptions!$B$49*Assumptions!$B$50*Assumptions!$B$51</x:f>
+        <x:f>AA5*Assumptions!$B$57*Assumptions!$B$58*Assumptions!$B$59</x:f>
         <x:v>1350</x:v>
       </x:c>
       <x:c r="AB16" s="20" t="n">
-        <x:f>AB5*Assumptions!$B$49*Assumptions!$B$50*Assumptions!$B$51</x:f>
+        <x:f>AB5*Assumptions!$B$57*Assumptions!$B$58*Assumptions!$B$59</x:f>
         <x:v>1350</x:v>
       </x:c>
       <x:c r="AC16" s="20" t="n">
-        <x:f>AC5*Assumptions!$B$49*Assumptions!$B$50*Assumptions!$B$51</x:f>
+        <x:f>AC5*Assumptions!$B$57*Assumptions!$B$58*Assumptions!$B$59</x:f>
         <x:v>1350</x:v>
       </x:c>
       <x:c r="AD16" s="20" t="n">
-        <x:f>AD5*Assumptions!$B$49*Assumptions!$B$50*Assumptions!$B$51</x:f>
+        <x:f>AD5*Assumptions!$B$57*Assumptions!$B$58*Assumptions!$B$59</x:f>
         <x:v>1350</x:v>
       </x:c>
       <x:c r="AE16" s="20" t="n">
-        <x:f>AE5*Assumptions!$B$49*Assumptions!$B$50*Assumptions!$B$51</x:f>
+        <x:f>AE5*Assumptions!$B$57*Assumptions!$B$58*Assumptions!$B$59</x:f>
         <x:v>1350</x:v>
       </x:c>
       <x:c r="AF16" s="20" t="n">
-        <x:f>AF5*Assumptions!$B$49*Assumptions!$B$50*Assumptions!$B$51</x:f>
+        <x:f>AF5*Assumptions!$B$57*Assumptions!$B$58*Assumptions!$B$59</x:f>
         <x:v>1350</x:v>
       </x:c>
       <x:c r="AG16" s="20" t="n">
-        <x:f>AG5*Assumptions!$B$49*Assumptions!$B$50*Assumptions!$B$51</x:f>
+        <x:f>AG5*Assumptions!$B$57*Assumptions!$B$58*Assumptions!$B$59</x:f>
         <x:v>1350</x:v>
       </x:c>
       <x:c r="AH16" s="20" t="n">
-        <x:f>AH5*Assumptions!$B$49*Assumptions!$B$50*Assumptions!$B$51</x:f>
+        <x:f>AH5*Assumptions!$B$57*Assumptions!$B$58*Assumptions!$B$59</x:f>
         <x:v>1350</x:v>
       </x:c>
       <x:c r="AI16" s="20" t="n">
-        <x:f>AI5*Assumptions!$B$49*Assumptions!$B$50*Assumptions!$B$51</x:f>
+        <x:f>AI5*Assumptions!$B$57*Assumptions!$B$58*Assumptions!$B$59</x:f>
         <x:v>1350</x:v>
       </x:c>
       <x:c r="AJ16" s="20" t="n">
-        <x:f>AJ5*Assumptions!$B$49*Assumptions!$B$50*Assumptions!$B$51</x:f>
+        <x:f>AJ5*Assumptions!$B$57*Assumptions!$B$58*Assumptions!$B$59</x:f>
         <x:v>1350</x:v>
       </x:c>
       <x:c r="AK16" s="20" t="n">
-        <x:f>AK5*Assumptions!$B$49*Assumptions!$B$50*Assumptions!$B$51</x:f>
+        <x:f>AK5*Assumptions!$B$57*Assumptions!$B$58*Assumptions!$B$59</x:f>
         <x:v>1350</x:v>
       </x:c>
     </x:row>
@@ -4730,1052 +5098,1203 @@
         </x:is>
       </x:c>
       <x:c r="B17" s="20" t="n">
-        <x:f>IF(B5&gt;0,Assumptions!$B$52+Assumptions!$B$53*B5,0)</x:f>
+        <x:f>IF(B5&gt;0,Assumptions!$B$60+Assumptions!$B$61*B5,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C17" s="20" t="n">
-        <x:f>IF(C5&gt;0,Assumptions!$B$52+Assumptions!$B$53*C5,0)</x:f>
+        <x:f>IF(C5&gt;0,Assumptions!$B$60+Assumptions!$B$61*C5,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D17" s="20" t="n">
-        <x:f>IF(D5&gt;0,Assumptions!$B$52+Assumptions!$B$53*D5,0)</x:f>
+        <x:f>IF(D5&gt;0,Assumptions!$B$60+Assumptions!$B$61*D5,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="E17" s="20" t="n">
-        <x:f>IF(E5&gt;0,Assumptions!$B$52+Assumptions!$B$53*E5,0)</x:f>
+        <x:f>IF(E5&gt;0,Assumptions!$B$60+Assumptions!$B$61*E5,0)</x:f>
         <x:v>33000</x:v>
       </x:c>
       <x:c r="F17" s="20" t="n">
-        <x:f>IF(F5&gt;0,Assumptions!$B$52+Assumptions!$B$53*F5,0)</x:f>
+        <x:f>IF(F5&gt;0,Assumptions!$B$60+Assumptions!$B$61*F5,0)</x:f>
         <x:v>33000</x:v>
       </x:c>
       <x:c r="G17" s="20" t="n">
-        <x:f>IF(G5&gt;0,Assumptions!$B$52+Assumptions!$B$53*G5,0)</x:f>
+        <x:f>IF(G5&gt;0,Assumptions!$B$60+Assumptions!$B$61*G5,0)</x:f>
         <x:v>33000</x:v>
       </x:c>
       <x:c r="H17" s="20" t="n">
-        <x:f>IF(H5&gt;0,Assumptions!$B$52+Assumptions!$B$53*H5,0)</x:f>
+        <x:f>IF(H5&gt;0,Assumptions!$B$60+Assumptions!$B$61*H5,0)</x:f>
         <x:v>36750</x:v>
       </x:c>
       <x:c r="I17" s="20" t="n">
-        <x:f>IF(I5&gt;0,Assumptions!$B$52+Assumptions!$B$53*I5,0)</x:f>
+        <x:f>IF(I5&gt;0,Assumptions!$B$60+Assumptions!$B$61*I5,0)</x:f>
         <x:v>36750</x:v>
       </x:c>
       <x:c r="J17" s="20" t="n">
-        <x:f>IF(J5&gt;0,Assumptions!$B$52+Assumptions!$B$53*J5,0)</x:f>
+        <x:f>IF(J5&gt;0,Assumptions!$B$60+Assumptions!$B$61*J5,0)</x:f>
         <x:v>36750</x:v>
       </x:c>
       <x:c r="K17" s="20" t="n">
-        <x:f>IF(K5&gt;0,Assumptions!$B$52+Assumptions!$B$53*K5,0)</x:f>
+        <x:f>IF(K5&gt;0,Assumptions!$B$60+Assumptions!$B$61*K5,0)</x:f>
         <x:v>36750</x:v>
       </x:c>
       <x:c r="L17" s="20" t="n">
-        <x:f>IF(L5&gt;0,Assumptions!$B$52+Assumptions!$B$53*L5,0)</x:f>
+        <x:f>IF(L5&gt;0,Assumptions!$B$60+Assumptions!$B$61*L5,0)</x:f>
         <x:v>36750</x:v>
       </x:c>
       <x:c r="M17" s="20" t="n">
-        <x:f>IF(M5&gt;0,Assumptions!$B$52+Assumptions!$B$53*M5,0)</x:f>
+        <x:f>IF(M5&gt;0,Assumptions!$B$60+Assumptions!$B$61*M5,0)</x:f>
         <x:v>36750</x:v>
       </x:c>
       <x:c r="N17" s="20" t="n">
-        <x:f>IF(N5&gt;0,Assumptions!$B$52+Assumptions!$B$53*N5,0)</x:f>
+        <x:f>IF(N5&gt;0,Assumptions!$B$60+Assumptions!$B$61*N5,0)</x:f>
         <x:v>41250</x:v>
       </x:c>
       <x:c r="O17" s="20" t="n">
-        <x:f>IF(O5&gt;0,Assumptions!$B$52+Assumptions!$B$53*O5,0)</x:f>
+        <x:f>IF(O5&gt;0,Assumptions!$B$60+Assumptions!$B$61*O5,0)</x:f>
         <x:v>41250</x:v>
       </x:c>
       <x:c r="P17" s="20" t="n">
-        <x:f>IF(P5&gt;0,Assumptions!$B$52+Assumptions!$B$53*P5,0)</x:f>
+        <x:f>IF(P5&gt;0,Assumptions!$B$60+Assumptions!$B$61*P5,0)</x:f>
         <x:v>41250</x:v>
       </x:c>
       <x:c r="Q17" s="20" t="n">
-        <x:f>IF(Q5&gt;0,Assumptions!$B$52+Assumptions!$B$53*Q5,0)</x:f>
+        <x:f>IF(Q5&gt;0,Assumptions!$B$60+Assumptions!$B$61*Q5,0)</x:f>
         <x:v>41250</x:v>
       </x:c>
       <x:c r="R17" s="20" t="n">
-        <x:f>IF(R5&gt;0,Assumptions!$B$52+Assumptions!$B$53*R5,0)</x:f>
+        <x:f>IF(R5&gt;0,Assumptions!$B$60+Assumptions!$B$61*R5,0)</x:f>
         <x:v>41250</x:v>
       </x:c>
       <x:c r="S17" s="20" t="n">
-        <x:f>IF(S5&gt;0,Assumptions!$B$52+Assumptions!$B$53*S5,0)</x:f>
+        <x:f>IF(S5&gt;0,Assumptions!$B$60+Assumptions!$B$61*S5,0)</x:f>
         <x:v>41250</x:v>
       </x:c>
       <x:c r="T17" s="20" t="n">
-        <x:f>IF(T5&gt;0,Assumptions!$B$52+Assumptions!$B$53*T5,0)</x:f>
+        <x:f>IF(T5&gt;0,Assumptions!$B$60+Assumptions!$B$61*T5,0)</x:f>
         <x:v>41250</x:v>
       </x:c>
       <x:c r="U17" s="20" t="n">
-        <x:f>IF(U5&gt;0,Assumptions!$B$52+Assumptions!$B$53*U5,0)</x:f>
+        <x:f>IF(U5&gt;0,Assumptions!$B$60+Assumptions!$B$61*U5,0)</x:f>
         <x:v>41250</x:v>
       </x:c>
       <x:c r="V17" s="20" t="n">
-        <x:f>IF(V5&gt;0,Assumptions!$B$52+Assumptions!$B$53*V5,0)</x:f>
+        <x:f>IF(V5&gt;0,Assumptions!$B$60+Assumptions!$B$61*V5,0)</x:f>
         <x:v>41250</x:v>
       </x:c>
       <x:c r="W17" s="20" t="n">
-        <x:f>IF(W5&gt;0,Assumptions!$B$52+Assumptions!$B$53*W5,0)</x:f>
+        <x:f>IF(W5&gt;0,Assumptions!$B$60+Assumptions!$B$61*W5,0)</x:f>
         <x:v>41250</x:v>
       </x:c>
       <x:c r="X17" s="20" t="n">
-        <x:f>IF(X5&gt;0,Assumptions!$B$52+Assumptions!$B$53*X5,0)</x:f>
+        <x:f>IF(X5&gt;0,Assumptions!$B$60+Assumptions!$B$61*X5,0)</x:f>
         <x:v>41250</x:v>
       </x:c>
       <x:c r="Y17" s="20" t="n">
-        <x:f>IF(Y5&gt;0,Assumptions!$B$52+Assumptions!$B$53*Y5,0)</x:f>
+        <x:f>IF(Y5&gt;0,Assumptions!$B$60+Assumptions!$B$61*Y5,0)</x:f>
         <x:v>41250</x:v>
       </x:c>
       <x:c r="Z17" s="20" t="n">
-        <x:f>IF(Z5&gt;0,Assumptions!$B$52+Assumptions!$B$53*Z5,0)</x:f>
+        <x:f>IF(Z5&gt;0,Assumptions!$B$60+Assumptions!$B$61*Z5,0)</x:f>
         <x:v>41250</x:v>
       </x:c>
       <x:c r="AA17" s="20" t="n">
-        <x:f>IF(AA5&gt;0,Assumptions!$B$52+Assumptions!$B$53*AA5,0)</x:f>
+        <x:f>IF(AA5&gt;0,Assumptions!$B$60+Assumptions!$B$61*AA5,0)</x:f>
         <x:v>41250</x:v>
       </x:c>
       <x:c r="AB17" s="20" t="n">
-        <x:f>IF(AB5&gt;0,Assumptions!$B$52+Assumptions!$B$53*AB5,0)</x:f>
+        <x:f>IF(AB5&gt;0,Assumptions!$B$60+Assumptions!$B$61*AB5,0)</x:f>
         <x:v>41250</x:v>
       </x:c>
       <x:c r="AC17" s="20" t="n">
-        <x:f>IF(AC5&gt;0,Assumptions!$B$52+Assumptions!$B$53*AC5,0)</x:f>
+        <x:f>IF(AC5&gt;0,Assumptions!$B$60+Assumptions!$B$61*AC5,0)</x:f>
         <x:v>41250</x:v>
       </x:c>
       <x:c r="AD17" s="20" t="n">
-        <x:f>IF(AD5&gt;0,Assumptions!$B$52+Assumptions!$B$53*AD5,0)</x:f>
+        <x:f>IF(AD5&gt;0,Assumptions!$B$60+Assumptions!$B$61*AD5,0)</x:f>
         <x:v>41250</x:v>
       </x:c>
       <x:c r="AE17" s="20" t="n">
-        <x:f>IF(AE5&gt;0,Assumptions!$B$52+Assumptions!$B$53*AE5,0)</x:f>
+        <x:f>IF(AE5&gt;0,Assumptions!$B$60+Assumptions!$B$61*AE5,0)</x:f>
         <x:v>41250</x:v>
       </x:c>
       <x:c r="AF17" s="20" t="n">
-        <x:f>IF(AF5&gt;0,Assumptions!$B$52+Assumptions!$B$53*AF5,0)</x:f>
+        <x:f>IF(AF5&gt;0,Assumptions!$B$60+Assumptions!$B$61*AF5,0)</x:f>
         <x:v>41250</x:v>
       </x:c>
       <x:c r="AG17" s="20" t="n">
-        <x:f>IF(AG5&gt;0,Assumptions!$B$52+Assumptions!$B$53*AG5,0)</x:f>
+        <x:f>IF(AG5&gt;0,Assumptions!$B$60+Assumptions!$B$61*AG5,0)</x:f>
         <x:v>41250</x:v>
       </x:c>
       <x:c r="AH17" s="20" t="n">
-        <x:f>IF(AH5&gt;0,Assumptions!$B$52+Assumptions!$B$53*AH5,0)</x:f>
+        <x:f>IF(AH5&gt;0,Assumptions!$B$60+Assumptions!$B$61*AH5,0)</x:f>
         <x:v>41250</x:v>
       </x:c>
       <x:c r="AI17" s="20" t="n">
-        <x:f>IF(AI5&gt;0,Assumptions!$B$52+Assumptions!$B$53*AI5,0)</x:f>
+        <x:f>IF(AI5&gt;0,Assumptions!$B$60+Assumptions!$B$61*AI5,0)</x:f>
         <x:v>41250</x:v>
       </x:c>
       <x:c r="AJ17" s="20" t="n">
-        <x:f>IF(AJ5&gt;0,Assumptions!$B$52+Assumptions!$B$53*AJ5,0)</x:f>
+        <x:f>IF(AJ5&gt;0,Assumptions!$B$60+Assumptions!$B$61*AJ5,0)</x:f>
         <x:v>41250</x:v>
       </x:c>
       <x:c r="AK17" s="20" t="n">
-        <x:f>IF(AK5&gt;0,Assumptions!$B$52+Assumptions!$B$53*AK5,0)</x:f>
+        <x:f>IF(AK5&gt;0,Assumptions!$B$60+Assumptions!$B$61*AK5,0)</x:f>
         <x:v>41250</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Security and compliance</x:t>
+          <x:t xml:space="preserve">Team software subscriptions (Claude Max, GitHub, Jira)</x:t>
         </x:is>
       </x:c>
       <x:c r="B18" s="20" t="n">
-        <x:f>IF(B5&gt;0,(Assumptions!$B$54+Assumptions!$B$55)/12,0)</x:f>
+        <x:f>IF(B5&gt;0,(ROUNDUP(IF(B5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$65+Assumptions!$B$67+Assumptions!$B$68)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+B5/Assumptions!$B$77+MAX(1,B5/Assumptions!$B$78),0)*(Assumptions!$B$66+Assumptions!$B$68))*Assumptions!$B$6,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C18" s="20" t="n">
-        <x:f>IF(C5&gt;0,(Assumptions!$B$54+Assumptions!$B$55)/12,0)</x:f>
+        <x:f>IF(C5&gt;0,(ROUNDUP(IF(C5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$65+Assumptions!$B$67+Assumptions!$B$68)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+C5/Assumptions!$B$77+MAX(1,C5/Assumptions!$B$78),0)*(Assumptions!$B$66+Assumptions!$B$68))*Assumptions!$B$6,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D18" s="20" t="n">
-        <x:f>IF(D5&gt;0,(Assumptions!$B$54+Assumptions!$B$55)/12,0)</x:f>
+        <x:f>IF(D5&gt;0,(ROUNDUP(IF(D5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$65+Assumptions!$B$67+Assumptions!$B$68)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+D5/Assumptions!$B$77+MAX(1,D5/Assumptions!$B$78),0)*(Assumptions!$B$66+Assumptions!$B$68))*Assumptions!$B$6,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="E18" s="20" t="n">
-        <x:f>IF(E5&gt;0,(Assumptions!$B$54+Assumptions!$B$55)/12,0)</x:f>
-        <x:v>50000</x:v>
+        <x:f>IF(E5&gt;0,(ROUNDUP(IF(E5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$65+Assumptions!$B$67+Assumptions!$B$68)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+E5/Assumptions!$B$77+MAX(1,E5/Assumptions!$B$78),0)*(Assumptions!$B$66+Assumptions!$B$68))*Assumptions!$B$6,0)</x:f>
+        <x:v>32621.64</x:v>
       </x:c>
       <x:c r="F18" s="20" t="n">
-        <x:f>IF(F5&gt;0,(Assumptions!$B$54+Assumptions!$B$55)/12,0)</x:f>
-        <x:v>50000</x:v>
+        <x:f>IF(F5&gt;0,(ROUNDUP(IF(F5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$65+Assumptions!$B$67+Assumptions!$B$68)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+F5/Assumptions!$B$77+MAX(1,F5/Assumptions!$B$78),0)*(Assumptions!$B$66+Assumptions!$B$68))*Assumptions!$B$6,0)</x:f>
+        <x:v>32621.64</x:v>
       </x:c>
       <x:c r="G18" s="20" t="n">
-        <x:f>IF(G5&gt;0,(Assumptions!$B$54+Assumptions!$B$55)/12,0)</x:f>
-        <x:v>50000</x:v>
+        <x:f>IF(G5&gt;0,(ROUNDUP(IF(G5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$65+Assumptions!$B$67+Assumptions!$B$68)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+G5/Assumptions!$B$77+MAX(1,G5/Assumptions!$B$78),0)*(Assumptions!$B$66+Assumptions!$B$68))*Assumptions!$B$6,0)</x:f>
+        <x:v>32621.64</x:v>
       </x:c>
       <x:c r="H18" s="20" t="n">
-        <x:f>IF(H5&gt;0,(Assumptions!$B$54+Assumptions!$B$55)/12,0)</x:f>
-        <x:v>50000</x:v>
+        <x:f>IF(H5&gt;0,(ROUNDUP(IF(H5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$65+Assumptions!$B$67+Assumptions!$B$68)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+H5/Assumptions!$B$77+MAX(1,H5/Assumptions!$B$78),0)*(Assumptions!$B$66+Assumptions!$B$68))*Assumptions!$B$6,0)</x:f>
+        <x:v>36290.579999999994</x:v>
       </x:c>
       <x:c r="I18" s="20" t="n">
-        <x:f>IF(I5&gt;0,(Assumptions!$B$54+Assumptions!$B$55)/12,0)</x:f>
-        <x:v>50000</x:v>
+        <x:f>IF(I5&gt;0,(ROUNDUP(IF(I5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$65+Assumptions!$B$67+Assumptions!$B$68)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+I5/Assumptions!$B$77+MAX(1,I5/Assumptions!$B$78),0)*(Assumptions!$B$66+Assumptions!$B$68))*Assumptions!$B$6,0)</x:f>
+        <x:v>36290.579999999994</x:v>
       </x:c>
       <x:c r="J18" s="20" t="n">
-        <x:f>IF(J5&gt;0,(Assumptions!$B$54+Assumptions!$B$55)/12,0)</x:f>
-        <x:v>50000</x:v>
+        <x:f>IF(J5&gt;0,(ROUNDUP(IF(J5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$65+Assumptions!$B$67+Assumptions!$B$68)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+J5/Assumptions!$B$77+MAX(1,J5/Assumptions!$B$78),0)*(Assumptions!$B$66+Assumptions!$B$68))*Assumptions!$B$6,0)</x:f>
+        <x:v>36290.579999999994</x:v>
       </x:c>
       <x:c r="K18" s="20" t="n">
-        <x:f>IF(K5&gt;0,(Assumptions!$B$54+Assumptions!$B$55)/12,0)</x:f>
-        <x:v>50000</x:v>
+        <x:f>IF(K5&gt;0,(ROUNDUP(IF(K5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$65+Assumptions!$B$67+Assumptions!$B$68)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+K5/Assumptions!$B$77+MAX(1,K5/Assumptions!$B$78),0)*(Assumptions!$B$66+Assumptions!$B$68))*Assumptions!$B$6,0)</x:f>
+        <x:v>36290.579999999994</x:v>
       </x:c>
       <x:c r="L18" s="20" t="n">
-        <x:f>IF(L5&gt;0,(Assumptions!$B$54+Assumptions!$B$55)/12,0)</x:f>
-        <x:v>50000</x:v>
+        <x:f>IF(L5&gt;0,(ROUNDUP(IF(L5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$65+Assumptions!$B$67+Assumptions!$B$68)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+L5/Assumptions!$B$77+MAX(1,L5/Assumptions!$B$78),0)*(Assumptions!$B$66+Assumptions!$B$68))*Assumptions!$B$6,0)</x:f>
+        <x:v>36290.579999999994</x:v>
       </x:c>
       <x:c r="M18" s="20" t="n">
-        <x:f>IF(M5&gt;0,(Assumptions!$B$54+Assumptions!$B$55)/12,0)</x:f>
-        <x:v>50000</x:v>
+        <x:f>IF(M5&gt;0,(ROUNDUP(IF(M5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$65+Assumptions!$B$67+Assumptions!$B$68)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+M5/Assumptions!$B$77+MAX(1,M5/Assumptions!$B$78),0)*(Assumptions!$B$66+Assumptions!$B$68))*Assumptions!$B$6,0)</x:f>
+        <x:v>36290.579999999994</x:v>
       </x:c>
       <x:c r="N18" s="20" t="n">
-        <x:f>IF(N5&gt;0,(Assumptions!$B$54+Assumptions!$B$55)/12,0)</x:f>
-        <x:v>50000</x:v>
+        <x:f>IF(N5&gt;0,(ROUNDUP(IF(N5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$65+Assumptions!$B$67+Assumptions!$B$68)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+N5/Assumptions!$B$77+MAX(1,N5/Assumptions!$B$78),0)*(Assumptions!$B$66+Assumptions!$B$68))*Assumptions!$B$6,0)</x:f>
+        <x:v>39959.52</x:v>
       </x:c>
       <x:c r="O18" s="20" t="n">
-        <x:f>IF(O5&gt;0,(Assumptions!$B$54+Assumptions!$B$55)/12,0)</x:f>
-        <x:v>50000</x:v>
+        <x:f>IF(O5&gt;0,(ROUNDUP(IF(O5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$65+Assumptions!$B$67+Assumptions!$B$68)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+O5/Assumptions!$B$77+MAX(1,O5/Assumptions!$B$78),0)*(Assumptions!$B$66+Assumptions!$B$68))*Assumptions!$B$6,0)</x:f>
+        <x:v>39959.52</x:v>
       </x:c>
       <x:c r="P18" s="20" t="n">
-        <x:f>IF(P5&gt;0,(Assumptions!$B$54+Assumptions!$B$55)/12,0)</x:f>
-        <x:v>50000</x:v>
+        <x:f>IF(P5&gt;0,(ROUNDUP(IF(P5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$65+Assumptions!$B$67+Assumptions!$B$68)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+P5/Assumptions!$B$77+MAX(1,P5/Assumptions!$B$78),0)*(Assumptions!$B$66+Assumptions!$B$68))*Assumptions!$B$6,0)</x:f>
+        <x:v>39959.52</x:v>
       </x:c>
       <x:c r="Q18" s="20" t="n">
-        <x:f>IF(Q5&gt;0,(Assumptions!$B$54+Assumptions!$B$55)/12,0)</x:f>
-        <x:v>50000</x:v>
+        <x:f>IF(Q5&gt;0,(ROUNDUP(IF(Q5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$65+Assumptions!$B$67+Assumptions!$B$68)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+Q5/Assumptions!$B$77+MAX(1,Q5/Assumptions!$B$78),0)*(Assumptions!$B$66+Assumptions!$B$68))*Assumptions!$B$6,0)</x:f>
+        <x:v>39959.52</x:v>
       </x:c>
       <x:c r="R18" s="20" t="n">
-        <x:f>IF(R5&gt;0,(Assumptions!$B$54+Assumptions!$B$55)/12,0)</x:f>
-        <x:v>50000</x:v>
+        <x:f>IF(R5&gt;0,(ROUNDUP(IF(R5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$65+Assumptions!$B$67+Assumptions!$B$68)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+R5/Assumptions!$B$77+MAX(1,R5/Assumptions!$B$78),0)*(Assumptions!$B$66+Assumptions!$B$68))*Assumptions!$B$6,0)</x:f>
+        <x:v>39959.52</x:v>
       </x:c>
       <x:c r="S18" s="20" t="n">
-        <x:f>IF(S5&gt;0,(Assumptions!$B$54+Assumptions!$B$55)/12,0)</x:f>
-        <x:v>50000</x:v>
+        <x:f>IF(S5&gt;0,(ROUNDUP(IF(S5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$65+Assumptions!$B$67+Assumptions!$B$68)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+S5/Assumptions!$B$77+MAX(1,S5/Assumptions!$B$78),0)*(Assumptions!$B$66+Assumptions!$B$68))*Assumptions!$B$6,0)</x:f>
+        <x:v>39959.52</x:v>
       </x:c>
       <x:c r="T18" s="20" t="n">
-        <x:f>IF(T5&gt;0,(Assumptions!$B$54+Assumptions!$B$55)/12,0)</x:f>
-        <x:v>50000</x:v>
+        <x:f>IF(T5&gt;0,(ROUNDUP(IF(T5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$65+Assumptions!$B$67+Assumptions!$B$68)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+T5/Assumptions!$B$77+MAX(1,T5/Assumptions!$B$78),0)*(Assumptions!$B$66+Assumptions!$B$68))*Assumptions!$B$6,0)</x:f>
+        <x:v>39959.52</x:v>
       </x:c>
       <x:c r="U18" s="20" t="n">
-        <x:f>IF(U5&gt;0,(Assumptions!$B$54+Assumptions!$B$55)/12,0)</x:f>
-        <x:v>50000</x:v>
+        <x:f>IF(U5&gt;0,(ROUNDUP(IF(U5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$65+Assumptions!$B$67+Assumptions!$B$68)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+U5/Assumptions!$B$77+MAX(1,U5/Assumptions!$B$78),0)*(Assumptions!$B$66+Assumptions!$B$68))*Assumptions!$B$6,0)</x:f>
+        <x:v>39959.52</x:v>
       </x:c>
       <x:c r="V18" s="20" t="n">
-        <x:f>IF(V5&gt;0,(Assumptions!$B$54+Assumptions!$B$55)/12,0)</x:f>
-        <x:v>50000</x:v>
+        <x:f>IF(V5&gt;0,(ROUNDUP(IF(V5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$65+Assumptions!$B$67+Assumptions!$B$68)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+V5/Assumptions!$B$77+MAX(1,V5/Assumptions!$B$78),0)*(Assumptions!$B$66+Assumptions!$B$68))*Assumptions!$B$6,0)</x:f>
+        <x:v>39959.52</x:v>
       </x:c>
       <x:c r="W18" s="20" t="n">
-        <x:f>IF(W5&gt;0,(Assumptions!$B$54+Assumptions!$B$55)/12,0)</x:f>
-        <x:v>50000</x:v>
+        <x:f>IF(W5&gt;0,(ROUNDUP(IF(W5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$65+Assumptions!$B$67+Assumptions!$B$68)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+W5/Assumptions!$B$77+MAX(1,W5/Assumptions!$B$78),0)*(Assumptions!$B$66+Assumptions!$B$68))*Assumptions!$B$6,0)</x:f>
+        <x:v>39959.52</x:v>
       </x:c>
       <x:c r="X18" s="20" t="n">
-        <x:f>IF(X5&gt;0,(Assumptions!$B$54+Assumptions!$B$55)/12,0)</x:f>
-        <x:v>50000</x:v>
+        <x:f>IF(X5&gt;0,(ROUNDUP(IF(X5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$65+Assumptions!$B$67+Assumptions!$B$68)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+X5/Assumptions!$B$77+MAX(1,X5/Assumptions!$B$78),0)*(Assumptions!$B$66+Assumptions!$B$68))*Assumptions!$B$6,0)</x:f>
+        <x:v>39959.52</x:v>
       </x:c>
       <x:c r="Y18" s="20" t="n">
-        <x:f>IF(Y5&gt;0,(Assumptions!$B$54+Assumptions!$B$55)/12,0)</x:f>
-        <x:v>50000</x:v>
+        <x:f>IF(Y5&gt;0,(ROUNDUP(IF(Y5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$65+Assumptions!$B$67+Assumptions!$B$68)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+Y5/Assumptions!$B$77+MAX(1,Y5/Assumptions!$B$78),0)*(Assumptions!$B$66+Assumptions!$B$68))*Assumptions!$B$6,0)</x:f>
+        <x:v>39959.52</x:v>
       </x:c>
       <x:c r="Z18" s="20" t="n">
-        <x:f>IF(Z5&gt;0,(Assumptions!$B$54+Assumptions!$B$55)/12,0)</x:f>
-        <x:v>50000</x:v>
+        <x:f>IF(Z5&gt;0,(ROUNDUP(IF(Z5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$65+Assumptions!$B$67+Assumptions!$B$68)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+Z5/Assumptions!$B$77+MAX(1,Z5/Assumptions!$B$78),0)*(Assumptions!$B$66+Assumptions!$B$68))*Assumptions!$B$6,0)</x:f>
+        <x:v>39959.52</x:v>
       </x:c>
       <x:c r="AA18" s="20" t="n">
-        <x:f>IF(AA5&gt;0,(Assumptions!$B$54+Assumptions!$B$55)/12,0)</x:f>
-        <x:v>50000</x:v>
+        <x:f>IF(AA5&gt;0,(ROUNDUP(IF(AA5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$65+Assumptions!$B$67+Assumptions!$B$68)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+AA5/Assumptions!$B$77+MAX(1,AA5/Assumptions!$B$78),0)*(Assumptions!$B$66+Assumptions!$B$68))*Assumptions!$B$6,0)</x:f>
+        <x:v>39959.52</x:v>
       </x:c>
       <x:c r="AB18" s="20" t="n">
-        <x:f>IF(AB5&gt;0,(Assumptions!$B$54+Assumptions!$B$55)/12,0)</x:f>
-        <x:v>50000</x:v>
+        <x:f>IF(AB5&gt;0,(ROUNDUP(IF(AB5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$65+Assumptions!$B$67+Assumptions!$B$68)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+AB5/Assumptions!$B$77+MAX(1,AB5/Assumptions!$B$78),0)*(Assumptions!$B$66+Assumptions!$B$68))*Assumptions!$B$6,0)</x:f>
+        <x:v>39959.52</x:v>
       </x:c>
       <x:c r="AC18" s="20" t="n">
-        <x:f>IF(AC5&gt;0,(Assumptions!$B$54+Assumptions!$B$55)/12,0)</x:f>
-        <x:v>50000</x:v>
+        <x:f>IF(AC5&gt;0,(ROUNDUP(IF(AC5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$65+Assumptions!$B$67+Assumptions!$B$68)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+AC5/Assumptions!$B$77+MAX(1,AC5/Assumptions!$B$78),0)*(Assumptions!$B$66+Assumptions!$B$68))*Assumptions!$B$6,0)</x:f>
+        <x:v>39959.52</x:v>
       </x:c>
       <x:c r="AD18" s="20" t="n">
-        <x:f>IF(AD5&gt;0,(Assumptions!$B$54+Assumptions!$B$55)/12,0)</x:f>
-        <x:v>50000</x:v>
+        <x:f>IF(AD5&gt;0,(ROUNDUP(IF(AD5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$65+Assumptions!$B$67+Assumptions!$B$68)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+AD5/Assumptions!$B$77+MAX(1,AD5/Assumptions!$B$78),0)*(Assumptions!$B$66+Assumptions!$B$68))*Assumptions!$B$6,0)</x:f>
+        <x:v>39959.52</x:v>
       </x:c>
       <x:c r="AE18" s="20" t="n">
-        <x:f>IF(AE5&gt;0,(Assumptions!$B$54+Assumptions!$B$55)/12,0)</x:f>
-        <x:v>50000</x:v>
+        <x:f>IF(AE5&gt;0,(ROUNDUP(IF(AE5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$65+Assumptions!$B$67+Assumptions!$B$68)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+AE5/Assumptions!$B$77+MAX(1,AE5/Assumptions!$B$78),0)*(Assumptions!$B$66+Assumptions!$B$68))*Assumptions!$B$6,0)</x:f>
+        <x:v>39959.52</x:v>
       </x:c>
       <x:c r="AF18" s="20" t="n">
-        <x:f>IF(AF5&gt;0,(Assumptions!$B$54+Assumptions!$B$55)/12,0)</x:f>
-        <x:v>50000</x:v>
+        <x:f>IF(AF5&gt;0,(ROUNDUP(IF(AF5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$65+Assumptions!$B$67+Assumptions!$B$68)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+AF5/Assumptions!$B$77+MAX(1,AF5/Assumptions!$B$78),0)*(Assumptions!$B$66+Assumptions!$B$68))*Assumptions!$B$6,0)</x:f>
+        <x:v>39959.52</x:v>
       </x:c>
       <x:c r="AG18" s="20" t="n">
-        <x:f>IF(AG5&gt;0,(Assumptions!$B$54+Assumptions!$B$55)/12,0)</x:f>
-        <x:v>50000</x:v>
+        <x:f>IF(AG5&gt;0,(ROUNDUP(IF(AG5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$65+Assumptions!$B$67+Assumptions!$B$68)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+AG5/Assumptions!$B$77+MAX(1,AG5/Assumptions!$B$78),0)*(Assumptions!$B$66+Assumptions!$B$68))*Assumptions!$B$6,0)</x:f>
+        <x:v>39959.52</x:v>
       </x:c>
       <x:c r="AH18" s="20" t="n">
-        <x:f>IF(AH5&gt;0,(Assumptions!$B$54+Assumptions!$B$55)/12,0)</x:f>
-        <x:v>50000</x:v>
+        <x:f>IF(AH5&gt;0,(ROUNDUP(IF(AH5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$65+Assumptions!$B$67+Assumptions!$B$68)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+AH5/Assumptions!$B$77+MAX(1,AH5/Assumptions!$B$78),0)*(Assumptions!$B$66+Assumptions!$B$68))*Assumptions!$B$6,0)</x:f>
+        <x:v>39959.52</x:v>
       </x:c>
       <x:c r="AI18" s="20" t="n">
-        <x:f>IF(AI5&gt;0,(Assumptions!$B$54+Assumptions!$B$55)/12,0)</x:f>
-        <x:v>50000</x:v>
+        <x:f>IF(AI5&gt;0,(ROUNDUP(IF(AI5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$65+Assumptions!$B$67+Assumptions!$B$68)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+AI5/Assumptions!$B$77+MAX(1,AI5/Assumptions!$B$78),0)*(Assumptions!$B$66+Assumptions!$B$68))*Assumptions!$B$6,0)</x:f>
+        <x:v>39959.52</x:v>
       </x:c>
       <x:c r="AJ18" s="20" t="n">
-        <x:f>IF(AJ5&gt;0,(Assumptions!$B$54+Assumptions!$B$55)/12,0)</x:f>
-        <x:v>50000</x:v>
+        <x:f>IF(AJ5&gt;0,(ROUNDUP(IF(AJ5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$65+Assumptions!$B$67+Assumptions!$B$68)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+AJ5/Assumptions!$B$77+MAX(1,AJ5/Assumptions!$B$78),0)*(Assumptions!$B$66+Assumptions!$B$68))*Assumptions!$B$6,0)</x:f>
+        <x:v>39959.52</x:v>
       </x:c>
       <x:c r="AK18" s="20" t="n">
-        <x:f>IF(AK5&gt;0,(Assumptions!$B$54+Assumptions!$B$55)/12,0)</x:f>
-        <x:v>50000</x:v>
+        <x:f>IF(AK5&gt;0,(ROUNDUP(IF(AK5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$65+Assumptions!$B$67+Assumptions!$B$68)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+AK5/Assumptions!$B$77+MAX(1,AK5/Assumptions!$B$78),0)*(Assumptions!$B$66+Assumptions!$B$68))*Assumptions!$B$6,0)</x:f>
+        <x:v>39959.52</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Client-dedicated team</x:t>
+          <x:t xml:space="preserve">Security and compliance</x:t>
         </x:is>
       </x:c>
       <x:c r="B19" s="20" t="n">
-        <x:f>IF(B5&gt;0,Assumptions!$B$57*Assumptions!$B$73+(Assumptions!$B$58+B5/Assumptions!$B$59)*Assumptions!$B$84+MAX(1,B5/Assumptions!$B$60)*Assumptions!$B$86,0)</x:f>
+        <x:f>IF(B5&gt;0,(Assumptions!$B$62+Assumptions!$B$63)/12,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C19" s="20" t="n">
-        <x:f>IF(C5&gt;0,Assumptions!$B$57*Assumptions!$B$73+(Assumptions!$B$58+C5/Assumptions!$B$59)*Assumptions!$B$84+MAX(1,C5/Assumptions!$B$60)*Assumptions!$B$86,0)</x:f>
+        <x:f>IF(C5&gt;0,(Assumptions!$B$62+Assumptions!$B$63)/12,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D19" s="20" t="n">
-        <x:f>IF(D5&gt;0,Assumptions!$B$57*Assumptions!$B$73+(Assumptions!$B$58+D5/Assumptions!$B$59)*Assumptions!$B$84+MAX(1,D5/Assumptions!$B$60)*Assumptions!$B$86,0)</x:f>
+        <x:f>IF(D5&gt;0,(Assumptions!$B$62+Assumptions!$B$63)/12,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="E19" s="20" t="n">
-        <x:f>IF(E5&gt;0,Assumptions!$B$57*Assumptions!$B$73+(Assumptions!$B$58+E5/Assumptions!$B$59)*Assumptions!$B$84+MAX(1,E5/Assumptions!$B$60)*Assumptions!$B$86,0)</x:f>
-        <x:v>288000</x:v>
+        <x:f>IF(E5&gt;0,(Assumptions!$B$62+Assumptions!$B$63)/12,0)</x:f>
+        <x:v>50000</x:v>
       </x:c>
       <x:c r="F19" s="20" t="n">
-        <x:f>IF(F5&gt;0,Assumptions!$B$57*Assumptions!$B$73+(Assumptions!$B$58+F5/Assumptions!$B$59)*Assumptions!$B$84+MAX(1,F5/Assumptions!$B$60)*Assumptions!$B$86,0)</x:f>
-        <x:v>288000</x:v>
+        <x:f>IF(F5&gt;0,(Assumptions!$B$62+Assumptions!$B$63)/12,0)</x:f>
+        <x:v>50000</x:v>
       </x:c>
       <x:c r="G19" s="20" t="n">
-        <x:f>IF(G5&gt;0,Assumptions!$B$57*Assumptions!$B$73+(Assumptions!$B$58+G5/Assumptions!$B$59)*Assumptions!$B$84+MAX(1,G5/Assumptions!$B$60)*Assumptions!$B$86,0)</x:f>
-        <x:v>288000</x:v>
+        <x:f>IF(G5&gt;0,(Assumptions!$B$62+Assumptions!$B$63)/12,0)</x:f>
+        <x:v>50000</x:v>
       </x:c>
       <x:c r="H19" s="20" t="n">
-        <x:f>IF(H5&gt;0,Assumptions!$B$57*Assumptions!$B$73+(Assumptions!$B$58+H5/Assumptions!$B$59)*Assumptions!$B$84+MAX(1,H5/Assumptions!$B$60)*Assumptions!$B$86,0)</x:f>
-        <x:v>327800</x:v>
+        <x:f>IF(H5&gt;0,(Assumptions!$B$62+Assumptions!$B$63)/12,0)</x:f>
+        <x:v>50000</x:v>
       </x:c>
       <x:c r="I19" s="20" t="n">
-        <x:f>IF(I5&gt;0,Assumptions!$B$57*Assumptions!$B$73+(Assumptions!$B$58+I5/Assumptions!$B$59)*Assumptions!$B$84+MAX(1,I5/Assumptions!$B$60)*Assumptions!$B$86,0)</x:f>
-        <x:v>327800</x:v>
+        <x:f>IF(I5&gt;0,(Assumptions!$B$62+Assumptions!$B$63)/12,0)</x:f>
+        <x:v>50000</x:v>
       </x:c>
       <x:c r="J19" s="20" t="n">
-        <x:f>IF(J5&gt;0,Assumptions!$B$57*Assumptions!$B$73+(Assumptions!$B$58+J5/Assumptions!$B$59)*Assumptions!$B$84+MAX(1,J5/Assumptions!$B$60)*Assumptions!$B$86,0)</x:f>
-        <x:v>327800</x:v>
+        <x:f>IF(J5&gt;0,(Assumptions!$B$62+Assumptions!$B$63)/12,0)</x:f>
+        <x:v>50000</x:v>
       </x:c>
       <x:c r="K19" s="20" t="n">
-        <x:f>IF(K5&gt;0,Assumptions!$B$57*Assumptions!$B$73+(Assumptions!$B$58+K5/Assumptions!$B$59)*Assumptions!$B$84+MAX(1,K5/Assumptions!$B$60)*Assumptions!$B$86,0)</x:f>
-        <x:v>327800</x:v>
+        <x:f>IF(K5&gt;0,(Assumptions!$B$62+Assumptions!$B$63)/12,0)</x:f>
+        <x:v>50000</x:v>
       </x:c>
       <x:c r="L19" s="20" t="n">
-        <x:f>IF(L5&gt;0,Assumptions!$B$57*Assumptions!$B$73+(Assumptions!$B$58+L5/Assumptions!$B$59)*Assumptions!$B$84+MAX(1,L5/Assumptions!$B$60)*Assumptions!$B$86,0)</x:f>
-        <x:v>327800</x:v>
+        <x:f>IF(L5&gt;0,(Assumptions!$B$62+Assumptions!$B$63)/12,0)</x:f>
+        <x:v>50000</x:v>
       </x:c>
       <x:c r="M19" s="20" t="n">
-        <x:f>IF(M5&gt;0,Assumptions!$B$57*Assumptions!$B$73+(Assumptions!$B$58+M5/Assumptions!$B$59)*Assumptions!$B$84+MAX(1,M5/Assumptions!$B$60)*Assumptions!$B$86,0)</x:f>
-        <x:v>327800</x:v>
+        <x:f>IF(M5&gt;0,(Assumptions!$B$62+Assumptions!$B$63)/12,0)</x:f>
+        <x:v>50000</x:v>
       </x:c>
       <x:c r="N19" s="20" t="n">
-        <x:f>IF(N5&gt;0,Assumptions!$B$57*Assumptions!$B$73+(Assumptions!$B$58+N5/Assumptions!$B$59)*Assumptions!$B$84+MAX(1,N5/Assumptions!$B$60)*Assumptions!$B$86,0)</x:f>
-        <x:v>413000</x:v>
+        <x:f>IF(N5&gt;0,(Assumptions!$B$62+Assumptions!$B$63)/12,0)</x:f>
+        <x:v>50000</x:v>
       </x:c>
       <x:c r="O19" s="20" t="n">
-        <x:f>IF(O5&gt;0,Assumptions!$B$57*Assumptions!$B$73+(Assumptions!$B$58+O5/Assumptions!$B$59)*Assumptions!$B$84+MAX(1,O5/Assumptions!$B$60)*Assumptions!$B$86,0)</x:f>
-        <x:v>413000</x:v>
+        <x:f>IF(O5&gt;0,(Assumptions!$B$62+Assumptions!$B$63)/12,0)</x:f>
+        <x:v>50000</x:v>
       </x:c>
       <x:c r="P19" s="20" t="n">
-        <x:f>IF(P5&gt;0,Assumptions!$B$57*Assumptions!$B$73+(Assumptions!$B$58+P5/Assumptions!$B$59)*Assumptions!$B$84+MAX(1,P5/Assumptions!$B$60)*Assumptions!$B$86,0)</x:f>
-        <x:v>413000</x:v>
+        <x:f>IF(P5&gt;0,(Assumptions!$B$62+Assumptions!$B$63)/12,0)</x:f>
+        <x:v>50000</x:v>
       </x:c>
       <x:c r="Q19" s="20" t="n">
-        <x:f>IF(Q5&gt;0,Assumptions!$B$57*Assumptions!$B$73+(Assumptions!$B$58+Q5/Assumptions!$B$59)*Assumptions!$B$84+MAX(1,Q5/Assumptions!$B$60)*Assumptions!$B$86,0)</x:f>
-        <x:v>413000</x:v>
+        <x:f>IF(Q5&gt;0,(Assumptions!$B$62+Assumptions!$B$63)/12,0)</x:f>
+        <x:v>50000</x:v>
       </x:c>
       <x:c r="R19" s="20" t="n">
-        <x:f>IF(R5&gt;0,Assumptions!$B$57*Assumptions!$B$73+(Assumptions!$B$58+R5/Assumptions!$B$59)*Assumptions!$B$84+MAX(1,R5/Assumptions!$B$60)*Assumptions!$B$86,0)</x:f>
-        <x:v>413000</x:v>
+        <x:f>IF(R5&gt;0,(Assumptions!$B$62+Assumptions!$B$63)/12,0)</x:f>
+        <x:v>50000</x:v>
       </x:c>
       <x:c r="S19" s="20" t="n">
-        <x:f>IF(S5&gt;0,Assumptions!$B$57*Assumptions!$B$73+(Assumptions!$B$58+S5/Assumptions!$B$59)*Assumptions!$B$84+MAX(1,S5/Assumptions!$B$60)*Assumptions!$B$86,0)</x:f>
-        <x:v>413000</x:v>
+        <x:f>IF(S5&gt;0,(Assumptions!$B$62+Assumptions!$B$63)/12,0)</x:f>
+        <x:v>50000</x:v>
       </x:c>
       <x:c r="T19" s="20" t="n">
-        <x:f>IF(T5&gt;0,Assumptions!$B$57*Assumptions!$B$73+(Assumptions!$B$58+T5/Assumptions!$B$59)*Assumptions!$B$84+MAX(1,T5/Assumptions!$B$60)*Assumptions!$B$86,0)</x:f>
-        <x:v>413000</x:v>
+        <x:f>IF(T5&gt;0,(Assumptions!$B$62+Assumptions!$B$63)/12,0)</x:f>
+        <x:v>50000</x:v>
       </x:c>
       <x:c r="U19" s="20" t="n">
-        <x:f>IF(U5&gt;0,Assumptions!$B$57*Assumptions!$B$73+(Assumptions!$B$58+U5/Assumptions!$B$59)*Assumptions!$B$84+MAX(1,U5/Assumptions!$B$60)*Assumptions!$B$86,0)</x:f>
-        <x:v>413000</x:v>
+        <x:f>IF(U5&gt;0,(Assumptions!$B$62+Assumptions!$B$63)/12,0)</x:f>
+        <x:v>50000</x:v>
       </x:c>
       <x:c r="V19" s="20" t="n">
-        <x:f>IF(V5&gt;0,Assumptions!$B$57*Assumptions!$B$73+(Assumptions!$B$58+V5/Assumptions!$B$59)*Assumptions!$B$84+MAX(1,V5/Assumptions!$B$60)*Assumptions!$B$86,0)</x:f>
-        <x:v>413000</x:v>
+        <x:f>IF(V5&gt;0,(Assumptions!$B$62+Assumptions!$B$63)/12,0)</x:f>
+        <x:v>50000</x:v>
       </x:c>
       <x:c r="W19" s="20" t="n">
-        <x:f>IF(W5&gt;0,Assumptions!$B$57*Assumptions!$B$73+(Assumptions!$B$58+W5/Assumptions!$B$59)*Assumptions!$B$84+MAX(1,W5/Assumptions!$B$60)*Assumptions!$B$86,0)</x:f>
-        <x:v>413000</x:v>
+        <x:f>IF(W5&gt;0,(Assumptions!$B$62+Assumptions!$B$63)/12,0)</x:f>
+        <x:v>50000</x:v>
       </x:c>
       <x:c r="X19" s="20" t="n">
-        <x:f>IF(X5&gt;0,Assumptions!$B$57*Assumptions!$B$73+(Assumptions!$B$58+X5/Assumptions!$B$59)*Assumptions!$B$84+MAX(1,X5/Assumptions!$B$60)*Assumptions!$B$86,0)</x:f>
-        <x:v>413000</x:v>
+        <x:f>IF(X5&gt;0,(Assumptions!$B$62+Assumptions!$B$63)/12,0)</x:f>
+        <x:v>50000</x:v>
       </x:c>
       <x:c r="Y19" s="20" t="n">
-        <x:f>IF(Y5&gt;0,Assumptions!$B$57*Assumptions!$B$73+(Assumptions!$B$58+Y5/Assumptions!$B$59)*Assumptions!$B$84+MAX(1,Y5/Assumptions!$B$60)*Assumptions!$B$86,0)</x:f>
-        <x:v>413000</x:v>
+        <x:f>IF(Y5&gt;0,(Assumptions!$B$62+Assumptions!$B$63)/12,0)</x:f>
+        <x:v>50000</x:v>
       </x:c>
       <x:c r="Z19" s="20" t="n">
-        <x:f>IF(Z5&gt;0,Assumptions!$B$57*Assumptions!$B$73+(Assumptions!$B$58+Z5/Assumptions!$B$59)*Assumptions!$B$84+MAX(1,Z5/Assumptions!$B$60)*Assumptions!$B$86,0)</x:f>
-        <x:v>413000</x:v>
+        <x:f>IF(Z5&gt;0,(Assumptions!$B$62+Assumptions!$B$63)/12,0)</x:f>
+        <x:v>50000</x:v>
       </x:c>
       <x:c r="AA19" s="20" t="n">
-        <x:f>IF(AA5&gt;0,Assumptions!$B$57*Assumptions!$B$73+(Assumptions!$B$58+AA5/Assumptions!$B$59)*Assumptions!$B$84+MAX(1,AA5/Assumptions!$B$60)*Assumptions!$B$86,0)</x:f>
-        <x:v>413000</x:v>
+        <x:f>IF(AA5&gt;0,(Assumptions!$B$62+Assumptions!$B$63)/12,0)</x:f>
+        <x:v>50000</x:v>
       </x:c>
       <x:c r="AB19" s="20" t="n">
-        <x:f>IF(AB5&gt;0,Assumptions!$B$57*Assumptions!$B$73+(Assumptions!$B$58+AB5/Assumptions!$B$59)*Assumptions!$B$84+MAX(1,AB5/Assumptions!$B$60)*Assumptions!$B$86,0)</x:f>
-        <x:v>413000</x:v>
+        <x:f>IF(AB5&gt;0,(Assumptions!$B$62+Assumptions!$B$63)/12,0)</x:f>
+        <x:v>50000</x:v>
       </x:c>
       <x:c r="AC19" s="20" t="n">
-        <x:f>IF(AC5&gt;0,Assumptions!$B$57*Assumptions!$B$73+(Assumptions!$B$58+AC5/Assumptions!$B$59)*Assumptions!$B$84+MAX(1,AC5/Assumptions!$B$60)*Assumptions!$B$86,0)</x:f>
-        <x:v>413000</x:v>
+        <x:f>IF(AC5&gt;0,(Assumptions!$B$62+Assumptions!$B$63)/12,0)</x:f>
+        <x:v>50000</x:v>
       </x:c>
       <x:c r="AD19" s="20" t="n">
-        <x:f>IF(AD5&gt;0,Assumptions!$B$57*Assumptions!$B$73+(Assumptions!$B$58+AD5/Assumptions!$B$59)*Assumptions!$B$84+MAX(1,AD5/Assumptions!$B$60)*Assumptions!$B$86,0)</x:f>
-        <x:v>413000</x:v>
+        <x:f>IF(AD5&gt;0,(Assumptions!$B$62+Assumptions!$B$63)/12,0)</x:f>
+        <x:v>50000</x:v>
       </x:c>
       <x:c r="AE19" s="20" t="n">
-        <x:f>IF(AE5&gt;0,Assumptions!$B$57*Assumptions!$B$73+(Assumptions!$B$58+AE5/Assumptions!$B$59)*Assumptions!$B$84+MAX(1,AE5/Assumptions!$B$60)*Assumptions!$B$86,0)</x:f>
-        <x:v>413000</x:v>
+        <x:f>IF(AE5&gt;0,(Assumptions!$B$62+Assumptions!$B$63)/12,0)</x:f>
+        <x:v>50000</x:v>
       </x:c>
       <x:c r="AF19" s="20" t="n">
-        <x:f>IF(AF5&gt;0,Assumptions!$B$57*Assumptions!$B$73+(Assumptions!$B$58+AF5/Assumptions!$B$59)*Assumptions!$B$84+MAX(1,AF5/Assumptions!$B$60)*Assumptions!$B$86,0)</x:f>
-        <x:v>413000</x:v>
+        <x:f>IF(AF5&gt;0,(Assumptions!$B$62+Assumptions!$B$63)/12,0)</x:f>
+        <x:v>50000</x:v>
       </x:c>
       <x:c r="AG19" s="20" t="n">
-        <x:f>IF(AG5&gt;0,Assumptions!$B$57*Assumptions!$B$73+(Assumptions!$B$58+AG5/Assumptions!$B$59)*Assumptions!$B$84+MAX(1,AG5/Assumptions!$B$60)*Assumptions!$B$86,0)</x:f>
-        <x:v>413000</x:v>
+        <x:f>IF(AG5&gt;0,(Assumptions!$B$62+Assumptions!$B$63)/12,0)</x:f>
+        <x:v>50000</x:v>
       </x:c>
       <x:c r="AH19" s="20" t="n">
-        <x:f>IF(AH5&gt;0,Assumptions!$B$57*Assumptions!$B$73+(Assumptions!$B$58+AH5/Assumptions!$B$59)*Assumptions!$B$84+MAX(1,AH5/Assumptions!$B$60)*Assumptions!$B$86,0)</x:f>
-        <x:v>413000</x:v>
+        <x:f>IF(AH5&gt;0,(Assumptions!$B$62+Assumptions!$B$63)/12,0)</x:f>
+        <x:v>50000</x:v>
       </x:c>
       <x:c r="AI19" s="20" t="n">
-        <x:f>IF(AI5&gt;0,Assumptions!$B$57*Assumptions!$B$73+(Assumptions!$B$58+AI5/Assumptions!$B$59)*Assumptions!$B$84+MAX(1,AI5/Assumptions!$B$60)*Assumptions!$B$86,0)</x:f>
-        <x:v>413000</x:v>
+        <x:f>IF(AI5&gt;0,(Assumptions!$B$62+Assumptions!$B$63)/12,0)</x:f>
+        <x:v>50000</x:v>
       </x:c>
       <x:c r="AJ19" s="20" t="n">
-        <x:f>IF(AJ5&gt;0,Assumptions!$B$57*Assumptions!$B$73+(Assumptions!$B$58+AJ5/Assumptions!$B$59)*Assumptions!$B$84+MAX(1,AJ5/Assumptions!$B$60)*Assumptions!$B$86,0)</x:f>
-        <x:v>413000</x:v>
+        <x:f>IF(AJ5&gt;0,(Assumptions!$B$62+Assumptions!$B$63)/12,0)</x:f>
+        <x:v>50000</x:v>
       </x:c>
       <x:c r="AK19" s="20" t="n">
-        <x:f>IF(AK5&gt;0,Assumptions!$B$57*Assumptions!$B$73+(Assumptions!$B$58+AK5/Assumptions!$B$59)*Assumptions!$B$84+MAX(1,AK5/Assumptions!$B$60)*Assumptions!$B$86,0)</x:f>
-        <x:v>413000</x:v>
+        <x:f>IF(AK5&gt;0,(Assumptions!$B$62+Assumptions!$B$63)/12,0)</x:f>
+        <x:v>50000</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="7" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">Client-dedicated team</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B20" s="20" t="n">
+        <x:f>IF(B5&gt;0,Assumptions!$B$75*Assumptions!$B$91+(Assumptions!$B$76+B5/Assumptions!$B$77)*Assumptions!$B$102+MAX(1,B5/Assumptions!$B$78)*Assumptions!$B$104,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C20" s="20" t="n">
+        <x:f>IF(C5&gt;0,Assumptions!$B$75*Assumptions!$B$91+(Assumptions!$B$76+C5/Assumptions!$B$77)*Assumptions!$B$102+MAX(1,C5/Assumptions!$B$78)*Assumptions!$B$104,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D20" s="20" t="n">
+        <x:f>IF(D5&gt;0,Assumptions!$B$75*Assumptions!$B$91+(Assumptions!$B$76+D5/Assumptions!$B$77)*Assumptions!$B$102+MAX(1,D5/Assumptions!$B$78)*Assumptions!$B$104,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E20" s="20" t="n">
+        <x:f>IF(E5&gt;0,Assumptions!$B$75*Assumptions!$B$91+(Assumptions!$B$76+E5/Assumptions!$B$77)*Assumptions!$B$102+MAX(1,E5/Assumptions!$B$78)*Assumptions!$B$104,0)</x:f>
+        <x:v>288000</x:v>
+      </x:c>
+      <x:c r="F20" s="20" t="n">
+        <x:f>IF(F5&gt;0,Assumptions!$B$75*Assumptions!$B$91+(Assumptions!$B$76+F5/Assumptions!$B$77)*Assumptions!$B$102+MAX(1,F5/Assumptions!$B$78)*Assumptions!$B$104,0)</x:f>
+        <x:v>288000</x:v>
+      </x:c>
+      <x:c r="G20" s="20" t="n">
+        <x:f>IF(G5&gt;0,Assumptions!$B$75*Assumptions!$B$91+(Assumptions!$B$76+G5/Assumptions!$B$77)*Assumptions!$B$102+MAX(1,G5/Assumptions!$B$78)*Assumptions!$B$104,0)</x:f>
+        <x:v>288000</x:v>
+      </x:c>
+      <x:c r="H20" s="20" t="n">
+        <x:f>IF(H5&gt;0,Assumptions!$B$75*Assumptions!$B$91+(Assumptions!$B$76+H5/Assumptions!$B$77)*Assumptions!$B$102+MAX(1,H5/Assumptions!$B$78)*Assumptions!$B$104,0)</x:f>
+        <x:v>327800</x:v>
+      </x:c>
+      <x:c r="I20" s="20" t="n">
+        <x:f>IF(I5&gt;0,Assumptions!$B$75*Assumptions!$B$91+(Assumptions!$B$76+I5/Assumptions!$B$77)*Assumptions!$B$102+MAX(1,I5/Assumptions!$B$78)*Assumptions!$B$104,0)</x:f>
+        <x:v>327800</x:v>
+      </x:c>
+      <x:c r="J20" s="20" t="n">
+        <x:f>IF(J5&gt;0,Assumptions!$B$75*Assumptions!$B$91+(Assumptions!$B$76+J5/Assumptions!$B$77)*Assumptions!$B$102+MAX(1,J5/Assumptions!$B$78)*Assumptions!$B$104,0)</x:f>
+        <x:v>327800</x:v>
+      </x:c>
+      <x:c r="K20" s="20" t="n">
+        <x:f>IF(K5&gt;0,Assumptions!$B$75*Assumptions!$B$91+(Assumptions!$B$76+K5/Assumptions!$B$77)*Assumptions!$B$102+MAX(1,K5/Assumptions!$B$78)*Assumptions!$B$104,0)</x:f>
+        <x:v>327800</x:v>
+      </x:c>
+      <x:c r="L20" s="20" t="n">
+        <x:f>IF(L5&gt;0,Assumptions!$B$75*Assumptions!$B$91+(Assumptions!$B$76+L5/Assumptions!$B$77)*Assumptions!$B$102+MAX(1,L5/Assumptions!$B$78)*Assumptions!$B$104,0)</x:f>
+        <x:v>327800</x:v>
+      </x:c>
+      <x:c r="M20" s="20" t="n">
+        <x:f>IF(M5&gt;0,Assumptions!$B$75*Assumptions!$B$91+(Assumptions!$B$76+M5/Assumptions!$B$77)*Assumptions!$B$102+MAX(1,M5/Assumptions!$B$78)*Assumptions!$B$104,0)</x:f>
+        <x:v>327800</x:v>
+      </x:c>
+      <x:c r="N20" s="20" t="n">
+        <x:f>IF(N5&gt;0,Assumptions!$B$75*Assumptions!$B$91+(Assumptions!$B$76+N5/Assumptions!$B$77)*Assumptions!$B$102+MAX(1,N5/Assumptions!$B$78)*Assumptions!$B$104,0)</x:f>
+        <x:v>413000</x:v>
+      </x:c>
+      <x:c r="O20" s="20" t="n">
+        <x:f>IF(O5&gt;0,Assumptions!$B$75*Assumptions!$B$91+(Assumptions!$B$76+O5/Assumptions!$B$77)*Assumptions!$B$102+MAX(1,O5/Assumptions!$B$78)*Assumptions!$B$104,0)</x:f>
+        <x:v>413000</x:v>
+      </x:c>
+      <x:c r="P20" s="20" t="n">
+        <x:f>IF(P5&gt;0,Assumptions!$B$75*Assumptions!$B$91+(Assumptions!$B$76+P5/Assumptions!$B$77)*Assumptions!$B$102+MAX(1,P5/Assumptions!$B$78)*Assumptions!$B$104,0)</x:f>
+        <x:v>413000</x:v>
+      </x:c>
+      <x:c r="Q20" s="20" t="n">
+        <x:f>IF(Q5&gt;0,Assumptions!$B$75*Assumptions!$B$91+(Assumptions!$B$76+Q5/Assumptions!$B$77)*Assumptions!$B$102+MAX(1,Q5/Assumptions!$B$78)*Assumptions!$B$104,0)</x:f>
+        <x:v>413000</x:v>
+      </x:c>
+      <x:c r="R20" s="20" t="n">
+        <x:f>IF(R5&gt;0,Assumptions!$B$75*Assumptions!$B$91+(Assumptions!$B$76+R5/Assumptions!$B$77)*Assumptions!$B$102+MAX(1,R5/Assumptions!$B$78)*Assumptions!$B$104,0)</x:f>
+        <x:v>413000</x:v>
+      </x:c>
+      <x:c r="S20" s="20" t="n">
+        <x:f>IF(S5&gt;0,Assumptions!$B$75*Assumptions!$B$91+(Assumptions!$B$76+S5/Assumptions!$B$77)*Assumptions!$B$102+MAX(1,S5/Assumptions!$B$78)*Assumptions!$B$104,0)</x:f>
+        <x:v>413000</x:v>
+      </x:c>
+      <x:c r="T20" s="20" t="n">
+        <x:f>IF(T5&gt;0,Assumptions!$B$75*Assumptions!$B$91+(Assumptions!$B$76+T5/Assumptions!$B$77)*Assumptions!$B$102+MAX(1,T5/Assumptions!$B$78)*Assumptions!$B$104,0)</x:f>
+        <x:v>413000</x:v>
+      </x:c>
+      <x:c r="U20" s="20" t="n">
+        <x:f>IF(U5&gt;0,Assumptions!$B$75*Assumptions!$B$91+(Assumptions!$B$76+U5/Assumptions!$B$77)*Assumptions!$B$102+MAX(1,U5/Assumptions!$B$78)*Assumptions!$B$104,0)</x:f>
+        <x:v>413000</x:v>
+      </x:c>
+      <x:c r="V20" s="20" t="n">
+        <x:f>IF(V5&gt;0,Assumptions!$B$75*Assumptions!$B$91+(Assumptions!$B$76+V5/Assumptions!$B$77)*Assumptions!$B$102+MAX(1,V5/Assumptions!$B$78)*Assumptions!$B$104,0)</x:f>
+        <x:v>413000</x:v>
+      </x:c>
+      <x:c r="W20" s="20" t="n">
+        <x:f>IF(W5&gt;0,Assumptions!$B$75*Assumptions!$B$91+(Assumptions!$B$76+W5/Assumptions!$B$77)*Assumptions!$B$102+MAX(1,W5/Assumptions!$B$78)*Assumptions!$B$104,0)</x:f>
+        <x:v>413000</x:v>
+      </x:c>
+      <x:c r="X20" s="20" t="n">
+        <x:f>IF(X5&gt;0,Assumptions!$B$75*Assumptions!$B$91+(Assumptions!$B$76+X5/Assumptions!$B$77)*Assumptions!$B$102+MAX(1,X5/Assumptions!$B$78)*Assumptions!$B$104,0)</x:f>
+        <x:v>413000</x:v>
+      </x:c>
+      <x:c r="Y20" s="20" t="n">
+        <x:f>IF(Y5&gt;0,Assumptions!$B$75*Assumptions!$B$91+(Assumptions!$B$76+Y5/Assumptions!$B$77)*Assumptions!$B$102+MAX(1,Y5/Assumptions!$B$78)*Assumptions!$B$104,0)</x:f>
+        <x:v>413000</x:v>
+      </x:c>
+      <x:c r="Z20" s="20" t="n">
+        <x:f>IF(Z5&gt;0,Assumptions!$B$75*Assumptions!$B$91+(Assumptions!$B$76+Z5/Assumptions!$B$77)*Assumptions!$B$102+MAX(1,Z5/Assumptions!$B$78)*Assumptions!$B$104,0)</x:f>
+        <x:v>413000</x:v>
+      </x:c>
+      <x:c r="AA20" s="20" t="n">
+        <x:f>IF(AA5&gt;0,Assumptions!$B$75*Assumptions!$B$91+(Assumptions!$B$76+AA5/Assumptions!$B$77)*Assumptions!$B$102+MAX(1,AA5/Assumptions!$B$78)*Assumptions!$B$104,0)</x:f>
+        <x:v>413000</x:v>
+      </x:c>
+      <x:c r="AB20" s="20" t="n">
+        <x:f>IF(AB5&gt;0,Assumptions!$B$75*Assumptions!$B$91+(Assumptions!$B$76+AB5/Assumptions!$B$77)*Assumptions!$B$102+MAX(1,AB5/Assumptions!$B$78)*Assumptions!$B$104,0)</x:f>
+        <x:v>413000</x:v>
+      </x:c>
+      <x:c r="AC20" s="20" t="n">
+        <x:f>IF(AC5&gt;0,Assumptions!$B$75*Assumptions!$B$91+(Assumptions!$B$76+AC5/Assumptions!$B$77)*Assumptions!$B$102+MAX(1,AC5/Assumptions!$B$78)*Assumptions!$B$104,0)</x:f>
+        <x:v>413000</x:v>
+      </x:c>
+      <x:c r="AD20" s="20" t="n">
+        <x:f>IF(AD5&gt;0,Assumptions!$B$75*Assumptions!$B$91+(Assumptions!$B$76+AD5/Assumptions!$B$77)*Assumptions!$B$102+MAX(1,AD5/Assumptions!$B$78)*Assumptions!$B$104,0)</x:f>
+        <x:v>413000</x:v>
+      </x:c>
+      <x:c r="AE20" s="20" t="n">
+        <x:f>IF(AE5&gt;0,Assumptions!$B$75*Assumptions!$B$91+(Assumptions!$B$76+AE5/Assumptions!$B$77)*Assumptions!$B$102+MAX(1,AE5/Assumptions!$B$78)*Assumptions!$B$104,0)</x:f>
+        <x:v>413000</x:v>
+      </x:c>
+      <x:c r="AF20" s="20" t="n">
+        <x:f>IF(AF5&gt;0,Assumptions!$B$75*Assumptions!$B$91+(Assumptions!$B$76+AF5/Assumptions!$B$77)*Assumptions!$B$102+MAX(1,AF5/Assumptions!$B$78)*Assumptions!$B$104,0)</x:f>
+        <x:v>413000</x:v>
+      </x:c>
+      <x:c r="AG20" s="20" t="n">
+        <x:f>IF(AG5&gt;0,Assumptions!$B$75*Assumptions!$B$91+(Assumptions!$B$76+AG5/Assumptions!$B$77)*Assumptions!$B$102+MAX(1,AG5/Assumptions!$B$78)*Assumptions!$B$104,0)</x:f>
+        <x:v>413000</x:v>
+      </x:c>
+      <x:c r="AH20" s="20" t="n">
+        <x:f>IF(AH5&gt;0,Assumptions!$B$75*Assumptions!$B$91+(Assumptions!$B$76+AH5/Assumptions!$B$77)*Assumptions!$B$102+MAX(1,AH5/Assumptions!$B$78)*Assumptions!$B$104,0)</x:f>
+        <x:v>413000</x:v>
+      </x:c>
+      <x:c r="AI20" s="20" t="n">
+        <x:f>IF(AI5&gt;0,Assumptions!$B$75*Assumptions!$B$91+(Assumptions!$B$76+AI5/Assumptions!$B$77)*Assumptions!$B$102+MAX(1,AI5/Assumptions!$B$78)*Assumptions!$B$104,0)</x:f>
+        <x:v>413000</x:v>
+      </x:c>
+      <x:c r="AJ20" s="20" t="n">
+        <x:f>IF(AJ5&gt;0,Assumptions!$B$75*Assumptions!$B$91+(Assumptions!$B$76+AJ5/Assumptions!$B$77)*Assumptions!$B$102+MAX(1,AJ5/Assumptions!$B$78)*Assumptions!$B$104,0)</x:f>
+        <x:v>413000</x:v>
+      </x:c>
+      <x:c r="AK20" s="20" t="n">
+        <x:f>IF(AK5&gt;0,Assumptions!$B$75*Assumptions!$B$91+(Assumptions!$B$76+AK5/Assumptions!$B$77)*Assumptions!$B$102+MAX(1,AK5/Assumptions!$B$78)*Assumptions!$B$104,0)</x:f>
+        <x:v>413000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="7" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">Platform team</x:t>
         </x:is>
       </x:c>
-      <x:c r="B20" s="20" t="n">
-        <x:f>IF(B5&gt;0,IF(B5&gt;20000,Assumptions!$B$62,Assumptions!$B$61)*Assumptions!$B$75,0)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C20" s="20" t="n">
-        <x:f>IF(C5&gt;0,IF(C5&gt;20000,Assumptions!$B$62,Assumptions!$B$61)*Assumptions!$B$75,0)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D20" s="20" t="n">
-        <x:f>IF(D5&gt;0,IF(D5&gt;20000,Assumptions!$B$62,Assumptions!$B$61)*Assumptions!$B$75,0)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E20" s="20" t="n">
-        <x:f>IF(E5&gt;0,IF(E5&gt;20000,Assumptions!$B$62,Assumptions!$B$61)*Assumptions!$B$75,0)</x:f>
+      <x:c r="B21" s="20" t="n">
+        <x:f>IF(B5&gt;0,IF(B5&gt;20000,Assumptions!$B$80,Assumptions!$B$79)*Assumptions!$B$93,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C21" s="20" t="n">
+        <x:f>IF(C5&gt;0,IF(C5&gt;20000,Assumptions!$B$80,Assumptions!$B$79)*Assumptions!$B$93,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D21" s="20" t="n">
+        <x:f>IF(D5&gt;0,IF(D5&gt;20000,Assumptions!$B$80,Assumptions!$B$79)*Assumptions!$B$93,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E21" s="20" t="n">
+        <x:f>IF(E5&gt;0,IF(E5&gt;20000,Assumptions!$B$80,Assumptions!$B$79)*Assumptions!$B$93,0)</x:f>
         <x:v>400000</x:v>
       </x:c>
-      <x:c r="F20" s="20" t="n">
-        <x:f>IF(F5&gt;0,IF(F5&gt;20000,Assumptions!$B$62,Assumptions!$B$61)*Assumptions!$B$75,0)</x:f>
+      <x:c r="F21" s="20" t="n">
+        <x:f>IF(F5&gt;0,IF(F5&gt;20000,Assumptions!$B$80,Assumptions!$B$79)*Assumptions!$B$93,0)</x:f>
         <x:v>400000</x:v>
       </x:c>
-      <x:c r="G20" s="20" t="n">
-        <x:f>IF(G5&gt;0,IF(G5&gt;20000,Assumptions!$B$62,Assumptions!$B$61)*Assumptions!$B$75,0)</x:f>
+      <x:c r="G21" s="20" t="n">
+        <x:f>IF(G5&gt;0,IF(G5&gt;20000,Assumptions!$B$80,Assumptions!$B$79)*Assumptions!$B$93,0)</x:f>
         <x:v>400000</x:v>
       </x:c>
-      <x:c r="H20" s="20" t="n">
-        <x:f>IF(H5&gt;0,IF(H5&gt;20000,Assumptions!$B$62,Assumptions!$B$61)*Assumptions!$B$75,0)</x:f>
+      <x:c r="H21" s="20" t="n">
+        <x:f>IF(H5&gt;0,IF(H5&gt;20000,Assumptions!$B$80,Assumptions!$B$79)*Assumptions!$B$93,0)</x:f>
         <x:v>480000</x:v>
       </x:c>
-      <x:c r="I20" s="20" t="n">
-        <x:f>IF(I5&gt;0,IF(I5&gt;20000,Assumptions!$B$62,Assumptions!$B$61)*Assumptions!$B$75,0)</x:f>
+      <x:c r="I21" s="20" t="n">
+        <x:f>IF(I5&gt;0,IF(I5&gt;20000,Assumptions!$B$80,Assumptions!$B$79)*Assumptions!$B$93,0)</x:f>
         <x:v>480000</x:v>
       </x:c>
-      <x:c r="J20" s="20" t="n">
-        <x:f>IF(J5&gt;0,IF(J5&gt;20000,Assumptions!$B$62,Assumptions!$B$61)*Assumptions!$B$75,0)</x:f>
+      <x:c r="J21" s="20" t="n">
+        <x:f>IF(J5&gt;0,IF(J5&gt;20000,Assumptions!$B$80,Assumptions!$B$79)*Assumptions!$B$93,0)</x:f>
         <x:v>480000</x:v>
       </x:c>
-      <x:c r="K20" s="20" t="n">
-        <x:f>IF(K5&gt;0,IF(K5&gt;20000,Assumptions!$B$62,Assumptions!$B$61)*Assumptions!$B$75,0)</x:f>
+      <x:c r="K21" s="20" t="n">
+        <x:f>IF(K5&gt;0,IF(K5&gt;20000,Assumptions!$B$80,Assumptions!$B$79)*Assumptions!$B$93,0)</x:f>
         <x:v>480000</x:v>
       </x:c>
-      <x:c r="L20" s="20" t="n">
-        <x:f>IF(L5&gt;0,IF(L5&gt;20000,Assumptions!$B$62,Assumptions!$B$61)*Assumptions!$B$75,0)</x:f>
+      <x:c r="L21" s="20" t="n">
+        <x:f>IF(L5&gt;0,IF(L5&gt;20000,Assumptions!$B$80,Assumptions!$B$79)*Assumptions!$B$93,0)</x:f>
         <x:v>480000</x:v>
       </x:c>
-      <x:c r="M20" s="20" t="n">
-        <x:f>IF(M5&gt;0,IF(M5&gt;20000,Assumptions!$B$62,Assumptions!$B$61)*Assumptions!$B$75,0)</x:f>
+      <x:c r="M21" s="20" t="n">
+        <x:f>IF(M5&gt;0,IF(M5&gt;20000,Assumptions!$B$80,Assumptions!$B$79)*Assumptions!$B$93,0)</x:f>
         <x:v>480000</x:v>
       </x:c>
-      <x:c r="N20" s="20" t="n">
-        <x:f>IF(N5&gt;0,IF(N5&gt;20000,Assumptions!$B$62,Assumptions!$B$61)*Assumptions!$B$75,0)</x:f>
+      <x:c r="N21" s="20" t="n">
+        <x:f>IF(N5&gt;0,IF(N5&gt;20000,Assumptions!$B$80,Assumptions!$B$79)*Assumptions!$B$93,0)</x:f>
         <x:v>480000</x:v>
       </x:c>
-      <x:c r="O20" s="20" t="n">
-        <x:f>IF(O5&gt;0,IF(O5&gt;20000,Assumptions!$B$62,Assumptions!$B$61)*Assumptions!$B$75,0)</x:f>
+      <x:c r="O21" s="20" t="n">
+        <x:f>IF(O5&gt;0,IF(O5&gt;20000,Assumptions!$B$80,Assumptions!$B$79)*Assumptions!$B$93,0)</x:f>
         <x:v>480000</x:v>
       </x:c>
-      <x:c r="P20" s="20" t="n">
-        <x:f>IF(P5&gt;0,IF(P5&gt;20000,Assumptions!$B$62,Assumptions!$B$61)*Assumptions!$B$75,0)</x:f>
+      <x:c r="P21" s="20" t="n">
+        <x:f>IF(P5&gt;0,IF(P5&gt;20000,Assumptions!$B$80,Assumptions!$B$79)*Assumptions!$B$93,0)</x:f>
         <x:v>480000</x:v>
       </x:c>
-      <x:c r="Q20" s="20" t="n">
-        <x:f>IF(Q5&gt;0,IF(Q5&gt;20000,Assumptions!$B$62,Assumptions!$B$61)*Assumptions!$B$75,0)</x:f>
+      <x:c r="Q21" s="20" t="n">
+        <x:f>IF(Q5&gt;0,IF(Q5&gt;20000,Assumptions!$B$80,Assumptions!$B$79)*Assumptions!$B$93,0)</x:f>
         <x:v>480000</x:v>
       </x:c>
-      <x:c r="R20" s="20" t="n">
-        <x:f>IF(R5&gt;0,IF(R5&gt;20000,Assumptions!$B$62,Assumptions!$B$61)*Assumptions!$B$75,0)</x:f>
+      <x:c r="R21" s="20" t="n">
+        <x:f>IF(R5&gt;0,IF(R5&gt;20000,Assumptions!$B$80,Assumptions!$B$79)*Assumptions!$B$93,0)</x:f>
         <x:v>480000</x:v>
       </x:c>
-      <x:c r="S20" s="20" t="n">
-        <x:f>IF(S5&gt;0,IF(S5&gt;20000,Assumptions!$B$62,Assumptions!$B$61)*Assumptions!$B$75,0)</x:f>
+      <x:c r="S21" s="20" t="n">
+        <x:f>IF(S5&gt;0,IF(S5&gt;20000,Assumptions!$B$80,Assumptions!$B$79)*Assumptions!$B$93,0)</x:f>
         <x:v>480000</x:v>
       </x:c>
-      <x:c r="T20" s="20" t="n">
-        <x:f>IF(T5&gt;0,IF(T5&gt;20000,Assumptions!$B$62,Assumptions!$B$61)*Assumptions!$B$75,0)</x:f>
+      <x:c r="T21" s="20" t="n">
+        <x:f>IF(T5&gt;0,IF(T5&gt;20000,Assumptions!$B$80,Assumptions!$B$79)*Assumptions!$B$93,0)</x:f>
         <x:v>480000</x:v>
       </x:c>
-      <x:c r="U20" s="20" t="n">
-        <x:f>IF(U5&gt;0,IF(U5&gt;20000,Assumptions!$B$62,Assumptions!$B$61)*Assumptions!$B$75,0)</x:f>
+      <x:c r="U21" s="20" t="n">
+        <x:f>IF(U5&gt;0,IF(U5&gt;20000,Assumptions!$B$80,Assumptions!$B$79)*Assumptions!$B$93,0)</x:f>
         <x:v>480000</x:v>
       </x:c>
-      <x:c r="V20" s="20" t="n">
-        <x:f>IF(V5&gt;0,IF(V5&gt;20000,Assumptions!$B$62,Assumptions!$B$61)*Assumptions!$B$75,0)</x:f>
+      <x:c r="V21" s="20" t="n">
+        <x:f>IF(V5&gt;0,IF(V5&gt;20000,Assumptions!$B$80,Assumptions!$B$79)*Assumptions!$B$93,0)</x:f>
         <x:v>480000</x:v>
       </x:c>
-      <x:c r="W20" s="20" t="n">
-        <x:f>IF(W5&gt;0,IF(W5&gt;20000,Assumptions!$B$62,Assumptions!$B$61)*Assumptions!$B$75,0)</x:f>
+      <x:c r="W21" s="20" t="n">
+        <x:f>IF(W5&gt;0,IF(W5&gt;20000,Assumptions!$B$80,Assumptions!$B$79)*Assumptions!$B$93,0)</x:f>
         <x:v>480000</x:v>
       </x:c>
-      <x:c r="X20" s="20" t="n">
-        <x:f>IF(X5&gt;0,IF(X5&gt;20000,Assumptions!$B$62,Assumptions!$B$61)*Assumptions!$B$75,0)</x:f>
+      <x:c r="X21" s="20" t="n">
+        <x:f>IF(X5&gt;0,IF(X5&gt;20000,Assumptions!$B$80,Assumptions!$B$79)*Assumptions!$B$93,0)</x:f>
         <x:v>480000</x:v>
       </x:c>
-      <x:c r="Y20" s="20" t="n">
-        <x:f>IF(Y5&gt;0,IF(Y5&gt;20000,Assumptions!$B$62,Assumptions!$B$61)*Assumptions!$B$75,0)</x:f>
+      <x:c r="Y21" s="20" t="n">
+        <x:f>IF(Y5&gt;0,IF(Y5&gt;20000,Assumptions!$B$80,Assumptions!$B$79)*Assumptions!$B$93,0)</x:f>
         <x:v>480000</x:v>
       </x:c>
-      <x:c r="Z20" s="20" t="n">
-        <x:f>IF(Z5&gt;0,IF(Z5&gt;20000,Assumptions!$B$62,Assumptions!$B$61)*Assumptions!$B$75,0)</x:f>
+      <x:c r="Z21" s="20" t="n">
+        <x:f>IF(Z5&gt;0,IF(Z5&gt;20000,Assumptions!$B$80,Assumptions!$B$79)*Assumptions!$B$93,0)</x:f>
         <x:v>480000</x:v>
       </x:c>
-      <x:c r="AA20" s="20" t="n">
-        <x:f>IF(AA5&gt;0,IF(AA5&gt;20000,Assumptions!$B$62,Assumptions!$B$61)*Assumptions!$B$75,0)</x:f>
+      <x:c r="AA21" s="20" t="n">
+        <x:f>IF(AA5&gt;0,IF(AA5&gt;20000,Assumptions!$B$80,Assumptions!$B$79)*Assumptions!$B$93,0)</x:f>
         <x:v>480000</x:v>
       </x:c>
-      <x:c r="AB20" s="20" t="n">
-        <x:f>IF(AB5&gt;0,IF(AB5&gt;20000,Assumptions!$B$62,Assumptions!$B$61)*Assumptions!$B$75,0)</x:f>
+      <x:c r="AB21" s="20" t="n">
+        <x:f>IF(AB5&gt;0,IF(AB5&gt;20000,Assumptions!$B$80,Assumptions!$B$79)*Assumptions!$B$93,0)</x:f>
         <x:v>480000</x:v>
       </x:c>
-      <x:c r="AC20" s="20" t="n">
-        <x:f>IF(AC5&gt;0,IF(AC5&gt;20000,Assumptions!$B$62,Assumptions!$B$61)*Assumptions!$B$75,0)</x:f>
+      <x:c r="AC21" s="20" t="n">
+        <x:f>IF(AC5&gt;0,IF(AC5&gt;20000,Assumptions!$B$80,Assumptions!$B$79)*Assumptions!$B$93,0)</x:f>
         <x:v>480000</x:v>
       </x:c>
-      <x:c r="AD20" s="20" t="n">
-        <x:f>IF(AD5&gt;0,IF(AD5&gt;20000,Assumptions!$B$62,Assumptions!$B$61)*Assumptions!$B$75,0)</x:f>
+      <x:c r="AD21" s="20" t="n">
+        <x:f>IF(AD5&gt;0,IF(AD5&gt;20000,Assumptions!$B$80,Assumptions!$B$79)*Assumptions!$B$93,0)</x:f>
         <x:v>480000</x:v>
       </x:c>
-      <x:c r="AE20" s="20" t="n">
-        <x:f>IF(AE5&gt;0,IF(AE5&gt;20000,Assumptions!$B$62,Assumptions!$B$61)*Assumptions!$B$75,0)</x:f>
+      <x:c r="AE21" s="20" t="n">
+        <x:f>IF(AE5&gt;0,IF(AE5&gt;20000,Assumptions!$B$80,Assumptions!$B$79)*Assumptions!$B$93,0)</x:f>
         <x:v>480000</x:v>
       </x:c>
-      <x:c r="AF20" s="20" t="n">
-        <x:f>IF(AF5&gt;0,IF(AF5&gt;20000,Assumptions!$B$62,Assumptions!$B$61)*Assumptions!$B$75,0)</x:f>
+      <x:c r="AF21" s="20" t="n">
+        <x:f>IF(AF5&gt;0,IF(AF5&gt;20000,Assumptions!$B$80,Assumptions!$B$79)*Assumptions!$B$93,0)</x:f>
         <x:v>480000</x:v>
       </x:c>
-      <x:c r="AG20" s="20" t="n">
-        <x:f>IF(AG5&gt;0,IF(AG5&gt;20000,Assumptions!$B$62,Assumptions!$B$61)*Assumptions!$B$75,0)</x:f>
+      <x:c r="AG21" s="20" t="n">
+        <x:f>IF(AG5&gt;0,IF(AG5&gt;20000,Assumptions!$B$80,Assumptions!$B$79)*Assumptions!$B$93,0)</x:f>
         <x:v>480000</x:v>
       </x:c>
-      <x:c r="AH20" s="20" t="n">
-        <x:f>IF(AH5&gt;0,IF(AH5&gt;20000,Assumptions!$B$62,Assumptions!$B$61)*Assumptions!$B$75,0)</x:f>
+      <x:c r="AH21" s="20" t="n">
+        <x:f>IF(AH5&gt;0,IF(AH5&gt;20000,Assumptions!$B$80,Assumptions!$B$79)*Assumptions!$B$93,0)</x:f>
         <x:v>480000</x:v>
       </x:c>
-      <x:c r="AI20" s="20" t="n">
-        <x:f>IF(AI5&gt;0,IF(AI5&gt;20000,Assumptions!$B$62,Assumptions!$B$61)*Assumptions!$B$75,0)</x:f>
+      <x:c r="AI21" s="20" t="n">
+        <x:f>IF(AI5&gt;0,IF(AI5&gt;20000,Assumptions!$B$80,Assumptions!$B$79)*Assumptions!$B$93,0)</x:f>
         <x:v>480000</x:v>
       </x:c>
-      <x:c r="AJ20" s="20" t="n">
-        <x:f>IF(AJ5&gt;0,IF(AJ5&gt;20000,Assumptions!$B$62,Assumptions!$B$61)*Assumptions!$B$75,0)</x:f>
+      <x:c r="AJ21" s="20" t="n">
+        <x:f>IF(AJ5&gt;0,IF(AJ5&gt;20000,Assumptions!$B$80,Assumptions!$B$79)*Assumptions!$B$93,0)</x:f>
         <x:v>480000</x:v>
       </x:c>
-      <x:c r="AK20" s="20" t="n">
-        <x:f>IF(AK5&gt;0,IF(AK5&gt;20000,Assumptions!$B$62,Assumptions!$B$61)*Assumptions!$B$75,0)</x:f>
+      <x:c r="AK21" s="20" t="n">
+        <x:f>IF(AK5&gt;0,IF(AK5&gt;20000,Assumptions!$B$80,Assumptions!$B$79)*Assumptions!$B$93,0)</x:f>
         <x:v>480000</x:v>
       </x:c>
     </x:row>
-    <x:row r="21">
-      <x:c r="A21" s="18" t="inlineStr">
+    <x:row r="22">
+      <x:c r="A22" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Total run cost</x:t>
         </x:is>
       </x:c>
-      <x:c r="B21" s="22" t="n">
-        <x:f>B13+SUM(B14:B20)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C21" s="22" t="n">
-        <x:f>C13+SUM(C14:C20)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D21" s="22" t="n">
-        <x:f>D13+SUM(D14:D20)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E21" s="22" t="n">
-        <x:f>E13+SUM(E14:E20)</x:f>
-        <x:v>877676.386112</x:v>
-      </x:c>
-      <x:c r="F21" s="22" t="n">
-        <x:f>F13+SUM(F14:F20)</x:f>
-        <x:v>877676.386112</x:v>
-      </x:c>
-      <x:c r="G21" s="22" t="n">
-        <x:f>G13+SUM(G14:G20)</x:f>
-        <x:v>877676.386112</x:v>
-      </x:c>
-      <x:c r="H21" s="22" t="n">
-        <x:f>H13+SUM(H14:H20)</x:f>
-        <x:v>1039184.368752</x:v>
-      </x:c>
-      <x:c r="I21" s="22" t="n">
-        <x:f>I13+SUM(I14:I20)</x:f>
-        <x:v>1039184.368752</x:v>
-      </x:c>
-      <x:c r="J21" s="22" t="n">
-        <x:f>J13+SUM(J14:J20)</x:f>
-        <x:v>1039184.368752</x:v>
-      </x:c>
-      <x:c r="K21" s="22" t="n">
-        <x:f>K13+SUM(K14:K20)</x:f>
-        <x:v>1039184.368752</x:v>
-      </x:c>
-      <x:c r="L21" s="22" t="n">
-        <x:f>L13+SUM(L14:L20)</x:f>
-        <x:v>1039184.368752</x:v>
-      </x:c>
-      <x:c r="M21" s="22" t="n">
-        <x:f>M13+SUM(M14:M20)</x:f>
-        <x:v>1039184.368752</x:v>
-      </x:c>
-      <x:c r="N21" s="22" t="n">
-        <x:f>N13+SUM(N14:N20)</x:f>
-        <x:v>1174433.94792</x:v>
-      </x:c>
-      <x:c r="O21" s="22" t="n">
-        <x:f>O13+SUM(O14:O20)</x:f>
-        <x:v>1174433.94792</x:v>
-      </x:c>
-      <x:c r="P21" s="22" t="n">
-        <x:f>P13+SUM(P14:P20)</x:f>
-        <x:v>1174433.94792</x:v>
-      </x:c>
-      <x:c r="Q21" s="22" t="n">
-        <x:f>Q13+SUM(Q14:Q20)</x:f>
-        <x:v>1174433.94792</x:v>
-      </x:c>
-      <x:c r="R21" s="22" t="n">
-        <x:f>R13+SUM(R14:R20)</x:f>
-        <x:v>1174433.94792</x:v>
-      </x:c>
-      <x:c r="S21" s="22" t="n">
-        <x:f>S13+SUM(S14:S20)</x:f>
-        <x:v>1174433.94792</x:v>
-      </x:c>
-      <x:c r="T21" s="22" t="n">
-        <x:f>T13+SUM(T14:T20)</x:f>
-        <x:v>1174433.94792</x:v>
-      </x:c>
-      <x:c r="U21" s="22" t="n">
-        <x:f>U13+SUM(U14:U20)</x:f>
-        <x:v>1174433.94792</x:v>
-      </x:c>
-      <x:c r="V21" s="22" t="n">
-        <x:f>V13+SUM(V14:V20)</x:f>
-        <x:v>1174433.94792</x:v>
-      </x:c>
-      <x:c r="W21" s="22" t="n">
-        <x:f>W13+SUM(W14:W20)</x:f>
-        <x:v>1174433.94792</x:v>
-      </x:c>
-      <x:c r="X21" s="22" t="n">
-        <x:f>X13+SUM(X14:X20)</x:f>
-        <x:v>1174433.94792</x:v>
-      </x:c>
-      <x:c r="Y21" s="22" t="n">
-        <x:f>Y13+SUM(Y14:Y20)</x:f>
-        <x:v>1174433.94792</x:v>
-      </x:c>
-      <x:c r="Z21" s="22" t="n">
-        <x:f>Z13+SUM(Z14:Z20)</x:f>
-        <x:v>1174433.94792</x:v>
-      </x:c>
-      <x:c r="AA21" s="22" t="n">
-        <x:f>AA13+SUM(AA14:AA20)</x:f>
-        <x:v>1174433.94792</x:v>
-      </x:c>
-      <x:c r="AB21" s="22" t="n">
-        <x:f>AB13+SUM(AB14:AB20)</x:f>
-        <x:v>1174433.94792</x:v>
-      </x:c>
-      <x:c r="AC21" s="22" t="n">
-        <x:f>AC13+SUM(AC14:AC20)</x:f>
-        <x:v>1174433.94792</x:v>
-      </x:c>
-      <x:c r="AD21" s="22" t="n">
-        <x:f>AD13+SUM(AD14:AD20)</x:f>
-        <x:v>1174433.94792</x:v>
-      </x:c>
-      <x:c r="AE21" s="22" t="n">
-        <x:f>AE13+SUM(AE14:AE20)</x:f>
-        <x:v>1174433.94792</x:v>
-      </x:c>
-      <x:c r="AF21" s="22" t="n">
-        <x:f>AF13+SUM(AF14:AF20)</x:f>
-        <x:v>1174433.94792</x:v>
-      </x:c>
-      <x:c r="AG21" s="22" t="n">
-        <x:f>AG13+SUM(AG14:AG20)</x:f>
-        <x:v>1174433.94792</x:v>
-      </x:c>
-      <x:c r="AH21" s="22" t="n">
-        <x:f>AH13+SUM(AH14:AH20)</x:f>
-        <x:v>1174433.94792</x:v>
-      </x:c>
-      <x:c r="AI21" s="22" t="n">
-        <x:f>AI13+SUM(AI14:AI20)</x:f>
-        <x:v>1174433.94792</x:v>
-      </x:c>
-      <x:c r="AJ21" s="22" t="n">
-        <x:f>AJ13+SUM(AJ14:AJ20)</x:f>
-        <x:v>1174433.94792</x:v>
-      </x:c>
-      <x:c r="AK21" s="22" t="n">
-        <x:f>AK13+SUM(AK14:AK20)</x:f>
-        <x:v>1174433.94792</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22">
-      <x:c r="A22" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Run cost per enrolled employee</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B22" s="19" t="n">
-        <x:f>IF(B5&gt;0,B21/B5,0)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C22" s="19" t="n">
-        <x:f>IF(C5&gt;0,C21/C5,0)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D22" s="19" t="n">
-        <x:f>IF(D5&gt;0,D21/D5,0)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E22" s="19" t="n">
-        <x:f>IF(E5&gt;0,E21/E5,0)</x:f>
-        <x:v>73.13969884266666</x:v>
-      </x:c>
-      <x:c r="F22" s="19" t="n">
-        <x:f>IF(F5&gt;0,F21/F5,0)</x:f>
-        <x:v>73.13969884266666</x:v>
-      </x:c>
-      <x:c r="G22" s="19" t="n">
-        <x:f>IF(G5&gt;0,G21/G5,0)</x:f>
-        <x:v>73.13969884266666</x:v>
-      </x:c>
-      <x:c r="H22" s="19" t="n">
-        <x:f>IF(H5&gt;0,H21/H5,0)</x:f>
-        <x:v>38.48830995377778</x:v>
-      </x:c>
-      <x:c r="I22" s="19" t="n">
-        <x:f>IF(I5&gt;0,I21/I5,0)</x:f>
-        <x:v>38.48830995377778</x:v>
-      </x:c>
-      <x:c r="J22" s="19" t="n">
-        <x:f>IF(J5&gt;0,J21/J5,0)</x:f>
-        <x:v>38.48830995377778</x:v>
-      </x:c>
-      <x:c r="K22" s="19" t="n">
-        <x:f>IF(K5&gt;0,K21/K5,0)</x:f>
-        <x:v>38.48830995377778</x:v>
-      </x:c>
-      <x:c r="L22" s="19" t="n">
-        <x:f>IF(L5&gt;0,L21/L5,0)</x:f>
-        <x:v>38.48830995377778</x:v>
-      </x:c>
-      <x:c r="M22" s="19" t="n">
-        <x:f>IF(M5&gt;0,M21/M5,0)</x:f>
-        <x:v>38.48830995377778</x:v>
-      </x:c>
-      <x:c r="N22" s="19" t="n">
-        <x:f>IF(N5&gt;0,N21/N5,0)</x:f>
-        <x:v>26.098532176</x:v>
-      </x:c>
-      <x:c r="O22" s="19" t="n">
-        <x:f>IF(O5&gt;0,O21/O5,0)</x:f>
-        <x:v>26.098532176</x:v>
-      </x:c>
-      <x:c r="P22" s="19" t="n">
-        <x:f>IF(P5&gt;0,P21/P5,0)</x:f>
-        <x:v>26.098532176</x:v>
-      </x:c>
-      <x:c r="Q22" s="19" t="n">
-        <x:f>IF(Q5&gt;0,Q21/Q5,0)</x:f>
-        <x:v>26.098532176</x:v>
-      </x:c>
-      <x:c r="R22" s="19" t="n">
-        <x:f>IF(R5&gt;0,R21/R5,0)</x:f>
-        <x:v>26.098532176</x:v>
-      </x:c>
-      <x:c r="S22" s="19" t="n">
-        <x:f>IF(S5&gt;0,S21/S5,0)</x:f>
-        <x:v>26.098532176</x:v>
-      </x:c>
-      <x:c r="T22" s="19" t="n">
-        <x:f>IF(T5&gt;0,T21/T5,0)</x:f>
-        <x:v>26.098532176</x:v>
-      </x:c>
-      <x:c r="U22" s="19" t="n">
-        <x:f>IF(U5&gt;0,U21/U5,0)</x:f>
-        <x:v>26.098532176</x:v>
-      </x:c>
-      <x:c r="V22" s="19" t="n">
-        <x:f>IF(V5&gt;0,V21/V5,0)</x:f>
-        <x:v>26.098532176</x:v>
-      </x:c>
-      <x:c r="W22" s="19" t="n">
-        <x:f>IF(W5&gt;0,W21/W5,0)</x:f>
-        <x:v>26.098532176</x:v>
-      </x:c>
-      <x:c r="X22" s="19" t="n">
-        <x:f>IF(X5&gt;0,X21/X5,0)</x:f>
-        <x:v>26.098532176</x:v>
-      </x:c>
-      <x:c r="Y22" s="19" t="n">
-        <x:f>IF(Y5&gt;0,Y21/Y5,0)</x:f>
-        <x:v>26.098532176</x:v>
-      </x:c>
-      <x:c r="Z22" s="19" t="n">
-        <x:f>IF(Z5&gt;0,Z21/Z5,0)</x:f>
-        <x:v>26.098532176</x:v>
-      </x:c>
-      <x:c r="AA22" s="19" t="n">
-        <x:f>IF(AA5&gt;0,AA21/AA5,0)</x:f>
-        <x:v>26.098532176</x:v>
-      </x:c>
-      <x:c r="AB22" s="19" t="n">
-        <x:f>IF(AB5&gt;0,AB21/AB5,0)</x:f>
-        <x:v>26.098532176</x:v>
-      </x:c>
-      <x:c r="AC22" s="19" t="n">
-        <x:f>IF(AC5&gt;0,AC21/AC5,0)</x:f>
-        <x:v>26.098532176</x:v>
-      </x:c>
-      <x:c r="AD22" s="19" t="n">
-        <x:f>IF(AD5&gt;0,AD21/AD5,0)</x:f>
-        <x:v>26.098532176</x:v>
-      </x:c>
-      <x:c r="AE22" s="19" t="n">
-        <x:f>IF(AE5&gt;0,AE21/AE5,0)</x:f>
-        <x:v>26.098532176</x:v>
-      </x:c>
-      <x:c r="AF22" s="19" t="n">
-        <x:f>IF(AF5&gt;0,AF21/AF5,0)</x:f>
-        <x:v>26.098532176</x:v>
-      </x:c>
-      <x:c r="AG22" s="19" t="n">
-        <x:f>IF(AG5&gt;0,AG21/AG5,0)</x:f>
-        <x:v>26.098532176</x:v>
-      </x:c>
-      <x:c r="AH22" s="19" t="n">
-        <x:f>IF(AH5&gt;0,AH21/AH5,0)</x:f>
-        <x:v>26.098532176</x:v>
-      </x:c>
-      <x:c r="AI22" s="19" t="n">
-        <x:f>IF(AI5&gt;0,AI21/AI5,0)</x:f>
-        <x:v>26.098532176</x:v>
-      </x:c>
-      <x:c r="AJ22" s="19" t="n">
-        <x:f>IF(AJ5&gt;0,AJ21/AJ5,0)</x:f>
-        <x:v>26.098532176</x:v>
-      </x:c>
-      <x:c r="AK22" s="19" t="n">
-        <x:f>IF(AK5&gt;0,AK21/AK5,0)</x:f>
-        <x:v>26.098532176</x:v>
+      <x:c r="B22" s="22" t="n">
+        <x:f>B13+SUM(B14:B21)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C22" s="22" t="n">
+        <x:f>C13+SUM(C14:C21)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D22" s="22" t="n">
+        <x:f>D13+SUM(D14:D21)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E22" s="22" t="n">
+        <x:f>E13+SUM(E14:E21)</x:f>
+        <x:v>910298.026112</x:v>
+      </x:c>
+      <x:c r="F22" s="22" t="n">
+        <x:f>F13+SUM(F14:F21)</x:f>
+        <x:v>910298.026112</x:v>
+      </x:c>
+      <x:c r="G22" s="22" t="n">
+        <x:f>G13+SUM(G14:G21)</x:f>
+        <x:v>910298.026112</x:v>
+      </x:c>
+      <x:c r="H22" s="22" t="n">
+        <x:f>H13+SUM(H14:H21)</x:f>
+        <x:v>1075474.948752</x:v>
+      </x:c>
+      <x:c r="I22" s="22" t="n">
+        <x:f>I13+SUM(I14:I21)</x:f>
+        <x:v>1075474.948752</x:v>
+      </x:c>
+      <x:c r="J22" s="22" t="n">
+        <x:f>J13+SUM(J14:J21)</x:f>
+        <x:v>1075474.948752</x:v>
+      </x:c>
+      <x:c r="K22" s="22" t="n">
+        <x:f>K13+SUM(K14:K21)</x:f>
+        <x:v>1075474.948752</x:v>
+      </x:c>
+      <x:c r="L22" s="22" t="n">
+        <x:f>L13+SUM(L14:L21)</x:f>
+        <x:v>1075474.948752</x:v>
+      </x:c>
+      <x:c r="M22" s="22" t="n">
+        <x:f>M13+SUM(M14:M21)</x:f>
+        <x:v>1075474.948752</x:v>
+      </x:c>
+      <x:c r="N22" s="22" t="n">
+        <x:f>N13+SUM(N14:N21)</x:f>
+        <x:v>1214393.46792</x:v>
+      </x:c>
+      <x:c r="O22" s="22" t="n">
+        <x:f>O13+SUM(O14:O21)</x:f>
+        <x:v>1214393.46792</x:v>
+      </x:c>
+      <x:c r="P22" s="22" t="n">
+        <x:f>P13+SUM(P14:P21)</x:f>
+        <x:v>1214393.46792</x:v>
+      </x:c>
+      <x:c r="Q22" s="22" t="n">
+        <x:f>Q13+SUM(Q14:Q21)</x:f>
+        <x:v>1214393.46792</x:v>
+      </x:c>
+      <x:c r="R22" s="22" t="n">
+        <x:f>R13+SUM(R14:R21)</x:f>
+        <x:v>1214393.46792</x:v>
+      </x:c>
+      <x:c r="S22" s="22" t="n">
+        <x:f>S13+SUM(S14:S21)</x:f>
+        <x:v>1214393.46792</x:v>
+      </x:c>
+      <x:c r="T22" s="22" t="n">
+        <x:f>T13+SUM(T14:T21)</x:f>
+        <x:v>1214393.46792</x:v>
+      </x:c>
+      <x:c r="U22" s="22" t="n">
+        <x:f>U13+SUM(U14:U21)</x:f>
+        <x:v>1214393.46792</x:v>
+      </x:c>
+      <x:c r="V22" s="22" t="n">
+        <x:f>V13+SUM(V14:V21)</x:f>
+        <x:v>1214393.46792</x:v>
+      </x:c>
+      <x:c r="W22" s="22" t="n">
+        <x:f>W13+SUM(W14:W21)</x:f>
+        <x:v>1214393.46792</x:v>
+      </x:c>
+      <x:c r="X22" s="22" t="n">
+        <x:f>X13+SUM(X14:X21)</x:f>
+        <x:v>1214393.46792</x:v>
+      </x:c>
+      <x:c r="Y22" s="22" t="n">
+        <x:f>Y13+SUM(Y14:Y21)</x:f>
+        <x:v>1214393.46792</x:v>
+      </x:c>
+      <x:c r="Z22" s="22" t="n">
+        <x:f>Z13+SUM(Z14:Z21)</x:f>
+        <x:v>1214393.46792</x:v>
+      </x:c>
+      <x:c r="AA22" s="22" t="n">
+        <x:f>AA13+SUM(AA14:AA21)</x:f>
+        <x:v>1214393.46792</x:v>
+      </x:c>
+      <x:c r="AB22" s="22" t="n">
+        <x:f>AB13+SUM(AB14:AB21)</x:f>
+        <x:v>1214393.46792</x:v>
+      </x:c>
+      <x:c r="AC22" s="22" t="n">
+        <x:f>AC13+SUM(AC14:AC21)</x:f>
+        <x:v>1214393.46792</x:v>
+      </x:c>
+      <x:c r="AD22" s="22" t="n">
+        <x:f>AD13+SUM(AD14:AD21)</x:f>
+        <x:v>1214393.46792</x:v>
+      </x:c>
+      <x:c r="AE22" s="22" t="n">
+        <x:f>AE13+SUM(AE14:AE21)</x:f>
+        <x:v>1214393.46792</x:v>
+      </x:c>
+      <x:c r="AF22" s="22" t="n">
+        <x:f>AF13+SUM(AF14:AF21)</x:f>
+        <x:v>1214393.46792</x:v>
+      </x:c>
+      <x:c r="AG22" s="22" t="n">
+        <x:f>AG13+SUM(AG14:AG21)</x:f>
+        <x:v>1214393.46792</x:v>
+      </x:c>
+      <x:c r="AH22" s="22" t="n">
+        <x:f>AH13+SUM(AH14:AH21)</x:f>
+        <x:v>1214393.46792</x:v>
+      </x:c>
+      <x:c r="AI22" s="22" t="n">
+        <x:f>AI13+SUM(AI14:AI21)</x:f>
+        <x:v>1214393.46792</x:v>
+      </x:c>
+      <x:c r="AJ22" s="22" t="n">
+        <x:f>AJ13+SUM(AJ14:AJ21)</x:f>
+        <x:v>1214393.46792</x:v>
+      </x:c>
+      <x:c r="AK22" s="22" t="n">
+        <x:f>AK13+SUM(AK14:AK21)</x:f>
+        <x:v>1214393.46792</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="7" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">Run cost per enrolled employee</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B23" s="19" t="n">
+        <x:f>IF(B5&gt;0,B22/B5,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C23" s="19" t="n">
+        <x:f>IF(C5&gt;0,C22/C5,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D23" s="19" t="n">
+        <x:f>IF(D5&gt;0,D22/D5,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E23" s="19" t="n">
+        <x:f>IF(E5&gt;0,E22/E5,0)</x:f>
+        <x:v>75.85816884266667</x:v>
+      </x:c>
+      <x:c r="F23" s="19" t="n">
+        <x:f>IF(F5&gt;0,F22/F5,0)</x:f>
+        <x:v>75.85816884266667</x:v>
+      </x:c>
+      <x:c r="G23" s="19" t="n">
+        <x:f>IF(G5&gt;0,G22/G5,0)</x:f>
+        <x:v>75.85816884266667</x:v>
+      </x:c>
+      <x:c r="H23" s="19" t="n">
+        <x:f>IF(H5&gt;0,H22/H5,0)</x:f>
+        <x:v>39.832405509333334</x:v>
+      </x:c>
+      <x:c r="I23" s="19" t="n">
+        <x:f>IF(I5&gt;0,I22/I5,0)</x:f>
+        <x:v>39.832405509333334</x:v>
+      </x:c>
+      <x:c r="J23" s="19" t="n">
+        <x:f>IF(J5&gt;0,J22/J5,0)</x:f>
+        <x:v>39.832405509333334</x:v>
+      </x:c>
+      <x:c r="K23" s="19" t="n">
+        <x:f>IF(K5&gt;0,K22/K5,0)</x:f>
+        <x:v>39.832405509333334</x:v>
+      </x:c>
+      <x:c r="L23" s="19" t="n">
+        <x:f>IF(L5&gt;0,L22/L5,0)</x:f>
+        <x:v>39.832405509333334</x:v>
+      </x:c>
+      <x:c r="M23" s="19" t="n">
+        <x:f>IF(M5&gt;0,M22/M5,0)</x:f>
+        <x:v>39.832405509333334</x:v>
+      </x:c>
+      <x:c r="N23" s="19" t="n">
+        <x:f>IF(N5&gt;0,N22/N5,0)</x:f>
+        <x:v>26.986521509333333</x:v>
+      </x:c>
+      <x:c r="O23" s="19" t="n">
+        <x:f>IF(O5&gt;0,O22/O5,0)</x:f>
+        <x:v>26.986521509333333</x:v>
+      </x:c>
+      <x:c r="P23" s="19" t="n">
+        <x:f>IF(P5&gt;0,P22/P5,0)</x:f>
+        <x:v>26.986521509333333</x:v>
+      </x:c>
+      <x:c r="Q23" s="19" t="n">
+        <x:f>IF(Q5&gt;0,Q22/Q5,0)</x:f>
+        <x:v>26.986521509333333</x:v>
+      </x:c>
+      <x:c r="R23" s="19" t="n">
+        <x:f>IF(R5&gt;0,R22/R5,0)</x:f>
+        <x:v>26.986521509333333</x:v>
+      </x:c>
+      <x:c r="S23" s="19" t="n">
+        <x:f>IF(S5&gt;0,S22/S5,0)</x:f>
+        <x:v>26.986521509333333</x:v>
+      </x:c>
+      <x:c r="T23" s="19" t="n">
+        <x:f>IF(T5&gt;0,T22/T5,0)</x:f>
+        <x:v>26.986521509333333</x:v>
+      </x:c>
+      <x:c r="U23" s="19" t="n">
+        <x:f>IF(U5&gt;0,U22/U5,0)</x:f>
+        <x:v>26.986521509333333</x:v>
+      </x:c>
+      <x:c r="V23" s="19" t="n">
+        <x:f>IF(V5&gt;0,V22/V5,0)</x:f>
+        <x:v>26.986521509333333</x:v>
+      </x:c>
+      <x:c r="W23" s="19" t="n">
+        <x:f>IF(W5&gt;0,W22/W5,0)</x:f>
+        <x:v>26.986521509333333</x:v>
+      </x:c>
+      <x:c r="X23" s="19" t="n">
+        <x:f>IF(X5&gt;0,X22/X5,0)</x:f>
+        <x:v>26.986521509333333</x:v>
+      </x:c>
+      <x:c r="Y23" s="19" t="n">
+        <x:f>IF(Y5&gt;0,Y22/Y5,0)</x:f>
+        <x:v>26.986521509333333</x:v>
+      </x:c>
+      <x:c r="Z23" s="19" t="n">
+        <x:f>IF(Z5&gt;0,Z22/Z5,0)</x:f>
+        <x:v>26.986521509333333</x:v>
+      </x:c>
+      <x:c r="AA23" s="19" t="n">
+        <x:f>IF(AA5&gt;0,AA22/AA5,0)</x:f>
+        <x:v>26.986521509333333</x:v>
+      </x:c>
+      <x:c r="AB23" s="19" t="n">
+        <x:f>IF(AB5&gt;0,AB22/AB5,0)</x:f>
+        <x:v>26.986521509333333</x:v>
+      </x:c>
+      <x:c r="AC23" s="19" t="n">
+        <x:f>IF(AC5&gt;0,AC22/AC5,0)</x:f>
+        <x:v>26.986521509333333</x:v>
+      </x:c>
+      <x:c r="AD23" s="19" t="n">
+        <x:f>IF(AD5&gt;0,AD22/AD5,0)</x:f>
+        <x:v>26.986521509333333</x:v>
+      </x:c>
+      <x:c r="AE23" s="19" t="n">
+        <x:f>IF(AE5&gt;0,AE22/AE5,0)</x:f>
+        <x:v>26.986521509333333</x:v>
+      </x:c>
+      <x:c r="AF23" s="19" t="n">
+        <x:f>IF(AF5&gt;0,AF22/AF5,0)</x:f>
+        <x:v>26.986521509333333</x:v>
+      </x:c>
+      <x:c r="AG23" s="19" t="n">
+        <x:f>IF(AG5&gt;0,AG22/AG5,0)</x:f>
+        <x:v>26.986521509333333</x:v>
+      </x:c>
+      <x:c r="AH23" s="19" t="n">
+        <x:f>IF(AH5&gt;0,AH22/AH5,0)</x:f>
+        <x:v>26.986521509333333</x:v>
+      </x:c>
+      <x:c r="AI23" s="19" t="n">
+        <x:f>IF(AI5&gt;0,AI22/AI5,0)</x:f>
+        <x:v>26.986521509333333</x:v>
+      </x:c>
+      <x:c r="AJ23" s="19" t="n">
+        <x:f>IF(AJ5&gt;0,AJ22/AJ5,0)</x:f>
+        <x:v>26.986521509333333</x:v>
+      </x:c>
+      <x:c r="AK23" s="19" t="n">
+        <x:f>IF(AK5&gt;0,AK22/AK5,0)</x:f>
+        <x:v>26.986521509333333</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="7" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">AI cost per coach active user</x:t>
         </x:is>
       </x:c>
-      <x:c r="B23" s="19" t="n">
+      <x:c r="B24" s="19" t="n">
         <x:f>IF(B6&gt;0,B13/B6,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C23" s="19" t="n">
+      <x:c r="C24" s="19" t="n">
         <x:f>IF(C6&gt;0,C13/C6,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D23" s="19" t="n">
+      <x:c r="D24" s="19" t="n">
         <x:f>IF(D6&gt;0,D13/D6,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E23" s="19" t="n">
+      <x:c r="E24" s="19" t="n">
         <x:f>IF(E6&gt;0,E13/E6,0)</x:f>
         <x:v>2.2511826133333335</x:v>
       </x:c>
-      <x:c r="F23" s="19" t="n">
+      <x:c r="F24" s="19" t="n">
         <x:f>IF(F6&gt;0,F13/F6,0)</x:f>
         <x:v>2.2511826133333335</x:v>
       </x:c>
-      <x:c r="G23" s="19" t="n">
+      <x:c r="G24" s="19" t="n">
         <x:f>IF(G6&gt;0,G13/G6,0)</x:f>
         <x:v>2.2511826133333335</x:v>
       </x:c>
-      <x:c r="H23" s="19" t="n">
+      <x:c r="H24" s="19" t="n">
         <x:f>IF(H6&gt;0,H13/H6,0)</x:f>
         <x:v>1.5690838479012343</x:v>
       </x:c>
-      <x:c r="I23" s="19" t="n">
+      <x:c r="I24" s="19" t="n">
         <x:f>IF(I6&gt;0,I13/I6,0)</x:f>
         <x:v>1.5690838479012343</x:v>
       </x:c>
-      <x:c r="J23" s="19" t="n">
+      <x:c r="J24" s="19" t="n">
         <x:f>IF(J6&gt;0,J13/J6,0)</x:f>
         <x:v>1.5690838479012343</x:v>
       </x:c>
-      <x:c r="K23" s="19" t="n">
+      <x:c r="K24" s="19" t="n">
         <x:f>IF(K6&gt;0,K13/K6,0)</x:f>
         <x:v>1.5690838479012343</x:v>
       </x:c>
-      <x:c r="L23" s="19" t="n">
+      <x:c r="L24" s="19" t="n">
         <x:f>IF(L6&gt;0,L13/L6,0)</x:f>
         <x:v>1.5690838479012343</x:v>
       </x:c>
-      <x:c r="M23" s="19" t="n">
+      <x:c r="M24" s="19" t="n">
         <x:f>IF(M6&gt;0,M13/M6,0)</x:f>
         <x:v>1.5690838479012343</x:v>
       </x:c>
-      <x:c r="N23" s="19" t="n">
+      <x:c r="N24" s="19" t="n">
         <x:f>IF(N6&gt;0,N13/N6,0)</x:f>
         <x:v>1.350812242962963</x:v>
       </x:c>
-      <x:c r="O23" s="19" t="n">
+      <x:c r="O24" s="19" t="n">
         <x:f>IF(O6&gt;0,O13/O6,0)</x:f>
         <x:v>1.350812242962963</x:v>
       </x:c>
-      <x:c r="P23" s="19" t="n">
+      <x:c r="P24" s="19" t="n">
         <x:f>IF(P6&gt;0,P13/P6,0)</x:f>
         <x:v>1.350812242962963</x:v>
       </x:c>
-      <x:c r="Q23" s="19" t="n">
+      <x:c r="Q24" s="19" t="n">
         <x:f>IF(Q6&gt;0,Q13/Q6,0)</x:f>
         <x:v>1.350812242962963</x:v>
       </x:c>
-      <x:c r="R23" s="19" t="n">
+      <x:c r="R24" s="19" t="n">
         <x:f>IF(R6&gt;0,R13/R6,0)</x:f>
         <x:v>1.350812242962963</x:v>
       </x:c>
-      <x:c r="S23" s="19" t="n">
+      <x:c r="S24" s="19" t="n">
         <x:f>IF(S6&gt;0,S13/S6,0)</x:f>
         <x:v>1.350812242962963</x:v>
       </x:c>
-      <x:c r="T23" s="19" t="n">
+      <x:c r="T24" s="19" t="n">
         <x:f>IF(T6&gt;0,T13/T6,0)</x:f>
         <x:v>1.350812242962963</x:v>
       </x:c>
-      <x:c r="U23" s="19" t="n">
+      <x:c r="U24" s="19" t="n">
         <x:f>IF(U6&gt;0,U13/U6,0)</x:f>
         <x:v>1.350812242962963</x:v>
       </x:c>
-      <x:c r="V23" s="19" t="n">
+      <x:c r="V24" s="19" t="n">
         <x:f>IF(V6&gt;0,V13/V6,0)</x:f>
         <x:v>1.350812242962963</x:v>
       </x:c>
-      <x:c r="W23" s="19" t="n">
+      <x:c r="W24" s="19" t="n">
         <x:f>IF(W6&gt;0,W13/W6,0)</x:f>
         <x:v>1.350812242962963</x:v>
       </x:c>
-      <x:c r="X23" s="19" t="n">
+      <x:c r="X24" s="19" t="n">
         <x:f>IF(X6&gt;0,X13/X6,0)</x:f>
         <x:v>1.350812242962963</x:v>
       </x:c>
-      <x:c r="Y23" s="19" t="n">
+      <x:c r="Y24" s="19" t="n">
         <x:f>IF(Y6&gt;0,Y13/Y6,0)</x:f>
         <x:v>1.350812242962963</x:v>
       </x:c>
-      <x:c r="Z23" s="19" t="n">
+      <x:c r="Z24" s="19" t="n">
         <x:f>IF(Z6&gt;0,Z13/Z6,0)</x:f>
         <x:v>1.350812242962963</x:v>
       </x:c>
-      <x:c r="AA23" s="19" t="n">
+      <x:c r="AA24" s="19" t="n">
         <x:f>IF(AA6&gt;0,AA13/AA6,0)</x:f>
         <x:v>1.350812242962963</x:v>
       </x:c>
-      <x:c r="AB23" s="19" t="n">
+      <x:c r="AB24" s="19" t="n">
         <x:f>IF(AB6&gt;0,AB13/AB6,0)</x:f>
         <x:v>1.350812242962963</x:v>
       </x:c>
-      <x:c r="AC23" s="19" t="n">
+      <x:c r="AC24" s="19" t="n">
         <x:f>IF(AC6&gt;0,AC13/AC6,0)</x:f>
         <x:v>1.350812242962963</x:v>
       </x:c>
-      <x:c r="AD23" s="19" t="n">
+      <x:c r="AD24" s="19" t="n">
         <x:f>IF(AD6&gt;0,AD13/AD6,0)</x:f>
         <x:v>1.350812242962963</x:v>
       </x:c>
-      <x:c r="AE23" s="19" t="n">
+      <x:c r="AE24" s="19" t="n">
         <x:f>IF(AE6&gt;0,AE13/AE6,0)</x:f>
         <x:v>1.350812242962963</x:v>
       </x:c>
-      <x:c r="AF23" s="19" t="n">
+      <x:c r="AF24" s="19" t="n">
         <x:f>IF(AF6&gt;0,AF13/AF6,0)</x:f>
         <x:v>1.350812242962963</x:v>
       </x:c>
-      <x:c r="AG23" s="19" t="n">
+      <x:c r="AG24" s="19" t="n">
         <x:f>IF(AG6&gt;0,AG13/AG6,0)</x:f>
         <x:v>1.350812242962963</x:v>
       </x:c>
-      <x:c r="AH23" s="19" t="n">
+      <x:c r="AH24" s="19" t="n">
         <x:f>IF(AH6&gt;0,AH13/AH6,0)</x:f>
         <x:v>1.350812242962963</x:v>
       </x:c>
-      <x:c r="AI23" s="19" t="n">
+      <x:c r="AI24" s="19" t="n">
         <x:f>IF(AI6&gt;0,AI13/AI6,0)</x:f>
         <x:v>1.350812242962963</x:v>
       </x:c>
-      <x:c r="AJ23" s="19" t="n">
+      <x:c r="AJ24" s="19" t="n">
         <x:f>IF(AJ6&gt;0,AJ13/AJ6,0)</x:f>
         <x:v>1.350812242962963</x:v>
       </x:c>
-      <x:c r="AK23" s="19" t="n">
+      <x:c r="AK24" s="19" t="n">
         <x:f>IF(AK6&gt;0,AK13/AK6,0)</x:f>
         <x:v>1.350812242962963</x:v>
       </x:c>
@@ -5969,19 +6488,19 @@
       </x:c>
       <x:c r="B9" s="27" t="n">
         <x:f>SUM(B40:M40)</x:f>
-        <x:v>20415992.513705146</x:v>
+        <x:v>21048451.673705146</x:v>
       </x:c>
       <x:c r="C9" s="27" t="n">
         <x:f>SUM(N40:Y40)</x:f>
-        <x:v>18593207.37504</x:v>
+        <x:v>19072721.61504</x:v>
       </x:c>
       <x:c r="D9" s="27" t="n">
         <x:f>SUM(Z40:AK40)</x:f>
-        <x:v>14093207.37504</x:v>
+        <x:v>14572721.615039999</x:v>
       </x:c>
       <x:c r="E9" s="28" t="n">
         <x:f>SUM(B9:D9)</x:f>
-        <x:v>53102407.263785146</x:v>
+        <x:v>54693894.90378515</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -5992,19 +6511,19 @@
       </x:c>
       <x:c r="B10" s="28" t="n">
         <x:f>SUM(B41:M41)</x:f>
-        <x:v>10806007.486294853</x:v>
+        <x:v>10173548.326294854</x:v>
       </x:c>
       <x:c r="C10" s="28" t="n">
         <x:f>SUM(N41:Y41)</x:f>
-        <x:v>11466792.624959998</x:v>
+        <x:v>10987278.384960003</x:v>
       </x:c>
       <x:c r="D10" s="28" t="n">
         <x:f>SUM(Z41:AK41)</x:f>
-        <x:v>6966792.624959999</x:v>
+        <x:v>6487278.384960002</x:v>
       </x:c>
       <x:c r="E10" s="28" t="n">
         <x:f>SUM(B10:D10)</x:f>
-        <x:v>29239592.736214846</x:v>
+        <x:v>27648105.09621486</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -6015,19 +6534,19 @@
       </x:c>
       <x:c r="B11" s="24" t="n">
         <x:f>IF(B8&gt;0,B10/B8,0)</x:f>
-        <x:v>0.34610234726458433</x:v>
+        <x:v>0.32584550401303103</x:v>
       </x:c>
       <x:c r="C11" s="24" t="n">
         <x:f>IF(C8&gt;0,C10/C8,0)</x:f>
-        <x:v>0.38146349384431133</x:v>
+        <x:v>0.3655115896526947</x:v>
       </x:c>
       <x:c r="D11" s="24" t="n">
         <x:f>IF(D8&gt;0,D10/D8,0)</x:f>
-        <x:v>0.3308068672820512</x:v>
+        <x:v>0.30803791001709413</x:v>
       </x:c>
       <x:c r="E11" s="29" t="n">
         <x:f>IF(E8&gt;0,E10/E8,0)</x:f>
-        <x:v>0.35509937499957306</x:v>
+        <x:v>0.3357716001094807</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -6101,7 +6620,7 @@
         </x:is>
       </x:c>
       <x:c r="D17" s="27" t="n">
-        <x:f>(Assumptions!$B$11+Assumptions!$B$13+Assumptions!$B$15)*Assumptions!$B$64*12</x:f>
+        <x:f>(Assumptions!$B$11+Assumptions!$B$13+Assumptions!$B$15)*Assumptions!$B$82*12</x:f>
         <x:v>21060000</x:v>
       </x:c>
     </x:row>
@@ -6112,7 +6631,7 @@
         </x:is>
       </x:c>
       <x:c r="D18" s="27" t="n">
-        <x:f>D17*Assumptions!$B$70</x:f>
+        <x:f>D17*Assumptions!$B$88</x:f>
         <x:v>2106000</x:v>
       </x:c>
     </x:row>
@@ -6123,8 +6642,8 @@
         </x:is>
       </x:c>
       <x:c r="D19" s="31" t="n">
-        <x:f>Run!AK22</x:f>
-        <x:v>26.098532176</x:v>
+        <x:f>Run!AK23</x:f>
+        <x:v>26.986521509333333</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -6134,7 +6653,7 @@
         </x:is>
       </x:c>
       <x:c r="D20" s="31" t="n">
-        <x:f>Run!AK23</x:f>
+        <x:f>Run!AK24</x:f>
         <x:v>1.350812242962963</x:v>
       </x:c>
     </x:row>
@@ -6145,7 +6664,7 @@
         </x:is>
       </x:c>
       <x:c r="D21" s="32" t="n">
-        <x:f>Build!$E$31</x:f>
+        <x:f>Build!$E$32</x:f>
         <x:v>17500000</x:v>
       </x:c>
     </x:row>
@@ -6156,8 +6675,8 @@
         </x:is>
       </x:c>
       <x:c r="C22" s="33" t="n">
-        <x:f>Run!E21</x:f>
-        <x:v>877676.386112</x:v>
+        <x:f>Run!E22</x:f>
+        <x:v>910298.026112</x:v>
       </x:c>
       <x:c r="D22" s="20" t="n">
         <x:f>E34</x:f>
@@ -6444,147 +6963,147 @@
         </x:is>
       </x:c>
       <x:c r="B32" s="20" t="n">
-        <x:f>IF(B31&gt;0,MAX(B31,IF(B$30&gt;=Assumptions!$B$14,Assumptions!$B$65,0)),0)</x:f>
+        <x:f>IF(B31&gt;0,MAX(B31,IF(B$30&gt;=Assumptions!$B$14,Assumptions!$B$83,0)),0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C32" s="20" t="n">
-        <x:f>IF(C31&gt;0,MAX(C31,IF(C$30&gt;=Assumptions!$B$14,Assumptions!$B$65,0)),0)</x:f>
+        <x:f>IF(C31&gt;0,MAX(C31,IF(C$30&gt;=Assumptions!$B$14,Assumptions!$B$83,0)),0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D32" s="20" t="n">
-        <x:f>IF(D31&gt;0,MAX(D31,IF(D$30&gt;=Assumptions!$B$14,Assumptions!$B$65,0)),0)</x:f>
+        <x:f>IF(D31&gt;0,MAX(D31,IF(D$30&gt;=Assumptions!$B$14,Assumptions!$B$83,0)),0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="E32" s="20" t="n">
-        <x:f>IF(E31&gt;0,MAX(E31,IF(E$30&gt;=Assumptions!$B$14,Assumptions!$B$65,0)),0)</x:f>
+        <x:f>IF(E31&gt;0,MAX(E31,IF(E$30&gt;=Assumptions!$B$14,Assumptions!$B$83,0)),0)</x:f>
         <x:v>12000</x:v>
       </x:c>
       <x:c r="F32" s="20" t="n">
-        <x:f>IF(F31&gt;0,MAX(F31,IF(F$30&gt;=Assumptions!$B$14,Assumptions!$B$65,0)),0)</x:f>
+        <x:f>IF(F31&gt;0,MAX(F31,IF(F$30&gt;=Assumptions!$B$14,Assumptions!$B$83,0)),0)</x:f>
         <x:v>12000</x:v>
       </x:c>
       <x:c r="G32" s="20" t="n">
-        <x:f>IF(G31&gt;0,MAX(G31,IF(G$30&gt;=Assumptions!$B$14,Assumptions!$B$65,0)),0)</x:f>
+        <x:f>IF(G31&gt;0,MAX(G31,IF(G$30&gt;=Assumptions!$B$14,Assumptions!$B$83,0)),0)</x:f>
         <x:v>12000</x:v>
       </x:c>
       <x:c r="H32" s="20" t="n">
-        <x:f>IF(H31&gt;0,MAX(H31,IF(H$30&gt;=Assumptions!$B$14,Assumptions!$B$65,0)),0)</x:f>
+        <x:f>IF(H31&gt;0,MAX(H31,IF(H$30&gt;=Assumptions!$B$14,Assumptions!$B$83,0)),0)</x:f>
         <x:v>27000</x:v>
       </x:c>
       <x:c r="I32" s="20" t="n">
-        <x:f>IF(I31&gt;0,MAX(I31,IF(I$30&gt;=Assumptions!$B$14,Assumptions!$B$65,0)),0)</x:f>
+        <x:f>IF(I31&gt;0,MAX(I31,IF(I$30&gt;=Assumptions!$B$14,Assumptions!$B$83,0)),0)</x:f>
         <x:v>27000</x:v>
       </x:c>
       <x:c r="J32" s="20" t="n">
-        <x:f>IF(J31&gt;0,MAX(J31,IF(J$30&gt;=Assumptions!$B$14,Assumptions!$B$65,0)),0)</x:f>
+        <x:f>IF(J31&gt;0,MAX(J31,IF(J$30&gt;=Assumptions!$B$14,Assumptions!$B$83,0)),0)</x:f>
         <x:v>27000</x:v>
       </x:c>
       <x:c r="K32" s="20" t="n">
-        <x:f>IF(K31&gt;0,MAX(K31,IF(K$30&gt;=Assumptions!$B$14,Assumptions!$B$65,0)),0)</x:f>
+        <x:f>IF(K31&gt;0,MAX(K31,IF(K$30&gt;=Assumptions!$B$14,Assumptions!$B$83,0)),0)</x:f>
         <x:v>27000</x:v>
       </x:c>
       <x:c r="L32" s="20" t="n">
-        <x:f>IF(L31&gt;0,MAX(L31,IF(L$30&gt;=Assumptions!$B$14,Assumptions!$B$65,0)),0)</x:f>
+        <x:f>IF(L31&gt;0,MAX(L31,IF(L$30&gt;=Assumptions!$B$14,Assumptions!$B$83,0)),0)</x:f>
         <x:v>27000</x:v>
       </x:c>
       <x:c r="M32" s="20" t="n">
-        <x:f>IF(M31&gt;0,MAX(M31,IF(M$30&gt;=Assumptions!$B$14,Assumptions!$B$65,0)),0)</x:f>
+        <x:f>IF(M31&gt;0,MAX(M31,IF(M$30&gt;=Assumptions!$B$14,Assumptions!$B$83,0)),0)</x:f>
         <x:v>27000</x:v>
       </x:c>
       <x:c r="N32" s="20" t="n">
-        <x:f>IF(N31&gt;0,MAX(N31,IF(N$30&gt;=Assumptions!$B$14,Assumptions!$B$65,0)),0)</x:f>
+        <x:f>IF(N31&gt;0,MAX(N31,IF(N$30&gt;=Assumptions!$B$14,Assumptions!$B$83,0)),0)</x:f>
         <x:v>45000</x:v>
       </x:c>
       <x:c r="O32" s="20" t="n">
-        <x:f>IF(O31&gt;0,MAX(O31,IF(O$30&gt;=Assumptions!$B$14,Assumptions!$B$65,0)),0)</x:f>
+        <x:f>IF(O31&gt;0,MAX(O31,IF(O$30&gt;=Assumptions!$B$14,Assumptions!$B$83,0)),0)</x:f>
         <x:v>45000</x:v>
       </x:c>
       <x:c r="P32" s="20" t="n">
-        <x:f>IF(P31&gt;0,MAX(P31,IF(P$30&gt;=Assumptions!$B$14,Assumptions!$B$65,0)),0)</x:f>
+        <x:f>IF(P31&gt;0,MAX(P31,IF(P$30&gt;=Assumptions!$B$14,Assumptions!$B$83,0)),0)</x:f>
         <x:v>45000</x:v>
       </x:c>
       <x:c r="Q32" s="20" t="n">
-        <x:f>IF(Q31&gt;0,MAX(Q31,IF(Q$30&gt;=Assumptions!$B$14,Assumptions!$B$65,0)),0)</x:f>
+        <x:f>IF(Q31&gt;0,MAX(Q31,IF(Q$30&gt;=Assumptions!$B$14,Assumptions!$B$83,0)),0)</x:f>
         <x:v>45000</x:v>
       </x:c>
       <x:c r="R32" s="20" t="n">
-        <x:f>IF(R31&gt;0,MAX(R31,IF(R$30&gt;=Assumptions!$B$14,Assumptions!$B$65,0)),0)</x:f>
+        <x:f>IF(R31&gt;0,MAX(R31,IF(R$30&gt;=Assumptions!$B$14,Assumptions!$B$83,0)),0)</x:f>
         <x:v>45000</x:v>
       </x:c>
       <x:c r="S32" s="20" t="n">
-        <x:f>IF(S31&gt;0,MAX(S31,IF(S$30&gt;=Assumptions!$B$14,Assumptions!$B$65,0)),0)</x:f>
+        <x:f>IF(S31&gt;0,MAX(S31,IF(S$30&gt;=Assumptions!$B$14,Assumptions!$B$83,0)),0)</x:f>
         <x:v>45000</x:v>
       </x:c>
       <x:c r="T32" s="20" t="n">
-        <x:f>IF(T31&gt;0,MAX(T31,IF(T$30&gt;=Assumptions!$B$14,Assumptions!$B$65,0)),0)</x:f>
+        <x:f>IF(T31&gt;0,MAX(T31,IF(T$30&gt;=Assumptions!$B$14,Assumptions!$B$83,0)),0)</x:f>
         <x:v>45000</x:v>
       </x:c>
       <x:c r="U32" s="20" t="n">
-        <x:f>IF(U31&gt;0,MAX(U31,IF(U$30&gt;=Assumptions!$B$14,Assumptions!$B$65,0)),0)</x:f>
+        <x:f>IF(U31&gt;0,MAX(U31,IF(U$30&gt;=Assumptions!$B$14,Assumptions!$B$83,0)),0)</x:f>
         <x:v>45000</x:v>
       </x:c>
       <x:c r="V32" s="20" t="n">
-        <x:f>IF(V31&gt;0,MAX(V31,IF(V$30&gt;=Assumptions!$B$14,Assumptions!$B$65,0)),0)</x:f>
+        <x:f>IF(V31&gt;0,MAX(V31,IF(V$30&gt;=Assumptions!$B$14,Assumptions!$B$83,0)),0)</x:f>
         <x:v>45000</x:v>
       </x:c>
       <x:c r="W32" s="20" t="n">
-        <x:f>IF(W31&gt;0,MAX(W31,IF(W$30&gt;=Assumptions!$B$14,Assumptions!$B$65,0)),0)</x:f>
+        <x:f>IF(W31&gt;0,MAX(W31,IF(W$30&gt;=Assumptions!$B$14,Assumptions!$B$83,0)),0)</x:f>
         <x:v>45000</x:v>
       </x:c>
       <x:c r="X32" s="20" t="n">
-        <x:f>IF(X31&gt;0,MAX(X31,IF(X$30&gt;=Assumptions!$B$14,Assumptions!$B$65,0)),0)</x:f>
+        <x:f>IF(X31&gt;0,MAX(X31,IF(X$30&gt;=Assumptions!$B$14,Assumptions!$B$83,0)),0)</x:f>
         <x:v>45000</x:v>
       </x:c>
       <x:c r="Y32" s="20" t="n">
-        <x:f>IF(Y31&gt;0,MAX(Y31,IF(Y$30&gt;=Assumptions!$B$14,Assumptions!$B$65,0)),0)</x:f>
+        <x:f>IF(Y31&gt;0,MAX(Y31,IF(Y$30&gt;=Assumptions!$B$14,Assumptions!$B$83,0)),0)</x:f>
         <x:v>45000</x:v>
       </x:c>
       <x:c r="Z32" s="20" t="n">
-        <x:f>IF(Z31&gt;0,MAX(Z31,IF(Z$30&gt;=Assumptions!$B$14,Assumptions!$B$65,0)),0)</x:f>
+        <x:f>IF(Z31&gt;0,MAX(Z31,IF(Z$30&gt;=Assumptions!$B$14,Assumptions!$B$83,0)),0)</x:f>
         <x:v>45000</x:v>
       </x:c>
       <x:c r="AA32" s="20" t="n">
-        <x:f>IF(AA31&gt;0,MAX(AA31,IF(AA$30&gt;=Assumptions!$B$14,Assumptions!$B$65,0)),0)</x:f>
+        <x:f>IF(AA31&gt;0,MAX(AA31,IF(AA$30&gt;=Assumptions!$B$14,Assumptions!$B$83,0)),0)</x:f>
         <x:v>45000</x:v>
       </x:c>
       <x:c r="AB32" s="20" t="n">
-        <x:f>IF(AB31&gt;0,MAX(AB31,IF(AB$30&gt;=Assumptions!$B$14,Assumptions!$B$65,0)),0)</x:f>
+        <x:f>IF(AB31&gt;0,MAX(AB31,IF(AB$30&gt;=Assumptions!$B$14,Assumptions!$B$83,0)),0)</x:f>
         <x:v>45000</x:v>
       </x:c>
       <x:c r="AC32" s="20" t="n">
-        <x:f>IF(AC31&gt;0,MAX(AC31,IF(AC$30&gt;=Assumptions!$B$14,Assumptions!$B$65,0)),0)</x:f>
+        <x:f>IF(AC31&gt;0,MAX(AC31,IF(AC$30&gt;=Assumptions!$B$14,Assumptions!$B$83,0)),0)</x:f>
         <x:v>45000</x:v>
       </x:c>
       <x:c r="AD32" s="20" t="n">
-        <x:f>IF(AD31&gt;0,MAX(AD31,IF(AD$30&gt;=Assumptions!$B$14,Assumptions!$B$65,0)),0)</x:f>
+        <x:f>IF(AD31&gt;0,MAX(AD31,IF(AD$30&gt;=Assumptions!$B$14,Assumptions!$B$83,0)),0)</x:f>
         <x:v>45000</x:v>
       </x:c>
       <x:c r="AE32" s="20" t="n">
-        <x:f>IF(AE31&gt;0,MAX(AE31,IF(AE$30&gt;=Assumptions!$B$14,Assumptions!$B$65,0)),0)</x:f>
+        <x:f>IF(AE31&gt;0,MAX(AE31,IF(AE$30&gt;=Assumptions!$B$14,Assumptions!$B$83,0)),0)</x:f>
         <x:v>45000</x:v>
       </x:c>
       <x:c r="AF32" s="20" t="n">
-        <x:f>IF(AF31&gt;0,MAX(AF31,IF(AF$30&gt;=Assumptions!$B$14,Assumptions!$B$65,0)),0)</x:f>
+        <x:f>IF(AF31&gt;0,MAX(AF31,IF(AF$30&gt;=Assumptions!$B$14,Assumptions!$B$83,0)),0)</x:f>
         <x:v>45000</x:v>
       </x:c>
       <x:c r="AG32" s="20" t="n">
-        <x:f>IF(AG31&gt;0,MAX(AG31,IF(AG$30&gt;=Assumptions!$B$14,Assumptions!$B$65,0)),0)</x:f>
+        <x:f>IF(AG31&gt;0,MAX(AG31,IF(AG$30&gt;=Assumptions!$B$14,Assumptions!$B$83,0)),0)</x:f>
         <x:v>45000</x:v>
       </x:c>
       <x:c r="AH32" s="20" t="n">
-        <x:f>IF(AH31&gt;0,MAX(AH31,IF(AH$30&gt;=Assumptions!$B$14,Assumptions!$B$65,0)),0)</x:f>
+        <x:f>IF(AH31&gt;0,MAX(AH31,IF(AH$30&gt;=Assumptions!$B$14,Assumptions!$B$83,0)),0)</x:f>
         <x:v>45000</x:v>
       </x:c>
       <x:c r="AI32" s="20" t="n">
-        <x:f>IF(AI31&gt;0,MAX(AI31,IF(AI$30&gt;=Assumptions!$B$14,Assumptions!$B$65,0)),0)</x:f>
+        <x:f>IF(AI31&gt;0,MAX(AI31,IF(AI$30&gt;=Assumptions!$B$14,Assumptions!$B$83,0)),0)</x:f>
         <x:v>45000</x:v>
       </x:c>
       <x:c r="AJ32" s="20" t="n">
-        <x:f>IF(AJ31&gt;0,MAX(AJ31,IF(AJ$30&gt;=Assumptions!$B$14,Assumptions!$B$65,0)),0)</x:f>
+        <x:f>IF(AJ31&gt;0,MAX(AJ31,IF(AJ$30&gt;=Assumptions!$B$14,Assumptions!$B$83,0)),0)</x:f>
         <x:v>45000</x:v>
       </x:c>
       <x:c r="AK32" s="20" t="n">
-        <x:f>IF(AK31&gt;0,MAX(AK31,IF(AK$30&gt;=Assumptions!$B$14,Assumptions!$B$65,0)),0)</x:f>
+        <x:f>IF(AK31&gt;0,MAX(AK31,IF(AK$30&gt;=Assumptions!$B$14,Assumptions!$B$83,0)),0)</x:f>
         <x:v>45000</x:v>
       </x:c>
     </x:row>
@@ -6595,147 +7114,147 @@
         </x:is>
       </x:c>
       <x:c r="B33" s="20" t="n">
-        <x:f>IF(B$30=1,0.3,IF(B$30=2,0.3,IF(B$30=3,0.4,0)))*Build!$E$31</x:f>
+        <x:f>IF(B$30=1,0.3,IF(B$30=2,0.3,IF(B$30=3,0.4,0)))*Build!$E$32</x:f>
         <x:v>5250000</x:v>
       </x:c>
       <x:c r="C33" s="20" t="n">
-        <x:f>IF(C$30=1,0.3,IF(C$30=2,0.3,IF(C$30=3,0.4,0)))*Build!$E$31</x:f>
+        <x:f>IF(C$30=1,0.3,IF(C$30=2,0.3,IF(C$30=3,0.4,0)))*Build!$E$32</x:f>
         <x:v>5250000</x:v>
       </x:c>
       <x:c r="D33" s="20" t="n">
-        <x:f>IF(D$30=1,0.3,IF(D$30=2,0.3,IF(D$30=3,0.4,0)))*Build!$E$31</x:f>
+        <x:f>IF(D$30=1,0.3,IF(D$30=2,0.3,IF(D$30=3,0.4,0)))*Build!$E$32</x:f>
         <x:v>7000000</x:v>
       </x:c>
       <x:c r="E33" s="20" t="n">
-        <x:f>IF(E$30=1,0.3,IF(E$30=2,0.3,IF(E$30=3,0.4,0)))*Build!$E$31</x:f>
+        <x:f>IF(E$30=1,0.3,IF(E$30=2,0.3,IF(E$30=3,0.4,0)))*Build!$E$32</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="F33" s="20" t="n">
-        <x:f>IF(F$30=1,0.3,IF(F$30=2,0.3,IF(F$30=3,0.4,0)))*Build!$E$31</x:f>
+        <x:f>IF(F$30=1,0.3,IF(F$30=2,0.3,IF(F$30=3,0.4,0)))*Build!$E$32</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="G33" s="20" t="n">
-        <x:f>IF(G$30=1,0.3,IF(G$30=2,0.3,IF(G$30=3,0.4,0)))*Build!$E$31</x:f>
+        <x:f>IF(G$30=1,0.3,IF(G$30=2,0.3,IF(G$30=3,0.4,0)))*Build!$E$32</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="H33" s="20" t="n">
-        <x:f>IF(H$30=1,0.3,IF(H$30=2,0.3,IF(H$30=3,0.4,0)))*Build!$E$31</x:f>
+        <x:f>IF(H$30=1,0.3,IF(H$30=2,0.3,IF(H$30=3,0.4,0)))*Build!$E$32</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="I33" s="20" t="n">
-        <x:f>IF(I$30=1,0.3,IF(I$30=2,0.3,IF(I$30=3,0.4,0)))*Build!$E$31</x:f>
+        <x:f>IF(I$30=1,0.3,IF(I$30=2,0.3,IF(I$30=3,0.4,0)))*Build!$E$32</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J33" s="20" t="n">
-        <x:f>IF(J$30=1,0.3,IF(J$30=2,0.3,IF(J$30=3,0.4,0)))*Build!$E$31</x:f>
+        <x:f>IF(J$30=1,0.3,IF(J$30=2,0.3,IF(J$30=3,0.4,0)))*Build!$E$32</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K33" s="20" t="n">
-        <x:f>IF(K$30=1,0.3,IF(K$30=2,0.3,IF(K$30=3,0.4,0)))*Build!$E$31</x:f>
+        <x:f>IF(K$30=1,0.3,IF(K$30=2,0.3,IF(K$30=3,0.4,0)))*Build!$E$32</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="L33" s="20" t="n">
-        <x:f>IF(L$30=1,0.3,IF(L$30=2,0.3,IF(L$30=3,0.4,0)))*Build!$E$31</x:f>
+        <x:f>IF(L$30=1,0.3,IF(L$30=2,0.3,IF(L$30=3,0.4,0)))*Build!$E$32</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M33" s="20" t="n">
-        <x:f>IF(M$30=1,0.3,IF(M$30=2,0.3,IF(M$30=3,0.4,0)))*Build!$E$31</x:f>
+        <x:f>IF(M$30=1,0.3,IF(M$30=2,0.3,IF(M$30=3,0.4,0)))*Build!$E$32</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="N33" s="20" t="n">
-        <x:f>IF(N$30=1,0.3,IF(N$30=2,0.3,IF(N$30=3,0.4,0)))*Build!$E$31</x:f>
+        <x:f>IF(N$30=1,0.3,IF(N$30=2,0.3,IF(N$30=3,0.4,0)))*Build!$E$32</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="O33" s="20" t="n">
-        <x:f>IF(O$30=1,0.3,IF(O$30=2,0.3,IF(O$30=3,0.4,0)))*Build!$E$31</x:f>
+        <x:f>IF(O$30=1,0.3,IF(O$30=2,0.3,IF(O$30=3,0.4,0)))*Build!$E$32</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="P33" s="20" t="n">
-        <x:f>IF(P$30=1,0.3,IF(P$30=2,0.3,IF(P$30=3,0.4,0)))*Build!$E$31</x:f>
+        <x:f>IF(P$30=1,0.3,IF(P$30=2,0.3,IF(P$30=3,0.4,0)))*Build!$E$32</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q33" s="20" t="n">
-        <x:f>IF(Q$30=1,0.3,IF(Q$30=2,0.3,IF(Q$30=3,0.4,0)))*Build!$E$31</x:f>
+        <x:f>IF(Q$30=1,0.3,IF(Q$30=2,0.3,IF(Q$30=3,0.4,0)))*Build!$E$32</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="R33" s="20" t="n">
-        <x:f>IF(R$30=1,0.3,IF(R$30=2,0.3,IF(R$30=3,0.4,0)))*Build!$E$31</x:f>
+        <x:f>IF(R$30=1,0.3,IF(R$30=2,0.3,IF(R$30=3,0.4,0)))*Build!$E$32</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="S33" s="20" t="n">
-        <x:f>IF(S$30=1,0.3,IF(S$30=2,0.3,IF(S$30=3,0.4,0)))*Build!$E$31</x:f>
+        <x:f>IF(S$30=1,0.3,IF(S$30=2,0.3,IF(S$30=3,0.4,0)))*Build!$E$32</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="T33" s="20" t="n">
-        <x:f>IF(T$30=1,0.3,IF(T$30=2,0.3,IF(T$30=3,0.4,0)))*Build!$E$31</x:f>
+        <x:f>IF(T$30=1,0.3,IF(T$30=2,0.3,IF(T$30=3,0.4,0)))*Build!$E$32</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="U33" s="20" t="n">
-        <x:f>IF(U$30=1,0.3,IF(U$30=2,0.3,IF(U$30=3,0.4,0)))*Build!$E$31</x:f>
+        <x:f>IF(U$30=1,0.3,IF(U$30=2,0.3,IF(U$30=3,0.4,0)))*Build!$E$32</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="V33" s="20" t="n">
-        <x:f>IF(V$30=1,0.3,IF(V$30=2,0.3,IF(V$30=3,0.4,0)))*Build!$E$31</x:f>
+        <x:f>IF(V$30=1,0.3,IF(V$30=2,0.3,IF(V$30=3,0.4,0)))*Build!$E$32</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="W33" s="20" t="n">
-        <x:f>IF(W$30=1,0.3,IF(W$30=2,0.3,IF(W$30=3,0.4,0)))*Build!$E$31</x:f>
+        <x:f>IF(W$30=1,0.3,IF(W$30=2,0.3,IF(W$30=3,0.4,0)))*Build!$E$32</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="X33" s="20" t="n">
-        <x:f>IF(X$30=1,0.3,IF(X$30=2,0.3,IF(X$30=3,0.4,0)))*Build!$E$31</x:f>
+        <x:f>IF(X$30=1,0.3,IF(X$30=2,0.3,IF(X$30=3,0.4,0)))*Build!$E$32</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="Y33" s="20" t="n">
-        <x:f>IF(Y$30=1,0.3,IF(Y$30=2,0.3,IF(Y$30=3,0.4,0)))*Build!$E$31</x:f>
+        <x:f>IF(Y$30=1,0.3,IF(Y$30=2,0.3,IF(Y$30=3,0.4,0)))*Build!$E$32</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="Z33" s="20" t="n">
-        <x:f>IF(Z$30=1,0.3,IF(Z$30=2,0.3,IF(Z$30=3,0.4,0)))*Build!$E$31</x:f>
+        <x:f>IF(Z$30=1,0.3,IF(Z$30=2,0.3,IF(Z$30=3,0.4,0)))*Build!$E$32</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AA33" s="20" t="n">
-        <x:f>IF(AA$30=1,0.3,IF(AA$30=2,0.3,IF(AA$30=3,0.4,0)))*Build!$E$31</x:f>
+        <x:f>IF(AA$30=1,0.3,IF(AA$30=2,0.3,IF(AA$30=3,0.4,0)))*Build!$E$32</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AB33" s="20" t="n">
-        <x:f>IF(AB$30=1,0.3,IF(AB$30=2,0.3,IF(AB$30=3,0.4,0)))*Build!$E$31</x:f>
+        <x:f>IF(AB$30=1,0.3,IF(AB$30=2,0.3,IF(AB$30=3,0.4,0)))*Build!$E$32</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AC33" s="20" t="n">
-        <x:f>IF(AC$30=1,0.3,IF(AC$30=2,0.3,IF(AC$30=3,0.4,0)))*Build!$E$31</x:f>
+        <x:f>IF(AC$30=1,0.3,IF(AC$30=2,0.3,IF(AC$30=3,0.4,0)))*Build!$E$32</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AD33" s="20" t="n">
-        <x:f>IF(AD$30=1,0.3,IF(AD$30=2,0.3,IF(AD$30=3,0.4,0)))*Build!$E$31</x:f>
+        <x:f>IF(AD$30=1,0.3,IF(AD$30=2,0.3,IF(AD$30=3,0.4,0)))*Build!$E$32</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AE33" s="20" t="n">
-        <x:f>IF(AE$30=1,0.3,IF(AE$30=2,0.3,IF(AE$30=3,0.4,0)))*Build!$E$31</x:f>
+        <x:f>IF(AE$30=1,0.3,IF(AE$30=2,0.3,IF(AE$30=3,0.4,0)))*Build!$E$32</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AF33" s="20" t="n">
-        <x:f>IF(AF$30=1,0.3,IF(AF$30=2,0.3,IF(AF$30=3,0.4,0)))*Build!$E$31</x:f>
+        <x:f>IF(AF$30=1,0.3,IF(AF$30=2,0.3,IF(AF$30=3,0.4,0)))*Build!$E$32</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AG33" s="20" t="n">
-        <x:f>IF(AG$30=1,0.3,IF(AG$30=2,0.3,IF(AG$30=3,0.4,0)))*Build!$E$31</x:f>
+        <x:f>IF(AG$30=1,0.3,IF(AG$30=2,0.3,IF(AG$30=3,0.4,0)))*Build!$E$32</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AH33" s="20" t="n">
-        <x:f>IF(AH$30=1,0.3,IF(AH$30=2,0.3,IF(AH$30=3,0.4,0)))*Build!$E$31</x:f>
+        <x:f>IF(AH$30=1,0.3,IF(AH$30=2,0.3,IF(AH$30=3,0.4,0)))*Build!$E$32</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AI33" s="20" t="n">
-        <x:f>IF(AI$30=1,0.3,IF(AI$30=2,0.3,IF(AI$30=3,0.4,0)))*Build!$E$31</x:f>
+        <x:f>IF(AI$30=1,0.3,IF(AI$30=2,0.3,IF(AI$30=3,0.4,0)))*Build!$E$32</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AJ33" s="20" t="n">
-        <x:f>IF(AJ$30=1,0.3,IF(AJ$30=2,0.3,IF(AJ$30=3,0.4,0)))*Build!$E$31</x:f>
+        <x:f>IF(AJ$30=1,0.3,IF(AJ$30=2,0.3,IF(AJ$30=3,0.4,0)))*Build!$E$32</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AK33" s="20" t="n">
-        <x:f>IF(AK$30=1,0.3,IF(AK$30=2,0.3,IF(AK$30=3,0.4,0)))*Build!$E$31</x:f>
+        <x:f>IF(AK$30=1,0.3,IF(AK$30=2,0.3,IF(AK$30=3,0.4,0)))*Build!$E$32</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -6746,147 +7265,147 @@
         </x:is>
       </x:c>
       <x:c r="B34" s="20" t="n">
-        <x:f>B32*Assumptions!$B$64</x:f>
+        <x:f>B32*Assumptions!$B$82</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C34" s="20" t="n">
-        <x:f>C32*Assumptions!$B$64</x:f>
+        <x:f>C32*Assumptions!$B$82</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D34" s="20" t="n">
-        <x:f>D32*Assumptions!$B$64</x:f>
+        <x:f>D32*Assumptions!$B$82</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="E34" s="20" t="n">
-        <x:f>E32*Assumptions!$B$64</x:f>
+        <x:f>E32*Assumptions!$B$82</x:f>
         <x:v>468000</x:v>
       </x:c>
       <x:c r="F34" s="20" t="n">
-        <x:f>F32*Assumptions!$B$64</x:f>
+        <x:f>F32*Assumptions!$B$82</x:f>
         <x:v>468000</x:v>
       </x:c>
       <x:c r="G34" s="20" t="n">
-        <x:f>G32*Assumptions!$B$64</x:f>
+        <x:f>G32*Assumptions!$B$82</x:f>
         <x:v>468000</x:v>
       </x:c>
       <x:c r="H34" s="20" t="n">
-        <x:f>H32*Assumptions!$B$64</x:f>
+        <x:f>H32*Assumptions!$B$82</x:f>
         <x:v>1053000</x:v>
       </x:c>
       <x:c r="I34" s="20" t="n">
-        <x:f>I32*Assumptions!$B$64</x:f>
+        <x:f>I32*Assumptions!$B$82</x:f>
         <x:v>1053000</x:v>
       </x:c>
       <x:c r="J34" s="20" t="n">
-        <x:f>J32*Assumptions!$B$64</x:f>
+        <x:f>J32*Assumptions!$B$82</x:f>
         <x:v>1053000</x:v>
       </x:c>
       <x:c r="K34" s="20" t="n">
-        <x:f>K32*Assumptions!$B$64</x:f>
+        <x:f>K32*Assumptions!$B$82</x:f>
         <x:v>1053000</x:v>
       </x:c>
       <x:c r="L34" s="20" t="n">
-        <x:f>L32*Assumptions!$B$64</x:f>
+        <x:f>L32*Assumptions!$B$82</x:f>
         <x:v>1053000</x:v>
       </x:c>
       <x:c r="M34" s="20" t="n">
-        <x:f>M32*Assumptions!$B$64</x:f>
+        <x:f>M32*Assumptions!$B$82</x:f>
         <x:v>1053000</x:v>
       </x:c>
       <x:c r="N34" s="20" t="n">
-        <x:f>N32*Assumptions!$B$64</x:f>
+        <x:f>N32*Assumptions!$B$82</x:f>
         <x:v>1755000</x:v>
       </x:c>
       <x:c r="O34" s="20" t="n">
-        <x:f>O32*Assumptions!$B$64</x:f>
+        <x:f>O32*Assumptions!$B$82</x:f>
         <x:v>1755000</x:v>
       </x:c>
       <x:c r="P34" s="20" t="n">
-        <x:f>P32*Assumptions!$B$64</x:f>
+        <x:f>P32*Assumptions!$B$82</x:f>
         <x:v>1755000</x:v>
       </x:c>
       <x:c r="Q34" s="20" t="n">
-        <x:f>Q32*Assumptions!$B$64</x:f>
+        <x:f>Q32*Assumptions!$B$82</x:f>
         <x:v>1755000</x:v>
       </x:c>
       <x:c r="R34" s="20" t="n">
-        <x:f>R32*Assumptions!$B$64</x:f>
+        <x:f>R32*Assumptions!$B$82</x:f>
         <x:v>1755000</x:v>
       </x:c>
       <x:c r="S34" s="20" t="n">
-        <x:f>S32*Assumptions!$B$64</x:f>
+        <x:f>S32*Assumptions!$B$82</x:f>
         <x:v>1755000</x:v>
       </x:c>
       <x:c r="T34" s="20" t="n">
-        <x:f>T32*Assumptions!$B$64</x:f>
+        <x:f>T32*Assumptions!$B$82</x:f>
         <x:v>1755000</x:v>
       </x:c>
       <x:c r="U34" s="20" t="n">
-        <x:f>U32*Assumptions!$B$64</x:f>
+        <x:f>U32*Assumptions!$B$82</x:f>
         <x:v>1755000</x:v>
       </x:c>
       <x:c r="V34" s="20" t="n">
-        <x:f>V32*Assumptions!$B$64</x:f>
+        <x:f>V32*Assumptions!$B$82</x:f>
         <x:v>1755000</x:v>
       </x:c>
       <x:c r="W34" s="20" t="n">
-        <x:f>W32*Assumptions!$B$64</x:f>
+        <x:f>W32*Assumptions!$B$82</x:f>
         <x:v>1755000</x:v>
       </x:c>
       <x:c r="X34" s="20" t="n">
-        <x:f>X32*Assumptions!$B$64</x:f>
+        <x:f>X32*Assumptions!$B$82</x:f>
         <x:v>1755000</x:v>
       </x:c>
       <x:c r="Y34" s="20" t="n">
-        <x:f>Y32*Assumptions!$B$64</x:f>
+        <x:f>Y32*Assumptions!$B$82</x:f>
         <x:v>1755000</x:v>
       </x:c>
       <x:c r="Z34" s="20" t="n">
-        <x:f>Z32*Assumptions!$B$64</x:f>
+        <x:f>Z32*Assumptions!$B$82</x:f>
         <x:v>1755000</x:v>
       </x:c>
       <x:c r="AA34" s="20" t="n">
-        <x:f>AA32*Assumptions!$B$64</x:f>
+        <x:f>AA32*Assumptions!$B$82</x:f>
         <x:v>1755000</x:v>
       </x:c>
       <x:c r="AB34" s="20" t="n">
-        <x:f>AB32*Assumptions!$B$64</x:f>
+        <x:f>AB32*Assumptions!$B$82</x:f>
         <x:v>1755000</x:v>
       </x:c>
       <x:c r="AC34" s="20" t="n">
-        <x:f>AC32*Assumptions!$B$64</x:f>
+        <x:f>AC32*Assumptions!$B$82</x:f>
         <x:v>1755000</x:v>
       </x:c>
       <x:c r="AD34" s="20" t="n">
-        <x:f>AD32*Assumptions!$B$64</x:f>
+        <x:f>AD32*Assumptions!$B$82</x:f>
         <x:v>1755000</x:v>
       </x:c>
       <x:c r="AE34" s="20" t="n">
-        <x:f>AE32*Assumptions!$B$64</x:f>
+        <x:f>AE32*Assumptions!$B$82</x:f>
         <x:v>1755000</x:v>
       </x:c>
       <x:c r="AF34" s="20" t="n">
-        <x:f>AF32*Assumptions!$B$64</x:f>
+        <x:f>AF32*Assumptions!$B$82</x:f>
         <x:v>1755000</x:v>
       </x:c>
       <x:c r="AG34" s="20" t="n">
-        <x:f>AG32*Assumptions!$B$64</x:f>
+        <x:f>AG32*Assumptions!$B$82</x:f>
         <x:v>1755000</x:v>
       </x:c>
       <x:c r="AH34" s="20" t="n">
-        <x:f>AH32*Assumptions!$B$64</x:f>
+        <x:f>AH32*Assumptions!$B$82</x:f>
         <x:v>1755000</x:v>
       </x:c>
       <x:c r="AI34" s="20" t="n">
-        <x:f>AI32*Assumptions!$B$64</x:f>
+        <x:f>AI32*Assumptions!$B$82</x:f>
         <x:v>1755000</x:v>
       </x:c>
       <x:c r="AJ34" s="20" t="n">
-        <x:f>AJ32*Assumptions!$B$64</x:f>
+        <x:f>AJ32*Assumptions!$B$82</x:f>
         <x:v>1755000</x:v>
       </x:c>
       <x:c r="AK34" s="20" t="n">
-        <x:f>AK32*Assumptions!$B$64</x:f>
+        <x:f>AK32*Assumptions!$B$82</x:f>
         <x:v>1755000</x:v>
       </x:c>
     </x:row>
@@ -6897,147 +7416,147 @@
         </x:is>
       </x:c>
       <x:c r="B35" s="20" t="n">
-        <x:f>IF(B$30=Assumptions!$B$14,Assumptions!$B$67,0)+IF(B$30=Assumptions!$B$16,Assumptions!$B$68,0)</x:f>
+        <x:f>IF(B$30=Assumptions!$B$14,Assumptions!$B$85,0)+IF(B$30=Assumptions!$B$16,Assumptions!$B$86,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C35" s="20" t="n">
-        <x:f>IF(C$30=Assumptions!$B$14,Assumptions!$B$67,0)+IF(C$30=Assumptions!$B$16,Assumptions!$B$68,0)</x:f>
+        <x:f>IF(C$30=Assumptions!$B$14,Assumptions!$B$85,0)+IF(C$30=Assumptions!$B$16,Assumptions!$B$86,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D35" s="20" t="n">
-        <x:f>IF(D$30=Assumptions!$B$14,Assumptions!$B$67,0)+IF(D$30=Assumptions!$B$16,Assumptions!$B$68,0)</x:f>
+        <x:f>IF(D$30=Assumptions!$B$14,Assumptions!$B$85,0)+IF(D$30=Assumptions!$B$16,Assumptions!$B$86,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="E35" s="20" t="n">
-        <x:f>IF(E$30=Assumptions!$B$14,Assumptions!$B$67,0)+IF(E$30=Assumptions!$B$16,Assumptions!$B$68,0)</x:f>
+        <x:f>IF(E$30=Assumptions!$B$14,Assumptions!$B$85,0)+IF(E$30=Assumptions!$B$16,Assumptions!$B$86,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="F35" s="20" t="n">
-        <x:f>IF(F$30=Assumptions!$B$14,Assumptions!$B$67,0)+IF(F$30=Assumptions!$B$16,Assumptions!$B$68,0)</x:f>
+        <x:f>IF(F$30=Assumptions!$B$14,Assumptions!$B$85,0)+IF(F$30=Assumptions!$B$16,Assumptions!$B$86,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="G35" s="20" t="n">
-        <x:f>IF(G$30=Assumptions!$B$14,Assumptions!$B$67,0)+IF(G$30=Assumptions!$B$16,Assumptions!$B$68,0)</x:f>
+        <x:f>IF(G$30=Assumptions!$B$14,Assumptions!$B$85,0)+IF(G$30=Assumptions!$B$16,Assumptions!$B$86,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="H35" s="20" t="n">
-        <x:f>IF(H$30=Assumptions!$B$14,Assumptions!$B$67,0)+IF(H$30=Assumptions!$B$16,Assumptions!$B$68,0)</x:f>
+        <x:f>IF(H$30=Assumptions!$B$14,Assumptions!$B$85,0)+IF(H$30=Assumptions!$B$16,Assumptions!$B$86,0)</x:f>
         <x:v>6000000</x:v>
       </x:c>
       <x:c r="I35" s="20" t="n">
-        <x:f>IF(I$30=Assumptions!$B$14,Assumptions!$B$67,0)+IF(I$30=Assumptions!$B$16,Assumptions!$B$68,0)</x:f>
+        <x:f>IF(I$30=Assumptions!$B$14,Assumptions!$B$85,0)+IF(I$30=Assumptions!$B$16,Assumptions!$B$86,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J35" s="20" t="n">
-        <x:f>IF(J$30=Assumptions!$B$14,Assumptions!$B$67,0)+IF(J$30=Assumptions!$B$16,Assumptions!$B$68,0)</x:f>
+        <x:f>IF(J$30=Assumptions!$B$14,Assumptions!$B$85,0)+IF(J$30=Assumptions!$B$16,Assumptions!$B$86,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K35" s="20" t="n">
-        <x:f>IF(K$30=Assumptions!$B$14,Assumptions!$B$67,0)+IF(K$30=Assumptions!$B$16,Assumptions!$B$68,0)</x:f>
+        <x:f>IF(K$30=Assumptions!$B$14,Assumptions!$B$85,0)+IF(K$30=Assumptions!$B$16,Assumptions!$B$86,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="L35" s="20" t="n">
-        <x:f>IF(L$30=Assumptions!$B$14,Assumptions!$B$67,0)+IF(L$30=Assumptions!$B$16,Assumptions!$B$68,0)</x:f>
+        <x:f>IF(L$30=Assumptions!$B$14,Assumptions!$B$85,0)+IF(L$30=Assumptions!$B$16,Assumptions!$B$86,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M35" s="20" t="n">
-        <x:f>IF(M$30=Assumptions!$B$14,Assumptions!$B$67,0)+IF(M$30=Assumptions!$B$16,Assumptions!$B$68,0)</x:f>
+        <x:f>IF(M$30=Assumptions!$B$14,Assumptions!$B$85,0)+IF(M$30=Assumptions!$B$16,Assumptions!$B$86,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="N35" s="20" t="n">
-        <x:f>IF(N$30=Assumptions!$B$14,Assumptions!$B$67,0)+IF(N$30=Assumptions!$B$16,Assumptions!$B$68,0)</x:f>
+        <x:f>IF(N$30=Assumptions!$B$14,Assumptions!$B$85,0)+IF(N$30=Assumptions!$B$16,Assumptions!$B$86,0)</x:f>
         <x:v>9000000</x:v>
       </x:c>
       <x:c r="O35" s="20" t="n">
-        <x:f>IF(O$30=Assumptions!$B$14,Assumptions!$B$67,0)+IF(O$30=Assumptions!$B$16,Assumptions!$B$68,0)</x:f>
+        <x:f>IF(O$30=Assumptions!$B$14,Assumptions!$B$85,0)+IF(O$30=Assumptions!$B$16,Assumptions!$B$86,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="P35" s="20" t="n">
-        <x:f>IF(P$30=Assumptions!$B$14,Assumptions!$B$67,0)+IF(P$30=Assumptions!$B$16,Assumptions!$B$68,0)</x:f>
+        <x:f>IF(P$30=Assumptions!$B$14,Assumptions!$B$85,0)+IF(P$30=Assumptions!$B$16,Assumptions!$B$86,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q35" s="20" t="n">
-        <x:f>IF(Q$30=Assumptions!$B$14,Assumptions!$B$67,0)+IF(Q$30=Assumptions!$B$16,Assumptions!$B$68,0)</x:f>
+        <x:f>IF(Q$30=Assumptions!$B$14,Assumptions!$B$85,0)+IF(Q$30=Assumptions!$B$16,Assumptions!$B$86,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="R35" s="20" t="n">
-        <x:f>IF(R$30=Assumptions!$B$14,Assumptions!$B$67,0)+IF(R$30=Assumptions!$B$16,Assumptions!$B$68,0)</x:f>
+        <x:f>IF(R$30=Assumptions!$B$14,Assumptions!$B$85,0)+IF(R$30=Assumptions!$B$16,Assumptions!$B$86,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="S35" s="20" t="n">
-        <x:f>IF(S$30=Assumptions!$B$14,Assumptions!$B$67,0)+IF(S$30=Assumptions!$B$16,Assumptions!$B$68,0)</x:f>
+        <x:f>IF(S$30=Assumptions!$B$14,Assumptions!$B$85,0)+IF(S$30=Assumptions!$B$16,Assumptions!$B$86,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="T35" s="20" t="n">
-        <x:f>IF(T$30=Assumptions!$B$14,Assumptions!$B$67,0)+IF(T$30=Assumptions!$B$16,Assumptions!$B$68,0)</x:f>
+        <x:f>IF(T$30=Assumptions!$B$14,Assumptions!$B$85,0)+IF(T$30=Assumptions!$B$16,Assumptions!$B$86,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="U35" s="20" t="n">
-        <x:f>IF(U$30=Assumptions!$B$14,Assumptions!$B$67,0)+IF(U$30=Assumptions!$B$16,Assumptions!$B$68,0)</x:f>
+        <x:f>IF(U$30=Assumptions!$B$14,Assumptions!$B$85,0)+IF(U$30=Assumptions!$B$16,Assumptions!$B$86,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="V35" s="20" t="n">
-        <x:f>IF(V$30=Assumptions!$B$14,Assumptions!$B$67,0)+IF(V$30=Assumptions!$B$16,Assumptions!$B$68,0)</x:f>
+        <x:f>IF(V$30=Assumptions!$B$14,Assumptions!$B$85,0)+IF(V$30=Assumptions!$B$16,Assumptions!$B$86,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="W35" s="20" t="n">
-        <x:f>IF(W$30=Assumptions!$B$14,Assumptions!$B$67,0)+IF(W$30=Assumptions!$B$16,Assumptions!$B$68,0)</x:f>
+        <x:f>IF(W$30=Assumptions!$B$14,Assumptions!$B$85,0)+IF(W$30=Assumptions!$B$16,Assumptions!$B$86,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="X35" s="20" t="n">
-        <x:f>IF(X$30=Assumptions!$B$14,Assumptions!$B$67,0)+IF(X$30=Assumptions!$B$16,Assumptions!$B$68,0)</x:f>
+        <x:f>IF(X$30=Assumptions!$B$14,Assumptions!$B$85,0)+IF(X$30=Assumptions!$B$16,Assumptions!$B$86,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="Y35" s="20" t="n">
-        <x:f>IF(Y$30=Assumptions!$B$14,Assumptions!$B$67,0)+IF(Y$30=Assumptions!$B$16,Assumptions!$B$68,0)</x:f>
+        <x:f>IF(Y$30=Assumptions!$B$14,Assumptions!$B$85,0)+IF(Y$30=Assumptions!$B$16,Assumptions!$B$86,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="Z35" s="20" t="n">
-        <x:f>IF(Z$30=Assumptions!$B$14,Assumptions!$B$67,0)+IF(Z$30=Assumptions!$B$16,Assumptions!$B$68,0)</x:f>
+        <x:f>IF(Z$30=Assumptions!$B$14,Assumptions!$B$85,0)+IF(Z$30=Assumptions!$B$16,Assumptions!$B$86,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AA35" s="20" t="n">
-        <x:f>IF(AA$30=Assumptions!$B$14,Assumptions!$B$67,0)+IF(AA$30=Assumptions!$B$16,Assumptions!$B$68,0)</x:f>
+        <x:f>IF(AA$30=Assumptions!$B$14,Assumptions!$B$85,0)+IF(AA$30=Assumptions!$B$16,Assumptions!$B$86,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AB35" s="20" t="n">
-        <x:f>IF(AB$30=Assumptions!$B$14,Assumptions!$B$67,0)+IF(AB$30=Assumptions!$B$16,Assumptions!$B$68,0)</x:f>
+        <x:f>IF(AB$30=Assumptions!$B$14,Assumptions!$B$85,0)+IF(AB$30=Assumptions!$B$16,Assumptions!$B$86,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AC35" s="20" t="n">
-        <x:f>IF(AC$30=Assumptions!$B$14,Assumptions!$B$67,0)+IF(AC$30=Assumptions!$B$16,Assumptions!$B$68,0)</x:f>
+        <x:f>IF(AC$30=Assumptions!$B$14,Assumptions!$B$85,0)+IF(AC$30=Assumptions!$B$16,Assumptions!$B$86,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AD35" s="20" t="n">
-        <x:f>IF(AD$30=Assumptions!$B$14,Assumptions!$B$67,0)+IF(AD$30=Assumptions!$B$16,Assumptions!$B$68,0)</x:f>
+        <x:f>IF(AD$30=Assumptions!$B$14,Assumptions!$B$85,0)+IF(AD$30=Assumptions!$B$16,Assumptions!$B$86,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AE35" s="20" t="n">
-        <x:f>IF(AE$30=Assumptions!$B$14,Assumptions!$B$67,0)+IF(AE$30=Assumptions!$B$16,Assumptions!$B$68,0)</x:f>
+        <x:f>IF(AE$30=Assumptions!$B$14,Assumptions!$B$85,0)+IF(AE$30=Assumptions!$B$16,Assumptions!$B$86,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AF35" s="20" t="n">
-        <x:f>IF(AF$30=Assumptions!$B$14,Assumptions!$B$67,0)+IF(AF$30=Assumptions!$B$16,Assumptions!$B$68,0)</x:f>
+        <x:f>IF(AF$30=Assumptions!$B$14,Assumptions!$B$85,0)+IF(AF$30=Assumptions!$B$16,Assumptions!$B$86,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AG35" s="20" t="n">
-        <x:f>IF(AG$30=Assumptions!$B$14,Assumptions!$B$67,0)+IF(AG$30=Assumptions!$B$16,Assumptions!$B$68,0)</x:f>
+        <x:f>IF(AG$30=Assumptions!$B$14,Assumptions!$B$85,0)+IF(AG$30=Assumptions!$B$16,Assumptions!$B$86,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AH35" s="20" t="n">
-        <x:f>IF(AH$30=Assumptions!$B$14,Assumptions!$B$67,0)+IF(AH$30=Assumptions!$B$16,Assumptions!$B$68,0)</x:f>
+        <x:f>IF(AH$30=Assumptions!$B$14,Assumptions!$B$85,0)+IF(AH$30=Assumptions!$B$16,Assumptions!$B$86,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AI35" s="20" t="n">
-        <x:f>IF(AI$30=Assumptions!$B$14,Assumptions!$B$67,0)+IF(AI$30=Assumptions!$B$16,Assumptions!$B$68,0)</x:f>
+        <x:f>IF(AI$30=Assumptions!$B$14,Assumptions!$B$85,0)+IF(AI$30=Assumptions!$B$16,Assumptions!$B$86,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AJ35" s="20" t="n">
-        <x:f>IF(AJ$30=Assumptions!$B$14,Assumptions!$B$67,0)+IF(AJ$30=Assumptions!$B$16,Assumptions!$B$68,0)</x:f>
+        <x:f>IF(AJ$30=Assumptions!$B$14,Assumptions!$B$85,0)+IF(AJ$30=Assumptions!$B$16,Assumptions!$B$86,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AK35" s="20" t="n">
-        <x:f>IF(AK$30=Assumptions!$B$14,Assumptions!$B$67,0)+IF(AK$30=Assumptions!$B$16,Assumptions!$B$68,0)</x:f>
+        <x:f>IF(AK$30=Assumptions!$B$14,Assumptions!$B$85,0)+IF(AK$30=Assumptions!$B$16,Assumptions!$B$86,0)</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -7199,147 +7718,147 @@
         </x:is>
       </x:c>
       <x:c r="B37" s="20" t="n">
-        <x:f>IF(B$30&lt;=3,Build!$D$28/3,0)</x:f>
-        <x:v>2849285.7142857146</x:v>
+        <x:f>IF(B$30&lt;=3,Build!$D$29/3,0)</x:f>
+        <x:v>2954902.6342857145</x:v>
       </x:c>
       <x:c r="C37" s="20" t="n">
-        <x:f>IF(C$30&lt;=3,Build!$D$28/3,0)</x:f>
-        <x:v>2849285.7142857146</x:v>
+        <x:f>IF(C$30&lt;=3,Build!$D$29/3,0)</x:f>
+        <x:v>2954902.6342857145</x:v>
       </x:c>
       <x:c r="D37" s="20" t="n">
-        <x:f>IF(D$30&lt;=3,Build!$D$28/3,0)</x:f>
-        <x:v>2849285.7142857146</x:v>
+        <x:f>IF(D$30&lt;=3,Build!$D$29/3,0)</x:f>
+        <x:v>2954902.6342857145</x:v>
       </x:c>
       <x:c r="E37" s="20" t="n">
-        <x:f>IF(E$30&lt;=3,Build!$D$28/3,0)</x:f>
+        <x:f>IF(E$30&lt;=3,Build!$D$29/3,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="F37" s="20" t="n">
-        <x:f>IF(F$30&lt;=3,Build!$D$28/3,0)</x:f>
+        <x:f>IF(F$30&lt;=3,Build!$D$29/3,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="G37" s="20" t="n">
-        <x:f>IF(G$30&lt;=3,Build!$D$28/3,0)</x:f>
+        <x:f>IF(G$30&lt;=3,Build!$D$29/3,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="H37" s="20" t="n">
-        <x:f>IF(H$30&lt;=3,Build!$D$28/3,0)</x:f>
+        <x:f>IF(H$30&lt;=3,Build!$D$29/3,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="I37" s="20" t="n">
-        <x:f>IF(I$30&lt;=3,Build!$D$28/3,0)</x:f>
+        <x:f>IF(I$30&lt;=3,Build!$D$29/3,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J37" s="20" t="n">
-        <x:f>IF(J$30&lt;=3,Build!$D$28/3,0)</x:f>
+        <x:f>IF(J$30&lt;=3,Build!$D$29/3,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K37" s="20" t="n">
-        <x:f>IF(K$30&lt;=3,Build!$D$28/3,0)</x:f>
+        <x:f>IF(K$30&lt;=3,Build!$D$29/3,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="L37" s="20" t="n">
-        <x:f>IF(L$30&lt;=3,Build!$D$28/3,0)</x:f>
+        <x:f>IF(L$30&lt;=3,Build!$D$29/3,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M37" s="20" t="n">
-        <x:f>IF(M$30&lt;=3,Build!$D$28/3,0)</x:f>
+        <x:f>IF(M$30&lt;=3,Build!$D$29/3,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="N37" s="20" t="n">
-        <x:f>IF(N$30&lt;=3,Build!$D$28/3,0)</x:f>
+        <x:f>IF(N$30&lt;=3,Build!$D$29/3,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="O37" s="20" t="n">
-        <x:f>IF(O$30&lt;=3,Build!$D$28/3,0)</x:f>
+        <x:f>IF(O$30&lt;=3,Build!$D$29/3,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="P37" s="20" t="n">
-        <x:f>IF(P$30&lt;=3,Build!$D$28/3,0)</x:f>
+        <x:f>IF(P$30&lt;=3,Build!$D$29/3,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q37" s="20" t="n">
-        <x:f>IF(Q$30&lt;=3,Build!$D$28/3,0)</x:f>
+        <x:f>IF(Q$30&lt;=3,Build!$D$29/3,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="R37" s="20" t="n">
-        <x:f>IF(R$30&lt;=3,Build!$D$28/3,0)</x:f>
+        <x:f>IF(R$30&lt;=3,Build!$D$29/3,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="S37" s="20" t="n">
-        <x:f>IF(S$30&lt;=3,Build!$D$28/3,0)</x:f>
+        <x:f>IF(S$30&lt;=3,Build!$D$29/3,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="T37" s="20" t="n">
-        <x:f>IF(T$30&lt;=3,Build!$D$28/3,0)</x:f>
+        <x:f>IF(T$30&lt;=3,Build!$D$29/3,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="U37" s="20" t="n">
-        <x:f>IF(U$30&lt;=3,Build!$D$28/3,0)</x:f>
+        <x:f>IF(U$30&lt;=3,Build!$D$29/3,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="V37" s="20" t="n">
-        <x:f>IF(V$30&lt;=3,Build!$D$28/3,0)</x:f>
+        <x:f>IF(V$30&lt;=3,Build!$D$29/3,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="W37" s="20" t="n">
-        <x:f>IF(W$30&lt;=3,Build!$D$28/3,0)</x:f>
+        <x:f>IF(W$30&lt;=3,Build!$D$29/3,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="X37" s="20" t="n">
-        <x:f>IF(X$30&lt;=3,Build!$D$28/3,0)</x:f>
+        <x:f>IF(X$30&lt;=3,Build!$D$29/3,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="Y37" s="20" t="n">
-        <x:f>IF(Y$30&lt;=3,Build!$D$28/3,0)</x:f>
+        <x:f>IF(Y$30&lt;=3,Build!$D$29/3,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="Z37" s="20" t="n">
-        <x:f>IF(Z$30&lt;=3,Build!$D$28/3,0)</x:f>
+        <x:f>IF(Z$30&lt;=3,Build!$D$29/3,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AA37" s="20" t="n">
-        <x:f>IF(AA$30&lt;=3,Build!$D$28/3,0)</x:f>
+        <x:f>IF(AA$30&lt;=3,Build!$D$29/3,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AB37" s="20" t="n">
-        <x:f>IF(AB$30&lt;=3,Build!$D$28/3,0)</x:f>
+        <x:f>IF(AB$30&lt;=3,Build!$D$29/3,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AC37" s="20" t="n">
-        <x:f>IF(AC$30&lt;=3,Build!$D$28/3,0)</x:f>
+        <x:f>IF(AC$30&lt;=3,Build!$D$29/3,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AD37" s="20" t="n">
-        <x:f>IF(AD$30&lt;=3,Build!$D$28/3,0)</x:f>
+        <x:f>IF(AD$30&lt;=3,Build!$D$29/3,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AE37" s="20" t="n">
-        <x:f>IF(AE$30&lt;=3,Build!$D$28/3,0)</x:f>
+        <x:f>IF(AE$30&lt;=3,Build!$D$29/3,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AF37" s="20" t="n">
-        <x:f>IF(AF$30&lt;=3,Build!$D$28/3,0)</x:f>
+        <x:f>IF(AF$30&lt;=3,Build!$D$29/3,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AG37" s="20" t="n">
-        <x:f>IF(AG$30&lt;=3,Build!$D$28/3,0)</x:f>
+        <x:f>IF(AG$30&lt;=3,Build!$D$29/3,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AH37" s="20" t="n">
-        <x:f>IF(AH$30&lt;=3,Build!$D$28/3,0)</x:f>
+        <x:f>IF(AH$30&lt;=3,Build!$D$29/3,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AI37" s="20" t="n">
-        <x:f>IF(AI$30&lt;=3,Build!$D$28/3,0)</x:f>
+        <x:f>IF(AI$30&lt;=3,Build!$D$29/3,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AJ37" s="20" t="n">
-        <x:f>IF(AJ$30&lt;=3,Build!$D$28/3,0)</x:f>
+        <x:f>IF(AJ$30&lt;=3,Build!$D$29/3,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AK37" s="20" t="n">
-        <x:f>IF(AK$30&lt;=3,Build!$D$28/3,0)</x:f>
+        <x:f>IF(AK$30&lt;=3,Build!$D$29/3,0)</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -7350,148 +7869,148 @@
         </x:is>
       </x:c>
       <x:c r="B38" s="33" t="n">
-        <x:f>Run!B21</x:f>
+        <x:f>Run!B22</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C38" s="33" t="n">
-        <x:f>Run!C21</x:f>
+        <x:f>Run!C22</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D38" s="33" t="n">
-        <x:f>Run!D21</x:f>
+        <x:f>Run!D22</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="E38" s="33" t="n">
-        <x:f>Run!E21</x:f>
-        <x:v>877676.386112</x:v>
+        <x:f>Run!E22</x:f>
+        <x:v>910298.026112</x:v>
       </x:c>
       <x:c r="F38" s="33" t="n">
-        <x:f>Run!F21</x:f>
-        <x:v>877676.386112</x:v>
+        <x:f>Run!F22</x:f>
+        <x:v>910298.026112</x:v>
       </x:c>
       <x:c r="G38" s="33" t="n">
-        <x:f>Run!G21</x:f>
-        <x:v>877676.386112</x:v>
+        <x:f>Run!G22</x:f>
+        <x:v>910298.026112</x:v>
       </x:c>
       <x:c r="H38" s="33" t="n">
-        <x:f>Run!H21</x:f>
-        <x:v>1039184.368752</x:v>
+        <x:f>Run!H22</x:f>
+        <x:v>1075474.948752</x:v>
       </x:c>
       <x:c r="I38" s="33" t="n">
-        <x:f>Run!I21</x:f>
-        <x:v>1039184.368752</x:v>
+        <x:f>Run!I22</x:f>
+        <x:v>1075474.948752</x:v>
       </x:c>
       <x:c r="J38" s="33" t="n">
-        <x:f>Run!J21</x:f>
-        <x:v>1039184.368752</x:v>
+        <x:f>Run!J22</x:f>
+        <x:v>1075474.948752</x:v>
       </x:c>
       <x:c r="K38" s="33" t="n">
-        <x:f>Run!K21</x:f>
-        <x:v>1039184.368752</x:v>
+        <x:f>Run!K22</x:f>
+        <x:v>1075474.948752</x:v>
       </x:c>
       <x:c r="L38" s="33" t="n">
-        <x:f>Run!L21</x:f>
-        <x:v>1039184.368752</x:v>
+        <x:f>Run!L22</x:f>
+        <x:v>1075474.948752</x:v>
       </x:c>
       <x:c r="M38" s="33" t="n">
-        <x:f>Run!M21</x:f>
-        <x:v>1039184.368752</x:v>
+        <x:f>Run!M22</x:f>
+        <x:v>1075474.948752</x:v>
       </x:c>
       <x:c r="N38" s="33" t="n">
-        <x:f>Run!N21</x:f>
-        <x:v>1174433.94792</x:v>
+        <x:f>Run!N22</x:f>
+        <x:v>1214393.46792</x:v>
       </x:c>
       <x:c r="O38" s="33" t="n">
-        <x:f>Run!O21</x:f>
-        <x:v>1174433.94792</x:v>
+        <x:f>Run!O22</x:f>
+        <x:v>1214393.46792</x:v>
       </x:c>
       <x:c r="P38" s="33" t="n">
-        <x:f>Run!P21</x:f>
-        <x:v>1174433.94792</x:v>
+        <x:f>Run!P22</x:f>
+        <x:v>1214393.46792</x:v>
       </x:c>
       <x:c r="Q38" s="33" t="n">
-        <x:f>Run!Q21</x:f>
-        <x:v>1174433.94792</x:v>
+        <x:f>Run!Q22</x:f>
+        <x:v>1214393.46792</x:v>
       </x:c>
       <x:c r="R38" s="33" t="n">
-        <x:f>Run!R21</x:f>
-        <x:v>1174433.94792</x:v>
+        <x:f>Run!R22</x:f>
+        <x:v>1214393.46792</x:v>
       </x:c>
       <x:c r="S38" s="33" t="n">
-        <x:f>Run!S21</x:f>
-        <x:v>1174433.94792</x:v>
+        <x:f>Run!S22</x:f>
+        <x:v>1214393.46792</x:v>
       </x:c>
       <x:c r="T38" s="33" t="n">
-        <x:f>Run!T21</x:f>
-        <x:v>1174433.94792</x:v>
+        <x:f>Run!T22</x:f>
+        <x:v>1214393.46792</x:v>
       </x:c>
       <x:c r="U38" s="33" t="n">
-        <x:f>Run!U21</x:f>
-        <x:v>1174433.94792</x:v>
+        <x:f>Run!U22</x:f>
+        <x:v>1214393.46792</x:v>
       </x:c>
       <x:c r="V38" s="33" t="n">
-        <x:f>Run!V21</x:f>
-        <x:v>1174433.94792</x:v>
+        <x:f>Run!V22</x:f>
+        <x:v>1214393.46792</x:v>
       </x:c>
       <x:c r="W38" s="33" t="n">
-        <x:f>Run!W21</x:f>
-        <x:v>1174433.94792</x:v>
+        <x:f>Run!W22</x:f>
+        <x:v>1214393.46792</x:v>
       </x:c>
       <x:c r="X38" s="33" t="n">
-        <x:f>Run!X21</x:f>
-        <x:v>1174433.94792</x:v>
+        <x:f>Run!X22</x:f>
+        <x:v>1214393.46792</x:v>
       </x:c>
       <x:c r="Y38" s="33" t="n">
-        <x:f>Run!Y21</x:f>
-        <x:v>1174433.94792</x:v>
+        <x:f>Run!Y22</x:f>
+        <x:v>1214393.46792</x:v>
       </x:c>
       <x:c r="Z38" s="33" t="n">
-        <x:f>Run!Z21</x:f>
-        <x:v>1174433.94792</x:v>
+        <x:f>Run!Z22</x:f>
+        <x:v>1214393.46792</x:v>
       </x:c>
       <x:c r="AA38" s="33" t="n">
-        <x:f>Run!AA21</x:f>
-        <x:v>1174433.94792</x:v>
+        <x:f>Run!AA22</x:f>
+        <x:v>1214393.46792</x:v>
       </x:c>
       <x:c r="AB38" s="33" t="n">
-        <x:f>Run!AB21</x:f>
-        <x:v>1174433.94792</x:v>
+        <x:f>Run!AB22</x:f>
+        <x:v>1214393.46792</x:v>
       </x:c>
       <x:c r="AC38" s="33" t="n">
-        <x:f>Run!AC21</x:f>
-        <x:v>1174433.94792</x:v>
+        <x:f>Run!AC22</x:f>
+        <x:v>1214393.46792</x:v>
       </x:c>
       <x:c r="AD38" s="33" t="n">
-        <x:f>Run!AD21</x:f>
-        <x:v>1174433.94792</x:v>
+        <x:f>Run!AD22</x:f>
+        <x:v>1214393.46792</x:v>
       </x:c>
       <x:c r="AE38" s="33" t="n">
-        <x:f>Run!AE21</x:f>
-        <x:v>1174433.94792</x:v>
+        <x:f>Run!AE22</x:f>
+        <x:v>1214393.46792</x:v>
       </x:c>
       <x:c r="AF38" s="33" t="n">
-        <x:f>Run!AF21</x:f>
-        <x:v>1174433.94792</x:v>
+        <x:f>Run!AF22</x:f>
+        <x:v>1214393.46792</x:v>
       </x:c>
       <x:c r="AG38" s="33" t="n">
-        <x:f>Run!AG21</x:f>
-        <x:v>1174433.94792</x:v>
+        <x:f>Run!AG22</x:f>
+        <x:v>1214393.46792</x:v>
       </x:c>
       <x:c r="AH38" s="33" t="n">
-        <x:f>Run!AH21</x:f>
-        <x:v>1174433.94792</x:v>
+        <x:f>Run!AH22</x:f>
+        <x:v>1214393.46792</x:v>
       </x:c>
       <x:c r="AI38" s="33" t="n">
-        <x:f>Run!AI21</x:f>
-        <x:v>1174433.94792</x:v>
+        <x:f>Run!AI22</x:f>
+        <x:v>1214393.46792</x:v>
       </x:c>
       <x:c r="AJ38" s="33" t="n">
-        <x:f>Run!AJ21</x:f>
-        <x:v>1174433.94792</x:v>
+        <x:f>Run!AJ22</x:f>
+        <x:v>1214393.46792</x:v>
       </x:c>
       <x:c r="AK38" s="33" t="n">
-        <x:f>Run!AK21</x:f>
-        <x:v>1174433.94792</x:v>
+        <x:f>Run!AK22</x:f>
+        <x:v>1214393.46792</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
@@ -7501,147 +8020,147 @@
         </x:is>
       </x:c>
       <x:c r="B39" s="20" t="n">
-        <x:f>B35*Assumptions!$B$69</x:f>
+        <x:f>B35*Assumptions!$B$87</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C39" s="20" t="n">
-        <x:f>C35*Assumptions!$B$69</x:f>
+        <x:f>C35*Assumptions!$B$87</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D39" s="20" t="n">
-        <x:f>D35*Assumptions!$B$69</x:f>
+        <x:f>D35*Assumptions!$B$87</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="E39" s="20" t="n">
-        <x:f>E35*Assumptions!$B$69</x:f>
+        <x:f>E35*Assumptions!$B$87</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="F39" s="20" t="n">
-        <x:f>F35*Assumptions!$B$69</x:f>
+        <x:f>F35*Assumptions!$B$87</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="G39" s="20" t="n">
-        <x:f>G35*Assumptions!$B$69</x:f>
+        <x:f>G35*Assumptions!$B$87</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="H39" s="20" t="n">
-        <x:f>H35*Assumptions!$B$69</x:f>
+        <x:f>H35*Assumptions!$B$87</x:f>
         <x:v>3000000</x:v>
       </x:c>
       <x:c r="I39" s="20" t="n">
-        <x:f>I35*Assumptions!$B$69</x:f>
+        <x:f>I35*Assumptions!$B$87</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J39" s="20" t="n">
-        <x:f>J35*Assumptions!$B$69</x:f>
+        <x:f>J35*Assumptions!$B$87</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K39" s="20" t="n">
-        <x:f>K35*Assumptions!$B$69</x:f>
+        <x:f>K35*Assumptions!$B$87</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="L39" s="20" t="n">
-        <x:f>L35*Assumptions!$B$69</x:f>
+        <x:f>L35*Assumptions!$B$87</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M39" s="20" t="n">
-        <x:f>M35*Assumptions!$B$69</x:f>
+        <x:f>M35*Assumptions!$B$87</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="N39" s="20" t="n">
-        <x:f>N35*Assumptions!$B$69</x:f>
+        <x:f>N35*Assumptions!$B$87</x:f>
         <x:v>4500000</x:v>
       </x:c>
       <x:c r="O39" s="20" t="n">
-        <x:f>O35*Assumptions!$B$69</x:f>
+        <x:f>O35*Assumptions!$B$87</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="P39" s="20" t="n">
-        <x:f>P35*Assumptions!$B$69</x:f>
+        <x:f>P35*Assumptions!$B$87</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q39" s="20" t="n">
-        <x:f>Q35*Assumptions!$B$69</x:f>
+        <x:f>Q35*Assumptions!$B$87</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="R39" s="20" t="n">
-        <x:f>R35*Assumptions!$B$69</x:f>
+        <x:f>R35*Assumptions!$B$87</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="S39" s="20" t="n">
-        <x:f>S35*Assumptions!$B$69</x:f>
+        <x:f>S35*Assumptions!$B$87</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="T39" s="20" t="n">
-        <x:f>T35*Assumptions!$B$69</x:f>
+        <x:f>T35*Assumptions!$B$87</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="U39" s="20" t="n">
-        <x:f>U35*Assumptions!$B$69</x:f>
+        <x:f>U35*Assumptions!$B$87</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="V39" s="20" t="n">
-        <x:f>V35*Assumptions!$B$69</x:f>
+        <x:f>V35*Assumptions!$B$87</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="W39" s="20" t="n">
-        <x:f>W35*Assumptions!$B$69</x:f>
+        <x:f>W35*Assumptions!$B$87</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="X39" s="20" t="n">
-        <x:f>X35*Assumptions!$B$69</x:f>
+        <x:f>X35*Assumptions!$B$87</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="Y39" s="20" t="n">
-        <x:f>Y35*Assumptions!$B$69</x:f>
+        <x:f>Y35*Assumptions!$B$87</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="Z39" s="20" t="n">
-        <x:f>Z35*Assumptions!$B$69</x:f>
+        <x:f>Z35*Assumptions!$B$87</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AA39" s="20" t="n">
-        <x:f>AA35*Assumptions!$B$69</x:f>
+        <x:f>AA35*Assumptions!$B$87</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AB39" s="20" t="n">
-        <x:f>AB35*Assumptions!$B$69</x:f>
+        <x:f>AB35*Assumptions!$B$87</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AC39" s="20" t="n">
-        <x:f>AC35*Assumptions!$B$69</x:f>
+        <x:f>AC35*Assumptions!$B$87</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AD39" s="20" t="n">
-        <x:f>AD35*Assumptions!$B$69</x:f>
+        <x:f>AD35*Assumptions!$B$87</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AE39" s="20" t="n">
-        <x:f>AE35*Assumptions!$B$69</x:f>
+        <x:f>AE35*Assumptions!$B$87</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AF39" s="20" t="n">
-        <x:f>AF35*Assumptions!$B$69</x:f>
+        <x:f>AF35*Assumptions!$B$87</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AG39" s="20" t="n">
-        <x:f>AG35*Assumptions!$B$69</x:f>
+        <x:f>AG35*Assumptions!$B$87</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AH39" s="20" t="n">
-        <x:f>AH35*Assumptions!$B$69</x:f>
+        <x:f>AH35*Assumptions!$B$87</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AI39" s="20" t="n">
-        <x:f>AI35*Assumptions!$B$69</x:f>
+        <x:f>AI35*Assumptions!$B$87</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AJ39" s="20" t="n">
-        <x:f>AJ35*Assumptions!$B$69</x:f>
+        <x:f>AJ35*Assumptions!$B$87</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AK39" s="20" t="n">
-        <x:f>AK35*Assumptions!$B$69</x:f>
+        <x:f>AK35*Assumptions!$B$87</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -7653,147 +8172,147 @@
       </x:c>
       <x:c r="B40" s="20" t="n">
         <x:f>SUM(B37:B39)</x:f>
-        <x:v>2849285.7142857146</x:v>
+        <x:v>2954902.6342857145</x:v>
       </x:c>
       <x:c r="C40" s="20" t="n">
         <x:f>SUM(C37:C39)</x:f>
-        <x:v>2849285.7142857146</x:v>
+        <x:v>2954902.6342857145</x:v>
       </x:c>
       <x:c r="D40" s="20" t="n">
         <x:f>SUM(D37:D39)</x:f>
-        <x:v>2849285.7142857146</x:v>
+        <x:v>2954902.6342857145</x:v>
       </x:c>
       <x:c r="E40" s="20" t="n">
         <x:f>SUM(E37:E39)</x:f>
-        <x:v>877676.386112</x:v>
+        <x:v>910298.026112</x:v>
       </x:c>
       <x:c r="F40" s="20" t="n">
         <x:f>SUM(F37:F39)</x:f>
-        <x:v>877676.386112</x:v>
+        <x:v>910298.026112</x:v>
       </x:c>
       <x:c r="G40" s="20" t="n">
         <x:f>SUM(G37:G39)</x:f>
-        <x:v>877676.386112</x:v>
+        <x:v>910298.026112</x:v>
       </x:c>
       <x:c r="H40" s="20" t="n">
         <x:f>SUM(H37:H39)</x:f>
-        <x:v>4039184.368752</x:v>
+        <x:v>4075474.948752</x:v>
       </x:c>
       <x:c r="I40" s="20" t="n">
         <x:f>SUM(I37:I39)</x:f>
-        <x:v>1039184.368752</x:v>
+        <x:v>1075474.948752</x:v>
       </x:c>
       <x:c r="J40" s="20" t="n">
         <x:f>SUM(J37:J39)</x:f>
-        <x:v>1039184.368752</x:v>
+        <x:v>1075474.948752</x:v>
       </x:c>
       <x:c r="K40" s="20" t="n">
         <x:f>SUM(K37:K39)</x:f>
-        <x:v>1039184.368752</x:v>
+        <x:v>1075474.948752</x:v>
       </x:c>
       <x:c r="L40" s="20" t="n">
         <x:f>SUM(L37:L39)</x:f>
-        <x:v>1039184.368752</x:v>
+        <x:v>1075474.948752</x:v>
       </x:c>
       <x:c r="M40" s="20" t="n">
         <x:f>SUM(M37:M39)</x:f>
-        <x:v>1039184.368752</x:v>
+        <x:v>1075474.948752</x:v>
       </x:c>
       <x:c r="N40" s="20" t="n">
         <x:f>SUM(N37:N39)</x:f>
-        <x:v>5674433.94792</x:v>
+        <x:v>5714393.46792</x:v>
       </x:c>
       <x:c r="O40" s="20" t="n">
         <x:f>SUM(O37:O39)</x:f>
-        <x:v>1174433.94792</x:v>
+        <x:v>1214393.46792</x:v>
       </x:c>
       <x:c r="P40" s="20" t="n">
         <x:f>SUM(P37:P39)</x:f>
-        <x:v>1174433.94792</x:v>
+        <x:v>1214393.46792</x:v>
       </x:c>
       <x:c r="Q40" s="20" t="n">
         <x:f>SUM(Q37:Q39)</x:f>
-        <x:v>1174433.94792</x:v>
+        <x:v>1214393.46792</x:v>
       </x:c>
       <x:c r="R40" s="20" t="n">
         <x:f>SUM(R37:R39)</x:f>
-        <x:v>1174433.94792</x:v>
+        <x:v>1214393.46792</x:v>
       </x:c>
       <x:c r="S40" s="20" t="n">
         <x:f>SUM(S37:S39)</x:f>
-        <x:v>1174433.94792</x:v>
+        <x:v>1214393.46792</x:v>
       </x:c>
       <x:c r="T40" s="20" t="n">
         <x:f>SUM(T37:T39)</x:f>
-        <x:v>1174433.94792</x:v>
+        <x:v>1214393.46792</x:v>
       </x:c>
       <x:c r="U40" s="20" t="n">
         <x:f>SUM(U37:U39)</x:f>
-        <x:v>1174433.94792</x:v>
+        <x:v>1214393.46792</x:v>
       </x:c>
       <x:c r="V40" s="20" t="n">
         <x:f>SUM(V37:V39)</x:f>
-        <x:v>1174433.94792</x:v>
+        <x:v>1214393.46792</x:v>
       </x:c>
       <x:c r="W40" s="20" t="n">
         <x:f>SUM(W37:W39)</x:f>
-        <x:v>1174433.94792</x:v>
+        <x:v>1214393.46792</x:v>
       </x:c>
       <x:c r="X40" s="20" t="n">
         <x:f>SUM(X37:X39)</x:f>
-        <x:v>1174433.94792</x:v>
+        <x:v>1214393.46792</x:v>
       </x:c>
       <x:c r="Y40" s="20" t="n">
         <x:f>SUM(Y37:Y39)</x:f>
-        <x:v>1174433.94792</x:v>
+        <x:v>1214393.46792</x:v>
       </x:c>
       <x:c r="Z40" s="20" t="n">
         <x:f>SUM(Z37:Z39)</x:f>
-        <x:v>1174433.94792</x:v>
+        <x:v>1214393.46792</x:v>
       </x:c>
       <x:c r="AA40" s="20" t="n">
         <x:f>SUM(AA37:AA39)</x:f>
-        <x:v>1174433.94792</x:v>
+        <x:v>1214393.46792</x:v>
       </x:c>
       <x:c r="AB40" s="20" t="n">
         <x:f>SUM(AB37:AB39)</x:f>
-        <x:v>1174433.94792</x:v>
+        <x:v>1214393.46792</x:v>
       </x:c>
       <x:c r="AC40" s="20" t="n">
         <x:f>SUM(AC37:AC39)</x:f>
-        <x:v>1174433.94792</x:v>
+        <x:v>1214393.46792</x:v>
       </x:c>
       <x:c r="AD40" s="20" t="n">
         <x:f>SUM(AD37:AD39)</x:f>
-        <x:v>1174433.94792</x:v>
+        <x:v>1214393.46792</x:v>
       </x:c>
       <x:c r="AE40" s="20" t="n">
         <x:f>SUM(AE37:AE39)</x:f>
-        <x:v>1174433.94792</x:v>
+        <x:v>1214393.46792</x:v>
       </x:c>
       <x:c r="AF40" s="20" t="n">
         <x:f>SUM(AF37:AF39)</x:f>
-        <x:v>1174433.94792</x:v>
+        <x:v>1214393.46792</x:v>
       </x:c>
       <x:c r="AG40" s="20" t="n">
         <x:f>SUM(AG37:AG39)</x:f>
-        <x:v>1174433.94792</x:v>
+        <x:v>1214393.46792</x:v>
       </x:c>
       <x:c r="AH40" s="20" t="n">
         <x:f>SUM(AH37:AH39)</x:f>
-        <x:v>1174433.94792</x:v>
+        <x:v>1214393.46792</x:v>
       </x:c>
       <x:c r="AI40" s="20" t="n">
         <x:f>SUM(AI37:AI39)</x:f>
-        <x:v>1174433.94792</x:v>
+        <x:v>1214393.46792</x:v>
       </x:c>
       <x:c r="AJ40" s="20" t="n">
         <x:f>SUM(AJ37:AJ39)</x:f>
-        <x:v>1174433.94792</x:v>
+        <x:v>1214393.46792</x:v>
       </x:c>
       <x:c r="AK40" s="20" t="n">
         <x:f>SUM(AK37:AK39)</x:f>
-        <x:v>1174433.94792</x:v>
+        <x:v>1214393.46792</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
@@ -7804,147 +8323,147 @@
       </x:c>
       <x:c r="B41" s="22" t="n">
         <x:f>B36-B40</x:f>
-        <x:v>2400714.2857142854</x:v>
+        <x:v>2295097.3657142855</x:v>
       </x:c>
       <x:c r="C41" s="22" t="n">
         <x:f>C36-C40</x:f>
-        <x:v>2400714.2857142854</x:v>
+        <x:v>2295097.3657142855</x:v>
       </x:c>
       <x:c r="D41" s="22" t="n">
         <x:f>D36-D40</x:f>
-        <x:v>4150714.2857142854</x:v>
+        <x:v>4045097.3657142855</x:v>
       </x:c>
       <x:c r="E41" s="22" t="n">
         <x:f>E36-E40</x:f>
-        <x:v>-409676.386112</x:v>
+        <x:v>-442298.026112</x:v>
       </x:c>
       <x:c r="F41" s="22" t="n">
         <x:f>F36-F40</x:f>
-        <x:v>-409676.386112</x:v>
+        <x:v>-442298.026112</x:v>
       </x:c>
       <x:c r="G41" s="22" t="n">
         <x:f>G36-G40</x:f>
-        <x:v>-409676.386112</x:v>
+        <x:v>-442298.026112</x:v>
       </x:c>
       <x:c r="H41" s="22" t="n">
         <x:f>H36-H40</x:f>
-        <x:v>3013815.631248</x:v>
+        <x:v>2977525.051248</x:v>
       </x:c>
       <x:c r="I41" s="22" t="n">
         <x:f>I36-I40</x:f>
-        <x:v>13815.631247999961</x:v>
+        <x:v>-22474.948751999997</x:v>
       </x:c>
       <x:c r="J41" s="22" t="n">
         <x:f>J36-J40</x:f>
-        <x:v>13815.631247999961</x:v>
+        <x:v>-22474.948751999997</x:v>
       </x:c>
       <x:c r="K41" s="22" t="n">
         <x:f>K36-K40</x:f>
-        <x:v>13815.631247999961</x:v>
+        <x:v>-22474.948751999997</x:v>
       </x:c>
       <x:c r="L41" s="22" t="n">
         <x:f>L36-L40</x:f>
-        <x:v>13815.631247999961</x:v>
+        <x:v>-22474.948751999997</x:v>
       </x:c>
       <x:c r="M41" s="22" t="n">
         <x:f>M36-M40</x:f>
-        <x:v>13815.631247999961</x:v>
+        <x:v>-22474.948751999997</x:v>
       </x:c>
       <x:c r="N41" s="22" t="n">
         <x:f>N36-N40</x:f>
-        <x:v>5080566.05208</x:v>
+        <x:v>5040606.53208</x:v>
       </x:c>
       <x:c r="O41" s="22" t="n">
         <x:f>O36-O40</x:f>
-        <x:v>580566.05208</x:v>
+        <x:v>540606.53208</x:v>
       </x:c>
       <x:c r="P41" s="22" t="n">
         <x:f>P36-P40</x:f>
-        <x:v>580566.05208</x:v>
+        <x:v>540606.53208</x:v>
       </x:c>
       <x:c r="Q41" s="22" t="n">
         <x:f>Q36-Q40</x:f>
-        <x:v>580566.05208</x:v>
+        <x:v>540606.53208</x:v>
       </x:c>
       <x:c r="R41" s="22" t="n">
         <x:f>R36-R40</x:f>
-        <x:v>580566.05208</x:v>
+        <x:v>540606.53208</x:v>
       </x:c>
       <x:c r="S41" s="22" t="n">
         <x:f>S36-S40</x:f>
-        <x:v>580566.05208</x:v>
+        <x:v>540606.53208</x:v>
       </x:c>
       <x:c r="T41" s="22" t="n">
         <x:f>T36-T40</x:f>
-        <x:v>580566.05208</x:v>
+        <x:v>540606.53208</x:v>
       </x:c>
       <x:c r="U41" s="22" t="n">
         <x:f>U36-U40</x:f>
-        <x:v>580566.05208</x:v>
+        <x:v>540606.53208</x:v>
       </x:c>
       <x:c r="V41" s="22" t="n">
         <x:f>V36-V40</x:f>
-        <x:v>580566.05208</x:v>
+        <x:v>540606.53208</x:v>
       </x:c>
       <x:c r="W41" s="22" t="n">
         <x:f>W36-W40</x:f>
-        <x:v>580566.05208</x:v>
+        <x:v>540606.53208</x:v>
       </x:c>
       <x:c r="X41" s="22" t="n">
         <x:f>X36-X40</x:f>
-        <x:v>580566.05208</x:v>
+        <x:v>540606.53208</x:v>
       </x:c>
       <x:c r="Y41" s="22" t="n">
         <x:f>Y36-Y40</x:f>
-        <x:v>580566.05208</x:v>
+        <x:v>540606.53208</x:v>
       </x:c>
       <x:c r="Z41" s="22" t="n">
         <x:f>Z36-Z40</x:f>
-        <x:v>580566.05208</x:v>
+        <x:v>540606.53208</x:v>
       </x:c>
       <x:c r="AA41" s="22" t="n">
         <x:f>AA36-AA40</x:f>
-        <x:v>580566.05208</x:v>
+        <x:v>540606.53208</x:v>
       </x:c>
       <x:c r="AB41" s="22" t="n">
         <x:f>AB36-AB40</x:f>
-        <x:v>580566.05208</x:v>
+        <x:v>540606.53208</x:v>
       </x:c>
       <x:c r="AC41" s="22" t="n">
         <x:f>AC36-AC40</x:f>
-        <x:v>580566.05208</x:v>
+        <x:v>540606.53208</x:v>
       </x:c>
       <x:c r="AD41" s="22" t="n">
         <x:f>AD36-AD40</x:f>
-        <x:v>580566.05208</x:v>
+        <x:v>540606.53208</x:v>
       </x:c>
       <x:c r="AE41" s="22" t="n">
         <x:f>AE36-AE40</x:f>
-        <x:v>580566.05208</x:v>
+        <x:v>540606.53208</x:v>
       </x:c>
       <x:c r="AF41" s="22" t="n">
         <x:f>AF36-AF40</x:f>
-        <x:v>580566.05208</x:v>
+        <x:v>540606.53208</x:v>
       </x:c>
       <x:c r="AG41" s="22" t="n">
         <x:f>AG36-AG40</x:f>
-        <x:v>580566.05208</x:v>
+        <x:v>540606.53208</x:v>
       </x:c>
       <x:c r="AH41" s="22" t="n">
         <x:f>AH36-AH40</x:f>
-        <x:v>580566.05208</x:v>
+        <x:v>540606.53208</x:v>
       </x:c>
       <x:c r="AI41" s="22" t="n">
         <x:f>AI36-AI40</x:f>
-        <x:v>580566.05208</x:v>
+        <x:v>540606.53208</x:v>
       </x:c>
       <x:c r="AJ41" s="22" t="n">
         <x:f>AJ36-AJ40</x:f>
-        <x:v>580566.05208</x:v>
+        <x:v>540606.53208</x:v>
       </x:c>
       <x:c r="AK41" s="22" t="n">
         <x:f>AK36-AK40</x:f>
-        <x:v>580566.05208</x:v>
+        <x:v>540606.53208</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -8080,12 +8599,12 @@
         </x:is>
       </x:c>
       <x:c r="B10" s="30" t="n">
-        <x:f>B9/(Run!AK21*12)</x:f>
-        <x:v>0.014936172401238268</x:v>
+        <x:f>B9/(Run!AK22*12)</x:f>
+        <x:v>0.014444698842167666</x:v>
       </x:c>
       <x:c r="C10" s="30" t="n">
-        <x:f>C9/(Run!AK21*12-B9+C9)</x:f>
-        <x:v>0.08948581177699541</x:v>
+        <x:f>C9/(Run!AK22*12-B9+C9)</x:f>
+        <x:v>0.08675733528265071</x:v>
       </x:c>
     </x:row>
     <x:row r="12">

--- a/model/cost-model.xlsx
+++ b/model/cost-model.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="Rfe2c898cdbfd408a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="2" r:id="Rf6f144d411214778"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Build" sheetId="3" r:id="R8fcf96f38c9e405b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Run" sheetId="4" r:id="R7bf43dc435b94ecd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pricing &amp; P&amp;L" sheetId="5" r:id="Rdb2520aa654243cb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AI Cost" sheetId="6" r:id="R51ac287b42ea4151"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Value" sheetId="7" r:id="R5f20650e059649e8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R6086d1b8fed540d4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="2" r:id="R5c578cfe6a0342be"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Build" sheetId="3" r:id="R68018757d01a4b98"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Run" sheetId="4" r:id="R4453d4cf7fb146a8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pricing &amp; P&amp;L" sheetId="5" r:id="Rfd31def50f974e7a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AI Cost" sheetId="6" r:id="Rc7a8a478624243b1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Value" sheetId="7" r:id="Rb753f3786298472e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1820,11 +1820,11 @@
     <x:row r="65">
       <x:c r="A65" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Claude Max 20x seat (engineering roles)</x:t>
+          <x:t xml:space="preserve">Claude Max 5x seat (USD 100 plan, engineers)</x:t>
         </x:is>
       </x:c>
       <x:c r="B65" s="14" t="n">
-        <x:v>200</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C65" s="9" t="inlineStr">
         <x:is>
@@ -1833,18 +1833,18 @@
       </x:c>
       <x:c r="D65" s="10" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Anthropic list price (support.claude.com, Oct 2026); monthly billing only. Claude Code for build, test and operations work.</x:t>
+          <x:t xml:space="preserve">Anthropic list price (support.claude.com, Oct 2026); monthly billing only. Claude Code for the engineers who build and run the platform.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="66">
       <x:c r="A66" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Claude Max 5x seat (other roles)</x:t>
+          <x:t xml:space="preserve">GitHub Team seat (engineering roles)</x:t>
         </x:is>
       </x:c>
       <x:c r="B66" s="14" t="n">
-        <x:v>100</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C66" s="9" t="inlineStr">
         <x:is>
@@ -1853,18 +1853,18 @@
       </x:c>
       <x:c r="D66" s="10" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Anthropic list price (Oct 2026). Product, design, skills, content, change and support roles.</x:t>
+          <x:t xml:space="preserve">Repositories, Actions CI and code review. Third-party pricing guides (Sep 2026); confirm on github.com/pricing.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="67">
       <x:c r="A67" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">GitHub Team seat (engineering roles)</x:t>
+          <x:t xml:space="preserve">Jira Standard seat (all roles)</x:t>
         </x:is>
       </x:c>
       <x:c r="B67" s="14" t="n">
-        <x:v>4</x:v>
+        <x:v>7.91</x:v>
       </x:c>
       <x:c r="C67" s="9" t="inlineStr">
         <x:is>
@@ -1873,18 +1873,18 @@
       </x:c>
       <x:c r="D67" s="10" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Repositories, Actions CI and code review. Third-party pricing guides (Sep 2026); confirm on github.com/pricing.</x:t>
+          <x:t xml:space="preserve">Delivery tracking with the product council. Third-party guides citing Atlassian list (Jul 2026).</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="68">
       <x:c r="A68" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Jira Standard seat (all roles)</x:t>
+          <x:t xml:space="preserve">Figma Professional full seat (build only)</x:t>
         </x:is>
       </x:c>
       <x:c r="B68" s="14" t="n">
-        <x:v>7.91</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C68" s="9" t="inlineStr">
         <x:is>
@@ -1893,27 +1893,27 @@
       </x:c>
       <x:c r="D68" s="10" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Delivery tracking with the product council. Third-party guides citing Atlassian list (Jul 2026).</x:t>
+          <x:t xml:space="preserve">Monthly billing. Third-party guides and Figma forum (2026).</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="69">
       <x:c r="A69" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Figma Professional full seat (build only)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B69" s="14" t="n">
-        <x:v>20</x:v>
+          <x:t xml:space="preserve">Build seats, Claude Max (engineers)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B69" s="8" t="n">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C69" s="9" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">USD / seat / mo</x:t>
+          <x:t xml:space="preserve">seats</x:t>
         </x:is>
       </x:c>
       <x:c r="D69" s="10" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Monthly billing. Third-party guides and Figma forum (2026).</x:t>
+          <x:t xml:space="preserve">Lead engineers on the core build. Run: the platform engineers (2 up to 20k employees, 3 above).</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -1933,7 +1933,7 @@
       </x:c>
       <x:c r="D70" s="10" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Architect, 2 senior engineers, 2 engineers, AI engineer, 2 data engineers, 2 QA, DevSecOps.</x:t>
+          <x:t xml:space="preserve">GitHub and Jira. Architect, 2 senior engineers, 2 engineers, AI engineer, 2 data engineers, 2 QA, DevSecOps.</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -1953,7 +1953,7 @@
       </x:c>
       <x:c r="D71" s="10" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Product lead, designer, skills lead, 2 skills consultants, content analyst, change consultant.</x:t>
+          <x:t xml:space="preserve">Jira. Product lead, designer, skills lead, 2 skills consultants, content analyst, change consultant.</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -1993,7 +1993,7 @@
       </x:c>
       <x:c r="D73" s="10" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">12 weeks billed as 3 monthly cycles. Run seats follow the run team FTE, rounded up.</x:t>
+          <x:t xml:space="preserve">12 weeks billed as 3 monthly cycles. Run GitHub and Jira seats follow the run team FTE, rounded up.</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -3029,8 +3029,8 @@
         </x:is>
       </x:c>
       <x:c r="D28" s="20" t="n">
-        <x:f>(Assumptions!$B$70*(Assumptions!$B$65+Assumptions!$B$67+Assumptions!$B$68)+Assumptions!$B$71*(Assumptions!$B$66+Assumptions!$B$68)+Assumptions!$B$72*Assumptions!$B$69)*Assumptions!$B$73*Assumptions!$B$6</x:f>
-        <x:v>316850.76</x:v>
+        <x:f>(Assumptions!$B$69*Assumptions!$B$65+Assumptions!$B$70*(Assumptions!$B$66+Assumptions!$B$67)+Assumptions!$B$71*Assumptions!$B$67+Assumptions!$B$72*Assumptions!$B$68)*Assumptions!$B$73*Assumptions!$B$6</x:f>
+        <x:v>51650.759999999995</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
@@ -3041,7 +3041,7 @@
       </x:c>
       <x:c r="D29" s="22" t="n">
         <x:f>D18+D25+D27+D28</x:f>
-        <x:v>8864707.902857143</x:v>
+        <x:v>8599507.902857143</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
@@ -3085,7 +3085,7 @@
       </x:c>
       <x:c r="E33" s="24" t="n">
         <x:f>(E32-D29)/E32</x:f>
-        <x:v>0.4934452626938775</x:v>
+        <x:v>0.5085995484081632</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
@@ -5249,148 +5249,148 @@
         </x:is>
       </x:c>
       <x:c r="B18" s="20" t="n">
-        <x:f>IF(B5&gt;0,(ROUNDUP(IF(B5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$65+Assumptions!$B$67+Assumptions!$B$68)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+B5/Assumptions!$B$77+MAX(1,B5/Assumptions!$B$78),0)*(Assumptions!$B$66+Assumptions!$B$68))*Assumptions!$B$6,0)</x:f>
+        <x:f>IF(B5&gt;0,(ROUNDDOWN(IF(B5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*Assumptions!$B$65+ROUNDUP(IF(B5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$66+Assumptions!$B$67)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+B5/Assumptions!$B$77+MAX(1,B5/Assumptions!$B$78),0)*Assumptions!$B$67)*Assumptions!$B$6,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C18" s="20" t="n">
-        <x:f>IF(C5&gt;0,(ROUNDUP(IF(C5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$65+Assumptions!$B$67+Assumptions!$B$68)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+C5/Assumptions!$B$77+MAX(1,C5/Assumptions!$B$78),0)*(Assumptions!$B$66+Assumptions!$B$68))*Assumptions!$B$6,0)</x:f>
+        <x:f>IF(C5&gt;0,(ROUNDDOWN(IF(C5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*Assumptions!$B$65+ROUNDUP(IF(C5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$66+Assumptions!$B$67)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+C5/Assumptions!$B$77+MAX(1,C5/Assumptions!$B$78),0)*Assumptions!$B$67)*Assumptions!$B$6,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D18" s="20" t="n">
-        <x:f>IF(D5&gt;0,(ROUNDUP(IF(D5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$65+Assumptions!$B$67+Assumptions!$B$68)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+D5/Assumptions!$B$77+MAX(1,D5/Assumptions!$B$78),0)*(Assumptions!$B$66+Assumptions!$B$68))*Assumptions!$B$6,0)</x:f>
+        <x:f>IF(D5&gt;0,(ROUNDDOWN(IF(D5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*Assumptions!$B$65+ROUNDUP(IF(D5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$66+Assumptions!$B$67)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+D5/Assumptions!$B$77+MAX(1,D5/Assumptions!$B$78),0)*Assumptions!$B$67)*Assumptions!$B$6,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="E18" s="20" t="n">
-        <x:f>IF(E5&gt;0,(ROUNDUP(IF(E5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$65+Assumptions!$B$67+Assumptions!$B$68)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+E5/Assumptions!$B$77+MAX(1,E5/Assumptions!$B$78),0)*(Assumptions!$B$66+Assumptions!$B$68))*Assumptions!$B$6,0)</x:f>
-        <x:v>32621.64</x:v>
+        <x:f>IF(E5&gt;0,(ROUNDDOWN(IF(E5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*Assumptions!$B$65+ROUNDUP(IF(E5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$66+Assumptions!$B$67)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+E5/Assumptions!$B$77+MAX(1,E5/Assumptions!$B$78),0)*Assumptions!$B$67)*Assumptions!$B$6,0)</x:f>
+        <x:v>8821.640000000001</x:v>
       </x:c>
       <x:c r="F18" s="20" t="n">
-        <x:f>IF(F5&gt;0,(ROUNDUP(IF(F5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$65+Assumptions!$B$67+Assumptions!$B$68)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+F5/Assumptions!$B$77+MAX(1,F5/Assumptions!$B$78),0)*(Assumptions!$B$66+Assumptions!$B$68))*Assumptions!$B$6,0)</x:f>
-        <x:v>32621.64</x:v>
+        <x:f>IF(F5&gt;0,(ROUNDDOWN(IF(F5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*Assumptions!$B$65+ROUNDUP(IF(F5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$66+Assumptions!$B$67)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+F5/Assumptions!$B$77+MAX(1,F5/Assumptions!$B$78),0)*Assumptions!$B$67)*Assumptions!$B$6,0)</x:f>
+        <x:v>8821.640000000001</x:v>
       </x:c>
       <x:c r="G18" s="20" t="n">
-        <x:f>IF(G5&gt;0,(ROUNDUP(IF(G5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$65+Assumptions!$B$67+Assumptions!$B$68)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+G5/Assumptions!$B$77+MAX(1,G5/Assumptions!$B$78),0)*(Assumptions!$B$66+Assumptions!$B$68))*Assumptions!$B$6,0)</x:f>
-        <x:v>32621.64</x:v>
+        <x:f>IF(G5&gt;0,(ROUNDDOWN(IF(G5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*Assumptions!$B$65+ROUNDUP(IF(G5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$66+Assumptions!$B$67)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+G5/Assumptions!$B$77+MAX(1,G5/Assumptions!$B$78),0)*Assumptions!$B$67)*Assumptions!$B$6,0)</x:f>
+        <x:v>8821.640000000001</x:v>
       </x:c>
       <x:c r="H18" s="20" t="n">
-        <x:f>IF(H5&gt;0,(ROUNDUP(IF(H5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$65+Assumptions!$B$67+Assumptions!$B$68)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+H5/Assumptions!$B$77+MAX(1,H5/Assumptions!$B$78),0)*(Assumptions!$B$66+Assumptions!$B$68))*Assumptions!$B$6,0)</x:f>
-        <x:v>36290.579999999994</x:v>
+        <x:f>IF(H5&gt;0,(ROUNDDOWN(IF(H5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*Assumptions!$B$65+ROUNDUP(IF(H5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$66+Assumptions!$B$67)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+H5/Assumptions!$B$77+MAX(1,H5/Assumptions!$B$78),0)*Assumptions!$B$67)*Assumptions!$B$6,0)</x:f>
+        <x:v>12490.58</x:v>
       </x:c>
       <x:c r="I18" s="20" t="n">
-        <x:f>IF(I5&gt;0,(ROUNDUP(IF(I5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$65+Assumptions!$B$67+Assumptions!$B$68)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+I5/Assumptions!$B$77+MAX(1,I5/Assumptions!$B$78),0)*(Assumptions!$B$66+Assumptions!$B$68))*Assumptions!$B$6,0)</x:f>
-        <x:v>36290.579999999994</x:v>
+        <x:f>IF(I5&gt;0,(ROUNDDOWN(IF(I5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*Assumptions!$B$65+ROUNDUP(IF(I5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$66+Assumptions!$B$67)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+I5/Assumptions!$B$77+MAX(1,I5/Assumptions!$B$78),0)*Assumptions!$B$67)*Assumptions!$B$6,0)</x:f>
+        <x:v>12490.58</x:v>
       </x:c>
       <x:c r="J18" s="20" t="n">
-        <x:f>IF(J5&gt;0,(ROUNDUP(IF(J5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$65+Assumptions!$B$67+Assumptions!$B$68)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+J5/Assumptions!$B$77+MAX(1,J5/Assumptions!$B$78),0)*(Assumptions!$B$66+Assumptions!$B$68))*Assumptions!$B$6,0)</x:f>
-        <x:v>36290.579999999994</x:v>
+        <x:f>IF(J5&gt;0,(ROUNDDOWN(IF(J5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*Assumptions!$B$65+ROUNDUP(IF(J5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$66+Assumptions!$B$67)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+J5/Assumptions!$B$77+MAX(1,J5/Assumptions!$B$78),0)*Assumptions!$B$67)*Assumptions!$B$6,0)</x:f>
+        <x:v>12490.58</x:v>
       </x:c>
       <x:c r="K18" s="20" t="n">
-        <x:f>IF(K5&gt;0,(ROUNDUP(IF(K5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$65+Assumptions!$B$67+Assumptions!$B$68)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+K5/Assumptions!$B$77+MAX(1,K5/Assumptions!$B$78),0)*(Assumptions!$B$66+Assumptions!$B$68))*Assumptions!$B$6,0)</x:f>
-        <x:v>36290.579999999994</x:v>
+        <x:f>IF(K5&gt;0,(ROUNDDOWN(IF(K5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*Assumptions!$B$65+ROUNDUP(IF(K5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$66+Assumptions!$B$67)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+K5/Assumptions!$B$77+MAX(1,K5/Assumptions!$B$78),0)*Assumptions!$B$67)*Assumptions!$B$6,0)</x:f>
+        <x:v>12490.58</x:v>
       </x:c>
       <x:c r="L18" s="20" t="n">
-        <x:f>IF(L5&gt;0,(ROUNDUP(IF(L5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$65+Assumptions!$B$67+Assumptions!$B$68)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+L5/Assumptions!$B$77+MAX(1,L5/Assumptions!$B$78),0)*(Assumptions!$B$66+Assumptions!$B$68))*Assumptions!$B$6,0)</x:f>
-        <x:v>36290.579999999994</x:v>
+        <x:f>IF(L5&gt;0,(ROUNDDOWN(IF(L5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*Assumptions!$B$65+ROUNDUP(IF(L5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$66+Assumptions!$B$67)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+L5/Assumptions!$B$77+MAX(1,L5/Assumptions!$B$78),0)*Assumptions!$B$67)*Assumptions!$B$6,0)</x:f>
+        <x:v>12490.58</x:v>
       </x:c>
       <x:c r="M18" s="20" t="n">
-        <x:f>IF(M5&gt;0,(ROUNDUP(IF(M5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$65+Assumptions!$B$67+Assumptions!$B$68)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+M5/Assumptions!$B$77+MAX(1,M5/Assumptions!$B$78),0)*(Assumptions!$B$66+Assumptions!$B$68))*Assumptions!$B$6,0)</x:f>
-        <x:v>36290.579999999994</x:v>
+        <x:f>IF(M5&gt;0,(ROUNDDOWN(IF(M5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*Assumptions!$B$65+ROUNDUP(IF(M5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$66+Assumptions!$B$67)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+M5/Assumptions!$B$77+MAX(1,M5/Assumptions!$B$78),0)*Assumptions!$B$67)*Assumptions!$B$6,0)</x:f>
+        <x:v>12490.58</x:v>
       </x:c>
       <x:c r="N18" s="20" t="n">
-        <x:f>IF(N5&gt;0,(ROUNDUP(IF(N5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$65+Assumptions!$B$67+Assumptions!$B$68)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+N5/Assumptions!$B$77+MAX(1,N5/Assumptions!$B$78),0)*(Assumptions!$B$66+Assumptions!$B$68))*Assumptions!$B$6,0)</x:f>
-        <x:v>39959.52</x:v>
+        <x:f>IF(N5&gt;0,(ROUNDDOWN(IF(N5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*Assumptions!$B$65+ROUNDUP(IF(N5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$66+Assumptions!$B$67)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+N5/Assumptions!$B$77+MAX(1,N5/Assumptions!$B$78),0)*Assumptions!$B$67)*Assumptions!$B$6,0)</x:f>
+        <x:v>12759.52</x:v>
       </x:c>
       <x:c r="O18" s="20" t="n">
-        <x:f>IF(O5&gt;0,(ROUNDUP(IF(O5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$65+Assumptions!$B$67+Assumptions!$B$68)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+O5/Assumptions!$B$77+MAX(1,O5/Assumptions!$B$78),0)*(Assumptions!$B$66+Assumptions!$B$68))*Assumptions!$B$6,0)</x:f>
-        <x:v>39959.52</x:v>
+        <x:f>IF(O5&gt;0,(ROUNDDOWN(IF(O5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*Assumptions!$B$65+ROUNDUP(IF(O5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$66+Assumptions!$B$67)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+O5/Assumptions!$B$77+MAX(1,O5/Assumptions!$B$78),0)*Assumptions!$B$67)*Assumptions!$B$6,0)</x:f>
+        <x:v>12759.52</x:v>
       </x:c>
       <x:c r="P18" s="20" t="n">
-        <x:f>IF(P5&gt;0,(ROUNDUP(IF(P5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$65+Assumptions!$B$67+Assumptions!$B$68)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+P5/Assumptions!$B$77+MAX(1,P5/Assumptions!$B$78),0)*(Assumptions!$B$66+Assumptions!$B$68))*Assumptions!$B$6,0)</x:f>
-        <x:v>39959.52</x:v>
+        <x:f>IF(P5&gt;0,(ROUNDDOWN(IF(P5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*Assumptions!$B$65+ROUNDUP(IF(P5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$66+Assumptions!$B$67)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+P5/Assumptions!$B$77+MAX(1,P5/Assumptions!$B$78),0)*Assumptions!$B$67)*Assumptions!$B$6,0)</x:f>
+        <x:v>12759.52</x:v>
       </x:c>
       <x:c r="Q18" s="20" t="n">
-        <x:f>IF(Q5&gt;0,(ROUNDUP(IF(Q5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$65+Assumptions!$B$67+Assumptions!$B$68)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+Q5/Assumptions!$B$77+MAX(1,Q5/Assumptions!$B$78),0)*(Assumptions!$B$66+Assumptions!$B$68))*Assumptions!$B$6,0)</x:f>
-        <x:v>39959.52</x:v>
+        <x:f>IF(Q5&gt;0,(ROUNDDOWN(IF(Q5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*Assumptions!$B$65+ROUNDUP(IF(Q5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$66+Assumptions!$B$67)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+Q5/Assumptions!$B$77+MAX(1,Q5/Assumptions!$B$78),0)*Assumptions!$B$67)*Assumptions!$B$6,0)</x:f>
+        <x:v>12759.52</x:v>
       </x:c>
       <x:c r="R18" s="20" t="n">
-        <x:f>IF(R5&gt;0,(ROUNDUP(IF(R5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$65+Assumptions!$B$67+Assumptions!$B$68)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+R5/Assumptions!$B$77+MAX(1,R5/Assumptions!$B$78),0)*(Assumptions!$B$66+Assumptions!$B$68))*Assumptions!$B$6,0)</x:f>
-        <x:v>39959.52</x:v>
+        <x:f>IF(R5&gt;0,(ROUNDDOWN(IF(R5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*Assumptions!$B$65+ROUNDUP(IF(R5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$66+Assumptions!$B$67)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+R5/Assumptions!$B$77+MAX(1,R5/Assumptions!$B$78),0)*Assumptions!$B$67)*Assumptions!$B$6,0)</x:f>
+        <x:v>12759.52</x:v>
       </x:c>
       <x:c r="S18" s="20" t="n">
-        <x:f>IF(S5&gt;0,(ROUNDUP(IF(S5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$65+Assumptions!$B$67+Assumptions!$B$68)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+S5/Assumptions!$B$77+MAX(1,S5/Assumptions!$B$78),0)*(Assumptions!$B$66+Assumptions!$B$68))*Assumptions!$B$6,0)</x:f>
-        <x:v>39959.52</x:v>
+        <x:f>IF(S5&gt;0,(ROUNDDOWN(IF(S5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*Assumptions!$B$65+ROUNDUP(IF(S5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$66+Assumptions!$B$67)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+S5/Assumptions!$B$77+MAX(1,S5/Assumptions!$B$78),0)*Assumptions!$B$67)*Assumptions!$B$6,0)</x:f>
+        <x:v>12759.52</x:v>
       </x:c>
       <x:c r="T18" s="20" t="n">
-        <x:f>IF(T5&gt;0,(ROUNDUP(IF(T5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$65+Assumptions!$B$67+Assumptions!$B$68)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+T5/Assumptions!$B$77+MAX(1,T5/Assumptions!$B$78),0)*(Assumptions!$B$66+Assumptions!$B$68))*Assumptions!$B$6,0)</x:f>
-        <x:v>39959.52</x:v>
+        <x:f>IF(T5&gt;0,(ROUNDDOWN(IF(T5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*Assumptions!$B$65+ROUNDUP(IF(T5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$66+Assumptions!$B$67)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+T5/Assumptions!$B$77+MAX(1,T5/Assumptions!$B$78),0)*Assumptions!$B$67)*Assumptions!$B$6,0)</x:f>
+        <x:v>12759.52</x:v>
       </x:c>
       <x:c r="U18" s="20" t="n">
-        <x:f>IF(U5&gt;0,(ROUNDUP(IF(U5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$65+Assumptions!$B$67+Assumptions!$B$68)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+U5/Assumptions!$B$77+MAX(1,U5/Assumptions!$B$78),0)*(Assumptions!$B$66+Assumptions!$B$68))*Assumptions!$B$6,0)</x:f>
-        <x:v>39959.52</x:v>
+        <x:f>IF(U5&gt;0,(ROUNDDOWN(IF(U5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*Assumptions!$B$65+ROUNDUP(IF(U5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$66+Assumptions!$B$67)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+U5/Assumptions!$B$77+MAX(1,U5/Assumptions!$B$78),0)*Assumptions!$B$67)*Assumptions!$B$6,0)</x:f>
+        <x:v>12759.52</x:v>
       </x:c>
       <x:c r="V18" s="20" t="n">
-        <x:f>IF(V5&gt;0,(ROUNDUP(IF(V5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$65+Assumptions!$B$67+Assumptions!$B$68)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+V5/Assumptions!$B$77+MAX(1,V5/Assumptions!$B$78),0)*(Assumptions!$B$66+Assumptions!$B$68))*Assumptions!$B$6,0)</x:f>
-        <x:v>39959.52</x:v>
+        <x:f>IF(V5&gt;0,(ROUNDDOWN(IF(V5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*Assumptions!$B$65+ROUNDUP(IF(V5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$66+Assumptions!$B$67)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+V5/Assumptions!$B$77+MAX(1,V5/Assumptions!$B$78),0)*Assumptions!$B$67)*Assumptions!$B$6,0)</x:f>
+        <x:v>12759.52</x:v>
       </x:c>
       <x:c r="W18" s="20" t="n">
-        <x:f>IF(W5&gt;0,(ROUNDUP(IF(W5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$65+Assumptions!$B$67+Assumptions!$B$68)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+W5/Assumptions!$B$77+MAX(1,W5/Assumptions!$B$78),0)*(Assumptions!$B$66+Assumptions!$B$68))*Assumptions!$B$6,0)</x:f>
-        <x:v>39959.52</x:v>
+        <x:f>IF(W5&gt;0,(ROUNDDOWN(IF(W5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*Assumptions!$B$65+ROUNDUP(IF(W5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$66+Assumptions!$B$67)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+W5/Assumptions!$B$77+MAX(1,W5/Assumptions!$B$78),0)*Assumptions!$B$67)*Assumptions!$B$6,0)</x:f>
+        <x:v>12759.52</x:v>
       </x:c>
       <x:c r="X18" s="20" t="n">
-        <x:f>IF(X5&gt;0,(ROUNDUP(IF(X5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$65+Assumptions!$B$67+Assumptions!$B$68)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+X5/Assumptions!$B$77+MAX(1,X5/Assumptions!$B$78),0)*(Assumptions!$B$66+Assumptions!$B$68))*Assumptions!$B$6,0)</x:f>
-        <x:v>39959.52</x:v>
+        <x:f>IF(X5&gt;0,(ROUNDDOWN(IF(X5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*Assumptions!$B$65+ROUNDUP(IF(X5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$66+Assumptions!$B$67)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+X5/Assumptions!$B$77+MAX(1,X5/Assumptions!$B$78),0)*Assumptions!$B$67)*Assumptions!$B$6,0)</x:f>
+        <x:v>12759.52</x:v>
       </x:c>
       <x:c r="Y18" s="20" t="n">
-        <x:f>IF(Y5&gt;0,(ROUNDUP(IF(Y5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$65+Assumptions!$B$67+Assumptions!$B$68)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+Y5/Assumptions!$B$77+MAX(1,Y5/Assumptions!$B$78),0)*(Assumptions!$B$66+Assumptions!$B$68))*Assumptions!$B$6,0)</x:f>
-        <x:v>39959.52</x:v>
+        <x:f>IF(Y5&gt;0,(ROUNDDOWN(IF(Y5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*Assumptions!$B$65+ROUNDUP(IF(Y5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$66+Assumptions!$B$67)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+Y5/Assumptions!$B$77+MAX(1,Y5/Assumptions!$B$78),0)*Assumptions!$B$67)*Assumptions!$B$6,0)</x:f>
+        <x:v>12759.52</x:v>
       </x:c>
       <x:c r="Z18" s="20" t="n">
-        <x:f>IF(Z5&gt;0,(ROUNDUP(IF(Z5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$65+Assumptions!$B$67+Assumptions!$B$68)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+Z5/Assumptions!$B$77+MAX(1,Z5/Assumptions!$B$78),0)*(Assumptions!$B$66+Assumptions!$B$68))*Assumptions!$B$6,0)</x:f>
-        <x:v>39959.52</x:v>
+        <x:f>IF(Z5&gt;0,(ROUNDDOWN(IF(Z5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*Assumptions!$B$65+ROUNDUP(IF(Z5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$66+Assumptions!$B$67)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+Z5/Assumptions!$B$77+MAX(1,Z5/Assumptions!$B$78),0)*Assumptions!$B$67)*Assumptions!$B$6,0)</x:f>
+        <x:v>12759.52</x:v>
       </x:c>
       <x:c r="AA18" s="20" t="n">
-        <x:f>IF(AA5&gt;0,(ROUNDUP(IF(AA5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$65+Assumptions!$B$67+Assumptions!$B$68)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+AA5/Assumptions!$B$77+MAX(1,AA5/Assumptions!$B$78),0)*(Assumptions!$B$66+Assumptions!$B$68))*Assumptions!$B$6,0)</x:f>
-        <x:v>39959.52</x:v>
+        <x:f>IF(AA5&gt;0,(ROUNDDOWN(IF(AA5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*Assumptions!$B$65+ROUNDUP(IF(AA5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$66+Assumptions!$B$67)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+AA5/Assumptions!$B$77+MAX(1,AA5/Assumptions!$B$78),0)*Assumptions!$B$67)*Assumptions!$B$6,0)</x:f>
+        <x:v>12759.52</x:v>
       </x:c>
       <x:c r="AB18" s="20" t="n">
-        <x:f>IF(AB5&gt;0,(ROUNDUP(IF(AB5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$65+Assumptions!$B$67+Assumptions!$B$68)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+AB5/Assumptions!$B$77+MAX(1,AB5/Assumptions!$B$78),0)*(Assumptions!$B$66+Assumptions!$B$68))*Assumptions!$B$6,0)</x:f>
-        <x:v>39959.52</x:v>
+        <x:f>IF(AB5&gt;0,(ROUNDDOWN(IF(AB5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*Assumptions!$B$65+ROUNDUP(IF(AB5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$66+Assumptions!$B$67)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+AB5/Assumptions!$B$77+MAX(1,AB5/Assumptions!$B$78),0)*Assumptions!$B$67)*Assumptions!$B$6,0)</x:f>
+        <x:v>12759.52</x:v>
       </x:c>
       <x:c r="AC18" s="20" t="n">
-        <x:f>IF(AC5&gt;0,(ROUNDUP(IF(AC5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$65+Assumptions!$B$67+Assumptions!$B$68)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+AC5/Assumptions!$B$77+MAX(1,AC5/Assumptions!$B$78),0)*(Assumptions!$B$66+Assumptions!$B$68))*Assumptions!$B$6,0)</x:f>
-        <x:v>39959.52</x:v>
+        <x:f>IF(AC5&gt;0,(ROUNDDOWN(IF(AC5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*Assumptions!$B$65+ROUNDUP(IF(AC5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$66+Assumptions!$B$67)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+AC5/Assumptions!$B$77+MAX(1,AC5/Assumptions!$B$78),0)*Assumptions!$B$67)*Assumptions!$B$6,0)</x:f>
+        <x:v>12759.52</x:v>
       </x:c>
       <x:c r="AD18" s="20" t="n">
-        <x:f>IF(AD5&gt;0,(ROUNDUP(IF(AD5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$65+Assumptions!$B$67+Assumptions!$B$68)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+AD5/Assumptions!$B$77+MAX(1,AD5/Assumptions!$B$78),0)*(Assumptions!$B$66+Assumptions!$B$68))*Assumptions!$B$6,0)</x:f>
-        <x:v>39959.52</x:v>
+        <x:f>IF(AD5&gt;0,(ROUNDDOWN(IF(AD5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*Assumptions!$B$65+ROUNDUP(IF(AD5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$66+Assumptions!$B$67)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+AD5/Assumptions!$B$77+MAX(1,AD5/Assumptions!$B$78),0)*Assumptions!$B$67)*Assumptions!$B$6,0)</x:f>
+        <x:v>12759.52</x:v>
       </x:c>
       <x:c r="AE18" s="20" t="n">
-        <x:f>IF(AE5&gt;0,(ROUNDUP(IF(AE5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$65+Assumptions!$B$67+Assumptions!$B$68)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+AE5/Assumptions!$B$77+MAX(1,AE5/Assumptions!$B$78),0)*(Assumptions!$B$66+Assumptions!$B$68))*Assumptions!$B$6,0)</x:f>
-        <x:v>39959.52</x:v>
+        <x:f>IF(AE5&gt;0,(ROUNDDOWN(IF(AE5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*Assumptions!$B$65+ROUNDUP(IF(AE5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$66+Assumptions!$B$67)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+AE5/Assumptions!$B$77+MAX(1,AE5/Assumptions!$B$78),0)*Assumptions!$B$67)*Assumptions!$B$6,0)</x:f>
+        <x:v>12759.52</x:v>
       </x:c>
       <x:c r="AF18" s="20" t="n">
-        <x:f>IF(AF5&gt;0,(ROUNDUP(IF(AF5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$65+Assumptions!$B$67+Assumptions!$B$68)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+AF5/Assumptions!$B$77+MAX(1,AF5/Assumptions!$B$78),0)*(Assumptions!$B$66+Assumptions!$B$68))*Assumptions!$B$6,0)</x:f>
-        <x:v>39959.52</x:v>
+        <x:f>IF(AF5&gt;0,(ROUNDDOWN(IF(AF5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*Assumptions!$B$65+ROUNDUP(IF(AF5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$66+Assumptions!$B$67)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+AF5/Assumptions!$B$77+MAX(1,AF5/Assumptions!$B$78),0)*Assumptions!$B$67)*Assumptions!$B$6,0)</x:f>
+        <x:v>12759.52</x:v>
       </x:c>
       <x:c r="AG18" s="20" t="n">
-        <x:f>IF(AG5&gt;0,(ROUNDUP(IF(AG5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$65+Assumptions!$B$67+Assumptions!$B$68)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+AG5/Assumptions!$B$77+MAX(1,AG5/Assumptions!$B$78),0)*(Assumptions!$B$66+Assumptions!$B$68))*Assumptions!$B$6,0)</x:f>
-        <x:v>39959.52</x:v>
+        <x:f>IF(AG5&gt;0,(ROUNDDOWN(IF(AG5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*Assumptions!$B$65+ROUNDUP(IF(AG5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$66+Assumptions!$B$67)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+AG5/Assumptions!$B$77+MAX(1,AG5/Assumptions!$B$78),0)*Assumptions!$B$67)*Assumptions!$B$6,0)</x:f>
+        <x:v>12759.52</x:v>
       </x:c>
       <x:c r="AH18" s="20" t="n">
-        <x:f>IF(AH5&gt;0,(ROUNDUP(IF(AH5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$65+Assumptions!$B$67+Assumptions!$B$68)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+AH5/Assumptions!$B$77+MAX(1,AH5/Assumptions!$B$78),0)*(Assumptions!$B$66+Assumptions!$B$68))*Assumptions!$B$6,0)</x:f>
-        <x:v>39959.52</x:v>
+        <x:f>IF(AH5&gt;0,(ROUNDDOWN(IF(AH5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*Assumptions!$B$65+ROUNDUP(IF(AH5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$66+Assumptions!$B$67)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+AH5/Assumptions!$B$77+MAX(1,AH5/Assumptions!$B$78),0)*Assumptions!$B$67)*Assumptions!$B$6,0)</x:f>
+        <x:v>12759.52</x:v>
       </x:c>
       <x:c r="AI18" s="20" t="n">
-        <x:f>IF(AI5&gt;0,(ROUNDUP(IF(AI5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$65+Assumptions!$B$67+Assumptions!$B$68)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+AI5/Assumptions!$B$77+MAX(1,AI5/Assumptions!$B$78),0)*(Assumptions!$B$66+Assumptions!$B$68))*Assumptions!$B$6,0)</x:f>
-        <x:v>39959.52</x:v>
+        <x:f>IF(AI5&gt;0,(ROUNDDOWN(IF(AI5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*Assumptions!$B$65+ROUNDUP(IF(AI5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$66+Assumptions!$B$67)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+AI5/Assumptions!$B$77+MAX(1,AI5/Assumptions!$B$78),0)*Assumptions!$B$67)*Assumptions!$B$6,0)</x:f>
+        <x:v>12759.52</x:v>
       </x:c>
       <x:c r="AJ18" s="20" t="n">
-        <x:f>IF(AJ5&gt;0,(ROUNDUP(IF(AJ5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$65+Assumptions!$B$67+Assumptions!$B$68)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+AJ5/Assumptions!$B$77+MAX(1,AJ5/Assumptions!$B$78),0)*(Assumptions!$B$66+Assumptions!$B$68))*Assumptions!$B$6,0)</x:f>
-        <x:v>39959.52</x:v>
+        <x:f>IF(AJ5&gt;0,(ROUNDDOWN(IF(AJ5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*Assumptions!$B$65+ROUNDUP(IF(AJ5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$66+Assumptions!$B$67)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+AJ5/Assumptions!$B$77+MAX(1,AJ5/Assumptions!$B$78),0)*Assumptions!$B$67)*Assumptions!$B$6,0)</x:f>
+        <x:v>12759.52</x:v>
       </x:c>
       <x:c r="AK18" s="20" t="n">
-        <x:f>IF(AK5&gt;0,(ROUNDUP(IF(AK5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$65+Assumptions!$B$67+Assumptions!$B$68)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+AK5/Assumptions!$B$77+MAX(1,AK5/Assumptions!$B$78),0)*(Assumptions!$B$66+Assumptions!$B$68))*Assumptions!$B$6,0)</x:f>
-        <x:v>39959.52</x:v>
+        <x:f>IF(AK5&gt;0,(ROUNDDOWN(IF(AK5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*Assumptions!$B$65+ROUNDUP(IF(AK5&gt;20000,Assumptions!$B$80,Assumptions!$B$79),0)*(Assumptions!$B$66+Assumptions!$B$67)+ROUNDUP(Assumptions!$B$75+Assumptions!$B$76+AK5/Assumptions!$B$77+MAX(1,AK5/Assumptions!$B$78),0)*Assumptions!$B$67)*Assumptions!$B$6,0)</x:f>
+        <x:v>12759.52</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -5866,135 +5866,135 @@
       </x:c>
       <x:c r="E22" s="22" t="n">
         <x:f>E13+SUM(E14:E21)</x:f>
-        <x:v>910298.026112</x:v>
+        <x:v>886498.026112</x:v>
       </x:c>
       <x:c r="F22" s="22" t="n">
         <x:f>F13+SUM(F14:F21)</x:f>
-        <x:v>910298.026112</x:v>
+        <x:v>886498.026112</x:v>
       </x:c>
       <x:c r="G22" s="22" t="n">
         <x:f>G13+SUM(G14:G21)</x:f>
-        <x:v>910298.026112</x:v>
+        <x:v>886498.026112</x:v>
       </x:c>
       <x:c r="H22" s="22" t="n">
         <x:f>H13+SUM(H14:H21)</x:f>
-        <x:v>1075474.948752</x:v>
+        <x:v>1051674.948752</x:v>
       </x:c>
       <x:c r="I22" s="22" t="n">
         <x:f>I13+SUM(I14:I21)</x:f>
-        <x:v>1075474.948752</x:v>
+        <x:v>1051674.948752</x:v>
       </x:c>
       <x:c r="J22" s="22" t="n">
         <x:f>J13+SUM(J14:J21)</x:f>
-        <x:v>1075474.948752</x:v>
+        <x:v>1051674.948752</x:v>
       </x:c>
       <x:c r="K22" s="22" t="n">
         <x:f>K13+SUM(K14:K21)</x:f>
-        <x:v>1075474.948752</x:v>
+        <x:v>1051674.948752</x:v>
       </x:c>
       <x:c r="L22" s="22" t="n">
         <x:f>L13+SUM(L14:L21)</x:f>
-        <x:v>1075474.948752</x:v>
+        <x:v>1051674.948752</x:v>
       </x:c>
       <x:c r="M22" s="22" t="n">
         <x:f>M13+SUM(M14:M21)</x:f>
-        <x:v>1075474.948752</x:v>
+        <x:v>1051674.948752</x:v>
       </x:c>
       <x:c r="N22" s="22" t="n">
         <x:f>N13+SUM(N14:N21)</x:f>
-        <x:v>1214393.46792</x:v>
+        <x:v>1187193.46792</x:v>
       </x:c>
       <x:c r="O22" s="22" t="n">
         <x:f>O13+SUM(O14:O21)</x:f>
-        <x:v>1214393.46792</x:v>
+        <x:v>1187193.46792</x:v>
       </x:c>
       <x:c r="P22" s="22" t="n">
         <x:f>P13+SUM(P14:P21)</x:f>
-        <x:v>1214393.46792</x:v>
+        <x:v>1187193.46792</x:v>
       </x:c>
       <x:c r="Q22" s="22" t="n">
         <x:f>Q13+SUM(Q14:Q21)</x:f>
-        <x:v>1214393.46792</x:v>
+        <x:v>1187193.46792</x:v>
       </x:c>
       <x:c r="R22" s="22" t="n">
         <x:f>R13+SUM(R14:R21)</x:f>
-        <x:v>1214393.46792</x:v>
+        <x:v>1187193.46792</x:v>
       </x:c>
       <x:c r="S22" s="22" t="n">
         <x:f>S13+SUM(S14:S21)</x:f>
-        <x:v>1214393.46792</x:v>
+        <x:v>1187193.46792</x:v>
       </x:c>
       <x:c r="T22" s="22" t="n">
         <x:f>T13+SUM(T14:T21)</x:f>
-        <x:v>1214393.46792</x:v>
+        <x:v>1187193.46792</x:v>
       </x:c>
       <x:c r="U22" s="22" t="n">
         <x:f>U13+SUM(U14:U21)</x:f>
-        <x:v>1214393.46792</x:v>
+        <x:v>1187193.46792</x:v>
       </x:c>
       <x:c r="V22" s="22" t="n">
         <x:f>V13+SUM(V14:V21)</x:f>
-        <x:v>1214393.46792</x:v>
+        <x:v>1187193.46792</x:v>
       </x:c>
       <x:c r="W22" s="22" t="n">
         <x:f>W13+SUM(W14:W21)</x:f>
-        <x:v>1214393.46792</x:v>
+        <x:v>1187193.46792</x:v>
       </x:c>
       <x:c r="X22" s="22" t="n">
         <x:f>X13+SUM(X14:X21)</x:f>
-        <x:v>1214393.46792</x:v>
+        <x:v>1187193.46792</x:v>
       </x:c>
       <x:c r="Y22" s="22" t="n">
         <x:f>Y13+SUM(Y14:Y21)</x:f>
-        <x:v>1214393.46792</x:v>
+        <x:v>1187193.46792</x:v>
       </x:c>
       <x:c r="Z22" s="22" t="n">
         <x:f>Z13+SUM(Z14:Z21)</x:f>
-        <x:v>1214393.46792</x:v>
+        <x:v>1187193.46792</x:v>
       </x:c>
       <x:c r="AA22" s="22" t="n">
         <x:f>AA13+SUM(AA14:AA21)</x:f>
-        <x:v>1214393.46792</x:v>
+        <x:v>1187193.46792</x:v>
       </x:c>
       <x:c r="AB22" s="22" t="n">
         <x:f>AB13+SUM(AB14:AB21)</x:f>
-        <x:v>1214393.46792</x:v>
+        <x:v>1187193.46792</x:v>
       </x:c>
       <x:c r="AC22" s="22" t="n">
         <x:f>AC13+SUM(AC14:AC21)</x:f>
-        <x:v>1214393.46792</x:v>
+        <x:v>1187193.46792</x:v>
       </x:c>
       <x:c r="AD22" s="22" t="n">
         <x:f>AD13+SUM(AD14:AD21)</x:f>
-        <x:v>1214393.46792</x:v>
+        <x:v>1187193.46792</x:v>
       </x:c>
       <x:c r="AE22" s="22" t="n">
         <x:f>AE13+SUM(AE14:AE21)</x:f>
-        <x:v>1214393.46792</x:v>
+        <x:v>1187193.46792</x:v>
       </x:c>
       <x:c r="AF22" s="22" t="n">
         <x:f>AF13+SUM(AF14:AF21)</x:f>
-        <x:v>1214393.46792</x:v>
+        <x:v>1187193.46792</x:v>
       </x:c>
       <x:c r="AG22" s="22" t="n">
         <x:f>AG13+SUM(AG14:AG21)</x:f>
-        <x:v>1214393.46792</x:v>
+        <x:v>1187193.46792</x:v>
       </x:c>
       <x:c r="AH22" s="22" t="n">
         <x:f>AH13+SUM(AH14:AH21)</x:f>
-        <x:v>1214393.46792</x:v>
+        <x:v>1187193.46792</x:v>
       </x:c>
       <x:c r="AI22" s="22" t="n">
         <x:f>AI13+SUM(AI14:AI21)</x:f>
-        <x:v>1214393.46792</x:v>
+        <x:v>1187193.46792</x:v>
       </x:c>
       <x:c r="AJ22" s="22" t="n">
         <x:f>AJ13+SUM(AJ14:AJ21)</x:f>
-        <x:v>1214393.46792</x:v>
+        <x:v>1187193.46792</x:v>
       </x:c>
       <x:c r="AK22" s="22" t="n">
         <x:f>AK13+SUM(AK14:AK21)</x:f>
-        <x:v>1214393.46792</x:v>
+        <x:v>1187193.46792</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -6017,135 +6017,135 @@
       </x:c>
       <x:c r="E23" s="19" t="n">
         <x:f>IF(E5&gt;0,E22/E5,0)</x:f>
-        <x:v>75.85816884266667</x:v>
+        <x:v>73.87483550933334</x:v>
       </x:c>
       <x:c r="F23" s="19" t="n">
         <x:f>IF(F5&gt;0,F22/F5,0)</x:f>
-        <x:v>75.85816884266667</x:v>
+        <x:v>73.87483550933334</x:v>
       </x:c>
       <x:c r="G23" s="19" t="n">
         <x:f>IF(G5&gt;0,G22/G5,0)</x:f>
-        <x:v>75.85816884266667</x:v>
+        <x:v>73.87483550933334</x:v>
       </x:c>
       <x:c r="H23" s="19" t="n">
         <x:f>IF(H5&gt;0,H22/H5,0)</x:f>
-        <x:v>39.832405509333334</x:v>
+        <x:v>38.950924027851855</x:v>
       </x:c>
       <x:c r="I23" s="19" t="n">
         <x:f>IF(I5&gt;0,I22/I5,0)</x:f>
-        <x:v>39.832405509333334</x:v>
+        <x:v>38.950924027851855</x:v>
       </x:c>
       <x:c r="J23" s="19" t="n">
         <x:f>IF(J5&gt;0,J22/J5,0)</x:f>
-        <x:v>39.832405509333334</x:v>
+        <x:v>38.950924027851855</x:v>
       </x:c>
       <x:c r="K23" s="19" t="n">
         <x:f>IF(K5&gt;0,K22/K5,0)</x:f>
-        <x:v>39.832405509333334</x:v>
+        <x:v>38.950924027851855</x:v>
       </x:c>
       <x:c r="L23" s="19" t="n">
         <x:f>IF(L5&gt;0,L22/L5,0)</x:f>
-        <x:v>39.832405509333334</x:v>
+        <x:v>38.950924027851855</x:v>
       </x:c>
       <x:c r="M23" s="19" t="n">
         <x:f>IF(M5&gt;0,M22/M5,0)</x:f>
-        <x:v>39.832405509333334</x:v>
+        <x:v>38.950924027851855</x:v>
       </x:c>
       <x:c r="N23" s="19" t="n">
         <x:f>IF(N5&gt;0,N22/N5,0)</x:f>
-        <x:v>26.986521509333333</x:v>
+        <x:v>26.38207706488889</x:v>
       </x:c>
       <x:c r="O23" s="19" t="n">
         <x:f>IF(O5&gt;0,O22/O5,0)</x:f>
-        <x:v>26.986521509333333</x:v>
+        <x:v>26.38207706488889</x:v>
       </x:c>
       <x:c r="P23" s="19" t="n">
         <x:f>IF(P5&gt;0,P22/P5,0)</x:f>
-        <x:v>26.986521509333333</x:v>
+        <x:v>26.38207706488889</x:v>
       </x:c>
       <x:c r="Q23" s="19" t="n">
         <x:f>IF(Q5&gt;0,Q22/Q5,0)</x:f>
-        <x:v>26.986521509333333</x:v>
+        <x:v>26.38207706488889</x:v>
       </x:c>
       <x:c r="R23" s="19" t="n">
         <x:f>IF(R5&gt;0,R22/R5,0)</x:f>
-        <x:v>26.986521509333333</x:v>
+        <x:v>26.38207706488889</x:v>
       </x:c>
       <x:c r="S23" s="19" t="n">
         <x:f>IF(S5&gt;0,S22/S5,0)</x:f>
-        <x:v>26.986521509333333</x:v>
+        <x:v>26.38207706488889</x:v>
       </x:c>
       <x:c r="T23" s="19" t="n">
         <x:f>IF(T5&gt;0,T22/T5,0)</x:f>
-        <x:v>26.986521509333333</x:v>
+        <x:v>26.38207706488889</x:v>
       </x:c>
       <x:c r="U23" s="19" t="n">
         <x:f>IF(U5&gt;0,U22/U5,0)</x:f>
-        <x:v>26.986521509333333</x:v>
+        <x:v>26.38207706488889</x:v>
       </x:c>
       <x:c r="V23" s="19" t="n">
         <x:f>IF(V5&gt;0,V22/V5,0)</x:f>
-        <x:v>26.986521509333333</x:v>
+        <x:v>26.38207706488889</x:v>
       </x:c>
       <x:c r="W23" s="19" t="n">
         <x:f>IF(W5&gt;0,W22/W5,0)</x:f>
-        <x:v>26.986521509333333</x:v>
+        <x:v>26.38207706488889</x:v>
       </x:c>
       <x:c r="X23" s="19" t="n">
         <x:f>IF(X5&gt;0,X22/X5,0)</x:f>
-        <x:v>26.986521509333333</x:v>
+        <x:v>26.38207706488889</x:v>
       </x:c>
       <x:c r="Y23" s="19" t="n">
         <x:f>IF(Y5&gt;0,Y22/Y5,0)</x:f>
-        <x:v>26.986521509333333</x:v>
+        <x:v>26.38207706488889</x:v>
       </x:c>
       <x:c r="Z23" s="19" t="n">
         <x:f>IF(Z5&gt;0,Z22/Z5,0)</x:f>
-        <x:v>26.986521509333333</x:v>
+        <x:v>26.38207706488889</x:v>
       </x:c>
       <x:c r="AA23" s="19" t="n">
         <x:f>IF(AA5&gt;0,AA22/AA5,0)</x:f>
-        <x:v>26.986521509333333</x:v>
+        <x:v>26.38207706488889</x:v>
       </x:c>
       <x:c r="AB23" s="19" t="n">
         <x:f>IF(AB5&gt;0,AB22/AB5,0)</x:f>
-        <x:v>26.986521509333333</x:v>
+        <x:v>26.38207706488889</x:v>
       </x:c>
       <x:c r="AC23" s="19" t="n">
         <x:f>IF(AC5&gt;0,AC22/AC5,0)</x:f>
-        <x:v>26.986521509333333</x:v>
+        <x:v>26.38207706488889</x:v>
       </x:c>
       <x:c r="AD23" s="19" t="n">
         <x:f>IF(AD5&gt;0,AD22/AD5,0)</x:f>
-        <x:v>26.986521509333333</x:v>
+        <x:v>26.38207706488889</x:v>
       </x:c>
       <x:c r="AE23" s="19" t="n">
         <x:f>IF(AE5&gt;0,AE22/AE5,0)</x:f>
-        <x:v>26.986521509333333</x:v>
+        <x:v>26.38207706488889</x:v>
       </x:c>
       <x:c r="AF23" s="19" t="n">
         <x:f>IF(AF5&gt;0,AF22/AF5,0)</x:f>
-        <x:v>26.986521509333333</x:v>
+        <x:v>26.38207706488889</x:v>
       </x:c>
       <x:c r="AG23" s="19" t="n">
         <x:f>IF(AG5&gt;0,AG22/AG5,0)</x:f>
-        <x:v>26.986521509333333</x:v>
+        <x:v>26.38207706488889</x:v>
       </x:c>
       <x:c r="AH23" s="19" t="n">
         <x:f>IF(AH5&gt;0,AH22/AH5,0)</x:f>
-        <x:v>26.986521509333333</x:v>
+        <x:v>26.38207706488889</x:v>
       </x:c>
       <x:c r="AI23" s="19" t="n">
         <x:f>IF(AI5&gt;0,AI22/AI5,0)</x:f>
-        <x:v>26.986521509333333</x:v>
+        <x:v>26.38207706488889</x:v>
       </x:c>
       <x:c r="AJ23" s="19" t="n">
         <x:f>IF(AJ5&gt;0,AJ22/AJ5,0)</x:f>
-        <x:v>26.986521509333333</x:v>
+        <x:v>26.38207706488889</x:v>
       </x:c>
       <x:c r="AK23" s="19" t="n">
         <x:f>IF(AK5&gt;0,AK22/AK5,0)</x:f>
-        <x:v>26.986521509333333</x:v>
+        <x:v>26.38207706488889</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -6488,19 +6488,19 @@
       </x:c>
       <x:c r="B9" s="27" t="n">
         <x:f>SUM(B40:M40)</x:f>
-        <x:v>21048451.673705146</x:v>
+        <x:v>20569051.673705146</x:v>
       </x:c>
       <x:c r="C9" s="27" t="n">
         <x:f>SUM(N40:Y40)</x:f>
-        <x:v>19072721.61504</x:v>
+        <x:v>18746321.61504</x:v>
       </x:c>
       <x:c r="D9" s="27" t="n">
         <x:f>SUM(Z40:AK40)</x:f>
-        <x:v>14572721.615039999</x:v>
+        <x:v>14246321.615039999</x:v>
       </x:c>
       <x:c r="E9" s="28" t="n">
         <x:f>SUM(B9:D9)</x:f>
-        <x:v>54693894.90378515</x:v>
+        <x:v>53561694.90378515</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -6511,19 +6511,19 @@
       </x:c>
       <x:c r="B10" s="28" t="n">
         <x:f>SUM(B41:M41)</x:f>
-        <x:v>10173548.326294854</x:v>
+        <x:v>10652948.326294854</x:v>
       </x:c>
       <x:c r="C10" s="28" t="n">
         <x:f>SUM(N41:Y41)</x:f>
-        <x:v>10987278.384960003</x:v>
+        <x:v>11313678.384960003</x:v>
       </x:c>
       <x:c r="D10" s="28" t="n">
         <x:f>SUM(Z41:AK41)</x:f>
-        <x:v>6487278.384960002</x:v>
+        <x:v>6813678.384960002</x:v>
       </x:c>
       <x:c r="E10" s="28" t="n">
         <x:f>SUM(B10:D10)</x:f>
-        <x:v>27648105.09621486</x:v>
+        <x:v>28780305.09621486</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -6534,19 +6534,19 @@
       </x:c>
       <x:c r="B11" s="24" t="n">
         <x:f>IF(B8&gt;0,B10/B8,0)</x:f>
-        <x:v>0.32584550401303103</x:v>
+        <x:v>0.3412000616967156</x:v>
       </x:c>
       <x:c r="C11" s="24" t="n">
         <x:f>IF(C8&gt;0,C10/C8,0)</x:f>
-        <x:v>0.3655115896526947</x:v>
+        <x:v>0.3763698730858285</x:v>
       </x:c>
       <x:c r="D11" s="24" t="n">
         <x:f>IF(D8&gt;0,D10/D8,0)</x:f>
-        <x:v>0.30803791001709413</x:v>
+        <x:v>0.3235364855156696</x:v>
       </x:c>
       <x:c r="E11" s="29" t="n">
         <x:f>IF(E8&gt;0,E10/E8,0)</x:f>
-        <x:v>0.3357716001094807</x:v>
+        <x:v>0.3495215697483042</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -6643,7 +6643,7 @@
       </x:c>
       <x:c r="D19" s="31" t="n">
         <x:f>Run!AK23</x:f>
-        <x:v>26.986521509333333</x:v>
+        <x:v>26.38207706488889</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -6676,7 +6676,7 @@
       </x:c>
       <x:c r="C22" s="33" t="n">
         <x:f>Run!E22</x:f>
-        <x:v>910298.026112</x:v>
+        <x:v>886498.026112</x:v>
       </x:c>
       <x:c r="D22" s="20" t="n">
         <x:f>E34</x:f>
@@ -7719,15 +7719,15 @@
       </x:c>
       <x:c r="B37" s="20" t="n">
         <x:f>IF(B$30&lt;=3,Build!$D$29/3,0)</x:f>
-        <x:v>2954902.6342857145</x:v>
+        <x:v>2866502.6342857145</x:v>
       </x:c>
       <x:c r="C37" s="20" t="n">
         <x:f>IF(C$30&lt;=3,Build!$D$29/3,0)</x:f>
-        <x:v>2954902.6342857145</x:v>
+        <x:v>2866502.6342857145</x:v>
       </x:c>
       <x:c r="D37" s="20" t="n">
         <x:f>IF(D$30&lt;=3,Build!$D$29/3,0)</x:f>
-        <x:v>2954902.6342857145</x:v>
+        <x:v>2866502.6342857145</x:v>
       </x:c>
       <x:c r="E37" s="20" t="n">
         <x:f>IF(E$30&lt;=3,Build!$D$29/3,0)</x:f>
@@ -7882,135 +7882,135 @@
       </x:c>
       <x:c r="E38" s="33" t="n">
         <x:f>Run!E22</x:f>
-        <x:v>910298.026112</x:v>
+        <x:v>886498.026112</x:v>
       </x:c>
       <x:c r="F38" s="33" t="n">
         <x:f>Run!F22</x:f>
-        <x:v>910298.026112</x:v>
+        <x:v>886498.026112</x:v>
       </x:c>
       <x:c r="G38" s="33" t="n">
         <x:f>Run!G22</x:f>
-        <x:v>910298.026112</x:v>
+        <x:v>886498.026112</x:v>
       </x:c>
       <x:c r="H38" s="33" t="n">
         <x:f>Run!H22</x:f>
-        <x:v>1075474.948752</x:v>
+        <x:v>1051674.948752</x:v>
       </x:c>
       <x:c r="I38" s="33" t="n">
         <x:f>Run!I22</x:f>
-        <x:v>1075474.948752</x:v>
+        <x:v>1051674.948752</x:v>
       </x:c>
       <x:c r="J38" s="33" t="n">
         <x:f>Run!J22</x:f>
-        <x:v>1075474.948752</x:v>
+        <x:v>1051674.948752</x:v>
       </x:c>
       <x:c r="K38" s="33" t="n">
         <x:f>Run!K22</x:f>
-        <x:v>1075474.948752</x:v>
+        <x:v>1051674.948752</x:v>
       </x:c>
       <x:c r="L38" s="33" t="n">
         <x:f>Run!L22</x:f>
-        <x:v>1075474.948752</x:v>
+        <x:v>1051674.948752</x:v>
       </x:c>
       <x:c r="M38" s="33" t="n">
         <x:f>Run!M22</x:f>
-        <x:v>1075474.948752</x:v>
+        <x:v>1051674.948752</x:v>
       </x:c>
       <x:c r="N38" s="33" t="n">
         <x:f>Run!N22</x:f>
-        <x:v>1214393.46792</x:v>
+        <x:v>1187193.46792</x:v>
       </x:c>
       <x:c r="O38" s="33" t="n">
         <x:f>Run!O22</x:f>
-        <x:v>1214393.46792</x:v>
+        <x:v>1187193.46792</x:v>
       </x:c>
       <x:c r="P38" s="33" t="n">
         <x:f>Run!P22</x:f>
-        <x:v>1214393.46792</x:v>
+        <x:v>1187193.46792</x:v>
       </x:c>
       <x:c r="Q38" s="33" t="n">
         <x:f>Run!Q22</x:f>
-        <x:v>1214393.46792</x:v>
+        <x:v>1187193.46792</x:v>
       </x:c>
       <x:c r="R38" s="33" t="n">
         <x:f>Run!R22</x:f>
-        <x:v>1214393.46792</x:v>
+        <x:v>1187193.46792</x:v>
       </x:c>
       <x:c r="S38" s="33" t="n">
         <x:f>Run!S22</x:f>
-        <x:v>1214393.46792</x:v>
+        <x:v>1187193.46792</x:v>
       </x:c>
       <x:c r="T38" s="33" t="n">
         <x:f>Run!T22</x:f>
-        <x:v>1214393.46792</x:v>
+        <x:v>1187193.46792</x:v>
       </x:c>
       <x:c r="U38" s="33" t="n">
         <x:f>Run!U22</x:f>
-        <x:v>1214393.46792</x:v>
+        <x:v>1187193.46792</x:v>
       </x:c>
       <x:c r="V38" s="33" t="n">
         <x:f>Run!V22</x:f>
-        <x:v>1214393.46792</x:v>
+        <x:v>1187193.46792</x:v>
       </x:c>
       <x:c r="W38" s="33" t="n">
         <x:f>Run!W22</x:f>
-        <x:v>1214393.46792</x:v>
+        <x:v>1187193.46792</x:v>
       </x:c>
       <x:c r="X38" s="33" t="n">
         <x:f>Run!X22</x:f>
-        <x:v>1214393.46792</x:v>
+        <x:v>1187193.46792</x:v>
       </x:c>
       <x:c r="Y38" s="33" t="n">
         <x:f>Run!Y22</x:f>
-        <x:v>1214393.46792</x:v>
+        <x:v>1187193.46792</x:v>
       </x:c>
       <x:c r="Z38" s="33" t="n">
         <x:f>Run!Z22</x:f>
-        <x:v>1214393.46792</x:v>
+        <x:v>1187193.46792</x:v>
       </x:c>
       <x:c r="AA38" s="33" t="n">
         <x:f>Run!AA22</x:f>
-        <x:v>1214393.46792</x:v>
+        <x:v>1187193.46792</x:v>
       </x:c>
       <x:c r="AB38" s="33" t="n">
         <x:f>Run!AB22</x:f>
-        <x:v>1214393.46792</x:v>
+        <x:v>1187193.46792</x:v>
       </x:c>
       <x:c r="AC38" s="33" t="n">
         <x:f>Run!AC22</x:f>
-        <x:v>1214393.46792</x:v>
+        <x:v>1187193.46792</x:v>
       </x:c>
       <x:c r="AD38" s="33" t="n">
         <x:f>Run!AD22</x:f>
-        <x:v>1214393.46792</x:v>
+        <x:v>1187193.46792</x:v>
       </x:c>
       <x:c r="AE38" s="33" t="n">
         <x:f>Run!AE22</x:f>
-        <x:v>1214393.46792</x:v>
+        <x:v>1187193.46792</x:v>
       </x:c>
       <x:c r="AF38" s="33" t="n">
         <x:f>Run!AF22</x:f>
-        <x:v>1214393.46792</x:v>
+        <x:v>1187193.46792</x:v>
       </x:c>
       <x:c r="AG38" s="33" t="n">
         <x:f>Run!AG22</x:f>
-        <x:v>1214393.46792</x:v>
+        <x:v>1187193.46792</x:v>
       </x:c>
       <x:c r="AH38" s="33" t="n">
         <x:f>Run!AH22</x:f>
-        <x:v>1214393.46792</x:v>
+        <x:v>1187193.46792</x:v>
       </x:c>
       <x:c r="AI38" s="33" t="n">
         <x:f>Run!AI22</x:f>
-        <x:v>1214393.46792</x:v>
+        <x:v>1187193.46792</x:v>
       </x:c>
       <x:c r="AJ38" s="33" t="n">
         <x:f>Run!AJ22</x:f>
-        <x:v>1214393.46792</x:v>
+        <x:v>1187193.46792</x:v>
       </x:c>
       <x:c r="AK38" s="33" t="n">
         <x:f>Run!AK22</x:f>
-        <x:v>1214393.46792</x:v>
+        <x:v>1187193.46792</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
@@ -8172,147 +8172,147 @@
       </x:c>
       <x:c r="B40" s="20" t="n">
         <x:f>SUM(B37:B39)</x:f>
-        <x:v>2954902.6342857145</x:v>
+        <x:v>2866502.6342857145</x:v>
       </x:c>
       <x:c r="C40" s="20" t="n">
         <x:f>SUM(C37:C39)</x:f>
-        <x:v>2954902.6342857145</x:v>
+        <x:v>2866502.6342857145</x:v>
       </x:c>
       <x:c r="D40" s="20" t="n">
         <x:f>SUM(D37:D39)</x:f>
-        <x:v>2954902.6342857145</x:v>
+        <x:v>2866502.6342857145</x:v>
       </x:c>
       <x:c r="E40" s="20" t="n">
         <x:f>SUM(E37:E39)</x:f>
-        <x:v>910298.026112</x:v>
+        <x:v>886498.026112</x:v>
       </x:c>
       <x:c r="F40" s="20" t="n">
         <x:f>SUM(F37:F39)</x:f>
-        <x:v>910298.026112</x:v>
+        <x:v>886498.026112</x:v>
       </x:c>
       <x:c r="G40" s="20" t="n">
         <x:f>SUM(G37:G39)</x:f>
-        <x:v>910298.026112</x:v>
+        <x:v>886498.026112</x:v>
       </x:c>
       <x:c r="H40" s="20" t="n">
         <x:f>SUM(H37:H39)</x:f>
-        <x:v>4075474.948752</x:v>
+        <x:v>4051674.948752</x:v>
       </x:c>
       <x:c r="I40" s="20" t="n">
         <x:f>SUM(I37:I39)</x:f>
-        <x:v>1075474.948752</x:v>
+        <x:v>1051674.948752</x:v>
       </x:c>
       <x:c r="J40" s="20" t="n">
         <x:f>SUM(J37:J39)</x:f>
-        <x:v>1075474.948752</x:v>
+        <x:v>1051674.948752</x:v>
       </x:c>
       <x:c r="K40" s="20" t="n">
         <x:f>SUM(K37:K39)</x:f>
-        <x:v>1075474.948752</x:v>
+        <x:v>1051674.948752</x:v>
       </x:c>
       <x:c r="L40" s="20" t="n">
         <x:f>SUM(L37:L39)</x:f>
-        <x:v>1075474.948752</x:v>
+        <x:v>1051674.948752</x:v>
       </x:c>
       <x:c r="M40" s="20" t="n">
         <x:f>SUM(M37:M39)</x:f>
-        <x:v>1075474.948752</x:v>
+        <x:v>1051674.948752</x:v>
       </x:c>
       <x:c r="N40" s="20" t="n">
         <x:f>SUM(N37:N39)</x:f>
-        <x:v>5714393.46792</x:v>
+        <x:v>5687193.46792</x:v>
       </x:c>
       <x:c r="O40" s="20" t="n">
         <x:f>SUM(O37:O39)</x:f>
-        <x:v>1214393.46792</x:v>
+        <x:v>1187193.46792</x:v>
       </x:c>
       <x:c r="P40" s="20" t="n">
         <x:f>SUM(P37:P39)</x:f>
-        <x:v>1214393.46792</x:v>
+        <x:v>1187193.46792</x:v>
       </x:c>
       <x:c r="Q40" s="20" t="n">
         <x:f>SUM(Q37:Q39)</x:f>
-        <x:v>1214393.46792</x:v>
+        <x:v>1187193.46792</x:v>
       </x:c>
       <x:c r="R40" s="20" t="n">
         <x:f>SUM(R37:R39)</x:f>
-        <x:v>1214393.46792</x:v>
+        <x:v>1187193.46792</x:v>
       </x:c>
       <x:c r="S40" s="20" t="n">
         <x:f>SUM(S37:S39)</x:f>
-        <x:v>1214393.46792</x:v>
+        <x:v>1187193.46792</x:v>
       </x:c>
       <x:c r="T40" s="20" t="n">
         <x:f>SUM(T37:T39)</x:f>
-        <x:v>1214393.46792</x:v>
+        <x:v>1187193.46792</x:v>
       </x:c>
       <x:c r="U40" s="20" t="n">
         <x:f>SUM(U37:U39)</x:f>
-        <x:v>1214393.46792</x:v>
+        <x:v>1187193.46792</x:v>
       </x:c>
       <x:c r="V40" s="20" t="n">
         <x:f>SUM(V37:V39)</x:f>
-        <x:v>1214393.46792</x:v>
+        <x:v>1187193.46792</x:v>
       </x:c>
       <x:c r="W40" s="20" t="n">
         <x:f>SUM(W37:W39)</x:f>
-        <x:v>1214393.46792</x:v>
+        <x:v>1187193.46792</x:v>
       </x:c>
       <x:c r="X40" s="20" t="n">
         <x:f>SUM(X37:X39)</x:f>
-        <x:v>1214393.46792</x:v>
+        <x:v>1187193.46792</x:v>
       </x:c>
       <x:c r="Y40" s="20" t="n">
         <x:f>SUM(Y37:Y39)</x:f>
-        <x:v>1214393.46792</x:v>
+        <x:v>1187193.46792</x:v>
       </x:c>
       <x:c r="Z40" s="20" t="n">
         <x:f>SUM(Z37:Z39)</x:f>
-        <x:v>1214393.46792</x:v>
+        <x:v>1187193.46792</x:v>
       </x:c>
       <x:c r="AA40" s="20" t="n">
         <x:f>SUM(AA37:AA39)</x:f>
-        <x:v>1214393.46792</x:v>
+        <x:v>1187193.46792</x:v>
       </x:c>
       <x:c r="AB40" s="20" t="n">
         <x:f>SUM(AB37:AB39)</x:f>
-        <x:v>1214393.46792</x:v>
+        <x:v>1187193.46792</x:v>
       </x:c>
       <x:c r="AC40" s="20" t="n">
         <x:f>SUM(AC37:AC39)</x:f>
-        <x:v>1214393.46792</x:v>
+        <x:v>1187193.46792</x:v>
       </x:c>
       <x:c r="AD40" s="20" t="n">
         <x:f>SUM(AD37:AD39)</x:f>
-        <x:v>1214393.46792</x:v>
+        <x:v>1187193.46792</x:v>
       </x:c>
       <x:c r="AE40" s="20" t="n">
         <x:f>SUM(AE37:AE39)</x:f>
-        <x:v>1214393.46792</x:v>
+        <x:v>1187193.46792</x:v>
       </x:c>
       <x:c r="AF40" s="20" t="n">
         <x:f>SUM(AF37:AF39)</x:f>
-        <x:v>1214393.46792</x:v>
+        <x:v>1187193.46792</x:v>
       </x:c>
       <x:c r="AG40" s="20" t="n">
         <x:f>SUM(AG37:AG39)</x:f>
-        <x:v>1214393.46792</x:v>
+        <x:v>1187193.46792</x:v>
       </x:c>
       <x:c r="AH40" s="20" t="n">
         <x:f>SUM(AH37:AH39)</x:f>
-        <x:v>1214393.46792</x:v>
+        <x:v>1187193.46792</x:v>
       </x:c>
       <x:c r="AI40" s="20" t="n">
         <x:f>SUM(AI37:AI39)</x:f>
-        <x:v>1214393.46792</x:v>
+        <x:v>1187193.46792</x:v>
       </x:c>
       <x:c r="AJ40" s="20" t="n">
         <x:f>SUM(AJ37:AJ39)</x:f>
-        <x:v>1214393.46792</x:v>
+        <x:v>1187193.46792</x:v>
       </x:c>
       <x:c r="AK40" s="20" t="n">
         <x:f>SUM(AK37:AK39)</x:f>
-        <x:v>1214393.46792</x:v>
+        <x:v>1187193.46792</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
@@ -8323,147 +8323,147 @@
       </x:c>
       <x:c r="B41" s="22" t="n">
         <x:f>B36-B40</x:f>
-        <x:v>2295097.3657142855</x:v>
+        <x:v>2383497.3657142855</x:v>
       </x:c>
       <x:c r="C41" s="22" t="n">
         <x:f>C36-C40</x:f>
-        <x:v>2295097.3657142855</x:v>
+        <x:v>2383497.3657142855</x:v>
       </x:c>
       <x:c r="D41" s="22" t="n">
         <x:f>D36-D40</x:f>
-        <x:v>4045097.3657142855</x:v>
+        <x:v>4133497.3657142855</x:v>
       </x:c>
       <x:c r="E41" s="22" t="n">
         <x:f>E36-E40</x:f>
-        <x:v>-442298.026112</x:v>
+        <x:v>-418498.026112</x:v>
       </x:c>
       <x:c r="F41" s="22" t="n">
         <x:f>F36-F40</x:f>
-        <x:v>-442298.026112</x:v>
+        <x:v>-418498.026112</x:v>
       </x:c>
       <x:c r="G41" s="22" t="n">
         <x:f>G36-G40</x:f>
-        <x:v>-442298.026112</x:v>
+        <x:v>-418498.026112</x:v>
       </x:c>
       <x:c r="H41" s="22" t="n">
         <x:f>H36-H40</x:f>
-        <x:v>2977525.051248</x:v>
+        <x:v>3001325.051248</x:v>
       </x:c>
       <x:c r="I41" s="22" t="n">
         <x:f>I36-I40</x:f>
-        <x:v>-22474.948751999997</x:v>
+        <x:v>1325.0512480000034</x:v>
       </x:c>
       <x:c r="J41" s="22" t="n">
         <x:f>J36-J40</x:f>
-        <x:v>-22474.948751999997</x:v>
+        <x:v>1325.0512480000034</x:v>
       </x:c>
       <x:c r="K41" s="22" t="n">
         <x:f>K36-K40</x:f>
-        <x:v>-22474.948751999997</x:v>
+        <x:v>1325.0512480000034</x:v>
       </x:c>
       <x:c r="L41" s="22" t="n">
         <x:f>L36-L40</x:f>
-        <x:v>-22474.948751999997</x:v>
+        <x:v>1325.0512480000034</x:v>
       </x:c>
       <x:c r="M41" s="22" t="n">
         <x:f>M36-M40</x:f>
-        <x:v>-22474.948751999997</x:v>
+        <x:v>1325.0512480000034</x:v>
       </x:c>
       <x:c r="N41" s="22" t="n">
         <x:f>N36-N40</x:f>
-        <x:v>5040606.53208</x:v>
+        <x:v>5067806.53208</x:v>
       </x:c>
       <x:c r="O41" s="22" t="n">
         <x:f>O36-O40</x:f>
-        <x:v>540606.53208</x:v>
+        <x:v>567806.53208</x:v>
       </x:c>
       <x:c r="P41" s="22" t="n">
         <x:f>P36-P40</x:f>
-        <x:v>540606.53208</x:v>
+        <x:v>567806.53208</x:v>
       </x:c>
       <x:c r="Q41" s="22" t="n">
         <x:f>Q36-Q40</x:f>
-        <x:v>540606.53208</x:v>
+        <x:v>567806.53208</x:v>
       </x:c>
       <x:c r="R41" s="22" t="n">
         <x:f>R36-R40</x:f>
-        <x:v>540606.53208</x:v>
+        <x:v>567806.53208</x:v>
       </x:c>
       <x:c r="S41" s="22" t="n">
         <x:f>S36-S40</x:f>
-        <x:v>540606.53208</x:v>
+        <x:v>567806.53208</x:v>
       </x:c>
       <x:c r="T41" s="22" t="n">
         <x:f>T36-T40</x:f>
-        <x:v>540606.53208</x:v>
+        <x:v>567806.53208</x:v>
       </x:c>
       <x:c r="U41" s="22" t="n">
         <x:f>U36-U40</x:f>
-        <x:v>540606.53208</x:v>
+        <x:v>567806.53208</x:v>
       </x:c>
       <x:c r="V41" s="22" t="n">
         <x:f>V36-V40</x:f>
-        <x:v>540606.53208</x:v>
+        <x:v>567806.53208</x:v>
       </x:c>
       <x:c r="W41" s="22" t="n">
         <x:f>W36-W40</x:f>
-        <x:v>540606.53208</x:v>
+        <x:v>567806.53208</x:v>
       </x:c>
       <x:c r="X41" s="22" t="n">
         <x:f>X36-X40</x:f>
-        <x:v>540606.53208</x:v>
+        <x:v>567806.53208</x:v>
       </x:c>
       <x:c r="Y41" s="22" t="n">
         <x:f>Y36-Y40</x:f>
-        <x:v>540606.53208</x:v>
+        <x:v>567806.53208</x:v>
       </x:c>
       <x:c r="Z41" s="22" t="n">
         <x:f>Z36-Z40</x:f>
-        <x:v>540606.53208</x:v>
+        <x:v>567806.53208</x:v>
       </x:c>
       <x:c r="AA41" s="22" t="n">
         <x:f>AA36-AA40</x:f>
-        <x:v>540606.53208</x:v>
+        <x:v>567806.53208</x:v>
       </x:c>
       <x:c r="AB41" s="22" t="n">
         <x:f>AB36-AB40</x:f>
-        <x:v>540606.53208</x:v>
+        <x:v>567806.53208</x:v>
       </x:c>
       <x:c r="AC41" s="22" t="n">
         <x:f>AC36-AC40</x:f>
-        <x:v>540606.53208</x:v>
+        <x:v>567806.53208</x:v>
       </x:c>
       <x:c r="AD41" s="22" t="n">
         <x:f>AD36-AD40</x:f>
-        <x:v>540606.53208</x:v>
+        <x:v>567806.53208</x:v>
       </x:c>
       <x:c r="AE41" s="22" t="n">
         <x:f>AE36-AE40</x:f>
-        <x:v>540606.53208</x:v>
+        <x:v>567806.53208</x:v>
       </x:c>
       <x:c r="AF41" s="22" t="n">
         <x:f>AF36-AF40</x:f>
-        <x:v>540606.53208</x:v>
+        <x:v>567806.53208</x:v>
       </x:c>
       <x:c r="AG41" s="22" t="n">
         <x:f>AG36-AG40</x:f>
-        <x:v>540606.53208</x:v>
+        <x:v>567806.53208</x:v>
       </x:c>
       <x:c r="AH41" s="22" t="n">
         <x:f>AH36-AH40</x:f>
-        <x:v>540606.53208</x:v>
+        <x:v>567806.53208</x:v>
       </x:c>
       <x:c r="AI41" s="22" t="n">
         <x:f>AI36-AI40</x:f>
-        <x:v>540606.53208</x:v>
+        <x:v>567806.53208</x:v>
       </x:c>
       <x:c r="AJ41" s="22" t="n">
         <x:f>AJ36-AJ40</x:f>
-        <x:v>540606.53208</x:v>
+        <x:v>567806.53208</x:v>
       </x:c>
       <x:c r="AK41" s="22" t="n">
         <x:f>AK36-AK40</x:f>
-        <x:v>540606.53208</x:v>
+        <x:v>567806.53208</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -8600,11 +8600,11 @@
       </x:c>
       <x:c r="B10" s="30" t="n">
         <x:f>B9/(Run!AK22*12)</x:f>
-        <x:v>0.014444698842167666</x:v>
+        <x:v>0.01477564389798517</x:v>
       </x:c>
       <x:c r="C10" s="30" t="n">
         <x:f>C9/(Run!AK22*12-B9+C9)</x:f>
-        <x:v>0.08675733528265071</x:v>
+        <x:v>0.08859611348398293</x:v>
       </x:c>
     </x:row>
     <x:row r="12">

--- a/model/cost-model.xlsx
+++ b/model/cost-model.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R6086d1b8fed540d4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="2" r:id="R5c578cfe6a0342be"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Build" sheetId="3" r:id="R68018757d01a4b98"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Run" sheetId="4" r:id="R4453d4cf7fb146a8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pricing &amp; P&amp;L" sheetId="5" r:id="Rfd31def50f974e7a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AI Cost" sheetId="6" r:id="Rc7a8a478624243b1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Value" sheetId="7" r:id="Rb753f3786298472e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R7a1beb191de247d1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="2" r:id="Rd4b614dbcef443d1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Build" sheetId="3" r:id="Rb655a578ffb3405f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Run" sheetId="4" r:id="Rb226e2c5e9a74ed9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pricing &amp; P&amp;L" sheetId="5" r:id="Rbeb14727791347df"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AI Cost" sheetId="6" r:id="R139bd7e9d47c45d6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Value" sheetId="7" r:id="R491dfbaf522c4c12"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1913,7 +1913,7 @@
       </x:c>
       <x:c r="D69" s="10" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Lead engineers on the core build. Run: the platform engineers (2 up to 20k employees, 3 above).</x:t>
+          <x:t xml:space="preserve">Senior fullstack, fullstack and AI engineers. Run: the platform engineers (2 up to 20k employees, 3 above).</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -1924,7 +1924,7 @@
         </x:is>
       </x:c>
       <x:c r="B70" s="8" t="n">
-        <x:v>11</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C70" s="9" t="inlineStr">
         <x:is>
@@ -1933,7 +1933,7 @@
       </x:c>
       <x:c r="D70" s="10" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">GitHub and Jira. Architect, 2 senior engineers, 2 engineers, AI engineer, 2 data engineers, 2 QA, DevSecOps.</x:t>
+          <x:t xml:space="preserve">GitHub and Jira. Senior fullstack, fullstack, AI and QA engineers.</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -1944,7 +1944,7 @@
         </x:is>
       </x:c>
       <x:c r="B71" s="8" t="n">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C71" s="9" t="inlineStr">
         <x:is>
@@ -1953,7 +1953,7 @@
       </x:c>
       <x:c r="D71" s="10" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Jira. Product lead, designer, skills lead, 2 skills consultants, content analyst, change consultant.</x:t>
+          <x:t xml:space="preserve">Jira. Product lead and UX/UI designer.</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -2343,7 +2343,7 @@
     <x:row r="93">
       <x:c r="A93" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Senior engineer</x:t>
+          <x:t xml:space="preserve">Senior fullstack engineer</x:t>
         </x:is>
       </x:c>
       <x:c r="B93" s="17" t="n">
@@ -2356,7 +2356,7 @@
     <x:row r="94">
       <x:c r="A94" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Engineer</x:t>
+          <x:t xml:space="preserve">Fullstack engineer</x:t>
         </x:is>
       </x:c>
       <x:c r="B94" s="17" t="n">
@@ -2523,7 +2523,7 @@
     <x:row r="2">
       <x:c r="A2" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">IRIS team, cost to IRIS vs price to client. FTE = average over the 12 weeks.</x:t>
+          <x:t xml:space="preserve">IRIS squad (product lead + 5), cost to IRIS vs price to client. FTE = average over the 12 weeks.</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -2582,14 +2582,14 @@
       </x:c>
       <x:c r="F5" s="10" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Owns product, scope and delivery; runs the product council.</x:t>
+          <x:t xml:space="preserve">Owns product, scope, client and delivery; runs the product council; guides client SMEs on the 18 role frameworks and the champions on adoption.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Solution architect</x:t>
+          <x:t xml:space="preserve">Senior fullstack engineer</x:t>
         </x:is>
       </x:c>
       <x:c r="B6" s="8" t="n">
@@ -2600,77 +2600,77 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="D6" s="20" t="n">
-        <x:f>C6*Assumptions!$B$92/Assumptions!$B$7</x:f>
-        <x:v>571428.5714285715</x:v>
+        <x:f>C6*Assumptions!$B$93/Assumptions!$B$7</x:f>
+        <x:v>457142.85714285716</x:v>
       </x:c>
       <x:c r="E6" s="20" t="n">
-        <x:f>C6*Assumptions!$C$92</x:f>
-        <x:v>1320000</x:v>
+        <x:f>C6*Assumptions!$C$93</x:f>
+        <x:v>960000</x:v>
       </x:c>
       <x:c r="F6" s="10" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Architecture, security review pack, integration design.</x:t>
+          <x:t xml:space="preserve">Architecture, backend and integrations (HR system, both LMSs, SSO, LINE Login); week-2 security pack, CI/CD and staged go-live.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Senior engineer</x:t>
+          <x:t xml:space="preserve">Fullstack engineer</x:t>
         </x:is>
       </x:c>
       <x:c r="B7" s="8" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C7" s="19" t="n">
         <x:f>B7*Assumptions!$B$8</x:f>
-        <x:v>120</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D7" s="20" t="n">
-        <x:f>C7*Assumptions!$B$93/Assumptions!$B$7</x:f>
-        <x:v>914285.7142857143</x:v>
+        <x:f>C7*Assumptions!$B$94/Assumptions!$B$7</x:f>
+        <x:v>257142.85714285713</x:v>
       </x:c>
       <x:c r="E7" s="20" t="n">
-        <x:f>C7*Assumptions!$C$93</x:f>
-        <x:v>1920000</x:v>
+        <x:f>C7*Assumptions!$C$94</x:f>
+        <x:v>570000</x:v>
       </x:c>
       <x:c r="F7" s="10" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1 backend + 1 frontend lead.</x:t>
+          <x:t xml:space="preserve">Mobile web / LINE LIFF front end, approvals and dashboards.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Engineer</x:t>
+          <x:t xml:space="preserve">AI engineer</x:t>
         </x:is>
       </x:c>
       <x:c r="B8" s="8" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C8" s="19" t="n">
         <x:f>B8*Assumptions!$B$8</x:f>
-        <x:v>120</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D8" s="20" t="n">
-        <x:f>C8*Assumptions!$B$94/Assumptions!$B$7</x:f>
-        <x:v>514285.71428571426</x:v>
+        <x:f>C8*Assumptions!$B$95/Assumptions!$B$7</x:f>
+        <x:v>457142.85714285716</x:v>
       </x:c>
       <x:c r="E8" s="20" t="n">
-        <x:f>C8*Assumptions!$C$94</x:f>
-        <x:v>1140000</x:v>
+        <x:f>C8*Assumptions!$C$95</x:f>
+        <x:v>960000</x:v>
       </x:c>
       <x:c r="F8" s="10" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1 backend + 1 frontend (mobile web / LINE LIFF).</x:t>
+          <x:t xml:space="preserve">Coach, path engine, retrieval, eval harness; AI-assisted tagging of both LMS catalogues.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">AI engineer</x:t>
+          <x:t xml:space="preserve">QA engineer</x:t>
         </x:is>
       </x:c>
       <x:c r="B9" s="8" t="n">
@@ -2681,422 +2681,233 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="D9" s="20" t="n">
-        <x:f>C9*Assumptions!$B$95/Assumptions!$B$7</x:f>
-        <x:v>457142.85714285716</x:v>
+        <x:f>C9*Assumptions!$B$97/Assumptions!$B$7</x:f>
+        <x:v>228571.42857142858</x:v>
       </x:c>
       <x:c r="E9" s="20" t="n">
-        <x:f>C9*Assumptions!$C$95</x:f>
-        <x:v>960000</x:v>
+        <x:f>C9*Assumptions!$C$97</x:f>
+        <x:v>510000</x:v>
       </x:c>
       <x:c r="F9" s="10" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Coach, path engine, retrieval, eval harness.</x:t>
+          <x:t xml:space="preserve">Thai and English test passes, automation, UAT and the 500-user pilot.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Data &amp; integration engineer</x:t>
+          <x:t xml:space="preserve">UX/UI designer</x:t>
         </x:is>
       </x:c>
       <x:c r="B10" s="8" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C10" s="19" t="n">
         <x:f>B10*Assumptions!$B$8</x:f>
-        <x:v>120</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D10" s="20" t="n">
-        <x:f>C10*Assumptions!$B$96/Assumptions!$B$7</x:f>
-        <x:v>857142.8571428572</x:v>
+        <x:f>C10*Assumptions!$B$98/Assumptions!$B$7</x:f>
+        <x:v>314285.71428571426</x:v>
       </x:c>
       <x:c r="E10" s="20" t="n">
-        <x:f>C10*Assumptions!$C$96</x:f>
-        <x:v>1920000</x:v>
+        <x:f>C10*Assumptions!$C$98</x:f>
+        <x:v>720000</x:v>
       </x:c>
       <x:c r="F10" s="10" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1 for HR system and sign-in (SSO, LINE Login, OTP); 1 for both LMSs, data model and dashboards.</x:t>
+          <x:t xml:space="preserve">Frontline and manager journeys, design system, usability tests with shift staff.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">QA engineer</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B11" s="8" t="n">
-        <x:v>1.5</x:v>
-      </x:c>
-      <x:c r="C11" s="19" t="n">
-        <x:f>B11*Assumptions!$B$8</x:f>
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="D11" s="20" t="n">
-        <x:f>C11*Assumptions!$B$97/Assumptions!$B$7</x:f>
-        <x:v>342857.14285714284</x:v>
-      </x:c>
-      <x:c r="E11" s="20" t="n">
-        <x:f>C11*Assumptions!$C$97</x:f>
-        <x:v>765000</x:v>
-      </x:c>
-      <x:c r="F11" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">From week 2; Thai and English test passes, automation, UAT and the 500-user pilot.</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="12">
-      <x:c r="A12" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">UX/UI designer</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B12" s="8" t="n">
-        <x:v>0.7</x:v>
-      </x:c>
-      <x:c r="C12" s="19" t="n">
-        <x:f>B12*Assumptions!$B$8</x:f>
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="D12" s="20" t="n">
-        <x:f>C12*Assumptions!$B$98/Assumptions!$B$7</x:f>
-        <x:v>220000</x:v>
-      </x:c>
-      <x:c r="E12" s="20" t="n">
-        <x:f>C12*Assumptions!$C$98</x:f>
-        <x:v>504000</x:v>
-      </x:c>
-      <x:c r="F12" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Weeks 1-8; frontline and manager journeys.</x:t>
-        </x:is>
+      <x:c r="A11" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Team total</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B11" s="21" t="n">
+        <x:f>SUM(B5:B10)</x:f>
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C11" s="21" t="n">
+        <x:f>SUM(C5:C10)</x:f>
+        <x:v>360</x:v>
+      </x:c>
+      <x:c r="D11" s="22" t="n">
+        <x:f>SUM(D5:D10)</x:f>
+        <x:v>2457142.857142857</x:v>
+      </x:c>
+      <x:c r="E11" s="22" t="n">
+        <x:f>SUM(E5:E10)</x:f>
+        <x:v>5400000</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">DevSecOps engineer</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B13" s="8" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C13" s="19" t="n">
-        <x:f>B13*Assumptions!$B$8</x:f>
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="D13" s="20" t="n">
-        <x:f>C13*Assumptions!$B$99/Assumptions!$B$7</x:f>
-        <x:v>457142.85714285716</x:v>
-      </x:c>
-      <x:c r="E13" s="20" t="n">
-        <x:f>C13*Assumptions!$C$99</x:f>
-        <x:v>960000</x:v>
-      </x:c>
-      <x:c r="F13" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Week-2 security pack, Thailand landing zone, CI/CD, pen-test fixes, staged go-live.</x:t>
+      <x:c r="A13" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Third-party and one-off</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Skills methodology lead</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B14" s="8" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C14" s="19" t="n">
-        <x:f>B14*Assumptions!$B$8</x:f>
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="D14" s="20" t="n">
-        <x:f>C14*Assumptions!$B$100/Assumptions!$B$7</x:f>
-        <x:v>571428.5714285715</x:v>
+          <x:t xml:space="preserve">Go-live penetration test</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D14" s="17" t="n">
+        <x:v>400000</x:v>
       </x:c>
       <x:c r="E14" s="20" t="n">
-        <x:f>C14*Assumptions!$C$100</x:f>
-        <x:v>1320000</x:v>
-      </x:c>
-      <x:c r="F14" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">IRIS method: frameworks and assessment design.</x:t>
-        </x:is>
+        <x:f>D14</x:f>
+        <x:v>400000</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Skills consultant</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B15" s="8" t="n">
-        <x:v>1.4</x:v>
-      </x:c>
-      <x:c r="C15" s="19" t="n">
-        <x:f>B15*Assumptions!$B$8</x:f>
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="D15" s="20" t="n">
-        <x:f>C15*Assumptions!$B$101/Assumptions!$B$7</x:f>
-        <x:v>560000</x:v>
+          <x:t xml:space="preserve">Cloud and environments during build</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D15" s="17" t="n">
+        <x:v>200000</x:v>
       </x:c>
       <x:c r="E15" s="20" t="n">
-        <x:f>C15*Assumptions!$C$101</x:f>
-        <x:v>1260000</x:v>
-      </x:c>
-      <x:c r="F15" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Frameworks for ~18 roles; SME validation (weeks 1-8).</x:t>
-        </x:is>
+        <x:f>D15</x:f>
+        <x:v>200000</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Content analyst</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B16" s="8" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C16" s="19" t="n">
-        <x:f>B16*Assumptions!$B$8</x:f>
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="D16" s="20" t="n">
-        <x:f>C16*Assumptions!$B$102/Assumptions!$B$7</x:f>
-        <x:v>200000</x:v>
+          <x:t xml:space="preserve">Content indexing: Thai ASR transcripts, embeddings</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D16" s="17" t="n">
+        <x:v>150000</x:v>
       </x:c>
       <x:c r="E16" s="20" t="n">
-        <x:f>C16*Assumptions!$C$102</x:f>
-        <x:v>420000</x:v>
-      </x:c>
-      <x:c r="F16" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Tag ~2 LMS catalogues to skills (AI-assisted, human-checked).</x:t>
-        </x:is>
+        <x:f>D16</x:f>
+        <x:v>150000</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Change &amp; adoption consultant</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B17" s="8" t="n">
-        <x:v>0.8</x:v>
-      </x:c>
-      <x:c r="C17" s="19" t="n">
-        <x:f>B17*Assumptions!$B$8</x:f>
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="D17" s="20" t="n">
-        <x:f>C17*Assumptions!$B$103/Assumptions!$B$7</x:f>
-        <x:v>320000</x:v>
+          <x:t xml:space="preserve">LLM usage during build and evals</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D17" s="17" t="n">
+        <x:v>60000</x:v>
       </x:c>
       <x:c r="E17" s="20" t="n">
-        <x:f>C17*Assumptions!$C$103</x:f>
-        <x:v>720000</x:v>
-      </x:c>
-      <x:c r="F17" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Weeks 4-12: champions, manager briefings, comms.</x:t>
-        </x:is>
+        <x:f>D17</x:f>
+        <x:v>60000</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="18" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Team total</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B18" s="21" t="n">
-        <x:f>SUM(B5:B17)</x:f>
-        <x:v>16.4</x:v>
-      </x:c>
-      <x:c r="C18" s="21" t="n">
-        <x:f>SUM(C5:C17)</x:f>
-        <x:v>984</x:v>
+          <x:t xml:space="preserve">Third-party total (passed through at cost)</x:t>
+        </x:is>
       </x:c>
       <x:c r="D18" s="22" t="n">
-        <x:f>SUM(D5:D17)</x:f>
-        <x:v>6728571.428571429</x:v>
+        <x:f>SUM(D14:D17)</x:f>
+        <x:v>810000</x:v>
       </x:c>
       <x:c r="E18" s="22" t="n">
-        <x:f>SUM(E5:E17)</x:f>
-        <x:v>14889000</x:v>
+        <x:f>SUM(E14:E17)</x:f>
+        <x:v>810000</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
-      <x:c r="A20" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Third-party and one-off</x:t>
-        </x:is>
+      <x:c r="A20" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Delivery contingency (15% of team cost)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D20" s="20" t="n">
+        <x:f>0.15*D11</x:f>
+        <x:v>368571.4285714285</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Go-live penetration test</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D21" s="17" t="n">
-        <x:v>400000</x:v>
-      </x:c>
-      <x:c r="E21" s="20" t="n">
-        <x:f>D21</x:f>
-        <x:v>400000</x:v>
+          <x:t xml:space="preserve">Team software subscriptions: Claude Max, GitHub, Jira, Figma (IRIS cost, not passed through)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D21" s="20" t="n">
+        <x:f>(Assumptions!$B$69*Assumptions!$B$65+Assumptions!$B$70*(Assumptions!$B$66+Assumptions!$B$67)+Assumptions!$B$71*Assumptions!$B$67+Assumptions!$B$72*Assumptions!$B$68)*Assumptions!$B$73*Assumptions!$B$6</x:f>
+        <x:v>39112.92</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
-      <x:c r="A22" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Cloud and environments during build</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D22" s="17" t="n">
-        <x:v>200000</x:v>
-      </x:c>
-      <x:c r="E22" s="20" t="n">
-        <x:f>D22</x:f>
-        <x:v>200000</x:v>
+      <x:c r="A22" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Total cost to IRIS</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D22" s="22" t="n">
+        <x:f>D11+D18+D20+D21</x:f>
+        <x:v>3674827.2057142854</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Content indexing: Thai ASR transcripts, embeddings</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D23" s="17" t="n">
-        <x:v>150000</x:v>
+          <x:t xml:space="preserve">Price before risk premium</x:t>
+        </x:is>
       </x:c>
       <x:c r="E23" s="20" t="n">
-        <x:f>D23</x:f>
-        <x:v>150000</x:v>
+        <x:f>E11+E18</x:f>
+        <x:v>6210000</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">LLM usage during build and evals</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D24" s="17" t="n">
-        <x:v>60000</x:v>
+          <x:t xml:space="preserve">Fixed-date risk premium</x:t>
+        </x:is>
       </x:c>
       <x:c r="E24" s="20" t="n">
-        <x:f>D24</x:f>
-        <x:v>60000</x:v>
+        <x:f>E23*Assumptions!$B$84</x:f>
+        <x:v>621000</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="18" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Third-party total (passed through at cost)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D25" s="22" t="n">
-        <x:f>SUM(D21:D24)</x:f>
-        <x:v>810000</x:v>
-      </x:c>
-      <x:c r="E25" s="22" t="n">
-        <x:f>SUM(E21:E24)</x:f>
-        <x:v>810000</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27">
-      <x:c r="A27" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Delivery contingency (15% of team cost)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D27" s="20" t="n">
-        <x:f>0.15*D18</x:f>
-        <x:v>1009285.7142857143</x:v>
+          <x:t xml:space="preserve">Implementation fee (rounded to 0.5M)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E25" s="23" t="n">
+        <x:f>ROUND((E23+E24)/500000,0)*500000</x:f>
+        <x:v>7000000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Gross margin on implementation</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E26" s="24" t="n">
+        <x:f>(E25-D22)/E25</x:f>
+        <x:v>0.47502468489795924</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
-      <x:c r="A28" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Team software subscriptions: Claude Max, GitHub, Jira, Figma (IRIS cost, not passed through)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D28" s="20" t="n">
-        <x:f>(Assumptions!$B$69*Assumptions!$B$65+Assumptions!$B$70*(Assumptions!$B$66+Assumptions!$B$67)+Assumptions!$B$71*Assumptions!$B$67+Assumptions!$B$72*Assumptions!$B$68)*Assumptions!$B$73*Assumptions!$B$6</x:f>
-        <x:v>51650.759999999995</x:v>
+      <x:c r="A28" s="9" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Milestones: 30% at kick-off, 30% at week 6 (integrated demo), 40% at go-live acceptance.</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="29">
-      <x:c r="A29" s="18" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Total cost to IRIS</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D29" s="22" t="n">
-        <x:f>D18+D25+D27+D28</x:f>
-        <x:v>8599507.902857143</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30">
-      <x:c r="A30" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Price before risk premium</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E30" s="20" t="n">
-        <x:f>E18+E25</x:f>
-        <x:v>15699000</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31">
-      <x:c r="A31" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Fixed-date risk premium</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E31" s="20" t="n">
-        <x:f>E30*Assumptions!$B$84</x:f>
-        <x:v>1569900</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32">
-      <x:c r="A32" s="18" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Implementation fee (rounded to 0.5M)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E32" s="23" t="n">
-        <x:f>ROUND((E30+E31)/500000,0)*500000</x:f>
-        <x:v>17500000</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33">
-      <x:c r="A33" s="18" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Gross margin on implementation</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E33" s="24" t="n">
-        <x:f>(E32-D29)/E32</x:f>
-        <x:v>0.5085995484081632</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35">
-      <x:c r="A35" s="9" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Milestones: 30% at kick-off, 30% at week 6 (integrated demo), 40% at go-live acceptance.</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="36">
-      <x:c r="A36" s="9" t="inlineStr">
+      <x:c r="A29" s="9" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Client-side roles (not priced): HRIS owner, 2 LMS admins, IT security, DPO, 2 SMEs per BU, comms lead, ~60 champions.</x:t>
         </x:is>
@@ -6396,7 +6207,7 @@
       </x:c>
       <x:c r="B5" s="27" t="n">
         <x:f>SUM(B33:M33)</x:f>
-        <x:v>17500000</x:v>
+        <x:v>7000000</x:v>
       </x:c>
       <x:c r="C5" s="27" t="n">
         <x:f>SUM(N33:Y33)</x:f>
@@ -6408,7 +6219,7 @@
       </x:c>
       <x:c r="E5" s="28" t="n">
         <x:f>SUM(B5:D5)</x:f>
-        <x:v>17500000</x:v>
+        <x:v>7000000</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -6465,7 +6276,7 @@
       </x:c>
       <x:c r="B8" s="28" t="n">
         <x:f>SUM(B36:M36)</x:f>
-        <x:v>31222000</x:v>
+        <x:v>20722000</x:v>
       </x:c>
       <x:c r="C8" s="28" t="n">
         <x:f>SUM(N36:Y36)</x:f>
@@ -6477,7 +6288,7 @@
       </x:c>
       <x:c r="E8" s="28" t="n">
         <x:f>SUM(B8:D8)</x:f>
-        <x:v>82342000</x:v>
+        <x:v>71842000</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -6488,7 +6299,7 @@
       </x:c>
       <x:c r="B9" s="27" t="n">
         <x:f>SUM(B40:M40)</x:f>
-        <x:v>20569051.673705146</x:v>
+        <x:v>15644370.976562288</x:v>
       </x:c>
       <x:c r="C9" s="27" t="n">
         <x:f>SUM(N40:Y40)</x:f>
@@ -6500,7 +6311,7 @@
       </x:c>
       <x:c r="E9" s="28" t="n">
         <x:f>SUM(B9:D9)</x:f>
-        <x:v>53561694.90378515</x:v>
+        <x:v>48637014.206642285</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -6511,7 +6322,7 @@
       </x:c>
       <x:c r="B10" s="28" t="n">
         <x:f>SUM(B41:M41)</x:f>
-        <x:v>10652948.326294854</x:v>
+        <x:v>5077629.023437715</x:v>
       </x:c>
       <x:c r="C10" s="28" t="n">
         <x:f>SUM(N41:Y41)</x:f>
@@ -6523,7 +6334,7 @@
       </x:c>
       <x:c r="E10" s="28" t="n">
         <x:f>SUM(B10:D10)</x:f>
-        <x:v>28780305.09621486</x:v>
+        <x:v>23204985.793357722</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -6534,7 +6345,7 @@
       </x:c>
       <x:c r="B11" s="24" t="n">
         <x:f>IF(B8&gt;0,B10/B8,0)</x:f>
-        <x:v>0.3412000616967156</x:v>
+        <x:v>0.24503566371188665</x:v>
       </x:c>
       <x:c r="C11" s="24" t="n">
         <x:f>IF(C8&gt;0,C10/C8,0)</x:f>
@@ -6546,7 +6357,7 @@
       </x:c>
       <x:c r="E11" s="29" t="n">
         <x:f>IF(E8&gt;0,E10/E8,0)</x:f>
-        <x:v>0.3495215697483042</x:v>
+        <x:v>0.32300027551234267</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -6583,7 +6394,7 @@
       </x:c>
       <x:c r="B15" s="20" t="n">
         <x:f>IF(B14&gt;0,B8/B14,0)</x:f>
-        <x:v>1156.3703703703704</x:v>
+        <x:v>767.4814814814815</x:v>
       </x:c>
       <x:c r="C15" s="20" t="n">
         <x:f>IF(C14&gt;0,C8/C14,0)</x:f>
@@ -6602,7 +6413,7 @@
       </x:c>
       <x:c r="B16" s="30" t="n">
         <x:f>IF(B15&gt;0,B15/Assumptions!$B$9,0)</x:f>
-        <x:v>0.3504152637485971</x:v>
+        <x:v>0.23257014590347924</x:v>
       </x:c>
       <x:c r="C16" s="30" t="n">
         <x:f>IF(C15&gt;0,C15/Assumptions!$B$9,0)</x:f>
@@ -6664,8 +6475,8 @@
         </x:is>
       </x:c>
       <x:c r="D21" s="32" t="n">
-        <x:f>Build!$E$32</x:f>
-        <x:v>17500000</x:v>
+        <x:f>Build!$E$25</x:f>
+        <x:v>7000000</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -7114,147 +6925,147 @@
         </x:is>
       </x:c>
       <x:c r="B33" s="20" t="n">
-        <x:f>IF(B$30=1,0.3,IF(B$30=2,0.3,IF(B$30=3,0.4,0)))*Build!$E$32</x:f>
-        <x:v>5250000</x:v>
+        <x:f>IF(B$30=1,0.3,IF(B$30=2,0.3,IF(B$30=3,0.4,0)))*Build!$E$25</x:f>
+        <x:v>2100000</x:v>
       </x:c>
       <x:c r="C33" s="20" t="n">
-        <x:f>IF(C$30=1,0.3,IF(C$30=2,0.3,IF(C$30=3,0.4,0)))*Build!$E$32</x:f>
-        <x:v>5250000</x:v>
+        <x:f>IF(C$30=1,0.3,IF(C$30=2,0.3,IF(C$30=3,0.4,0)))*Build!$E$25</x:f>
+        <x:v>2100000</x:v>
       </x:c>
       <x:c r="D33" s="20" t="n">
-        <x:f>IF(D$30=1,0.3,IF(D$30=2,0.3,IF(D$30=3,0.4,0)))*Build!$E$32</x:f>
-        <x:v>7000000</x:v>
+        <x:f>IF(D$30=1,0.3,IF(D$30=2,0.3,IF(D$30=3,0.4,0)))*Build!$E$25</x:f>
+        <x:v>2800000</x:v>
       </x:c>
       <x:c r="E33" s="20" t="n">
-        <x:f>IF(E$30=1,0.3,IF(E$30=2,0.3,IF(E$30=3,0.4,0)))*Build!$E$32</x:f>
+        <x:f>IF(E$30=1,0.3,IF(E$30=2,0.3,IF(E$30=3,0.4,0)))*Build!$E$25</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="F33" s="20" t="n">
-        <x:f>IF(F$30=1,0.3,IF(F$30=2,0.3,IF(F$30=3,0.4,0)))*Build!$E$32</x:f>
+        <x:f>IF(F$30=1,0.3,IF(F$30=2,0.3,IF(F$30=3,0.4,0)))*Build!$E$25</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="G33" s="20" t="n">
-        <x:f>IF(G$30=1,0.3,IF(G$30=2,0.3,IF(G$30=3,0.4,0)))*Build!$E$32</x:f>
+        <x:f>IF(G$30=1,0.3,IF(G$30=2,0.3,IF(G$30=3,0.4,0)))*Build!$E$25</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="H33" s="20" t="n">
-        <x:f>IF(H$30=1,0.3,IF(H$30=2,0.3,IF(H$30=3,0.4,0)))*Build!$E$32</x:f>
+        <x:f>IF(H$30=1,0.3,IF(H$30=2,0.3,IF(H$30=3,0.4,0)))*Build!$E$25</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="I33" s="20" t="n">
-        <x:f>IF(I$30=1,0.3,IF(I$30=2,0.3,IF(I$30=3,0.4,0)))*Build!$E$32</x:f>
+        <x:f>IF(I$30=1,0.3,IF(I$30=2,0.3,IF(I$30=3,0.4,0)))*Build!$E$25</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J33" s="20" t="n">
-        <x:f>IF(J$30=1,0.3,IF(J$30=2,0.3,IF(J$30=3,0.4,0)))*Build!$E$32</x:f>
+        <x:f>IF(J$30=1,0.3,IF(J$30=2,0.3,IF(J$30=3,0.4,0)))*Build!$E$25</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K33" s="20" t="n">
-        <x:f>IF(K$30=1,0.3,IF(K$30=2,0.3,IF(K$30=3,0.4,0)))*Build!$E$32</x:f>
+        <x:f>IF(K$30=1,0.3,IF(K$30=2,0.3,IF(K$30=3,0.4,0)))*Build!$E$25</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="L33" s="20" t="n">
-        <x:f>IF(L$30=1,0.3,IF(L$30=2,0.3,IF(L$30=3,0.4,0)))*Build!$E$32</x:f>
+        <x:f>IF(L$30=1,0.3,IF(L$30=2,0.3,IF(L$30=3,0.4,0)))*Build!$E$25</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M33" s="20" t="n">
-        <x:f>IF(M$30=1,0.3,IF(M$30=2,0.3,IF(M$30=3,0.4,0)))*Build!$E$32</x:f>
+        <x:f>IF(M$30=1,0.3,IF(M$30=2,0.3,IF(M$30=3,0.4,0)))*Build!$E$25</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="N33" s="20" t="n">
-        <x:f>IF(N$30=1,0.3,IF(N$30=2,0.3,IF(N$30=3,0.4,0)))*Build!$E$32</x:f>
+        <x:f>IF(N$30=1,0.3,IF(N$30=2,0.3,IF(N$30=3,0.4,0)))*Build!$E$25</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="O33" s="20" t="n">
-        <x:f>IF(O$30=1,0.3,IF(O$30=2,0.3,IF(O$30=3,0.4,0)))*Build!$E$32</x:f>
+        <x:f>IF(O$30=1,0.3,IF(O$30=2,0.3,IF(O$30=3,0.4,0)))*Build!$E$25</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="P33" s="20" t="n">
-        <x:f>IF(P$30=1,0.3,IF(P$30=2,0.3,IF(P$30=3,0.4,0)))*Build!$E$32</x:f>
+        <x:f>IF(P$30=1,0.3,IF(P$30=2,0.3,IF(P$30=3,0.4,0)))*Build!$E$25</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q33" s="20" t="n">
-        <x:f>IF(Q$30=1,0.3,IF(Q$30=2,0.3,IF(Q$30=3,0.4,0)))*Build!$E$32</x:f>
+        <x:f>IF(Q$30=1,0.3,IF(Q$30=2,0.3,IF(Q$30=3,0.4,0)))*Build!$E$25</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="R33" s="20" t="n">
-        <x:f>IF(R$30=1,0.3,IF(R$30=2,0.3,IF(R$30=3,0.4,0)))*Build!$E$32</x:f>
+        <x:f>IF(R$30=1,0.3,IF(R$30=2,0.3,IF(R$30=3,0.4,0)))*Build!$E$25</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="S33" s="20" t="n">
-        <x:f>IF(S$30=1,0.3,IF(S$30=2,0.3,IF(S$30=3,0.4,0)))*Build!$E$32</x:f>
+        <x:f>IF(S$30=1,0.3,IF(S$30=2,0.3,IF(S$30=3,0.4,0)))*Build!$E$25</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="T33" s="20" t="n">
-        <x:f>IF(T$30=1,0.3,IF(T$30=2,0.3,IF(T$30=3,0.4,0)))*Build!$E$32</x:f>
+        <x:f>IF(T$30=1,0.3,IF(T$30=2,0.3,IF(T$30=3,0.4,0)))*Build!$E$25</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="U33" s="20" t="n">
-        <x:f>IF(U$30=1,0.3,IF(U$30=2,0.3,IF(U$30=3,0.4,0)))*Build!$E$32</x:f>
+        <x:f>IF(U$30=1,0.3,IF(U$30=2,0.3,IF(U$30=3,0.4,0)))*Build!$E$25</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="V33" s="20" t="n">
-        <x:f>IF(V$30=1,0.3,IF(V$30=2,0.3,IF(V$30=3,0.4,0)))*Build!$E$32</x:f>
+        <x:f>IF(V$30=1,0.3,IF(V$30=2,0.3,IF(V$30=3,0.4,0)))*Build!$E$25</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="W33" s="20" t="n">
-        <x:f>IF(W$30=1,0.3,IF(W$30=2,0.3,IF(W$30=3,0.4,0)))*Build!$E$32</x:f>
+        <x:f>IF(W$30=1,0.3,IF(W$30=2,0.3,IF(W$30=3,0.4,0)))*Build!$E$25</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="X33" s="20" t="n">
-        <x:f>IF(X$30=1,0.3,IF(X$30=2,0.3,IF(X$30=3,0.4,0)))*Build!$E$32</x:f>
+        <x:f>IF(X$30=1,0.3,IF(X$30=2,0.3,IF(X$30=3,0.4,0)))*Build!$E$25</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="Y33" s="20" t="n">
-        <x:f>IF(Y$30=1,0.3,IF(Y$30=2,0.3,IF(Y$30=3,0.4,0)))*Build!$E$32</x:f>
+        <x:f>IF(Y$30=1,0.3,IF(Y$30=2,0.3,IF(Y$30=3,0.4,0)))*Build!$E$25</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="Z33" s="20" t="n">
-        <x:f>IF(Z$30=1,0.3,IF(Z$30=2,0.3,IF(Z$30=3,0.4,0)))*Build!$E$32</x:f>
+        <x:f>IF(Z$30=1,0.3,IF(Z$30=2,0.3,IF(Z$30=3,0.4,0)))*Build!$E$25</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AA33" s="20" t="n">
-        <x:f>IF(AA$30=1,0.3,IF(AA$30=2,0.3,IF(AA$30=3,0.4,0)))*Build!$E$32</x:f>
+        <x:f>IF(AA$30=1,0.3,IF(AA$30=2,0.3,IF(AA$30=3,0.4,0)))*Build!$E$25</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AB33" s="20" t="n">
-        <x:f>IF(AB$30=1,0.3,IF(AB$30=2,0.3,IF(AB$30=3,0.4,0)))*Build!$E$32</x:f>
+        <x:f>IF(AB$30=1,0.3,IF(AB$30=2,0.3,IF(AB$30=3,0.4,0)))*Build!$E$25</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AC33" s="20" t="n">
-        <x:f>IF(AC$30=1,0.3,IF(AC$30=2,0.3,IF(AC$30=3,0.4,0)))*Build!$E$32</x:f>
+        <x:f>IF(AC$30=1,0.3,IF(AC$30=2,0.3,IF(AC$30=3,0.4,0)))*Build!$E$25</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AD33" s="20" t="n">
-        <x:f>IF(AD$30=1,0.3,IF(AD$30=2,0.3,IF(AD$30=3,0.4,0)))*Build!$E$32</x:f>
+        <x:f>IF(AD$30=1,0.3,IF(AD$30=2,0.3,IF(AD$30=3,0.4,0)))*Build!$E$25</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AE33" s="20" t="n">
-        <x:f>IF(AE$30=1,0.3,IF(AE$30=2,0.3,IF(AE$30=3,0.4,0)))*Build!$E$32</x:f>
+        <x:f>IF(AE$30=1,0.3,IF(AE$30=2,0.3,IF(AE$30=3,0.4,0)))*Build!$E$25</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AF33" s="20" t="n">
-        <x:f>IF(AF$30=1,0.3,IF(AF$30=2,0.3,IF(AF$30=3,0.4,0)))*Build!$E$32</x:f>
+        <x:f>IF(AF$30=1,0.3,IF(AF$30=2,0.3,IF(AF$30=3,0.4,0)))*Build!$E$25</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AG33" s="20" t="n">
-        <x:f>IF(AG$30=1,0.3,IF(AG$30=2,0.3,IF(AG$30=3,0.4,0)))*Build!$E$32</x:f>
+        <x:f>IF(AG$30=1,0.3,IF(AG$30=2,0.3,IF(AG$30=3,0.4,0)))*Build!$E$25</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AH33" s="20" t="n">
-        <x:f>IF(AH$30=1,0.3,IF(AH$30=2,0.3,IF(AH$30=3,0.4,0)))*Build!$E$32</x:f>
+        <x:f>IF(AH$30=1,0.3,IF(AH$30=2,0.3,IF(AH$30=3,0.4,0)))*Build!$E$25</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AI33" s="20" t="n">
-        <x:f>IF(AI$30=1,0.3,IF(AI$30=2,0.3,IF(AI$30=3,0.4,0)))*Build!$E$32</x:f>
+        <x:f>IF(AI$30=1,0.3,IF(AI$30=2,0.3,IF(AI$30=3,0.4,0)))*Build!$E$25</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AJ33" s="20" t="n">
-        <x:f>IF(AJ$30=1,0.3,IF(AJ$30=2,0.3,IF(AJ$30=3,0.4,0)))*Build!$E$32</x:f>
+        <x:f>IF(AJ$30=1,0.3,IF(AJ$30=2,0.3,IF(AJ$30=3,0.4,0)))*Build!$E$25</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AK33" s="20" t="n">
-        <x:f>IF(AK$30=1,0.3,IF(AK$30=2,0.3,IF(AK$30=3,0.4,0)))*Build!$E$32</x:f>
+        <x:f>IF(AK$30=1,0.3,IF(AK$30=2,0.3,IF(AK$30=3,0.4,0)))*Build!$E$25</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -7568,15 +7379,15 @@
       </x:c>
       <x:c r="B36" s="22" t="n">
         <x:f>SUM(B33:B35)</x:f>
-        <x:v>5250000</x:v>
+        <x:v>2100000</x:v>
       </x:c>
       <x:c r="C36" s="22" t="n">
         <x:f>SUM(C33:C35)</x:f>
-        <x:v>5250000</x:v>
+        <x:v>2100000</x:v>
       </x:c>
       <x:c r="D36" s="22" t="n">
         <x:f>SUM(D33:D35)</x:f>
-        <x:v>7000000</x:v>
+        <x:v>2800000</x:v>
       </x:c>
       <x:c r="E36" s="22" t="n">
         <x:f>SUM(E33:E35)</x:f>
@@ -7718,147 +7529,147 @@
         </x:is>
       </x:c>
       <x:c r="B37" s="20" t="n">
-        <x:f>IF(B$30&lt;=3,Build!$D$29/3,0)</x:f>
-        <x:v>2866502.6342857145</x:v>
+        <x:f>IF(B$30&lt;=3,Build!$D$22/3,0)</x:f>
+        <x:v>1224942.4019047618</x:v>
       </x:c>
       <x:c r="C37" s="20" t="n">
-        <x:f>IF(C$30&lt;=3,Build!$D$29/3,0)</x:f>
-        <x:v>2866502.6342857145</x:v>
+        <x:f>IF(C$30&lt;=3,Build!$D$22/3,0)</x:f>
+        <x:v>1224942.4019047618</x:v>
       </x:c>
       <x:c r="D37" s="20" t="n">
-        <x:f>IF(D$30&lt;=3,Build!$D$29/3,0)</x:f>
-        <x:v>2866502.6342857145</x:v>
+        <x:f>IF(D$30&lt;=3,Build!$D$22/3,0)</x:f>
+        <x:v>1224942.4019047618</x:v>
       </x:c>
       <x:c r="E37" s="20" t="n">
-        <x:f>IF(E$30&lt;=3,Build!$D$29/3,0)</x:f>
+        <x:f>IF(E$30&lt;=3,Build!$D$22/3,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="F37" s="20" t="n">
-        <x:f>IF(F$30&lt;=3,Build!$D$29/3,0)</x:f>
+        <x:f>IF(F$30&lt;=3,Build!$D$22/3,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="G37" s="20" t="n">
-        <x:f>IF(G$30&lt;=3,Build!$D$29/3,0)</x:f>
+        <x:f>IF(G$30&lt;=3,Build!$D$22/3,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="H37" s="20" t="n">
-        <x:f>IF(H$30&lt;=3,Build!$D$29/3,0)</x:f>
+        <x:f>IF(H$30&lt;=3,Build!$D$22/3,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="I37" s="20" t="n">
-        <x:f>IF(I$30&lt;=3,Build!$D$29/3,0)</x:f>
+        <x:f>IF(I$30&lt;=3,Build!$D$22/3,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J37" s="20" t="n">
-        <x:f>IF(J$30&lt;=3,Build!$D$29/3,0)</x:f>
+        <x:f>IF(J$30&lt;=3,Build!$D$22/3,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K37" s="20" t="n">
-        <x:f>IF(K$30&lt;=3,Build!$D$29/3,0)</x:f>
+        <x:f>IF(K$30&lt;=3,Build!$D$22/3,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="L37" s="20" t="n">
-        <x:f>IF(L$30&lt;=3,Build!$D$29/3,0)</x:f>
+        <x:f>IF(L$30&lt;=3,Build!$D$22/3,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M37" s="20" t="n">
-        <x:f>IF(M$30&lt;=3,Build!$D$29/3,0)</x:f>
+        <x:f>IF(M$30&lt;=3,Build!$D$22/3,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="N37" s="20" t="n">
-        <x:f>IF(N$30&lt;=3,Build!$D$29/3,0)</x:f>
+        <x:f>IF(N$30&lt;=3,Build!$D$22/3,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="O37" s="20" t="n">
-        <x:f>IF(O$30&lt;=3,Build!$D$29/3,0)</x:f>
+        <x:f>IF(O$30&lt;=3,Build!$D$22/3,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="P37" s="20" t="n">
-        <x:f>IF(P$30&lt;=3,Build!$D$29/3,0)</x:f>
+        <x:f>IF(P$30&lt;=3,Build!$D$22/3,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q37" s="20" t="n">
-        <x:f>IF(Q$30&lt;=3,Build!$D$29/3,0)</x:f>
+        <x:f>IF(Q$30&lt;=3,Build!$D$22/3,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="R37" s="20" t="n">
-        <x:f>IF(R$30&lt;=3,Build!$D$29/3,0)</x:f>
+        <x:f>IF(R$30&lt;=3,Build!$D$22/3,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="S37" s="20" t="n">
-        <x:f>IF(S$30&lt;=3,Build!$D$29/3,0)</x:f>
+        <x:f>IF(S$30&lt;=3,Build!$D$22/3,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="T37" s="20" t="n">
-        <x:f>IF(T$30&lt;=3,Build!$D$29/3,0)</x:f>
+        <x:f>IF(T$30&lt;=3,Build!$D$22/3,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="U37" s="20" t="n">
-        <x:f>IF(U$30&lt;=3,Build!$D$29/3,0)</x:f>
+        <x:f>IF(U$30&lt;=3,Build!$D$22/3,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="V37" s="20" t="n">
-        <x:f>IF(V$30&lt;=3,Build!$D$29/3,0)</x:f>
+        <x:f>IF(V$30&lt;=3,Build!$D$22/3,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="W37" s="20" t="n">
-        <x:f>IF(W$30&lt;=3,Build!$D$29/3,0)</x:f>
+        <x:f>IF(W$30&lt;=3,Build!$D$22/3,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="X37" s="20" t="n">
-        <x:f>IF(X$30&lt;=3,Build!$D$29/3,0)</x:f>
+        <x:f>IF(X$30&lt;=3,Build!$D$22/3,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="Y37" s="20" t="n">
-        <x:f>IF(Y$30&lt;=3,Build!$D$29/3,0)</x:f>
+        <x:f>IF(Y$30&lt;=3,Build!$D$22/3,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="Z37" s="20" t="n">
-        <x:f>IF(Z$30&lt;=3,Build!$D$29/3,0)</x:f>
+        <x:f>IF(Z$30&lt;=3,Build!$D$22/3,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AA37" s="20" t="n">
-        <x:f>IF(AA$30&lt;=3,Build!$D$29/3,0)</x:f>
+        <x:f>IF(AA$30&lt;=3,Build!$D$22/3,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AB37" s="20" t="n">
-        <x:f>IF(AB$30&lt;=3,Build!$D$29/3,0)</x:f>
+        <x:f>IF(AB$30&lt;=3,Build!$D$22/3,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AC37" s="20" t="n">
-        <x:f>IF(AC$30&lt;=3,Build!$D$29/3,0)</x:f>
+        <x:f>IF(AC$30&lt;=3,Build!$D$22/3,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AD37" s="20" t="n">
-        <x:f>IF(AD$30&lt;=3,Build!$D$29/3,0)</x:f>
+        <x:f>IF(AD$30&lt;=3,Build!$D$22/3,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AE37" s="20" t="n">
-        <x:f>IF(AE$30&lt;=3,Build!$D$29/3,0)</x:f>
+        <x:f>IF(AE$30&lt;=3,Build!$D$22/3,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AF37" s="20" t="n">
-        <x:f>IF(AF$30&lt;=3,Build!$D$29/3,0)</x:f>
+        <x:f>IF(AF$30&lt;=3,Build!$D$22/3,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AG37" s="20" t="n">
-        <x:f>IF(AG$30&lt;=3,Build!$D$29/3,0)</x:f>
+        <x:f>IF(AG$30&lt;=3,Build!$D$22/3,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AH37" s="20" t="n">
-        <x:f>IF(AH$30&lt;=3,Build!$D$29/3,0)</x:f>
+        <x:f>IF(AH$30&lt;=3,Build!$D$22/3,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AI37" s="20" t="n">
-        <x:f>IF(AI$30&lt;=3,Build!$D$29/3,0)</x:f>
+        <x:f>IF(AI$30&lt;=3,Build!$D$22/3,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AJ37" s="20" t="n">
-        <x:f>IF(AJ$30&lt;=3,Build!$D$29/3,0)</x:f>
+        <x:f>IF(AJ$30&lt;=3,Build!$D$22/3,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AK37" s="20" t="n">
-        <x:f>IF(AK$30&lt;=3,Build!$D$29/3,0)</x:f>
+        <x:f>IF(AK$30&lt;=3,Build!$D$22/3,0)</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -8172,15 +7983,15 @@
       </x:c>
       <x:c r="B40" s="20" t="n">
         <x:f>SUM(B37:B39)</x:f>
-        <x:v>2866502.6342857145</x:v>
+        <x:v>1224942.4019047618</x:v>
       </x:c>
       <x:c r="C40" s="20" t="n">
         <x:f>SUM(C37:C39)</x:f>
-        <x:v>2866502.6342857145</x:v>
+        <x:v>1224942.4019047618</x:v>
       </x:c>
       <x:c r="D40" s="20" t="n">
         <x:f>SUM(D37:D39)</x:f>
-        <x:v>2866502.6342857145</x:v>
+        <x:v>1224942.4019047618</x:v>
       </x:c>
       <x:c r="E40" s="20" t="n">
         <x:f>SUM(E37:E39)</x:f>
@@ -8323,15 +8134,15 @@
       </x:c>
       <x:c r="B41" s="22" t="n">
         <x:f>B36-B40</x:f>
-        <x:v>2383497.3657142855</x:v>
+        <x:v>875057.5980952382</x:v>
       </x:c>
       <x:c r="C41" s="22" t="n">
         <x:f>C36-C40</x:f>
-        <x:v>2383497.3657142855</x:v>
+        <x:v>875057.5980952382</x:v>
       </x:c>
       <x:c r="D41" s="22" t="n">
         <x:f>D36-D40</x:f>
-        <x:v>4133497.3657142855</x:v>
+        <x:v>1575057.5980952382</x:v>
       </x:c>
       <x:c r="E41" s="22" t="n">
         <x:f>E36-E40</x:f>
@@ -9000,7 +8811,7 @@
       </x:c>
       <x:c r="C30" s="33" t="n">
         <x:f>'Pricing &amp; P&amp;L'!E8</x:f>
-        <x:v>82342000</x:v>
+        <x:v>71842000</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
@@ -9011,7 +8822,7 @@
       </x:c>
       <x:c r="C31" s="35" t="n">
         <x:f>IF(C30&gt;0,C29/C30,0)</x:f>
-        <x:v>0.9531891379854752</x:v>
+        <x:v>1.0925016007349462</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
